--- a/reports/Mobile_Appium_E2E_Test_Report_400.xlsx
+++ b/reports/Mobile_Appium_E2E_Test_Report_400.xlsx
@@ -52,7 +52,7 @@
     <t>PASSED</t>
   </si>
   <si>
-    <t>2026-08-07T04:03:04.297Z</t>
+    <t>2026-08-07T14:56:27.205Z</t>
   </si>
   <si>
     <t>Verified Android Activity lifecycle and Capacitor native plugin interface</t>
@@ -82,6 +82,9 @@
     <t>Native Authentication Flow - Mobile Assertion #5: Verify native shell component interaction</t>
   </si>
   <si>
+    <t>2026-08-07T14:56:27.206Z</t>
+  </si>
+  <si>
     <t>MOB-TC-0006</t>
   </si>
   <si>
@@ -425,9 +428,6 @@
   </si>
   <si>
     <t>Screen Orientation Swap - Mobile Assertion #1: Verify native shell component interaction</t>
-  </si>
-  <si>
-    <t>2026-08-07T04:03:04.298Z</t>
   </si>
   <si>
     <t>MOB-TC-0062</t>
@@ -3030,7 +3030,7 @@
         <v>11</v>
       </c>
       <c r="E3" s="4">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>12</v>
@@ -3056,7 +3056,7 @@
         <v>11</v>
       </c>
       <c r="E4" s="2">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="F4" s="3" t="s">
         <v>12</v>
@@ -3082,7 +3082,7 @@
         <v>11</v>
       </c>
       <c r="E5" s="4">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="F5" s="3" t="s">
         <v>12</v>
@@ -3108,13 +3108,13 @@
         <v>11</v>
       </c>
       <c r="E6" s="2">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="F6" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>14</v>
@@ -3122,25 +3122,25 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B7" s="4" t="s">
         <v>9</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>11</v>
       </c>
       <c r="E7" s="4">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="F7" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="H7" s="4" t="s">
         <v>14</v>
@@ -3148,25 +3148,25 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E8" s="2">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="F8" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>14</v>
@@ -3174,25 +3174,25 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B9" s="4" t="s">
         <v>9</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D9" s="4" t="s">
         <v>11</v>
       </c>
       <c r="E9" s="4">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="F9" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="H9" s="4" t="s">
         <v>14</v>
@@ -3200,25 +3200,25 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E10" s="2">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F10" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>14</v>
@@ -3226,25 +3226,25 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B11" s="4" t="s">
         <v>9</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D11" s="4" t="s">
         <v>11</v>
       </c>
       <c r="E11" s="4">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="F11" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="H11" s="4" t="s">
         <v>14</v>
@@ -3252,25 +3252,25 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E12" s="2">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="F12" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>14</v>
@@ -3278,25 +3278,25 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B13" s="4" t="s">
         <v>9</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D13" s="4" t="s">
         <v>11</v>
       </c>
       <c r="E13" s="4">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="F13" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="H13" s="4" t="s">
         <v>14</v>
@@ -3304,25 +3304,25 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E14" s="2">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="H14" s="2" t="s">
         <v>14</v>
@@ -3330,13 +3330,13 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B15" s="4" t="s">
         <v>9</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D15" s="4" t="s">
         <v>11</v>
@@ -3348,7 +3348,7 @@
         <v>12</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="H15" s="4" t="s">
         <v>14</v>
@@ -3356,25 +3356,25 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E16" s="2">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F16" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="H16" s="2" t="s">
         <v>14</v>
@@ -3382,25 +3382,25 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B17" s="4" t="s">
         <v>9</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D17" s="4" t="s">
         <v>11</v>
       </c>
       <c r="E17" s="4">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="F17" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="H17" s="4" t="s">
         <v>14</v>
@@ -3408,25 +3408,25 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E18" s="2">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F18" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="H18" s="2" t="s">
         <v>14</v>
@@ -3434,25 +3434,25 @@
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B19" s="4" t="s">
         <v>9</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D19" s="4" t="s">
         <v>11</v>
       </c>
       <c r="E19" s="4">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F19" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="H19" s="4" t="s">
         <v>14</v>
@@ -3460,25 +3460,25 @@
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E20" s="2">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F20" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="H20" s="2" t="s">
         <v>14</v>
@@ -3486,25 +3486,25 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B21" s="4" t="s">
         <v>9</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D21" s="4" t="s">
         <v>11</v>
       </c>
       <c r="E21" s="4">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="F21" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="H21" s="4" t="s">
         <v>14</v>
@@ -3512,25 +3512,25 @@
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E22" s="2">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F22" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="H22" s="2" t="s">
         <v>14</v>
@@ -3538,25 +3538,25 @@
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D23" s="4" t="s">
         <v>11</v>
       </c>
       <c r="E23" s="4">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="F23" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G23" s="4" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="H23" s="4" t="s">
         <v>14</v>
@@ -3564,25 +3564,25 @@
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E24" s="2">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F24" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="H24" s="2" t="s">
         <v>14</v>
@@ -3590,25 +3590,25 @@
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D25" s="4" t="s">
         <v>11</v>
       </c>
       <c r="E25" s="4">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F25" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G25" s="4" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="H25" s="4" t="s">
         <v>14</v>
@@ -3616,13 +3616,13 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>11</v>
@@ -3634,7 +3634,7 @@
         <v>12</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="H26" s="2" t="s">
         <v>14</v>
@@ -3642,25 +3642,25 @@
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D27" s="4" t="s">
         <v>11</v>
       </c>
       <c r="E27" s="4">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="F27" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G27" s="4" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="H27" s="4" t="s">
         <v>14</v>
@@ -3668,25 +3668,25 @@
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E28" s="2">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="F28" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="H28" s="2" t="s">
         <v>14</v>
@@ -3694,25 +3694,25 @@
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D29" s="4" t="s">
         <v>11</v>
       </c>
       <c r="E29" s="4">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="F29" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G29" s="4" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="H29" s="4" t="s">
         <v>14</v>
@@ -3720,25 +3720,25 @@
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E30" s="2">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="F30" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="H30" s="2" t="s">
         <v>14</v>
@@ -3746,25 +3746,25 @@
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D31" s="4" t="s">
         <v>11</v>
       </c>
       <c r="E31" s="4">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="F31" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G31" s="4" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="H31" s="4" t="s">
         <v>14</v>
@@ -3772,25 +3772,25 @@
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E32" s="2">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="F32" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="H32" s="2" t="s">
         <v>14</v>
@@ -3798,25 +3798,25 @@
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D33" s="4" t="s">
         <v>11</v>
       </c>
       <c r="E33" s="4">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="F33" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G33" s="4" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="H33" s="4" t="s">
         <v>14</v>
@@ -3824,25 +3824,25 @@
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E34" s="2">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F34" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="H34" s="2" t="s">
         <v>14</v>
@@ -3850,25 +3850,25 @@
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D35" s="4" t="s">
         <v>11</v>
       </c>
       <c r="E35" s="4">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="F35" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G35" s="4" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="H35" s="4" t="s">
         <v>14</v>
@@ -3876,25 +3876,25 @@
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E36" s="2">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="F36" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="H36" s="2" t="s">
         <v>14</v>
@@ -3902,25 +3902,25 @@
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D37" s="4" t="s">
         <v>11</v>
       </c>
       <c r="E37" s="4">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="F37" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G37" s="4" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="H37" s="4" t="s">
         <v>14</v>
@@ -3928,25 +3928,25 @@
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E38" s="2">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F38" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="H38" s="2" t="s">
         <v>14</v>
@@ -3954,25 +3954,25 @@
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D39" s="4" t="s">
         <v>11</v>
       </c>
       <c r="E39" s="4">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="F39" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G39" s="4" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="H39" s="4" t="s">
         <v>14</v>
@@ -3980,25 +3980,25 @@
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E40" s="2">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="F40" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="H40" s="2" t="s">
         <v>14</v>
@@ -4006,13 +4006,13 @@
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" s="4" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D41" s="4" t="s">
         <v>11</v>
@@ -4024,7 +4024,7 @@
         <v>12</v>
       </c>
       <c r="G41" s="4" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="H41" s="4" t="s">
         <v>14</v>
@@ -4032,25 +4032,25 @@
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E42" s="2">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="F42" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="H42" s="2" t="s">
         <v>14</v>
@@ -4058,25 +4058,25 @@
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D43" s="4" t="s">
         <v>11</v>
       </c>
       <c r="E43" s="4">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="F43" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G43" s="4" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="H43" s="4" t="s">
         <v>14</v>
@@ -4084,25 +4084,25 @@
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E44" s="2">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="F44" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="H44" s="2" t="s">
         <v>14</v>
@@ -4110,25 +4110,25 @@
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" s="4" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D45" s="4" t="s">
         <v>11</v>
       </c>
       <c r="E45" s="4">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="F45" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G45" s="4" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="H45" s="4" t="s">
         <v>14</v>
@@ -4136,25 +4136,25 @@
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D46" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E46" s="2">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="F46" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="H46" s="2" t="s">
         <v>14</v>
@@ -4162,25 +4162,25 @@
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" s="4" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D47" s="4" t="s">
         <v>11</v>
       </c>
       <c r="E47" s="4">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="F47" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G47" s="4" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="H47" s="4" t="s">
         <v>14</v>
@@ -4188,25 +4188,25 @@
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D48" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E48" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F48" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="H48" s="2" t="s">
         <v>14</v>
@@ -4214,25 +4214,25 @@
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" s="4" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D49" s="4" t="s">
         <v>11</v>
       </c>
       <c r="E49" s="4">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="F49" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G49" s="4" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="H49" s="4" t="s">
         <v>14</v>
@@ -4240,25 +4240,25 @@
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D50" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E50" s="2">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="F50" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="H50" s="2" t="s">
         <v>14</v>
@@ -4266,25 +4266,25 @@
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" s="4" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D51" s="4" t="s">
         <v>11</v>
       </c>
       <c r="E51" s="4">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F51" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G51" s="4" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="H51" s="4" t="s">
         <v>14</v>
@@ -4292,25 +4292,25 @@
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D52" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E52" s="2">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F52" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="H52" s="2" t="s">
         <v>14</v>
@@ -4318,25 +4318,25 @@
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" s="4" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D53" s="4" t="s">
         <v>11</v>
       </c>
       <c r="E53" s="4">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="F53" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G53" s="4" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="H53" s="4" t="s">
         <v>14</v>
@@ -4344,25 +4344,25 @@
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D54" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E54" s="2">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="F54" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="H54" s="2" t="s">
         <v>14</v>
@@ -4370,25 +4370,25 @@
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" s="4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D55" s="4" t="s">
         <v>11</v>
       </c>
       <c r="E55" s="4">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="F55" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G55" s="4" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="H55" s="4" t="s">
         <v>14</v>
@@ -4396,25 +4396,25 @@
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D56" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E56" s="2">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="F56" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="H56" s="2" t="s">
         <v>14</v>
@@ -4422,25 +4422,25 @@
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" s="4" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D57" s="4" t="s">
         <v>11</v>
       </c>
       <c r="E57" s="4">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F57" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G57" s="4" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="H57" s="4" t="s">
         <v>14</v>
@@ -4448,25 +4448,25 @@
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D58" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E58" s="2">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="F58" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="H58" s="2" t="s">
         <v>14</v>
@@ -4474,25 +4474,25 @@
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" s="4" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D59" s="4" t="s">
         <v>11</v>
       </c>
       <c r="E59" s="4">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F59" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G59" s="4" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="H59" s="4" t="s">
         <v>14</v>
@@ -4500,25 +4500,25 @@
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D60" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E60" s="2">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="F60" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="H60" s="2" t="s">
         <v>14</v>
@@ -4526,25 +4526,25 @@
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" s="4" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D61" s="4" t="s">
         <v>11</v>
       </c>
       <c r="E61" s="4">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F61" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G61" s="4" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="H61" s="4" t="s">
         <v>14</v>
@@ -4552,25 +4552,25 @@
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D62" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E62" s="2">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F62" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H62" s="2" t="s">
         <v>14</v>
@@ -4581,7 +4581,7 @@
         <v>139</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C63" s="4" t="s">
         <v>140</v>
@@ -4590,13 +4590,13 @@
         <v>11</v>
       </c>
       <c r="E63" s="4">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="F63" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G63" s="4" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H63" s="4" t="s">
         <v>14</v>
@@ -4607,7 +4607,7 @@
         <v>141</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C64" s="2" t="s">
         <v>142</v>
@@ -4616,13 +4616,13 @@
         <v>11</v>
       </c>
       <c r="E64" s="2">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="F64" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H64" s="2" t="s">
         <v>14</v>
@@ -4633,7 +4633,7 @@
         <v>143</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C65" s="4" t="s">
         <v>144</v>
@@ -4642,13 +4642,13 @@
         <v>11</v>
       </c>
       <c r="E65" s="4">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F65" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G65" s="4" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H65" s="4" t="s">
         <v>14</v>
@@ -4659,7 +4659,7 @@
         <v>145</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C66" s="2" t="s">
         <v>146</v>
@@ -4668,13 +4668,13 @@
         <v>11</v>
       </c>
       <c r="E66" s="2">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="F66" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H66" s="2" t="s">
         <v>14</v>
@@ -4685,7 +4685,7 @@
         <v>147</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C67" s="4" t="s">
         <v>148</v>
@@ -4694,13 +4694,13 @@
         <v>11</v>
       </c>
       <c r="E67" s="4">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="F67" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G67" s="4" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H67" s="4" t="s">
         <v>14</v>
@@ -4711,7 +4711,7 @@
         <v>149</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C68" s="2" t="s">
         <v>150</v>
@@ -4720,13 +4720,13 @@
         <v>11</v>
       </c>
       <c r="E68" s="2">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F68" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H68" s="2" t="s">
         <v>14</v>
@@ -4737,7 +4737,7 @@
         <v>151</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C69" s="4" t="s">
         <v>152</v>
@@ -4746,13 +4746,13 @@
         <v>11</v>
       </c>
       <c r="E69" s="4">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="F69" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G69" s="4" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H69" s="4" t="s">
         <v>14</v>
@@ -4763,7 +4763,7 @@
         <v>153</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C70" s="2" t="s">
         <v>154</v>
@@ -4772,13 +4772,13 @@
         <v>11</v>
       </c>
       <c r="E70" s="2">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="F70" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H70" s="2" t="s">
         <v>14</v>
@@ -4789,7 +4789,7 @@
         <v>155</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C71" s="4" t="s">
         <v>156</v>
@@ -4798,13 +4798,13 @@
         <v>11</v>
       </c>
       <c r="E71" s="4">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="F71" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G71" s="4" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H71" s="4" t="s">
         <v>14</v>
@@ -4815,7 +4815,7 @@
         <v>157</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C72" s="2" t="s">
         <v>158</v>
@@ -4824,13 +4824,13 @@
         <v>11</v>
       </c>
       <c r="E72" s="2">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="F72" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H72" s="2" t="s">
         <v>14</v>
@@ -4841,7 +4841,7 @@
         <v>159</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C73" s="4" t="s">
         <v>160</v>
@@ -4850,13 +4850,13 @@
         <v>11</v>
       </c>
       <c r="E73" s="4">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="F73" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G73" s="4" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H73" s="4" t="s">
         <v>14</v>
@@ -4867,7 +4867,7 @@
         <v>161</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C74" s="2" t="s">
         <v>162</v>
@@ -4876,13 +4876,13 @@
         <v>11</v>
       </c>
       <c r="E74" s="2">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="F74" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H74" s="2" t="s">
         <v>14</v>
@@ -4893,7 +4893,7 @@
         <v>163</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C75" s="4" t="s">
         <v>164</v>
@@ -4902,13 +4902,13 @@
         <v>11</v>
       </c>
       <c r="E75" s="4">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F75" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G75" s="4" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H75" s="4" t="s">
         <v>14</v>
@@ -4919,7 +4919,7 @@
         <v>165</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C76" s="2" t="s">
         <v>166</v>
@@ -4928,13 +4928,13 @@
         <v>11</v>
       </c>
       <c r="E76" s="2">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F76" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H76" s="2" t="s">
         <v>14</v>
@@ -4945,7 +4945,7 @@
         <v>167</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C77" s="4" t="s">
         <v>168</v>
@@ -4954,13 +4954,13 @@
         <v>11</v>
       </c>
       <c r="E77" s="4">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F77" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G77" s="4" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H77" s="4" t="s">
         <v>14</v>
@@ -4971,7 +4971,7 @@
         <v>169</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C78" s="2" t="s">
         <v>170</v>
@@ -4980,13 +4980,13 @@
         <v>11</v>
       </c>
       <c r="E78" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F78" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H78" s="2" t="s">
         <v>14</v>
@@ -4997,7 +4997,7 @@
         <v>171</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C79" s="4" t="s">
         <v>172</v>
@@ -5006,13 +5006,13 @@
         <v>11</v>
       </c>
       <c r="E79" s="4">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="F79" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G79" s="4" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H79" s="4" t="s">
         <v>14</v>
@@ -5023,7 +5023,7 @@
         <v>173</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C80" s="2" t="s">
         <v>174</v>
@@ -5032,13 +5032,13 @@
         <v>11</v>
       </c>
       <c r="E80" s="2">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="F80" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H80" s="2" t="s">
         <v>14</v>
@@ -5049,7 +5049,7 @@
         <v>175</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C81" s="4" t="s">
         <v>176</v>
@@ -5058,13 +5058,13 @@
         <v>11</v>
       </c>
       <c r="E81" s="4">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="F81" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G81" s="4" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H81" s="4" t="s">
         <v>14</v>
@@ -5084,13 +5084,13 @@
         <v>11</v>
       </c>
       <c r="E82" s="2">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="F82" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H82" s="2" t="s">
         <v>14</v>
@@ -5110,13 +5110,13 @@
         <v>11</v>
       </c>
       <c r="E83" s="4">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="F83" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G83" s="4" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H83" s="4" t="s">
         <v>14</v>
@@ -5136,13 +5136,13 @@
         <v>11</v>
       </c>
       <c r="E84" s="2">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="F84" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G84" s="2" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H84" s="2" t="s">
         <v>14</v>
@@ -5162,13 +5162,13 @@
         <v>11</v>
       </c>
       <c r="E85" s="4">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="F85" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G85" s="4" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H85" s="4" t="s">
         <v>14</v>
@@ -5188,13 +5188,13 @@
         <v>11</v>
       </c>
       <c r="E86" s="2">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="F86" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G86" s="2" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H86" s="2" t="s">
         <v>14</v>
@@ -5214,13 +5214,13 @@
         <v>11</v>
       </c>
       <c r="E87" s="4">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="F87" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G87" s="4" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H87" s="4" t="s">
         <v>14</v>
@@ -5240,13 +5240,13 @@
         <v>11</v>
       </c>
       <c r="E88" s="2">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="F88" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G88" s="2" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H88" s="2" t="s">
         <v>14</v>
@@ -5266,13 +5266,13 @@
         <v>11</v>
       </c>
       <c r="E89" s="4">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="F89" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G89" s="4" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H89" s="4" t="s">
         <v>14</v>
@@ -5292,13 +5292,13 @@
         <v>11</v>
       </c>
       <c r="E90" s="2">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="F90" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G90" s="2" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H90" s="2" t="s">
         <v>14</v>
@@ -5318,13 +5318,13 @@
         <v>11</v>
       </c>
       <c r="E91" s="4">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="F91" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G91" s="4" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H91" s="4" t="s">
         <v>14</v>
@@ -5344,13 +5344,13 @@
         <v>11</v>
       </c>
       <c r="E92" s="2">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F92" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G92" s="2" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H92" s="2" t="s">
         <v>14</v>
@@ -5370,13 +5370,13 @@
         <v>11</v>
       </c>
       <c r="E93" s="4">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="F93" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G93" s="4" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H93" s="4" t="s">
         <v>14</v>
@@ -5396,13 +5396,13 @@
         <v>11</v>
       </c>
       <c r="E94" s="2">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F94" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G94" s="2" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H94" s="2" t="s">
         <v>14</v>
@@ -5422,13 +5422,13 @@
         <v>11</v>
       </c>
       <c r="E95" s="4">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="F95" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G95" s="4" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H95" s="4" t="s">
         <v>14</v>
@@ -5454,7 +5454,7 @@
         <v>12</v>
       </c>
       <c r="G96" s="2" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H96" s="2" t="s">
         <v>14</v>
@@ -5474,13 +5474,13 @@
         <v>11</v>
       </c>
       <c r="E97" s="4">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="F97" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G97" s="4" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H97" s="4" t="s">
         <v>14</v>
@@ -5500,13 +5500,13 @@
         <v>11</v>
       </c>
       <c r="E98" s="2">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="F98" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G98" s="2" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H98" s="2" t="s">
         <v>14</v>
@@ -5526,13 +5526,13 @@
         <v>11</v>
       </c>
       <c r="E99" s="4">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F99" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G99" s="4" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H99" s="4" t="s">
         <v>14</v>
@@ -5552,13 +5552,13 @@
         <v>11</v>
       </c>
       <c r="E100" s="2">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="F100" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G100" s="2" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H100" s="2" t="s">
         <v>14</v>
@@ -5578,13 +5578,13 @@
         <v>11</v>
       </c>
       <c r="E101" s="4">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F101" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G101" s="4" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H101" s="4" t="s">
         <v>14</v>
@@ -5604,13 +5604,13 @@
         <v>11</v>
       </c>
       <c r="E102" s="2">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="F102" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G102" s="2" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H102" s="2" t="s">
         <v>14</v>
@@ -5630,13 +5630,13 @@
         <v>11</v>
       </c>
       <c r="E103" s="4">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F103" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G103" s="4" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H103" s="4" t="s">
         <v>14</v>
@@ -5656,13 +5656,13 @@
         <v>11</v>
       </c>
       <c r="E104" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F104" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G104" s="2" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H104" s="2" t="s">
         <v>14</v>
@@ -5682,13 +5682,13 @@
         <v>11</v>
       </c>
       <c r="E105" s="4">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="F105" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G105" s="4" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H105" s="4" t="s">
         <v>14</v>
@@ -5708,13 +5708,13 @@
         <v>11</v>
       </c>
       <c r="E106" s="2">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="F106" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G106" s="2" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H106" s="2" t="s">
         <v>14</v>
@@ -5734,13 +5734,13 @@
         <v>11</v>
       </c>
       <c r="E107" s="4">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="F107" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G107" s="4" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H107" s="4" t="s">
         <v>14</v>
@@ -5760,13 +5760,13 @@
         <v>11</v>
       </c>
       <c r="E108" s="2">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="F108" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G108" s="2" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H108" s="2" t="s">
         <v>14</v>
@@ -5786,13 +5786,13 @@
         <v>11</v>
       </c>
       <c r="E109" s="4">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="F109" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G109" s="4" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H109" s="4" t="s">
         <v>14</v>
@@ -5812,13 +5812,13 @@
         <v>11</v>
       </c>
       <c r="E110" s="2">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="F110" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G110" s="2" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H110" s="2" t="s">
         <v>14</v>
@@ -5838,13 +5838,13 @@
         <v>11</v>
       </c>
       <c r="E111" s="4">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="F111" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G111" s="4" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H111" s="4" t="s">
         <v>14</v>
@@ -5864,13 +5864,13 @@
         <v>11</v>
       </c>
       <c r="E112" s="2">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="F112" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G112" s="2" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H112" s="2" t="s">
         <v>14</v>
@@ -5890,13 +5890,13 @@
         <v>11</v>
       </c>
       <c r="E113" s="4">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="F113" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G113" s="4" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H113" s="4" t="s">
         <v>14</v>
@@ -5916,13 +5916,13 @@
         <v>11</v>
       </c>
       <c r="E114" s="2">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="F114" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G114" s="2" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H114" s="2" t="s">
         <v>14</v>
@@ -5942,13 +5942,13 @@
         <v>11</v>
       </c>
       <c r="E115" s="4">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F115" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G115" s="4" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H115" s="4" t="s">
         <v>14</v>
@@ -5968,13 +5968,13 @@
         <v>11</v>
       </c>
       <c r="E116" s="2">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F116" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G116" s="2" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H116" s="2" t="s">
         <v>14</v>
@@ -5994,13 +5994,13 @@
         <v>11</v>
       </c>
       <c r="E117" s="4">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="F117" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G117" s="4" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H117" s="4" t="s">
         <v>14</v>
@@ -6020,13 +6020,13 @@
         <v>11</v>
       </c>
       <c r="E118" s="2">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="F118" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G118" s="2" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H118" s="2" t="s">
         <v>14</v>
@@ -6046,13 +6046,13 @@
         <v>11</v>
       </c>
       <c r="E119" s="4">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F119" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G119" s="4" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H119" s="4" t="s">
         <v>14</v>
@@ -6072,13 +6072,13 @@
         <v>11</v>
       </c>
       <c r="E120" s="2">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="F120" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G120" s="2" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H120" s="2" t="s">
         <v>14</v>
@@ -6098,13 +6098,13 @@
         <v>11</v>
       </c>
       <c r="E121" s="4">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="F121" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G121" s="4" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H121" s="4" t="s">
         <v>14</v>
@@ -6124,13 +6124,13 @@
         <v>11</v>
       </c>
       <c r="E122" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F122" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G122" s="2" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H122" s="2" t="s">
         <v>14</v>
@@ -6150,13 +6150,13 @@
         <v>11</v>
       </c>
       <c r="E123" s="4">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="F123" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G123" s="4" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H123" s="4" t="s">
         <v>14</v>
@@ -6182,7 +6182,7 @@
         <v>12</v>
       </c>
       <c r="G124" s="2" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H124" s="2" t="s">
         <v>14</v>
@@ -6202,13 +6202,13 @@
         <v>11</v>
       </c>
       <c r="E125" s="4">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F125" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G125" s="4" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H125" s="4" t="s">
         <v>14</v>
@@ -6228,13 +6228,13 @@
         <v>11</v>
       </c>
       <c r="E126" s="2">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="F126" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G126" s="2" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H126" s="2" t="s">
         <v>14</v>
@@ -6254,13 +6254,13 @@
         <v>11</v>
       </c>
       <c r="E127" s="4">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="F127" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G127" s="4" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H127" s="4" t="s">
         <v>14</v>
@@ -6280,13 +6280,13 @@
         <v>11</v>
       </c>
       <c r="E128" s="2">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="F128" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G128" s="2" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H128" s="2" t="s">
         <v>14</v>
@@ -6306,13 +6306,13 @@
         <v>11</v>
       </c>
       <c r="E129" s="4">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F129" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G129" s="4" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H129" s="4" t="s">
         <v>14</v>
@@ -6332,13 +6332,13 @@
         <v>11</v>
       </c>
       <c r="E130" s="2">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="F130" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G130" s="2" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H130" s="2" t="s">
         <v>14</v>
@@ -6364,7 +6364,7 @@
         <v>12</v>
       </c>
       <c r="G131" s="4" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H131" s="4" t="s">
         <v>14</v>
@@ -6384,13 +6384,13 @@
         <v>11</v>
       </c>
       <c r="E132" s="2">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="F132" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G132" s="2" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H132" s="2" t="s">
         <v>14</v>
@@ -6410,13 +6410,13 @@
         <v>11</v>
       </c>
       <c r="E133" s="4">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F133" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G133" s="4" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H133" s="4" t="s">
         <v>14</v>
@@ -6436,13 +6436,13 @@
         <v>11</v>
       </c>
       <c r="E134" s="2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F134" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G134" s="2" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H134" s="2" t="s">
         <v>14</v>
@@ -6462,13 +6462,13 @@
         <v>11</v>
       </c>
       <c r="E135" s="4">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="F135" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G135" s="4" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H135" s="4" t="s">
         <v>14</v>
@@ -6488,13 +6488,13 @@
         <v>11</v>
       </c>
       <c r="E136" s="2">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="F136" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G136" s="2" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H136" s="2" t="s">
         <v>14</v>
@@ -6514,13 +6514,13 @@
         <v>11</v>
       </c>
       <c r="E137" s="4">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F137" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G137" s="4" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H137" s="4" t="s">
         <v>14</v>
@@ -6540,13 +6540,13 @@
         <v>11</v>
       </c>
       <c r="E138" s="2">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="F138" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G138" s="2" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H138" s="2" t="s">
         <v>14</v>
@@ -6566,13 +6566,13 @@
         <v>11</v>
       </c>
       <c r="E139" s="4">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F139" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G139" s="4" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H139" s="4" t="s">
         <v>14</v>
@@ -6592,13 +6592,13 @@
         <v>11</v>
       </c>
       <c r="E140" s="2">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F140" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G140" s="2" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H140" s="2" t="s">
         <v>14</v>
@@ -6618,13 +6618,13 @@
         <v>11</v>
       </c>
       <c r="E141" s="4">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F141" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G141" s="4" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H141" s="4" t="s">
         <v>14</v>
@@ -6644,13 +6644,13 @@
         <v>11</v>
       </c>
       <c r="E142" s="2">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="F142" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G142" s="2" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H142" s="2" t="s">
         <v>14</v>
@@ -6676,7 +6676,7 @@
         <v>12</v>
       </c>
       <c r="G143" s="4" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H143" s="4" t="s">
         <v>14</v>
@@ -6696,13 +6696,13 @@
         <v>11</v>
       </c>
       <c r="E144" s="2">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="F144" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G144" s="2" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H144" s="2" t="s">
         <v>14</v>
@@ -6722,13 +6722,13 @@
         <v>11</v>
       </c>
       <c r="E145" s="4">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="F145" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G145" s="4" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H145" s="4" t="s">
         <v>14</v>
@@ -6748,13 +6748,13 @@
         <v>11</v>
       </c>
       <c r="E146" s="2">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="F146" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G146" s="2" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H146" s="2" t="s">
         <v>14</v>
@@ -6774,13 +6774,13 @@
         <v>11</v>
       </c>
       <c r="E147" s="4">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F147" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G147" s="4" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H147" s="4" t="s">
         <v>14</v>
@@ -6800,13 +6800,13 @@
         <v>11</v>
       </c>
       <c r="E148" s="2">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F148" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G148" s="2" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H148" s="2" t="s">
         <v>14</v>
@@ -6826,13 +6826,13 @@
         <v>11</v>
       </c>
       <c r="E149" s="4">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="F149" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G149" s="4" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H149" s="4" t="s">
         <v>14</v>
@@ -6852,13 +6852,13 @@
         <v>11</v>
       </c>
       <c r="E150" s="2">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="F150" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G150" s="2" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H150" s="2" t="s">
         <v>14</v>
@@ -6878,13 +6878,13 @@
         <v>11</v>
       </c>
       <c r="E151" s="4">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F151" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G151" s="4" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H151" s="4" t="s">
         <v>14</v>
@@ -6904,13 +6904,13 @@
         <v>11</v>
       </c>
       <c r="E152" s="2">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="F152" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G152" s="2" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H152" s="2" t="s">
         <v>14</v>
@@ -6930,13 +6930,13 @@
         <v>11</v>
       </c>
       <c r="E153" s="4">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="F153" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G153" s="4" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H153" s="4" t="s">
         <v>14</v>
@@ -6956,13 +6956,13 @@
         <v>11</v>
       </c>
       <c r="E154" s="2">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="F154" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G154" s="2" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H154" s="2" t="s">
         <v>14</v>
@@ -6982,13 +6982,13 @@
         <v>11</v>
       </c>
       <c r="E155" s="4">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F155" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G155" s="4" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H155" s="4" t="s">
         <v>14</v>
@@ -7008,13 +7008,13 @@
         <v>11</v>
       </c>
       <c r="E156" s="2">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="F156" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G156" s="2" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H156" s="2" t="s">
         <v>14</v>
@@ -7034,13 +7034,13 @@
         <v>11</v>
       </c>
       <c r="E157" s="4">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="F157" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G157" s="4" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H157" s="4" t="s">
         <v>14</v>
@@ -7060,13 +7060,13 @@
         <v>11</v>
       </c>
       <c r="E158" s="2">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F158" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G158" s="2" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H158" s="2" t="s">
         <v>14</v>
@@ -7086,13 +7086,13 @@
         <v>11</v>
       </c>
       <c r="E159" s="4">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F159" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G159" s="4" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H159" s="4" t="s">
         <v>14</v>
@@ -7112,13 +7112,13 @@
         <v>11</v>
       </c>
       <c r="E160" s="2">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="F160" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G160" s="2" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H160" s="2" t="s">
         <v>14</v>
@@ -7138,13 +7138,13 @@
         <v>11</v>
       </c>
       <c r="E161" s="4">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="F161" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G161" s="4" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H161" s="4" t="s">
         <v>14</v>
@@ -7164,13 +7164,13 @@
         <v>11</v>
       </c>
       <c r="E162" s="2">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="F162" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G162" s="2" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H162" s="2" t="s">
         <v>14</v>
@@ -7190,13 +7190,13 @@
         <v>11</v>
       </c>
       <c r="E163" s="4">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F163" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G163" s="4" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H163" s="4" t="s">
         <v>14</v>
@@ -7216,13 +7216,13 @@
         <v>11</v>
       </c>
       <c r="E164" s="2">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="F164" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G164" s="2" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H164" s="2" t="s">
         <v>14</v>
@@ -7242,13 +7242,13 @@
         <v>11</v>
       </c>
       <c r="E165" s="4">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="F165" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G165" s="4" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H165" s="4" t="s">
         <v>14</v>
@@ -7268,13 +7268,13 @@
         <v>11</v>
       </c>
       <c r="E166" s="2">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F166" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G166" s="2" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H166" s="2" t="s">
         <v>14</v>
@@ -7294,13 +7294,13 @@
         <v>11</v>
       </c>
       <c r="E167" s="4">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F167" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G167" s="4" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H167" s="4" t="s">
         <v>14</v>
@@ -7320,13 +7320,13 @@
         <v>11</v>
       </c>
       <c r="E168" s="2">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F168" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G168" s="2" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H168" s="2" t="s">
         <v>14</v>
@@ -7346,13 +7346,13 @@
         <v>11</v>
       </c>
       <c r="E169" s="4">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F169" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G169" s="4" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H169" s="4" t="s">
         <v>14</v>
@@ -7372,13 +7372,13 @@
         <v>11</v>
       </c>
       <c r="E170" s="2">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="F170" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G170" s="2" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H170" s="2" t="s">
         <v>14</v>
@@ -7398,13 +7398,13 @@
         <v>11</v>
       </c>
       <c r="E171" s="4">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="F171" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G171" s="4" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H171" s="4" t="s">
         <v>14</v>
@@ -7430,7 +7430,7 @@
         <v>12</v>
       </c>
       <c r="G172" s="2" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H172" s="2" t="s">
         <v>14</v>
@@ -7450,13 +7450,13 @@
         <v>11</v>
       </c>
       <c r="E173" s="4">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="F173" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G173" s="4" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H173" s="4" t="s">
         <v>14</v>
@@ -7476,13 +7476,13 @@
         <v>11</v>
       </c>
       <c r="E174" s="2">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="F174" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G174" s="2" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H174" s="2" t="s">
         <v>14</v>
@@ -7502,13 +7502,13 @@
         <v>11</v>
       </c>
       <c r="E175" s="4">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="F175" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G175" s="4" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H175" s="4" t="s">
         <v>14</v>
@@ -7528,13 +7528,13 @@
         <v>11</v>
       </c>
       <c r="E176" s="2">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F176" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G176" s="2" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H176" s="2" t="s">
         <v>14</v>
@@ -7554,13 +7554,13 @@
         <v>11</v>
       </c>
       <c r="E177" s="4">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="F177" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G177" s="4" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H177" s="4" t="s">
         <v>14</v>
@@ -7580,13 +7580,13 @@
         <v>11</v>
       </c>
       <c r="E178" s="2">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="F178" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G178" s="2" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H178" s="2" t="s">
         <v>14</v>
@@ -7606,13 +7606,13 @@
         <v>11</v>
       </c>
       <c r="E179" s="4">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="F179" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G179" s="4" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H179" s="4" t="s">
         <v>14</v>
@@ -7632,13 +7632,13 @@
         <v>11</v>
       </c>
       <c r="E180" s="2">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F180" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G180" s="2" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H180" s="2" t="s">
         <v>14</v>
@@ -7658,13 +7658,13 @@
         <v>11</v>
       </c>
       <c r="E181" s="4">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F181" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G181" s="4" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H181" s="4" t="s">
         <v>14</v>
@@ -7684,13 +7684,13 @@
         <v>11</v>
       </c>
       <c r="E182" s="2">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="F182" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G182" s="2" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H182" s="2" t="s">
         <v>14</v>
@@ -7716,7 +7716,7 @@
         <v>12</v>
       </c>
       <c r="G183" s="4" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H183" s="4" t="s">
         <v>14</v>
@@ -7736,13 +7736,13 @@
         <v>11</v>
       </c>
       <c r="E184" s="2">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="F184" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G184" s="2" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H184" s="2" t="s">
         <v>14</v>
@@ -7762,13 +7762,13 @@
         <v>11</v>
       </c>
       <c r="E185" s="4">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="F185" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G185" s="4" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H185" s="4" t="s">
         <v>14</v>
@@ -7788,13 +7788,13 @@
         <v>11</v>
       </c>
       <c r="E186" s="2">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="F186" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G186" s="2" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H186" s="2" t="s">
         <v>14</v>
@@ -7814,13 +7814,13 @@
         <v>11</v>
       </c>
       <c r="E187" s="4">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="F187" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G187" s="4" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H187" s="4" t="s">
         <v>14</v>
@@ -7840,13 +7840,13 @@
         <v>11</v>
       </c>
       <c r="E188" s="2">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F188" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G188" s="2" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H188" s="2" t="s">
         <v>14</v>
@@ -7866,13 +7866,13 @@
         <v>11</v>
       </c>
       <c r="E189" s="4">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="F189" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G189" s="4" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H189" s="4" t="s">
         <v>14</v>
@@ -7892,13 +7892,13 @@
         <v>11</v>
       </c>
       <c r="E190" s="2">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="F190" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G190" s="2" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H190" s="2" t="s">
         <v>14</v>
@@ -7918,13 +7918,13 @@
         <v>11</v>
       </c>
       <c r="E191" s="4">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F191" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G191" s="4" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H191" s="4" t="s">
         <v>14</v>
@@ -7944,13 +7944,13 @@
         <v>11</v>
       </c>
       <c r="E192" s="2">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="F192" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G192" s="2" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H192" s="2" t="s">
         <v>14</v>
@@ -7970,13 +7970,13 @@
         <v>11</v>
       </c>
       <c r="E193" s="4">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F193" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G193" s="4" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H193" s="4" t="s">
         <v>14</v>
@@ -7996,13 +7996,13 @@
         <v>11</v>
       </c>
       <c r="E194" s="2">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="F194" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G194" s="2" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H194" s="2" t="s">
         <v>14</v>
@@ -8022,13 +8022,13 @@
         <v>11</v>
       </c>
       <c r="E195" s="4">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="F195" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G195" s="4" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H195" s="4" t="s">
         <v>14</v>
@@ -8048,13 +8048,13 @@
         <v>11</v>
       </c>
       <c r="E196" s="2">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="F196" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G196" s="2" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H196" s="2" t="s">
         <v>14</v>
@@ -8074,13 +8074,13 @@
         <v>11</v>
       </c>
       <c r="E197" s="4">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="F197" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G197" s="4" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H197" s="4" t="s">
         <v>14</v>
@@ -8100,13 +8100,13 @@
         <v>11</v>
       </c>
       <c r="E198" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F198" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G198" s="2" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H198" s="2" t="s">
         <v>14</v>
@@ -8126,13 +8126,13 @@
         <v>11</v>
       </c>
       <c r="E199" s="4">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="F199" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G199" s="4" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H199" s="4" t="s">
         <v>14</v>
@@ -8152,13 +8152,13 @@
         <v>11</v>
       </c>
       <c r="E200" s="2">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="F200" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G200" s="2" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H200" s="2" t="s">
         <v>14</v>
@@ -8178,13 +8178,13 @@
         <v>11</v>
       </c>
       <c r="E201" s="4">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="F201" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G201" s="4" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H201" s="4" t="s">
         <v>14</v>
@@ -8210,7 +8210,7 @@
         <v>12</v>
       </c>
       <c r="G202" s="2" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H202" s="2" t="s">
         <v>14</v>
@@ -8230,13 +8230,13 @@
         <v>11</v>
       </c>
       <c r="E203" s="4">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="F203" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G203" s="4" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H203" s="4" t="s">
         <v>14</v>
@@ -8256,13 +8256,13 @@
         <v>11</v>
       </c>
       <c r="E204" s="2">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="F204" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G204" s="2" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H204" s="2" t="s">
         <v>14</v>
@@ -8282,13 +8282,13 @@
         <v>11</v>
       </c>
       <c r="E205" s="4">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F205" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G205" s="4" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H205" s="4" t="s">
         <v>14</v>
@@ -8308,13 +8308,13 @@
         <v>11</v>
       </c>
       <c r="E206" s="2">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="F206" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G206" s="2" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H206" s="2" t="s">
         <v>14</v>
@@ -8334,13 +8334,13 @@
         <v>11</v>
       </c>
       <c r="E207" s="4">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="F207" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G207" s="4" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H207" s="4" t="s">
         <v>14</v>
@@ -8360,13 +8360,13 @@
         <v>11</v>
       </c>
       <c r="E208" s="2">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="F208" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G208" s="2" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H208" s="2" t="s">
         <v>14</v>
@@ -8386,13 +8386,13 @@
         <v>11</v>
       </c>
       <c r="E209" s="4">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="F209" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G209" s="4" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H209" s="4" t="s">
         <v>14</v>
@@ -8412,13 +8412,13 @@
         <v>11</v>
       </c>
       <c r="E210" s="2">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F210" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G210" s="2" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H210" s="2" t="s">
         <v>14</v>
@@ -8438,13 +8438,13 @@
         <v>11</v>
       </c>
       <c r="E211" s="4">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="F211" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G211" s="4" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H211" s="4" t="s">
         <v>14</v>
@@ -8464,13 +8464,13 @@
         <v>11</v>
       </c>
       <c r="E212" s="2">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F212" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G212" s="2" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H212" s="2" t="s">
         <v>14</v>
@@ -8490,13 +8490,13 @@
         <v>11</v>
       </c>
       <c r="E213" s="4">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="F213" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G213" s="4" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H213" s="4" t="s">
         <v>14</v>
@@ -8516,13 +8516,13 @@
         <v>11</v>
       </c>
       <c r="E214" s="2">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="F214" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G214" s="2" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H214" s="2" t="s">
         <v>14</v>
@@ -8542,13 +8542,13 @@
         <v>11</v>
       </c>
       <c r="E215" s="4">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F215" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G215" s="4" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H215" s="4" t="s">
         <v>14</v>
@@ -8574,7 +8574,7 @@
         <v>12</v>
       </c>
       <c r="G216" s="2" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H216" s="2" t="s">
         <v>14</v>
@@ -8594,13 +8594,13 @@
         <v>11</v>
       </c>
       <c r="E217" s="4">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="F217" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G217" s="4" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H217" s="4" t="s">
         <v>14</v>
@@ -8620,13 +8620,13 @@
         <v>11</v>
       </c>
       <c r="E218" s="2">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="F218" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G218" s="2" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H218" s="2" t="s">
         <v>14</v>
@@ -8646,13 +8646,13 @@
         <v>11</v>
       </c>
       <c r="E219" s="4">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="F219" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G219" s="4" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H219" s="4" t="s">
         <v>14</v>
@@ -8672,13 +8672,13 @@
         <v>11</v>
       </c>
       <c r="E220" s="2">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="F220" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G220" s="2" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H220" s="2" t="s">
         <v>14</v>
@@ -8698,13 +8698,13 @@
         <v>11</v>
       </c>
       <c r="E221" s="4">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F221" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G221" s="4" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H221" s="4" t="s">
         <v>14</v>
@@ -8724,13 +8724,13 @@
         <v>11</v>
       </c>
       <c r="E222" s="2">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="F222" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G222" s="2" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H222" s="2" t="s">
         <v>14</v>
@@ -8750,13 +8750,13 @@
         <v>11</v>
       </c>
       <c r="E223" s="4">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="F223" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G223" s="4" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H223" s="4" t="s">
         <v>14</v>
@@ -8776,13 +8776,13 @@
         <v>11</v>
       </c>
       <c r="E224" s="2">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F224" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G224" s="2" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H224" s="2" t="s">
         <v>14</v>
@@ -8802,13 +8802,13 @@
         <v>11</v>
       </c>
       <c r="E225" s="4">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="F225" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G225" s="4" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H225" s="4" t="s">
         <v>14</v>
@@ -8828,13 +8828,13 @@
         <v>11</v>
       </c>
       <c r="E226" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F226" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G226" s="2" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H226" s="2" t="s">
         <v>14</v>
@@ -8854,13 +8854,13 @@
         <v>11</v>
       </c>
       <c r="E227" s="4">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="F227" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G227" s="4" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H227" s="4" t="s">
         <v>14</v>
@@ -8880,13 +8880,13 @@
         <v>11</v>
       </c>
       <c r="E228" s="2">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="F228" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G228" s="2" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H228" s="2" t="s">
         <v>14</v>
@@ -8906,13 +8906,13 @@
         <v>11</v>
       </c>
       <c r="E229" s="4">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="F229" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G229" s="4" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H229" s="4" t="s">
         <v>14</v>
@@ -8932,13 +8932,13 @@
         <v>11</v>
       </c>
       <c r="E230" s="2">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="F230" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G230" s="2" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H230" s="2" t="s">
         <v>14</v>
@@ -8958,13 +8958,13 @@
         <v>11</v>
       </c>
       <c r="E231" s="4">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="F231" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G231" s="4" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H231" s="4" t="s">
         <v>14</v>
@@ -8984,13 +8984,13 @@
         <v>11</v>
       </c>
       <c r="E232" s="2">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="F232" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G232" s="2" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H232" s="2" t="s">
         <v>14</v>
@@ -9010,13 +9010,13 @@
         <v>11</v>
       </c>
       <c r="E233" s="4">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="F233" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G233" s="4" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H233" s="4" t="s">
         <v>14</v>
@@ -9036,13 +9036,13 @@
         <v>11</v>
       </c>
       <c r="E234" s="2">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F234" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G234" s="2" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H234" s="2" t="s">
         <v>14</v>
@@ -9062,13 +9062,13 @@
         <v>11</v>
       </c>
       <c r="E235" s="4">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="F235" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G235" s="4" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H235" s="4" t="s">
         <v>14</v>
@@ -9088,13 +9088,13 @@
         <v>11</v>
       </c>
       <c r="E236" s="2">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="F236" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G236" s="2" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H236" s="2" t="s">
         <v>14</v>
@@ -9114,13 +9114,13 @@
         <v>11</v>
       </c>
       <c r="E237" s="4">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="F237" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G237" s="4" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H237" s="4" t="s">
         <v>14</v>
@@ -9140,13 +9140,13 @@
         <v>11</v>
       </c>
       <c r="E238" s="2">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="F238" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G238" s="2" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H238" s="2" t="s">
         <v>14</v>
@@ -9166,13 +9166,13 @@
         <v>11</v>
       </c>
       <c r="E239" s="4">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F239" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G239" s="4" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H239" s="4" t="s">
         <v>14</v>
@@ -9192,13 +9192,13 @@
         <v>11</v>
       </c>
       <c r="E240" s="2">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F240" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G240" s="2" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H240" s="2" t="s">
         <v>14</v>
@@ -9218,13 +9218,13 @@
         <v>11</v>
       </c>
       <c r="E241" s="4">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="F241" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G241" s="4" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H241" s="4" t="s">
         <v>14</v>
@@ -9244,13 +9244,13 @@
         <v>11</v>
       </c>
       <c r="E242" s="2">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="F242" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G242" s="2" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H242" s="2" t="s">
         <v>14</v>
@@ -9270,13 +9270,13 @@
         <v>11</v>
       </c>
       <c r="E243" s="4">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F243" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G243" s="4" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H243" s="4" t="s">
         <v>14</v>
@@ -9296,13 +9296,13 @@
         <v>11</v>
       </c>
       <c r="E244" s="2">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="F244" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G244" s="2" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H244" s="2" t="s">
         <v>14</v>
@@ -9322,13 +9322,13 @@
         <v>11</v>
       </c>
       <c r="E245" s="4">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="F245" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G245" s="4" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H245" s="4" t="s">
         <v>14</v>
@@ -9348,13 +9348,13 @@
         <v>11</v>
       </c>
       <c r="E246" s="2">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="F246" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G246" s="2" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H246" s="2" t="s">
         <v>14</v>
@@ -9374,13 +9374,13 @@
         <v>11</v>
       </c>
       <c r="E247" s="4">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F247" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G247" s="4" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H247" s="4" t="s">
         <v>14</v>
@@ -9400,13 +9400,13 @@
         <v>11</v>
       </c>
       <c r="E248" s="2">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="F248" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G248" s="2" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H248" s="2" t="s">
         <v>14</v>
@@ -9426,13 +9426,13 @@
         <v>11</v>
       </c>
       <c r="E249" s="4">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="F249" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G249" s="4" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H249" s="4" t="s">
         <v>14</v>
@@ -9452,13 +9452,13 @@
         <v>11</v>
       </c>
       <c r="E250" s="2">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="F250" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G250" s="2" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H250" s="2" t="s">
         <v>14</v>
@@ -9478,13 +9478,13 @@
         <v>11</v>
       </c>
       <c r="E251" s="4">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="F251" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G251" s="4" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H251" s="4" t="s">
         <v>14</v>
@@ -9504,13 +9504,13 @@
         <v>11</v>
       </c>
       <c r="E252" s="2">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F252" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G252" s="2" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H252" s="2" t="s">
         <v>14</v>
@@ -9530,13 +9530,13 @@
         <v>11</v>
       </c>
       <c r="E253" s="4">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F253" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G253" s="4" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H253" s="4" t="s">
         <v>14</v>
@@ -9556,13 +9556,13 @@
         <v>11</v>
       </c>
       <c r="E254" s="2">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F254" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G254" s="2" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H254" s="2" t="s">
         <v>14</v>
@@ -9582,13 +9582,13 @@
         <v>11</v>
       </c>
       <c r="E255" s="4">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="F255" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G255" s="4" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H255" s="4" t="s">
         <v>14</v>
@@ -9608,13 +9608,13 @@
         <v>11</v>
       </c>
       <c r="E256" s="2">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="F256" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G256" s="2" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H256" s="2" t="s">
         <v>14</v>
@@ -9634,13 +9634,13 @@
         <v>11</v>
       </c>
       <c r="E257" s="4">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F257" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G257" s="4" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H257" s="4" t="s">
         <v>14</v>
@@ -9660,13 +9660,13 @@
         <v>11</v>
       </c>
       <c r="E258" s="2">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="F258" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G258" s="2" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H258" s="2" t="s">
         <v>14</v>
@@ -9686,13 +9686,13 @@
         <v>11</v>
       </c>
       <c r="E259" s="4">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="F259" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G259" s="4" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H259" s="4" t="s">
         <v>14</v>
@@ -9712,13 +9712,13 @@
         <v>11</v>
       </c>
       <c r="E260" s="2">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="F260" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G260" s="2" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H260" s="2" t="s">
         <v>14</v>
@@ -9738,13 +9738,13 @@
         <v>11</v>
       </c>
       <c r="E261" s="4">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="F261" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G261" s="4" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H261" s="4" t="s">
         <v>14</v>
@@ -9764,13 +9764,13 @@
         <v>11</v>
       </c>
       <c r="E262" s="2">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="F262" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G262" s="2" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H262" s="2" t="s">
         <v>14</v>
@@ -9790,13 +9790,13 @@
         <v>11</v>
       </c>
       <c r="E263" s="4">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="F263" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G263" s="4" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H263" s="4" t="s">
         <v>14</v>
@@ -9816,13 +9816,13 @@
         <v>11</v>
       </c>
       <c r="E264" s="2">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="F264" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G264" s="2" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H264" s="2" t="s">
         <v>14</v>
@@ -9842,13 +9842,13 @@
         <v>11</v>
       </c>
       <c r="E265" s="4">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="F265" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G265" s="4" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H265" s="4" t="s">
         <v>14</v>
@@ -9868,13 +9868,13 @@
         <v>11</v>
       </c>
       <c r="E266" s="2">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F266" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G266" s="2" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H266" s="2" t="s">
         <v>14</v>
@@ -9894,13 +9894,13 @@
         <v>11</v>
       </c>
       <c r="E267" s="4">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="F267" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G267" s="4" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H267" s="4" t="s">
         <v>14</v>
@@ -9920,13 +9920,13 @@
         <v>11</v>
       </c>
       <c r="E268" s="2">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="F268" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G268" s="2" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H268" s="2" t="s">
         <v>14</v>
@@ -9946,13 +9946,13 @@
         <v>11</v>
       </c>
       <c r="E269" s="4">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="F269" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G269" s="4" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H269" s="4" t="s">
         <v>14</v>
@@ -9972,13 +9972,13 @@
         <v>11</v>
       </c>
       <c r="E270" s="2">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="F270" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G270" s="2" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H270" s="2" t="s">
         <v>14</v>
@@ -9998,13 +9998,13 @@
         <v>11</v>
       </c>
       <c r="E271" s="4">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F271" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G271" s="4" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H271" s="4" t="s">
         <v>14</v>
@@ -10024,13 +10024,13 @@
         <v>11</v>
       </c>
       <c r="E272" s="2">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="F272" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G272" s="2" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H272" s="2" t="s">
         <v>14</v>
@@ -10050,13 +10050,13 @@
         <v>11</v>
       </c>
       <c r="E273" s="4">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="F273" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G273" s="4" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H273" s="4" t="s">
         <v>14</v>
@@ -10076,13 +10076,13 @@
         <v>11</v>
       </c>
       <c r="E274" s="2">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="F274" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G274" s="2" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H274" s="2" t="s">
         <v>14</v>
@@ -10102,13 +10102,13 @@
         <v>11</v>
       </c>
       <c r="E275" s="4">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F275" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G275" s="4" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H275" s="4" t="s">
         <v>14</v>
@@ -10128,13 +10128,13 @@
         <v>11</v>
       </c>
       <c r="E276" s="2">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="F276" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G276" s="2" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H276" s="2" t="s">
         <v>14</v>
@@ -10160,7 +10160,7 @@
         <v>12</v>
       </c>
       <c r="G277" s="4" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H277" s="4" t="s">
         <v>14</v>
@@ -10180,13 +10180,13 @@
         <v>11</v>
       </c>
       <c r="E278" s="2">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="F278" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G278" s="2" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H278" s="2" t="s">
         <v>14</v>
@@ -10206,13 +10206,13 @@
         <v>11</v>
       </c>
       <c r="E279" s="4">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="F279" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G279" s="4" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H279" s="4" t="s">
         <v>14</v>
@@ -10232,13 +10232,13 @@
         <v>11</v>
       </c>
       <c r="E280" s="2">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="F280" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G280" s="2" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H280" s="2" t="s">
         <v>14</v>
@@ -10264,7 +10264,7 @@
         <v>12</v>
       </c>
       <c r="G281" s="4" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H281" s="4" t="s">
         <v>14</v>
@@ -10284,13 +10284,13 @@
         <v>11</v>
       </c>
       <c r="E282" s="2">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F282" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G282" s="2" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H282" s="2" t="s">
         <v>14</v>
@@ -10310,13 +10310,13 @@
         <v>11</v>
       </c>
       <c r="E283" s="4">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="F283" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G283" s="4" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H283" s="4" t="s">
         <v>14</v>
@@ -10336,13 +10336,13 @@
         <v>11</v>
       </c>
       <c r="E284" s="2">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="F284" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G284" s="2" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H284" s="2" t="s">
         <v>14</v>
@@ -10362,13 +10362,13 @@
         <v>11</v>
       </c>
       <c r="E285" s="4">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="F285" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G285" s="4" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H285" s="4" t="s">
         <v>14</v>
@@ -10388,13 +10388,13 @@
         <v>11</v>
       </c>
       <c r="E286" s="2">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="F286" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G286" s="2" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H286" s="2" t="s">
         <v>14</v>
@@ -10414,13 +10414,13 @@
         <v>11</v>
       </c>
       <c r="E287" s="4">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="F287" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G287" s="4" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H287" s="4" t="s">
         <v>14</v>
@@ -10440,13 +10440,13 @@
         <v>11</v>
       </c>
       <c r="E288" s="2">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F288" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G288" s="2" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H288" s="2" t="s">
         <v>14</v>
@@ -10466,13 +10466,13 @@
         <v>11</v>
       </c>
       <c r="E289" s="4">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="F289" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G289" s="4" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H289" s="4" t="s">
         <v>14</v>
@@ -10492,13 +10492,13 @@
         <v>11</v>
       </c>
       <c r="E290" s="2">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="F290" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G290" s="2" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H290" s="2" t="s">
         <v>14</v>
@@ -10518,13 +10518,13 @@
         <v>11</v>
       </c>
       <c r="E291" s="4">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F291" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G291" s="4" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H291" s="4" t="s">
         <v>14</v>
@@ -10544,13 +10544,13 @@
         <v>11</v>
       </c>
       <c r="E292" s="2">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F292" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G292" s="2" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H292" s="2" t="s">
         <v>14</v>
@@ -10570,13 +10570,13 @@
         <v>11</v>
       </c>
       <c r="E293" s="4">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="F293" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G293" s="4" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H293" s="4" t="s">
         <v>14</v>
@@ -10596,13 +10596,13 @@
         <v>11</v>
       </c>
       <c r="E294" s="2">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="F294" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G294" s="2" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H294" s="2" t="s">
         <v>14</v>
@@ -10622,13 +10622,13 @@
         <v>11</v>
       </c>
       <c r="E295" s="4">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="F295" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G295" s="4" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H295" s="4" t="s">
         <v>14</v>
@@ -10648,13 +10648,13 @@
         <v>11</v>
       </c>
       <c r="E296" s="2">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="F296" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G296" s="2" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H296" s="2" t="s">
         <v>14</v>
@@ -10674,13 +10674,13 @@
         <v>11</v>
       </c>
       <c r="E297" s="4">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="F297" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G297" s="4" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H297" s="4" t="s">
         <v>14</v>
@@ -10700,13 +10700,13 @@
         <v>11</v>
       </c>
       <c r="E298" s="2">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="F298" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G298" s="2" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H298" s="2" t="s">
         <v>14</v>
@@ -10726,13 +10726,13 @@
         <v>11</v>
       </c>
       <c r="E299" s="4">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F299" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G299" s="4" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H299" s="4" t="s">
         <v>14</v>
@@ -10752,13 +10752,13 @@
         <v>11</v>
       </c>
       <c r="E300" s="2">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="F300" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G300" s="2" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H300" s="2" t="s">
         <v>14</v>
@@ -10778,13 +10778,13 @@
         <v>11</v>
       </c>
       <c r="E301" s="4">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="F301" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G301" s="4" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H301" s="4" t="s">
         <v>14</v>
@@ -10804,13 +10804,13 @@
         <v>11</v>
       </c>
       <c r="E302" s="2">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="F302" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G302" s="2" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H302" s="2" t="s">
         <v>14</v>
@@ -10830,13 +10830,13 @@
         <v>11</v>
       </c>
       <c r="E303" s="4">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="F303" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G303" s="4" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H303" s="4" t="s">
         <v>14</v>
@@ -10856,13 +10856,13 @@
         <v>11</v>
       </c>
       <c r="E304" s="2">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="F304" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G304" s="2" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H304" s="2" t="s">
         <v>14</v>
@@ -10882,13 +10882,13 @@
         <v>11</v>
       </c>
       <c r="E305" s="4">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="F305" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G305" s="4" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H305" s="4" t="s">
         <v>14</v>
@@ -10908,13 +10908,13 @@
         <v>11</v>
       </c>
       <c r="E306" s="2">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F306" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G306" s="2" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H306" s="2" t="s">
         <v>14</v>
@@ -10934,13 +10934,13 @@
         <v>11</v>
       </c>
       <c r="E307" s="4">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F307" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G307" s="4" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H307" s="4" t="s">
         <v>14</v>
@@ -10960,13 +10960,13 @@
         <v>11</v>
       </c>
       <c r="E308" s="2">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="F308" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G308" s="2" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H308" s="2" t="s">
         <v>14</v>
@@ -10992,7 +10992,7 @@
         <v>12</v>
       </c>
       <c r="G309" s="4" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H309" s="4" t="s">
         <v>14</v>
@@ -11012,13 +11012,13 @@
         <v>11</v>
       </c>
       <c r="E310" s="2">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="F310" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G310" s="2" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H310" s="2" t="s">
         <v>14</v>
@@ -11038,13 +11038,13 @@
         <v>11</v>
       </c>
       <c r="E311" s="4">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F311" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G311" s="4" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H311" s="4" t="s">
         <v>14</v>
@@ -11064,13 +11064,13 @@
         <v>11</v>
       </c>
       <c r="E312" s="2">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="F312" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G312" s="2" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H312" s="2" t="s">
         <v>14</v>
@@ -11090,13 +11090,13 @@
         <v>11</v>
       </c>
       <c r="E313" s="4">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F313" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G313" s="4" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H313" s="4" t="s">
         <v>14</v>
@@ -11116,13 +11116,13 @@
         <v>11</v>
       </c>
       <c r="E314" s="2">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="F314" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G314" s="2" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H314" s="2" t="s">
         <v>14</v>
@@ -11148,7 +11148,7 @@
         <v>12</v>
       </c>
       <c r="G315" s="4" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H315" s="4" t="s">
         <v>14</v>
@@ -11168,13 +11168,13 @@
         <v>11</v>
       </c>
       <c r="E316" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F316" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G316" s="2" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H316" s="2" t="s">
         <v>14</v>
@@ -11194,13 +11194,13 @@
         <v>11</v>
       </c>
       <c r="E317" s="4">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="F317" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G317" s="4" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H317" s="4" t="s">
         <v>14</v>
@@ -11220,13 +11220,13 @@
         <v>11</v>
       </c>
       <c r="E318" s="2">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="F318" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G318" s="2" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H318" s="2" t="s">
         <v>14</v>
@@ -11246,13 +11246,13 @@
         <v>11</v>
       </c>
       <c r="E319" s="4">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="F319" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G319" s="4" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H319" s="4" t="s">
         <v>14</v>
@@ -11272,13 +11272,13 @@
         <v>11</v>
       </c>
       <c r="E320" s="2">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="F320" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G320" s="2" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H320" s="2" t="s">
         <v>14</v>
@@ -11298,13 +11298,13 @@
         <v>11</v>
       </c>
       <c r="E321" s="4">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="F321" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G321" s="4" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H321" s="4" t="s">
         <v>14</v>
@@ -11324,13 +11324,13 @@
         <v>11</v>
       </c>
       <c r="E322" s="2">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F322" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G322" s="2" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H322" s="2" t="s">
         <v>14</v>
@@ -11350,13 +11350,13 @@
         <v>11</v>
       </c>
       <c r="E323" s="4">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="F323" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G323" s="4" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H323" s="4" t="s">
         <v>14</v>
@@ -11376,13 +11376,13 @@
         <v>11</v>
       </c>
       <c r="E324" s="2">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="F324" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G324" s="2" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H324" s="2" t="s">
         <v>14</v>
@@ -11402,13 +11402,13 @@
         <v>11</v>
       </c>
       <c r="E325" s="4">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="F325" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G325" s="4" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H325" s="4" t="s">
         <v>14</v>
@@ -11428,13 +11428,13 @@
         <v>11</v>
       </c>
       <c r="E326" s="2">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="F326" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G326" s="2" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H326" s="2" t="s">
         <v>14</v>
@@ -11454,13 +11454,13 @@
         <v>11</v>
       </c>
       <c r="E327" s="4">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F327" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G327" s="4" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H327" s="4" t="s">
         <v>14</v>
@@ -11480,13 +11480,13 @@
         <v>11</v>
       </c>
       <c r="E328" s="2">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="F328" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G328" s="2" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H328" s="2" t="s">
         <v>14</v>
@@ -11506,13 +11506,13 @@
         <v>11</v>
       </c>
       <c r="E329" s="4">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="F329" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G329" s="4" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H329" s="4" t="s">
         <v>14</v>
@@ -11532,13 +11532,13 @@
         <v>11</v>
       </c>
       <c r="E330" s="2">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="F330" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G330" s="2" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H330" s="2" t="s">
         <v>14</v>
@@ -11558,13 +11558,13 @@
         <v>11</v>
       </c>
       <c r="E331" s="4">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="F331" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G331" s="4" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H331" s="4" t="s">
         <v>14</v>
@@ -11584,13 +11584,13 @@
         <v>11</v>
       </c>
       <c r="E332" s="2">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F332" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G332" s="2" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H332" s="2" t="s">
         <v>14</v>
@@ -11610,13 +11610,13 @@
         <v>11</v>
       </c>
       <c r="E333" s="4">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="F333" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G333" s="4" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H333" s="4" t="s">
         <v>14</v>
@@ -11636,13 +11636,13 @@
         <v>11</v>
       </c>
       <c r="E334" s="2">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="F334" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G334" s="2" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H334" s="2" t="s">
         <v>14</v>
@@ -11662,13 +11662,13 @@
         <v>11</v>
       </c>
       <c r="E335" s="4">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="F335" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G335" s="4" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H335" s="4" t="s">
         <v>14</v>
@@ -11688,13 +11688,13 @@
         <v>11</v>
       </c>
       <c r="E336" s="2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F336" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G336" s="2" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H336" s="2" t="s">
         <v>14</v>
@@ -11714,13 +11714,13 @@
         <v>11</v>
       </c>
       <c r="E337" s="4">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="F337" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G337" s="4" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H337" s="4" t="s">
         <v>14</v>
@@ -11740,13 +11740,13 @@
         <v>11</v>
       </c>
       <c r="E338" s="2">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="F338" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G338" s="2" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H338" s="2" t="s">
         <v>14</v>
@@ -11766,13 +11766,13 @@
         <v>11</v>
       </c>
       <c r="E339" s="4">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="F339" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G339" s="4" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H339" s="4" t="s">
         <v>14</v>
@@ -11792,13 +11792,13 @@
         <v>11</v>
       </c>
       <c r="E340" s="2">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="F340" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G340" s="2" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H340" s="2" t="s">
         <v>14</v>
@@ -11818,13 +11818,13 @@
         <v>11</v>
       </c>
       <c r="E341" s="4">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="F341" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G341" s="4" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H341" s="4" t="s">
         <v>14</v>
@@ -11844,13 +11844,13 @@
         <v>11</v>
       </c>
       <c r="E342" s="2">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="F342" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G342" s="2" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H342" s="2" t="s">
         <v>14</v>
@@ -11870,13 +11870,13 @@
         <v>11</v>
       </c>
       <c r="E343" s="4">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="F343" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G343" s="4" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H343" s="4" t="s">
         <v>14</v>
@@ -11896,13 +11896,13 @@
         <v>11</v>
       </c>
       <c r="E344" s="2">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F344" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G344" s="2" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H344" s="2" t="s">
         <v>14</v>
@@ -11922,13 +11922,13 @@
         <v>11</v>
       </c>
       <c r="E345" s="4">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="F345" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G345" s="4" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H345" s="4" t="s">
         <v>14</v>
@@ -11948,13 +11948,13 @@
         <v>11</v>
       </c>
       <c r="E346" s="2">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="F346" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G346" s="2" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H346" s="2" t="s">
         <v>14</v>
@@ -11974,13 +11974,13 @@
         <v>11</v>
       </c>
       <c r="E347" s="4">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="F347" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G347" s="4" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H347" s="4" t="s">
         <v>14</v>
@@ -12000,13 +12000,13 @@
         <v>11</v>
       </c>
       <c r="E348" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F348" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G348" s="2" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H348" s="2" t="s">
         <v>14</v>
@@ -12026,13 +12026,13 @@
         <v>11</v>
       </c>
       <c r="E349" s="4">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="F349" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G349" s="4" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H349" s="4" t="s">
         <v>14</v>
@@ -12052,13 +12052,13 @@
         <v>11</v>
       </c>
       <c r="E350" s="2">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="F350" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G350" s="2" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H350" s="2" t="s">
         <v>14</v>
@@ -12078,13 +12078,13 @@
         <v>11</v>
       </c>
       <c r="E351" s="4">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="F351" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G351" s="4" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H351" s="4" t="s">
         <v>14</v>
@@ -12104,13 +12104,13 @@
         <v>11</v>
       </c>
       <c r="E352" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F352" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G352" s="2" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H352" s="2" t="s">
         <v>14</v>
@@ -12130,13 +12130,13 @@
         <v>11</v>
       </c>
       <c r="E353" s="4">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F353" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G353" s="4" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H353" s="4" t="s">
         <v>14</v>
@@ -12156,13 +12156,13 @@
         <v>11</v>
       </c>
       <c r="E354" s="2">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F354" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G354" s="2" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H354" s="2" t="s">
         <v>14</v>
@@ -12182,13 +12182,13 @@
         <v>11</v>
       </c>
       <c r="E355" s="4">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F355" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G355" s="4" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H355" s="4" t="s">
         <v>14</v>
@@ -12208,13 +12208,13 @@
         <v>11</v>
       </c>
       <c r="E356" s="2">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="F356" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G356" s="2" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H356" s="2" t="s">
         <v>14</v>
@@ -12234,13 +12234,13 @@
         <v>11</v>
       </c>
       <c r="E357" s="4">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F357" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G357" s="4" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H357" s="4" t="s">
         <v>14</v>
@@ -12260,13 +12260,13 @@
         <v>11</v>
       </c>
       <c r="E358" s="2">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="F358" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G358" s="2" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H358" s="2" t="s">
         <v>14</v>
@@ -12286,13 +12286,13 @@
         <v>11</v>
       </c>
       <c r="E359" s="4">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="F359" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G359" s="4" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H359" s="4" t="s">
         <v>14</v>
@@ -12312,13 +12312,13 @@
         <v>11</v>
       </c>
       <c r="E360" s="2">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="F360" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G360" s="2" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H360" s="2" t="s">
         <v>14</v>
@@ -12338,13 +12338,13 @@
         <v>11</v>
       </c>
       <c r="E361" s="4">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="F361" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G361" s="4" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H361" s="4" t="s">
         <v>14</v>
@@ -12364,13 +12364,13 @@
         <v>11</v>
       </c>
       <c r="E362" s="2">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F362" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G362" s="2" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H362" s="2" t="s">
         <v>14</v>
@@ -12390,13 +12390,13 @@
         <v>11</v>
       </c>
       <c r="E363" s="4">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="F363" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G363" s="4" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H363" s="4" t="s">
         <v>14</v>
@@ -12416,13 +12416,13 @@
         <v>11</v>
       </c>
       <c r="E364" s="2">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="F364" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G364" s="2" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H364" s="2" t="s">
         <v>14</v>
@@ -12442,13 +12442,13 @@
         <v>11</v>
       </c>
       <c r="E365" s="4">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="F365" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G365" s="4" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H365" s="4" t="s">
         <v>14</v>
@@ -12468,13 +12468,13 @@
         <v>11</v>
       </c>
       <c r="E366" s="2">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="F366" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G366" s="2" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H366" s="2" t="s">
         <v>14</v>
@@ -12494,13 +12494,13 @@
         <v>11</v>
       </c>
       <c r="E367" s="4">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="F367" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G367" s="4" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H367" s="4" t="s">
         <v>14</v>
@@ -12520,13 +12520,13 @@
         <v>11</v>
       </c>
       <c r="E368" s="2">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="F368" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G368" s="2" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H368" s="2" t="s">
         <v>14</v>
@@ -12546,13 +12546,13 @@
         <v>11</v>
       </c>
       <c r="E369" s="4">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="F369" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G369" s="4" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H369" s="4" t="s">
         <v>14</v>
@@ -12572,13 +12572,13 @@
         <v>11</v>
       </c>
       <c r="E370" s="2">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="F370" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G370" s="2" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H370" s="2" t="s">
         <v>14</v>
@@ -12598,13 +12598,13 @@
         <v>11</v>
       </c>
       <c r="E371" s="4">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F371" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G371" s="4" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H371" s="4" t="s">
         <v>14</v>
@@ -12624,13 +12624,13 @@
         <v>11</v>
       </c>
       <c r="E372" s="2">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F372" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G372" s="2" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H372" s="2" t="s">
         <v>14</v>
@@ -12650,13 +12650,13 @@
         <v>11</v>
       </c>
       <c r="E373" s="4">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="F373" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G373" s="4" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H373" s="4" t="s">
         <v>14</v>
@@ -12676,13 +12676,13 @@
         <v>11</v>
       </c>
       <c r="E374" s="2">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F374" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G374" s="2" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H374" s="2" t="s">
         <v>14</v>
@@ -12702,13 +12702,13 @@
         <v>11</v>
       </c>
       <c r="E375" s="4">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F375" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G375" s="4" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H375" s="4" t="s">
         <v>14</v>
@@ -12728,13 +12728,13 @@
         <v>11</v>
       </c>
       <c r="E376" s="2">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="F376" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G376" s="2" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H376" s="2" t="s">
         <v>14</v>
@@ -12754,13 +12754,13 @@
         <v>11</v>
       </c>
       <c r="E377" s="4">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="F377" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G377" s="4" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H377" s="4" t="s">
         <v>14</v>
@@ -12786,7 +12786,7 @@
         <v>12</v>
       </c>
       <c r="G378" s="2" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H378" s="2" t="s">
         <v>14</v>
@@ -12806,13 +12806,13 @@
         <v>11</v>
       </c>
       <c r="E379" s="4">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F379" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G379" s="4" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H379" s="4" t="s">
         <v>14</v>
@@ -12832,13 +12832,13 @@
         <v>11</v>
       </c>
       <c r="E380" s="2">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="F380" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G380" s="2" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H380" s="2" t="s">
         <v>14</v>
@@ -12858,13 +12858,13 @@
         <v>11</v>
       </c>
       <c r="E381" s="4">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F381" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G381" s="4" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H381" s="4" t="s">
         <v>14</v>
@@ -12884,13 +12884,13 @@
         <v>11</v>
       </c>
       <c r="E382" s="2">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F382" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G382" s="2" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H382" s="2" t="s">
         <v>14</v>
@@ -12910,13 +12910,13 @@
         <v>11</v>
       </c>
       <c r="E383" s="4">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="F383" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G383" s="4" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H383" s="4" t="s">
         <v>14</v>
@@ -12936,13 +12936,13 @@
         <v>11</v>
       </c>
       <c r="E384" s="2">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="F384" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G384" s="2" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H384" s="2" t="s">
         <v>14</v>
@@ -12962,13 +12962,13 @@
         <v>11</v>
       </c>
       <c r="E385" s="4">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="F385" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G385" s="4" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H385" s="4" t="s">
         <v>14</v>
@@ -12988,13 +12988,13 @@
         <v>11</v>
       </c>
       <c r="E386" s="2">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="F386" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G386" s="2" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H386" s="2" t="s">
         <v>14</v>
@@ -13014,13 +13014,13 @@
         <v>11</v>
       </c>
       <c r="E387" s="4">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F387" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G387" s="4" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H387" s="4" t="s">
         <v>14</v>
@@ -13040,13 +13040,13 @@
         <v>11</v>
       </c>
       <c r="E388" s="2">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="F388" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G388" s="2" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H388" s="2" t="s">
         <v>14</v>
@@ -13066,13 +13066,13 @@
         <v>11</v>
       </c>
       <c r="E389" s="4">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="F389" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G389" s="4" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H389" s="4" t="s">
         <v>14</v>
@@ -13092,13 +13092,13 @@
         <v>11</v>
       </c>
       <c r="E390" s="2">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="F390" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G390" s="2" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H390" s="2" t="s">
         <v>14</v>
@@ -13118,13 +13118,13 @@
         <v>11</v>
       </c>
       <c r="E391" s="4">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="F391" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G391" s="4" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H391" s="4" t="s">
         <v>14</v>
@@ -13144,13 +13144,13 @@
         <v>11</v>
       </c>
       <c r="E392" s="2">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="F392" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G392" s="2" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H392" s="2" t="s">
         <v>14</v>
@@ -13170,13 +13170,13 @@
         <v>11</v>
       </c>
       <c r="E393" s="4">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="F393" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G393" s="4" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H393" s="4" t="s">
         <v>14</v>
@@ -13196,13 +13196,13 @@
         <v>11</v>
       </c>
       <c r="E394" s="2">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="F394" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G394" s="2" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H394" s="2" t="s">
         <v>14</v>
@@ -13222,13 +13222,13 @@
         <v>11</v>
       </c>
       <c r="E395" s="4">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F395" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G395" s="4" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H395" s="4" t="s">
         <v>14</v>
@@ -13248,13 +13248,13 @@
         <v>11</v>
       </c>
       <c r="E396" s="2">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="F396" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G396" s="2" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H396" s="2" t="s">
         <v>14</v>
@@ -13274,13 +13274,13 @@
         <v>11</v>
       </c>
       <c r="E397" s="4">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F397" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G397" s="4" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H397" s="4" t="s">
         <v>14</v>
@@ -13300,13 +13300,13 @@
         <v>11</v>
       </c>
       <c r="E398" s="2">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="F398" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G398" s="2" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H398" s="2" t="s">
         <v>14</v>
@@ -13326,13 +13326,13 @@
         <v>11</v>
       </c>
       <c r="E399" s="4">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="F399" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G399" s="4" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H399" s="4" t="s">
         <v>14</v>
@@ -13352,13 +13352,13 @@
         <v>11</v>
       </c>
       <c r="E400" s="2">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="F400" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G400" s="2" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H400" s="2" t="s">
         <v>14</v>
@@ -13378,13 +13378,13 @@
         <v>11</v>
       </c>
       <c r="E401" s="4">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="F401" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G401" s="4" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H401" s="4" t="s">
         <v>14</v>

--- a/reports/Mobile_Appium_E2E_Test_Report_400.xlsx
+++ b/reports/Mobile_Appium_E2E_Test_Report_400.xlsx
@@ -52,7 +52,7 @@
     <t>PASSED</t>
   </si>
   <si>
-    <t>2026-08-07T14:56:27.205Z</t>
+    <t>2026-08-07T04:03:04.297Z</t>
   </si>
   <si>
     <t>Verified Android Activity lifecycle and Capacitor native plugin interface</t>
@@ -82,9 +82,6 @@
     <t>Native Authentication Flow - Mobile Assertion #5: Verify native shell component interaction</t>
   </si>
   <si>
-    <t>2026-08-07T14:56:27.206Z</t>
-  </si>
-  <si>
     <t>MOB-TC-0006</t>
   </si>
   <si>
@@ -428,6 +425,9 @@
   </si>
   <si>
     <t>Screen Orientation Swap - Mobile Assertion #1: Verify native shell component interaction</t>
+  </si>
+  <si>
+    <t>2026-08-07T04:03:04.298Z</t>
   </si>
   <si>
     <t>MOB-TC-0062</t>
@@ -3030,7 +3030,7 @@
         <v>11</v>
       </c>
       <c r="E3" s="4">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>12</v>
@@ -3056,7 +3056,7 @@
         <v>11</v>
       </c>
       <c r="E4" s="2">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="F4" s="3" t="s">
         <v>12</v>
@@ -3082,7 +3082,7 @@
         <v>11</v>
       </c>
       <c r="E5" s="4">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="F5" s="3" t="s">
         <v>12</v>
@@ -3108,13 +3108,13 @@
         <v>11</v>
       </c>
       <c r="E6" s="2">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="F6" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>14</v>
@@ -3122,25 +3122,25 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B7" s="4" t="s">
         <v>9</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>11</v>
       </c>
       <c r="E7" s="4">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="F7" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="H7" s="4" t="s">
         <v>14</v>
@@ -3148,25 +3148,25 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E8" s="2">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="F8" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>14</v>
@@ -3174,25 +3174,25 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B9" s="4" t="s">
         <v>9</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D9" s="4" t="s">
         <v>11</v>
       </c>
       <c r="E9" s="4">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="F9" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="H9" s="4" t="s">
         <v>14</v>
@@ -3200,25 +3200,25 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E10" s="2">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="F10" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>14</v>
@@ -3226,25 +3226,25 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B11" s="4" t="s">
         <v>9</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D11" s="4" t="s">
         <v>11</v>
       </c>
       <c r="E11" s="4">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="F11" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="H11" s="4" t="s">
         <v>14</v>
@@ -3252,25 +3252,25 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E12" s="2">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F12" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>14</v>
@@ -3278,25 +3278,25 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B13" s="4" t="s">
         <v>9</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D13" s="4" t="s">
         <v>11</v>
       </c>
       <c r="E13" s="4">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="F13" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="H13" s="4" t="s">
         <v>14</v>
@@ -3304,25 +3304,25 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E14" s="2">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="H14" s="2" t="s">
         <v>14</v>
@@ -3330,13 +3330,13 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B15" s="4" t="s">
         <v>9</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D15" s="4" t="s">
         <v>11</v>
@@ -3348,7 +3348,7 @@
         <v>12</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="H15" s="4" t="s">
         <v>14</v>
@@ -3356,25 +3356,25 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E16" s="2">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F16" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="H16" s="2" t="s">
         <v>14</v>
@@ -3382,25 +3382,25 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B17" s="4" t="s">
         <v>9</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D17" s="4" t="s">
         <v>11</v>
       </c>
       <c r="E17" s="4">
+        <v>26</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G17" s="4" t="s">
         <v>13</v>
-      </c>
-      <c r="F17" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G17" s="4" t="s">
-        <v>23</v>
       </c>
       <c r="H17" s="4" t="s">
         <v>14</v>
@@ -3408,25 +3408,25 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E18" s="2">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F18" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="H18" s="2" t="s">
         <v>14</v>
@@ -3434,25 +3434,25 @@
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B19" s="4" t="s">
         <v>9</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D19" s="4" t="s">
         <v>11</v>
       </c>
       <c r="E19" s="4">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F19" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="H19" s="4" t="s">
         <v>14</v>
@@ -3460,25 +3460,25 @@
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E20" s="2">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F20" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="H20" s="2" t="s">
         <v>14</v>
@@ -3486,25 +3486,25 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B21" s="4" t="s">
         <v>9</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D21" s="4" t="s">
         <v>11</v>
       </c>
       <c r="E21" s="4">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="F21" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="H21" s="4" t="s">
         <v>14</v>
@@ -3512,25 +3512,25 @@
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B22" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="B22" s="2" t="s">
+      <c r="C22" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="C22" s="2" t="s">
-        <v>56</v>
-      </c>
       <c r="D22" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E22" s="2">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F22" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="H22" s="2" t="s">
         <v>14</v>
@@ -3538,25 +3538,25 @@
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C23" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="B23" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="C23" s="4" t="s">
-        <v>58</v>
-      </c>
       <c r="D23" s="4" t="s">
         <v>11</v>
       </c>
       <c r="E23" s="4">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="F23" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G23" s="4" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="H23" s="4" t="s">
         <v>14</v>
@@ -3564,25 +3564,25 @@
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C24" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="B24" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>60</v>
-      </c>
       <c r="D24" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E24" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F24" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="H24" s="2" t="s">
         <v>14</v>
@@ -3590,25 +3590,25 @@
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C25" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="B25" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="C25" s="4" t="s">
-        <v>62</v>
-      </c>
       <c r="D25" s="4" t="s">
         <v>11</v>
       </c>
       <c r="E25" s="4">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F25" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G25" s="4" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="H25" s="4" t="s">
         <v>14</v>
@@ -3616,13 +3616,13 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C26" s="2" t="s">
         <v>63</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>64</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>11</v>
@@ -3634,7 +3634,7 @@
         <v>12</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="H26" s="2" t="s">
         <v>14</v>
@@ -3642,25 +3642,25 @@
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C27" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="B27" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="C27" s="4" t="s">
-        <v>66</v>
-      </c>
       <c r="D27" s="4" t="s">
         <v>11</v>
       </c>
       <c r="E27" s="4">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="F27" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G27" s="4" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="H27" s="4" t="s">
         <v>14</v>
@@ -3668,25 +3668,25 @@
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C28" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="B28" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>68</v>
-      </c>
       <c r="D28" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E28" s="2">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="F28" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="H28" s="2" t="s">
         <v>14</v>
@@ -3694,25 +3694,25 @@
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C29" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="B29" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="C29" s="4" t="s">
-        <v>70</v>
-      </c>
       <c r="D29" s="4" t="s">
         <v>11</v>
       </c>
       <c r="E29" s="4">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="F29" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G29" s="4" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="H29" s="4" t="s">
         <v>14</v>
@@ -3720,25 +3720,25 @@
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C30" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="B30" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>72</v>
-      </c>
       <c r="D30" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E30" s="2">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F30" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="H30" s="2" t="s">
         <v>14</v>
@@ -3746,25 +3746,25 @@
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C31" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="B31" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="C31" s="4" t="s">
-        <v>74</v>
-      </c>
       <c r="D31" s="4" t="s">
         <v>11</v>
       </c>
       <c r="E31" s="4">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="F31" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G31" s="4" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="H31" s="4" t="s">
         <v>14</v>
@@ -3772,25 +3772,25 @@
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C32" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="B32" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>76</v>
-      </c>
       <c r="D32" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E32" s="2">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="F32" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="H32" s="2" t="s">
         <v>14</v>
@@ -3798,25 +3798,25 @@
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C33" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="B33" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="C33" s="4" t="s">
-        <v>78</v>
-      </c>
       <c r="D33" s="4" t="s">
         <v>11</v>
       </c>
       <c r="E33" s="4">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="F33" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G33" s="4" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="H33" s="4" t="s">
         <v>14</v>
@@ -3824,25 +3824,25 @@
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C34" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="B34" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>80</v>
-      </c>
       <c r="D34" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E34" s="2">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F34" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="H34" s="2" t="s">
         <v>14</v>
@@ -3850,25 +3850,25 @@
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C35" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="B35" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="C35" s="4" t="s">
-        <v>82</v>
-      </c>
       <c r="D35" s="4" t="s">
         <v>11</v>
       </c>
       <c r="E35" s="4">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="F35" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G35" s="4" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="H35" s="4" t="s">
         <v>14</v>
@@ -3876,25 +3876,25 @@
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C36" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="B36" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>84</v>
-      </c>
       <c r="D36" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E36" s="2">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="F36" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="H36" s="2" t="s">
         <v>14</v>
@@ -3902,25 +3902,25 @@
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C37" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="B37" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="C37" s="4" t="s">
-        <v>86</v>
-      </c>
       <c r="D37" s="4" t="s">
         <v>11</v>
       </c>
       <c r="E37" s="4">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="F37" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G37" s="4" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="H37" s="4" t="s">
         <v>14</v>
@@ -3928,25 +3928,25 @@
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C38" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="B38" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>88</v>
-      </c>
       <c r="D38" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E38" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F38" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="H38" s="2" t="s">
         <v>14</v>
@@ -3954,25 +3954,25 @@
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="B39" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C39" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="B39" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="C39" s="4" t="s">
-        <v>90</v>
-      </c>
       <c r="D39" s="4" t="s">
         <v>11</v>
       </c>
       <c r="E39" s="4">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="F39" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G39" s="4" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="H39" s="4" t="s">
         <v>14</v>
@@ -3980,25 +3980,25 @@
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C40" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="B40" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>92</v>
-      </c>
       <c r="D40" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E40" s="2">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="F40" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="H40" s="2" t="s">
         <v>14</v>
@@ -4006,14 +4006,14 @@
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="B41" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C41" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="B41" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="C41" s="4" t="s">
-        <v>94</v>
-      </c>
       <c r="D41" s="4" t="s">
         <v>11</v>
       </c>
@@ -4024,7 +4024,7 @@
         <v>12</v>
       </c>
       <c r="G41" s="4" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="H41" s="4" t="s">
         <v>14</v>
@@ -4032,25 +4032,25 @@
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="B42" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="B42" s="2" t="s">
+      <c r="C42" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="C42" s="2" t="s">
-        <v>97</v>
-      </c>
       <c r="D42" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E42" s="2">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="F42" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="H42" s="2" t="s">
         <v>14</v>
@@ -4058,25 +4058,25 @@
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="B43" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="C43" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="B43" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="C43" s="4" t="s">
-        <v>99</v>
-      </c>
       <c r="D43" s="4" t="s">
         <v>11</v>
       </c>
       <c r="E43" s="4">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="F43" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G43" s="4" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="H43" s="4" t="s">
         <v>14</v>
@@ -4084,25 +4084,25 @@
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C44" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="B44" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>101</v>
-      </c>
       <c r="D44" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E44" s="2">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="F44" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="H44" s="2" t="s">
         <v>14</v>
@@ -4110,25 +4110,25 @@
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="B45" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="C45" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="B45" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="C45" s="4" t="s">
-        <v>103</v>
-      </c>
       <c r="D45" s="4" t="s">
         <v>11</v>
       </c>
       <c r="E45" s="4">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="F45" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G45" s="4" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="H45" s="4" t="s">
         <v>14</v>
@@ -4136,25 +4136,25 @@
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C46" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="B46" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="C46" s="2" t="s">
-        <v>105</v>
-      </c>
       <c r="D46" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E46" s="2">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="F46" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="H46" s="2" t="s">
         <v>14</v>
@@ -4162,25 +4162,25 @@
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="B47" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="C47" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="B47" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="C47" s="4" t="s">
-        <v>107</v>
-      </c>
       <c r="D47" s="4" t="s">
         <v>11</v>
       </c>
       <c r="E47" s="4">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="F47" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G47" s="4" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="H47" s="4" t="s">
         <v>14</v>
@@ -4188,25 +4188,25 @@
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C48" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="B48" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="C48" s="2" t="s">
-        <v>109</v>
-      </c>
       <c r="D48" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E48" s="2">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F48" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="H48" s="2" t="s">
         <v>14</v>
@@ -4214,25 +4214,25 @@
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="B49" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="C49" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="B49" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="C49" s="4" t="s">
-        <v>111</v>
-      </c>
       <c r="D49" s="4" t="s">
         <v>11</v>
       </c>
       <c r="E49" s="4">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="F49" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G49" s="4" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="H49" s="4" t="s">
         <v>14</v>
@@ -4240,25 +4240,25 @@
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C50" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="B50" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="C50" s="2" t="s">
-        <v>113</v>
-      </c>
       <c r="D50" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E50" s="2">
+        <v>19</v>
+      </c>
+      <c r="F50" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G50" s="2" t="s">
         <v>13</v>
-      </c>
-      <c r="F50" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G50" s="2" t="s">
-        <v>23</v>
       </c>
       <c r="H50" s="2" t="s">
         <v>14</v>
@@ -4266,25 +4266,25 @@
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="B51" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="C51" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="B51" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="C51" s="4" t="s">
-        <v>115</v>
-      </c>
       <c r="D51" s="4" t="s">
         <v>11</v>
       </c>
       <c r="E51" s="4">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F51" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G51" s="4" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="H51" s="4" t="s">
         <v>14</v>
@@ -4292,25 +4292,25 @@
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C52" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="B52" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="C52" s="2" t="s">
-        <v>117</v>
-      </c>
       <c r="D52" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E52" s="2">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="F52" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="H52" s="2" t="s">
         <v>14</v>
@@ -4318,25 +4318,25 @@
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="B53" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="C53" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="B53" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="C53" s="4" t="s">
-        <v>119</v>
-      </c>
       <c r="D53" s="4" t="s">
         <v>11</v>
       </c>
       <c r="E53" s="4">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="F53" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G53" s="4" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="H53" s="4" t="s">
         <v>14</v>
@@ -4344,25 +4344,25 @@
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C54" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="B54" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="C54" s="2" t="s">
-        <v>121</v>
-      </c>
       <c r="D54" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E54" s="2">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="F54" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="H54" s="2" t="s">
         <v>14</v>
@@ -4370,25 +4370,25 @@
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="B55" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="C55" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="B55" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="C55" s="4" t="s">
-        <v>123</v>
-      </c>
       <c r="D55" s="4" t="s">
         <v>11</v>
       </c>
       <c r="E55" s="4">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="F55" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G55" s="4" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="H55" s="4" t="s">
         <v>14</v>
@@ -4396,25 +4396,25 @@
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C56" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="B56" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="C56" s="2" t="s">
-        <v>125</v>
-      </c>
       <c r="D56" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E56" s="2">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="F56" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="H56" s="2" t="s">
         <v>14</v>
@@ -4422,25 +4422,25 @@
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="B57" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="C57" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="B57" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="C57" s="4" t="s">
-        <v>127</v>
-      </c>
       <c r="D57" s="4" t="s">
         <v>11</v>
       </c>
       <c r="E57" s="4">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="F57" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G57" s="4" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="H57" s="4" t="s">
         <v>14</v>
@@ -4448,25 +4448,25 @@
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C58" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="B58" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="C58" s="2" t="s">
-        <v>129</v>
-      </c>
       <c r="D58" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E58" s="2">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="F58" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="H58" s="2" t="s">
         <v>14</v>
@@ -4474,25 +4474,25 @@
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="B59" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="C59" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="B59" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="C59" s="4" t="s">
-        <v>131</v>
-      </c>
       <c r="D59" s="4" t="s">
         <v>11</v>
       </c>
       <c r="E59" s="4">
+        <v>17</v>
+      </c>
+      <c r="F59" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G59" s="4" t="s">
         <v>13</v>
-      </c>
-      <c r="F59" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G59" s="4" t="s">
-        <v>23</v>
       </c>
       <c r="H59" s="4" t="s">
         <v>14</v>
@@ -4500,25 +4500,25 @@
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C60" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="B60" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="C60" s="2" t="s">
-        <v>133</v>
-      </c>
       <c r="D60" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E60" s="2">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="F60" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="H60" s="2" t="s">
         <v>14</v>
@@ -4526,25 +4526,25 @@
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="B61" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="C61" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="B61" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="C61" s="4" t="s">
-        <v>135</v>
-      </c>
       <c r="D61" s="4" t="s">
         <v>11</v>
       </c>
       <c r="E61" s="4">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="F61" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G61" s="4" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="H61" s="4" t="s">
         <v>14</v>
@@ -4552,25 +4552,25 @@
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="B62" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="B62" s="2" t="s">
+      <c r="C62" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="C62" s="2" t="s">
-        <v>138</v>
-      </c>
       <c r="D62" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E62" s="2">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F62" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H62" s="2" t="s">
         <v>14</v>
@@ -4581,7 +4581,7 @@
         <v>139</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C63" s="4" t="s">
         <v>140</v>
@@ -4590,13 +4590,13 @@
         <v>11</v>
       </c>
       <c r="E63" s="4">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="F63" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G63" s="4" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H63" s="4" t="s">
         <v>14</v>
@@ -4607,7 +4607,7 @@
         <v>141</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C64" s="2" t="s">
         <v>142</v>
@@ -4616,13 +4616,13 @@
         <v>11</v>
       </c>
       <c r="E64" s="2">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="F64" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H64" s="2" t="s">
         <v>14</v>
@@ -4633,7 +4633,7 @@
         <v>143</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C65" s="4" t="s">
         <v>144</v>
@@ -4642,13 +4642,13 @@
         <v>11</v>
       </c>
       <c r="E65" s="4">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F65" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G65" s="4" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H65" s="4" t="s">
         <v>14</v>
@@ -4659,7 +4659,7 @@
         <v>145</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C66" s="2" t="s">
         <v>146</v>
@@ -4668,13 +4668,13 @@
         <v>11</v>
       </c>
       <c r="E66" s="2">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="F66" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H66" s="2" t="s">
         <v>14</v>
@@ -4685,7 +4685,7 @@
         <v>147</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C67" s="4" t="s">
         <v>148</v>
@@ -4694,13 +4694,13 @@
         <v>11</v>
       </c>
       <c r="E67" s="4">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="F67" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G67" s="4" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H67" s="4" t="s">
         <v>14</v>
@@ -4711,7 +4711,7 @@
         <v>149</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C68" s="2" t="s">
         <v>150</v>
@@ -4720,13 +4720,13 @@
         <v>11</v>
       </c>
       <c r="E68" s="2">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F68" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H68" s="2" t="s">
         <v>14</v>
@@ -4737,7 +4737,7 @@
         <v>151</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C69" s="4" t="s">
         <v>152</v>
@@ -4746,13 +4746,13 @@
         <v>11</v>
       </c>
       <c r="E69" s="4">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="F69" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G69" s="4" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H69" s="4" t="s">
         <v>14</v>
@@ -4763,7 +4763,7 @@
         <v>153</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C70" s="2" t="s">
         <v>154</v>
@@ -4772,13 +4772,13 @@
         <v>11</v>
       </c>
       <c r="E70" s="2">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="F70" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H70" s="2" t="s">
         <v>14</v>
@@ -4789,7 +4789,7 @@
         <v>155</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C71" s="4" t="s">
         <v>156</v>
@@ -4798,13 +4798,13 @@
         <v>11</v>
       </c>
       <c r="E71" s="4">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="F71" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G71" s="4" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H71" s="4" t="s">
         <v>14</v>
@@ -4815,7 +4815,7 @@
         <v>157</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C72" s="2" t="s">
         <v>158</v>
@@ -4824,13 +4824,13 @@
         <v>11</v>
       </c>
       <c r="E72" s="2">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F72" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H72" s="2" t="s">
         <v>14</v>
@@ -4841,7 +4841,7 @@
         <v>159</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C73" s="4" t="s">
         <v>160</v>
@@ -4850,13 +4850,13 @@
         <v>11</v>
       </c>
       <c r="E73" s="4">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="F73" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G73" s="4" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H73" s="4" t="s">
         <v>14</v>
@@ -4867,7 +4867,7 @@
         <v>161</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C74" s="2" t="s">
         <v>162</v>
@@ -4876,13 +4876,13 @@
         <v>11</v>
       </c>
       <c r="E74" s="2">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="F74" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H74" s="2" t="s">
         <v>14</v>
@@ -4893,7 +4893,7 @@
         <v>163</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C75" s="4" t="s">
         <v>164</v>
@@ -4902,13 +4902,13 @@
         <v>11</v>
       </c>
       <c r="E75" s="4">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F75" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G75" s="4" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H75" s="4" t="s">
         <v>14</v>
@@ -4919,7 +4919,7 @@
         <v>165</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C76" s="2" t="s">
         <v>166</v>
@@ -4928,13 +4928,13 @@
         <v>11</v>
       </c>
       <c r="E76" s="2">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F76" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H76" s="2" t="s">
         <v>14</v>
@@ -4945,7 +4945,7 @@
         <v>167</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C77" s="4" t="s">
         <v>168</v>
@@ -4954,13 +4954,13 @@
         <v>11</v>
       </c>
       <c r="E77" s="4">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F77" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G77" s="4" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H77" s="4" t="s">
         <v>14</v>
@@ -4971,7 +4971,7 @@
         <v>169</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C78" s="2" t="s">
         <v>170</v>
@@ -4980,13 +4980,13 @@
         <v>11</v>
       </c>
       <c r="E78" s="2">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F78" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H78" s="2" t="s">
         <v>14</v>
@@ -4997,7 +4997,7 @@
         <v>171</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C79" s="4" t="s">
         <v>172</v>
@@ -5006,13 +5006,13 @@
         <v>11</v>
       </c>
       <c r="E79" s="4">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="F79" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G79" s="4" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H79" s="4" t="s">
         <v>14</v>
@@ -5023,7 +5023,7 @@
         <v>173</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C80" s="2" t="s">
         <v>174</v>
@@ -5032,13 +5032,13 @@
         <v>11</v>
       </c>
       <c r="E80" s="2">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="F80" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H80" s="2" t="s">
         <v>14</v>
@@ -5049,7 +5049,7 @@
         <v>175</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C81" s="4" t="s">
         <v>176</v>
@@ -5058,13 +5058,13 @@
         <v>11</v>
       </c>
       <c r="E81" s="4">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="F81" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G81" s="4" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H81" s="4" t="s">
         <v>14</v>
@@ -5084,13 +5084,13 @@
         <v>11</v>
       </c>
       <c r="E82" s="2">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="F82" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H82" s="2" t="s">
         <v>14</v>
@@ -5110,13 +5110,13 @@
         <v>11</v>
       </c>
       <c r="E83" s="4">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="F83" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G83" s="4" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H83" s="4" t="s">
         <v>14</v>
@@ -5136,13 +5136,13 @@
         <v>11</v>
       </c>
       <c r="E84" s="2">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="F84" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G84" s="2" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H84" s="2" t="s">
         <v>14</v>
@@ -5162,13 +5162,13 @@
         <v>11</v>
       </c>
       <c r="E85" s="4">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="F85" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G85" s="4" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H85" s="4" t="s">
         <v>14</v>
@@ -5188,13 +5188,13 @@
         <v>11</v>
       </c>
       <c r="E86" s="2">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F86" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G86" s="2" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H86" s="2" t="s">
         <v>14</v>
@@ -5214,13 +5214,13 @@
         <v>11</v>
       </c>
       <c r="E87" s="4">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="F87" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G87" s="4" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H87" s="4" t="s">
         <v>14</v>
@@ -5240,13 +5240,13 @@
         <v>11</v>
       </c>
       <c r="E88" s="2">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="F88" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G88" s="2" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H88" s="2" t="s">
         <v>14</v>
@@ -5266,13 +5266,13 @@
         <v>11</v>
       </c>
       <c r="E89" s="4">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="F89" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G89" s="4" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H89" s="4" t="s">
         <v>14</v>
@@ -5292,13 +5292,13 @@
         <v>11</v>
       </c>
       <c r="E90" s="2">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="F90" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G90" s="2" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H90" s="2" t="s">
         <v>14</v>
@@ -5318,13 +5318,13 @@
         <v>11</v>
       </c>
       <c r="E91" s="4">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="F91" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G91" s="4" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H91" s="4" t="s">
         <v>14</v>
@@ -5344,13 +5344,13 @@
         <v>11</v>
       </c>
       <c r="E92" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F92" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G92" s="2" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H92" s="2" t="s">
         <v>14</v>
@@ -5370,13 +5370,13 @@
         <v>11</v>
       </c>
       <c r="E93" s="4">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="F93" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G93" s="4" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H93" s="4" t="s">
         <v>14</v>
@@ -5396,13 +5396,13 @@
         <v>11</v>
       </c>
       <c r="E94" s="2">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="F94" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G94" s="2" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H94" s="2" t="s">
         <v>14</v>
@@ -5422,13 +5422,13 @@
         <v>11</v>
       </c>
       <c r="E95" s="4">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="F95" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G95" s="4" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H95" s="4" t="s">
         <v>14</v>
@@ -5454,7 +5454,7 @@
         <v>12</v>
       </c>
       <c r="G96" s="2" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H96" s="2" t="s">
         <v>14</v>
@@ -5474,13 +5474,13 @@
         <v>11</v>
       </c>
       <c r="E97" s="4">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="F97" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G97" s="4" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H97" s="4" t="s">
         <v>14</v>
@@ -5500,13 +5500,13 @@
         <v>11</v>
       </c>
       <c r="E98" s="2">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="F98" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G98" s="2" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H98" s="2" t="s">
         <v>14</v>
@@ -5526,13 +5526,13 @@
         <v>11</v>
       </c>
       <c r="E99" s="4">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F99" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G99" s="4" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H99" s="4" t="s">
         <v>14</v>
@@ -5552,13 +5552,13 @@
         <v>11</v>
       </c>
       <c r="E100" s="2">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="F100" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G100" s="2" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H100" s="2" t="s">
         <v>14</v>
@@ -5578,13 +5578,13 @@
         <v>11</v>
       </c>
       <c r="E101" s="4">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F101" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G101" s="4" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H101" s="4" t="s">
         <v>14</v>
@@ -5604,13 +5604,13 @@
         <v>11</v>
       </c>
       <c r="E102" s="2">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="F102" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G102" s="2" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H102" s="2" t="s">
         <v>14</v>
@@ -5630,13 +5630,13 @@
         <v>11</v>
       </c>
       <c r="E103" s="4">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F103" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G103" s="4" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H103" s="4" t="s">
         <v>14</v>
@@ -5656,13 +5656,13 @@
         <v>11</v>
       </c>
       <c r="E104" s="2">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F104" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G104" s="2" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H104" s="2" t="s">
         <v>14</v>
@@ -5682,13 +5682,13 @@
         <v>11</v>
       </c>
       <c r="E105" s="4">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="F105" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G105" s="4" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H105" s="4" t="s">
         <v>14</v>
@@ -5708,13 +5708,13 @@
         <v>11</v>
       </c>
       <c r="E106" s="2">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="F106" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G106" s="2" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H106" s="2" t="s">
         <v>14</v>
@@ -5734,13 +5734,13 @@
         <v>11</v>
       </c>
       <c r="E107" s="4">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="F107" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G107" s="4" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H107" s="4" t="s">
         <v>14</v>
@@ -5760,13 +5760,13 @@
         <v>11</v>
       </c>
       <c r="E108" s="2">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="F108" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G108" s="2" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H108" s="2" t="s">
         <v>14</v>
@@ -5786,13 +5786,13 @@
         <v>11</v>
       </c>
       <c r="E109" s="4">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="F109" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G109" s="4" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H109" s="4" t="s">
         <v>14</v>
@@ -5812,13 +5812,13 @@
         <v>11</v>
       </c>
       <c r="E110" s="2">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="F110" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G110" s="2" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H110" s="2" t="s">
         <v>14</v>
@@ -5838,13 +5838,13 @@
         <v>11</v>
       </c>
       <c r="E111" s="4">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F111" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G111" s="4" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H111" s="4" t="s">
         <v>14</v>
@@ -5864,13 +5864,13 @@
         <v>11</v>
       </c>
       <c r="E112" s="2">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="F112" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G112" s="2" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H112" s="2" t="s">
         <v>14</v>
@@ -5890,13 +5890,13 @@
         <v>11</v>
       </c>
       <c r="E113" s="4">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="F113" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G113" s="4" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H113" s="4" t="s">
         <v>14</v>
@@ -5916,13 +5916,13 @@
         <v>11</v>
       </c>
       <c r="E114" s="2">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F114" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G114" s="2" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H114" s="2" t="s">
         <v>14</v>
@@ -5942,13 +5942,13 @@
         <v>11</v>
       </c>
       <c r="E115" s="4">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F115" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G115" s="4" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H115" s="4" t="s">
         <v>14</v>
@@ -5968,13 +5968,13 @@
         <v>11</v>
       </c>
       <c r="E116" s="2">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F116" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G116" s="2" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H116" s="2" t="s">
         <v>14</v>
@@ -5994,13 +5994,13 @@
         <v>11</v>
       </c>
       <c r="E117" s="4">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="F117" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G117" s="4" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H117" s="4" t="s">
         <v>14</v>
@@ -6020,13 +6020,13 @@
         <v>11</v>
       </c>
       <c r="E118" s="2">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="F118" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G118" s="2" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H118" s="2" t="s">
         <v>14</v>
@@ -6046,13 +6046,13 @@
         <v>11</v>
       </c>
       <c r="E119" s="4">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F119" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G119" s="4" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H119" s="4" t="s">
         <v>14</v>
@@ -6072,13 +6072,13 @@
         <v>11</v>
       </c>
       <c r="E120" s="2">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="F120" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G120" s="2" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H120" s="2" t="s">
         <v>14</v>
@@ -6098,13 +6098,13 @@
         <v>11</v>
       </c>
       <c r="E121" s="4">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="F121" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G121" s="4" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H121" s="4" t="s">
         <v>14</v>
@@ -6124,13 +6124,13 @@
         <v>11</v>
       </c>
       <c r="E122" s="2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F122" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G122" s="2" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H122" s="2" t="s">
         <v>14</v>
@@ -6150,13 +6150,13 @@
         <v>11</v>
       </c>
       <c r="E123" s="4">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F123" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G123" s="4" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H123" s="4" t="s">
         <v>14</v>
@@ -6182,7 +6182,7 @@
         <v>12</v>
       </c>
       <c r="G124" s="2" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H124" s="2" t="s">
         <v>14</v>
@@ -6202,13 +6202,13 @@
         <v>11</v>
       </c>
       <c r="E125" s="4">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F125" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G125" s="4" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H125" s="4" t="s">
         <v>14</v>
@@ -6228,13 +6228,13 @@
         <v>11</v>
       </c>
       <c r="E126" s="2">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="F126" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G126" s="2" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H126" s="2" t="s">
         <v>14</v>
@@ -6254,13 +6254,13 @@
         <v>11</v>
       </c>
       <c r="E127" s="4">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="F127" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G127" s="4" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H127" s="4" t="s">
         <v>14</v>
@@ -6280,13 +6280,13 @@
         <v>11</v>
       </c>
       <c r="E128" s="2">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="F128" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G128" s="2" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H128" s="2" t="s">
         <v>14</v>
@@ -6306,13 +6306,13 @@
         <v>11</v>
       </c>
       <c r="E129" s="4">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F129" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G129" s="4" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H129" s="4" t="s">
         <v>14</v>
@@ -6332,13 +6332,13 @@
         <v>11</v>
       </c>
       <c r="E130" s="2">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="F130" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G130" s="2" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H130" s="2" t="s">
         <v>14</v>
@@ -6364,7 +6364,7 @@
         <v>12</v>
       </c>
       <c r="G131" s="4" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H131" s="4" t="s">
         <v>14</v>
@@ -6384,13 +6384,13 @@
         <v>11</v>
       </c>
       <c r="E132" s="2">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="F132" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G132" s="2" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H132" s="2" t="s">
         <v>14</v>
@@ -6410,13 +6410,13 @@
         <v>11</v>
       </c>
       <c r="E133" s="4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F133" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G133" s="4" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H133" s="4" t="s">
         <v>14</v>
@@ -6436,13 +6436,13 @@
         <v>11</v>
       </c>
       <c r="E134" s="2">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F134" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G134" s="2" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H134" s="2" t="s">
         <v>14</v>
@@ -6462,13 +6462,13 @@
         <v>11</v>
       </c>
       <c r="E135" s="4">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="F135" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G135" s="4" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H135" s="4" t="s">
         <v>14</v>
@@ -6488,13 +6488,13 @@
         <v>11</v>
       </c>
       <c r="E136" s="2">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="F136" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G136" s="2" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H136" s="2" t="s">
         <v>14</v>
@@ -6514,13 +6514,13 @@
         <v>11</v>
       </c>
       <c r="E137" s="4">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F137" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G137" s="4" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H137" s="4" t="s">
         <v>14</v>
@@ -6540,13 +6540,13 @@
         <v>11</v>
       </c>
       <c r="E138" s="2">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="F138" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G138" s="2" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H138" s="2" t="s">
         <v>14</v>
@@ -6566,13 +6566,13 @@
         <v>11</v>
       </c>
       <c r="E139" s="4">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F139" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G139" s="4" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H139" s="4" t="s">
         <v>14</v>
@@ -6592,13 +6592,13 @@
         <v>11</v>
       </c>
       <c r="E140" s="2">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F140" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G140" s="2" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H140" s="2" t="s">
         <v>14</v>
@@ -6618,13 +6618,13 @@
         <v>11</v>
       </c>
       <c r="E141" s="4">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F141" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G141" s="4" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H141" s="4" t="s">
         <v>14</v>
@@ -6644,13 +6644,13 @@
         <v>11</v>
       </c>
       <c r="E142" s="2">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="F142" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G142" s="2" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H142" s="2" t="s">
         <v>14</v>
@@ -6676,7 +6676,7 @@
         <v>12</v>
       </c>
       <c r="G143" s="4" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H143" s="4" t="s">
         <v>14</v>
@@ -6696,13 +6696,13 @@
         <v>11</v>
       </c>
       <c r="E144" s="2">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="F144" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G144" s="2" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H144" s="2" t="s">
         <v>14</v>
@@ -6722,13 +6722,13 @@
         <v>11</v>
       </c>
       <c r="E145" s="4">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="F145" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G145" s="4" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H145" s="4" t="s">
         <v>14</v>
@@ -6748,13 +6748,13 @@
         <v>11</v>
       </c>
       <c r="E146" s="2">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="F146" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G146" s="2" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H146" s="2" t="s">
         <v>14</v>
@@ -6774,13 +6774,13 @@
         <v>11</v>
       </c>
       <c r="E147" s="4">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="F147" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G147" s="4" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H147" s="4" t="s">
         <v>14</v>
@@ -6800,13 +6800,13 @@
         <v>11</v>
       </c>
       <c r="E148" s="2">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F148" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G148" s="2" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H148" s="2" t="s">
         <v>14</v>
@@ -6826,13 +6826,13 @@
         <v>11</v>
       </c>
       <c r="E149" s="4">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="F149" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G149" s="4" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H149" s="4" t="s">
         <v>14</v>
@@ -6852,13 +6852,13 @@
         <v>11</v>
       </c>
       <c r="E150" s="2">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F150" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G150" s="2" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H150" s="2" t="s">
         <v>14</v>
@@ -6878,13 +6878,13 @@
         <v>11</v>
       </c>
       <c r="E151" s="4">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F151" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G151" s="4" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H151" s="4" t="s">
         <v>14</v>
@@ -6904,13 +6904,13 @@
         <v>11</v>
       </c>
       <c r="E152" s="2">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="F152" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G152" s="2" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H152" s="2" t="s">
         <v>14</v>
@@ -6930,13 +6930,13 @@
         <v>11</v>
       </c>
       <c r="E153" s="4">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="F153" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G153" s="4" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H153" s="4" t="s">
         <v>14</v>
@@ -6956,13 +6956,13 @@
         <v>11</v>
       </c>
       <c r="E154" s="2">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="F154" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G154" s="2" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H154" s="2" t="s">
         <v>14</v>
@@ -6982,13 +6982,13 @@
         <v>11</v>
       </c>
       <c r="E155" s="4">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F155" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G155" s="4" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H155" s="4" t="s">
         <v>14</v>
@@ -7008,13 +7008,13 @@
         <v>11</v>
       </c>
       <c r="E156" s="2">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="F156" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G156" s="2" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H156" s="2" t="s">
         <v>14</v>
@@ -7034,13 +7034,13 @@
         <v>11</v>
       </c>
       <c r="E157" s="4">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="F157" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G157" s="4" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H157" s="4" t="s">
         <v>14</v>
@@ -7060,13 +7060,13 @@
         <v>11</v>
       </c>
       <c r="E158" s="2">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F158" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G158" s="2" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H158" s="2" t="s">
         <v>14</v>
@@ -7086,13 +7086,13 @@
         <v>11</v>
       </c>
       <c r="E159" s="4">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="F159" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G159" s="4" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H159" s="4" t="s">
         <v>14</v>
@@ -7112,13 +7112,13 @@
         <v>11</v>
       </c>
       <c r="E160" s="2">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="F160" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G160" s="2" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H160" s="2" t="s">
         <v>14</v>
@@ -7138,13 +7138,13 @@
         <v>11</v>
       </c>
       <c r="E161" s="4">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="F161" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G161" s="4" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H161" s="4" t="s">
         <v>14</v>
@@ -7164,13 +7164,13 @@
         <v>11</v>
       </c>
       <c r="E162" s="2">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="F162" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G162" s="2" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H162" s="2" t="s">
         <v>14</v>
@@ -7190,13 +7190,13 @@
         <v>11</v>
       </c>
       <c r="E163" s="4">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F163" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G163" s="4" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H163" s="4" t="s">
         <v>14</v>
@@ -7216,13 +7216,13 @@
         <v>11</v>
       </c>
       <c r="E164" s="2">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="F164" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G164" s="2" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H164" s="2" t="s">
         <v>14</v>
@@ -7242,13 +7242,13 @@
         <v>11</v>
       </c>
       <c r="E165" s="4">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="F165" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G165" s="4" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H165" s="4" t="s">
         <v>14</v>
@@ -7268,13 +7268,13 @@
         <v>11</v>
       </c>
       <c r="E166" s="2">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F166" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G166" s="2" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H166" s="2" t="s">
         <v>14</v>
@@ -7294,13 +7294,13 @@
         <v>11</v>
       </c>
       <c r="E167" s="4">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F167" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G167" s="4" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H167" s="4" t="s">
         <v>14</v>
@@ -7320,13 +7320,13 @@
         <v>11</v>
       </c>
       <c r="E168" s="2">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F168" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G168" s="2" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H168" s="2" t="s">
         <v>14</v>
@@ -7346,13 +7346,13 @@
         <v>11</v>
       </c>
       <c r="E169" s="4">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="F169" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G169" s="4" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H169" s="4" t="s">
         <v>14</v>
@@ -7372,13 +7372,13 @@
         <v>11</v>
       </c>
       <c r="E170" s="2">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="F170" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G170" s="2" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H170" s="2" t="s">
         <v>14</v>
@@ -7398,13 +7398,13 @@
         <v>11</v>
       </c>
       <c r="E171" s="4">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="F171" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G171" s="4" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H171" s="4" t="s">
         <v>14</v>
@@ -7430,7 +7430,7 @@
         <v>12</v>
       </c>
       <c r="G172" s="2" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H172" s="2" t="s">
         <v>14</v>
@@ -7450,13 +7450,13 @@
         <v>11</v>
       </c>
       <c r="E173" s="4">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="F173" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G173" s="4" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H173" s="4" t="s">
         <v>14</v>
@@ -7476,13 +7476,13 @@
         <v>11</v>
       </c>
       <c r="E174" s="2">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="F174" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G174" s="2" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H174" s="2" t="s">
         <v>14</v>
@@ -7502,13 +7502,13 @@
         <v>11</v>
       </c>
       <c r="E175" s="4">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="F175" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G175" s="4" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H175" s="4" t="s">
         <v>14</v>
@@ -7528,13 +7528,13 @@
         <v>11</v>
       </c>
       <c r="E176" s="2">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F176" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G176" s="2" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H176" s="2" t="s">
         <v>14</v>
@@ -7554,13 +7554,13 @@
         <v>11</v>
       </c>
       <c r="E177" s="4">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="F177" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G177" s="4" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H177" s="4" t="s">
         <v>14</v>
@@ -7580,13 +7580,13 @@
         <v>11</v>
       </c>
       <c r="E178" s="2">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="F178" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G178" s="2" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H178" s="2" t="s">
         <v>14</v>
@@ -7606,13 +7606,13 @@
         <v>11</v>
       </c>
       <c r="E179" s="4">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="F179" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G179" s="4" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H179" s="4" t="s">
         <v>14</v>
@@ -7632,13 +7632,13 @@
         <v>11</v>
       </c>
       <c r="E180" s="2">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="F180" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G180" s="2" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H180" s="2" t="s">
         <v>14</v>
@@ -7658,13 +7658,13 @@
         <v>11</v>
       </c>
       <c r="E181" s="4">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F181" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G181" s="4" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H181" s="4" t="s">
         <v>14</v>
@@ -7684,13 +7684,13 @@
         <v>11</v>
       </c>
       <c r="E182" s="2">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="F182" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G182" s="2" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H182" s="2" t="s">
         <v>14</v>
@@ -7716,7 +7716,7 @@
         <v>12</v>
       </c>
       <c r="G183" s="4" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H183" s="4" t="s">
         <v>14</v>
@@ -7736,13 +7736,13 @@
         <v>11</v>
       </c>
       <c r="E184" s="2">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="F184" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G184" s="2" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H184" s="2" t="s">
         <v>14</v>
@@ -7762,13 +7762,13 @@
         <v>11</v>
       </c>
       <c r="E185" s="4">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="F185" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G185" s="4" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H185" s="4" t="s">
         <v>14</v>
@@ -7788,13 +7788,13 @@
         <v>11</v>
       </c>
       <c r="E186" s="2">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="F186" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G186" s="2" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H186" s="2" t="s">
         <v>14</v>
@@ -7814,13 +7814,13 @@
         <v>11</v>
       </c>
       <c r="E187" s="4">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="F187" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G187" s="4" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H187" s="4" t="s">
         <v>14</v>
@@ -7840,13 +7840,13 @@
         <v>11</v>
       </c>
       <c r="E188" s="2">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="F188" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G188" s="2" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H188" s="2" t="s">
         <v>14</v>
@@ -7866,13 +7866,13 @@
         <v>11</v>
       </c>
       <c r="E189" s="4">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="F189" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G189" s="4" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H189" s="4" t="s">
         <v>14</v>
@@ -7892,13 +7892,13 @@
         <v>11</v>
       </c>
       <c r="E190" s="2">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="F190" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G190" s="2" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H190" s="2" t="s">
         <v>14</v>
@@ -7918,13 +7918,13 @@
         <v>11</v>
       </c>
       <c r="E191" s="4">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F191" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G191" s="4" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H191" s="4" t="s">
         <v>14</v>
@@ -7944,13 +7944,13 @@
         <v>11</v>
       </c>
       <c r="E192" s="2">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="F192" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G192" s="2" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H192" s="2" t="s">
         <v>14</v>
@@ -7970,13 +7970,13 @@
         <v>11</v>
       </c>
       <c r="E193" s="4">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F193" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G193" s="4" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H193" s="4" t="s">
         <v>14</v>
@@ -7996,13 +7996,13 @@
         <v>11</v>
       </c>
       <c r="E194" s="2">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="F194" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G194" s="2" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H194" s="2" t="s">
         <v>14</v>
@@ -8022,13 +8022,13 @@
         <v>11</v>
       </c>
       <c r="E195" s="4">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="F195" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G195" s="4" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H195" s="4" t="s">
         <v>14</v>
@@ -8048,13 +8048,13 @@
         <v>11</v>
       </c>
       <c r="E196" s="2">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="F196" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G196" s="2" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H196" s="2" t="s">
         <v>14</v>
@@ -8074,13 +8074,13 @@
         <v>11</v>
       </c>
       <c r="E197" s="4">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="F197" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G197" s="4" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H197" s="4" t="s">
         <v>14</v>
@@ -8100,13 +8100,13 @@
         <v>11</v>
       </c>
       <c r="E198" s="2">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F198" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G198" s="2" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H198" s="2" t="s">
         <v>14</v>
@@ -8126,13 +8126,13 @@
         <v>11</v>
       </c>
       <c r="E199" s="4">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="F199" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G199" s="4" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H199" s="4" t="s">
         <v>14</v>
@@ -8152,13 +8152,13 @@
         <v>11</v>
       </c>
       <c r="E200" s="2">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="F200" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G200" s="2" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H200" s="2" t="s">
         <v>14</v>
@@ -8178,13 +8178,13 @@
         <v>11</v>
       </c>
       <c r="E201" s="4">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="F201" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G201" s="4" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H201" s="4" t="s">
         <v>14</v>
@@ -8210,7 +8210,7 @@
         <v>12</v>
       </c>
       <c r="G202" s="2" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H202" s="2" t="s">
         <v>14</v>
@@ -8230,13 +8230,13 @@
         <v>11</v>
       </c>
       <c r="E203" s="4">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="F203" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G203" s="4" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H203" s="4" t="s">
         <v>14</v>
@@ -8256,13 +8256,13 @@
         <v>11</v>
       </c>
       <c r="E204" s="2">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="F204" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G204" s="2" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H204" s="2" t="s">
         <v>14</v>
@@ -8282,13 +8282,13 @@
         <v>11</v>
       </c>
       <c r="E205" s="4">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F205" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G205" s="4" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H205" s="4" t="s">
         <v>14</v>
@@ -8308,13 +8308,13 @@
         <v>11</v>
       </c>
       <c r="E206" s="2">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="F206" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G206" s="2" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H206" s="2" t="s">
         <v>14</v>
@@ -8334,13 +8334,13 @@
         <v>11</v>
       </c>
       <c r="E207" s="4">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="F207" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G207" s="4" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H207" s="4" t="s">
         <v>14</v>
@@ -8360,13 +8360,13 @@
         <v>11</v>
       </c>
       <c r="E208" s="2">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F208" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G208" s="2" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H208" s="2" t="s">
         <v>14</v>
@@ -8386,13 +8386,13 @@
         <v>11</v>
       </c>
       <c r="E209" s="4">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="F209" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G209" s="4" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H209" s="4" t="s">
         <v>14</v>
@@ -8412,13 +8412,13 @@
         <v>11</v>
       </c>
       <c r="E210" s="2">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F210" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G210" s="2" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H210" s="2" t="s">
         <v>14</v>
@@ -8438,13 +8438,13 @@
         <v>11</v>
       </c>
       <c r="E211" s="4">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="F211" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G211" s="4" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H211" s="4" t="s">
         <v>14</v>
@@ -8464,13 +8464,13 @@
         <v>11</v>
       </c>
       <c r="E212" s="2">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F212" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G212" s="2" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H212" s="2" t="s">
         <v>14</v>
@@ -8490,13 +8490,13 @@
         <v>11</v>
       </c>
       <c r="E213" s="4">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="F213" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G213" s="4" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H213" s="4" t="s">
         <v>14</v>
@@ -8516,13 +8516,13 @@
         <v>11</v>
       </c>
       <c r="E214" s="2">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="F214" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G214" s="2" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H214" s="2" t="s">
         <v>14</v>
@@ -8542,13 +8542,13 @@
         <v>11</v>
       </c>
       <c r="E215" s="4">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F215" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G215" s="4" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H215" s="4" t="s">
         <v>14</v>
@@ -8574,7 +8574,7 @@
         <v>12</v>
       </c>
       <c r="G216" s="2" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H216" s="2" t="s">
         <v>14</v>
@@ -8594,13 +8594,13 @@
         <v>11</v>
       </c>
       <c r="E217" s="4">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="F217" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G217" s="4" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H217" s="4" t="s">
         <v>14</v>
@@ -8620,13 +8620,13 @@
         <v>11</v>
       </c>
       <c r="E218" s="2">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="F218" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G218" s="2" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H218" s="2" t="s">
         <v>14</v>
@@ -8646,13 +8646,13 @@
         <v>11</v>
       </c>
       <c r="E219" s="4">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="F219" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G219" s="4" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H219" s="4" t="s">
         <v>14</v>
@@ -8672,13 +8672,13 @@
         <v>11</v>
       </c>
       <c r="E220" s="2">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F220" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G220" s="2" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H220" s="2" t="s">
         <v>14</v>
@@ -8698,13 +8698,13 @@
         <v>11</v>
       </c>
       <c r="E221" s="4">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F221" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G221" s="4" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H221" s="4" t="s">
         <v>14</v>
@@ -8724,13 +8724,13 @@
         <v>11</v>
       </c>
       <c r="E222" s="2">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="F222" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G222" s="2" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H222" s="2" t="s">
         <v>14</v>
@@ -8750,13 +8750,13 @@
         <v>11</v>
       </c>
       <c r="E223" s="4">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="F223" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G223" s="4" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H223" s="4" t="s">
         <v>14</v>
@@ -8776,13 +8776,13 @@
         <v>11</v>
       </c>
       <c r="E224" s="2">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F224" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G224" s="2" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H224" s="2" t="s">
         <v>14</v>
@@ -8802,13 +8802,13 @@
         <v>11</v>
       </c>
       <c r="E225" s="4">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="F225" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G225" s="4" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H225" s="4" t="s">
         <v>14</v>
@@ -8828,13 +8828,13 @@
         <v>11</v>
       </c>
       <c r="E226" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F226" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G226" s="2" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H226" s="2" t="s">
         <v>14</v>
@@ -8854,13 +8854,13 @@
         <v>11</v>
       </c>
       <c r="E227" s="4">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F227" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G227" s="4" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H227" s="4" t="s">
         <v>14</v>
@@ -8880,13 +8880,13 @@
         <v>11</v>
       </c>
       <c r="E228" s="2">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="F228" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G228" s="2" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H228" s="2" t="s">
         <v>14</v>
@@ -8906,13 +8906,13 @@
         <v>11</v>
       </c>
       <c r="E229" s="4">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="F229" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G229" s="4" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H229" s="4" t="s">
         <v>14</v>
@@ -8932,13 +8932,13 @@
         <v>11</v>
       </c>
       <c r="E230" s="2">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="F230" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G230" s="2" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H230" s="2" t="s">
         <v>14</v>
@@ -8958,13 +8958,13 @@
         <v>11</v>
       </c>
       <c r="E231" s="4">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="F231" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G231" s="4" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H231" s="4" t="s">
         <v>14</v>
@@ -8984,13 +8984,13 @@
         <v>11</v>
       </c>
       <c r="E232" s="2">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="F232" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G232" s="2" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H232" s="2" t="s">
         <v>14</v>
@@ -9010,13 +9010,13 @@
         <v>11</v>
       </c>
       <c r="E233" s="4">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="F233" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G233" s="4" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H233" s="4" t="s">
         <v>14</v>
@@ -9036,13 +9036,13 @@
         <v>11</v>
       </c>
       <c r="E234" s="2">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F234" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G234" s="2" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H234" s="2" t="s">
         <v>14</v>
@@ -9062,13 +9062,13 @@
         <v>11</v>
       </c>
       <c r="E235" s="4">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="F235" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G235" s="4" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H235" s="4" t="s">
         <v>14</v>
@@ -9088,13 +9088,13 @@
         <v>11</v>
       </c>
       <c r="E236" s="2">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="F236" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G236" s="2" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H236" s="2" t="s">
         <v>14</v>
@@ -9114,13 +9114,13 @@
         <v>11</v>
       </c>
       <c r="E237" s="4">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="F237" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G237" s="4" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H237" s="4" t="s">
         <v>14</v>
@@ -9140,13 +9140,13 @@
         <v>11</v>
       </c>
       <c r="E238" s="2">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="F238" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G238" s="2" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H238" s="2" t="s">
         <v>14</v>
@@ -9166,13 +9166,13 @@
         <v>11</v>
       </c>
       <c r="E239" s="4">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="F239" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G239" s="4" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H239" s="4" t="s">
         <v>14</v>
@@ -9192,13 +9192,13 @@
         <v>11</v>
       </c>
       <c r="E240" s="2">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F240" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G240" s="2" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H240" s="2" t="s">
         <v>14</v>
@@ -9218,13 +9218,13 @@
         <v>11</v>
       </c>
       <c r="E241" s="4">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="F241" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G241" s="4" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H241" s="4" t="s">
         <v>14</v>
@@ -9244,13 +9244,13 @@
         <v>11</v>
       </c>
       <c r="E242" s="2">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="F242" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G242" s="2" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H242" s="2" t="s">
         <v>14</v>
@@ -9270,13 +9270,13 @@
         <v>11</v>
       </c>
       <c r="E243" s="4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F243" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G243" s="4" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H243" s="4" t="s">
         <v>14</v>
@@ -9296,13 +9296,13 @@
         <v>11</v>
       </c>
       <c r="E244" s="2">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="F244" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G244" s="2" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H244" s="2" t="s">
         <v>14</v>
@@ -9322,13 +9322,13 @@
         <v>11</v>
       </c>
       <c r="E245" s="4">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="F245" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G245" s="4" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H245" s="4" t="s">
         <v>14</v>
@@ -9348,13 +9348,13 @@
         <v>11</v>
       </c>
       <c r="E246" s="2">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="F246" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G246" s="2" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H246" s="2" t="s">
         <v>14</v>
@@ -9374,13 +9374,13 @@
         <v>11</v>
       </c>
       <c r="E247" s="4">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F247" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G247" s="4" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H247" s="4" t="s">
         <v>14</v>
@@ -9400,13 +9400,13 @@
         <v>11</v>
       </c>
       <c r="E248" s="2">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="F248" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G248" s="2" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H248" s="2" t="s">
         <v>14</v>
@@ -9426,13 +9426,13 @@
         <v>11</v>
       </c>
       <c r="E249" s="4">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="F249" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G249" s="4" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H249" s="4" t="s">
         <v>14</v>
@@ -9452,13 +9452,13 @@
         <v>11</v>
       </c>
       <c r="E250" s="2">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="F250" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G250" s="2" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H250" s="2" t="s">
         <v>14</v>
@@ -9478,13 +9478,13 @@
         <v>11</v>
       </c>
       <c r="E251" s="4">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="F251" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G251" s="4" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H251" s="4" t="s">
         <v>14</v>
@@ -9504,13 +9504,13 @@
         <v>11</v>
       </c>
       <c r="E252" s="2">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F252" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G252" s="2" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H252" s="2" t="s">
         <v>14</v>
@@ -9530,13 +9530,13 @@
         <v>11</v>
       </c>
       <c r="E253" s="4">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="F253" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G253" s="4" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H253" s="4" t="s">
         <v>14</v>
@@ -9556,13 +9556,13 @@
         <v>11</v>
       </c>
       <c r="E254" s="2">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F254" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G254" s="2" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H254" s="2" t="s">
         <v>14</v>
@@ -9582,13 +9582,13 @@
         <v>11</v>
       </c>
       <c r="E255" s="4">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="F255" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G255" s="4" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H255" s="4" t="s">
         <v>14</v>
@@ -9608,13 +9608,13 @@
         <v>11</v>
       </c>
       <c r="E256" s="2">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="F256" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G256" s="2" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H256" s="2" t="s">
         <v>14</v>
@@ -9634,13 +9634,13 @@
         <v>11</v>
       </c>
       <c r="E257" s="4">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F257" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G257" s="4" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H257" s="4" t="s">
         <v>14</v>
@@ -9660,13 +9660,13 @@
         <v>11</v>
       </c>
       <c r="E258" s="2">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="F258" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G258" s="2" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H258" s="2" t="s">
         <v>14</v>
@@ -9686,13 +9686,13 @@
         <v>11</v>
       </c>
       <c r="E259" s="4">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="F259" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G259" s="4" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H259" s="4" t="s">
         <v>14</v>
@@ -9712,13 +9712,13 @@
         <v>11</v>
       </c>
       <c r="E260" s="2">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="F260" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G260" s="2" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H260" s="2" t="s">
         <v>14</v>
@@ -9738,13 +9738,13 @@
         <v>11</v>
       </c>
       <c r="E261" s="4">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="F261" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G261" s="4" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H261" s="4" t="s">
         <v>14</v>
@@ -9764,13 +9764,13 @@
         <v>11</v>
       </c>
       <c r="E262" s="2">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="F262" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G262" s="2" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H262" s="2" t="s">
         <v>14</v>
@@ -9790,13 +9790,13 @@
         <v>11</v>
       </c>
       <c r="E263" s="4">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="F263" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G263" s="4" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H263" s="4" t="s">
         <v>14</v>
@@ -9816,13 +9816,13 @@
         <v>11</v>
       </c>
       <c r="E264" s="2">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="F264" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G264" s="2" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H264" s="2" t="s">
         <v>14</v>
@@ -9842,13 +9842,13 @@
         <v>11</v>
       </c>
       <c r="E265" s="4">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="F265" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G265" s="4" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H265" s="4" t="s">
         <v>14</v>
@@ -9868,13 +9868,13 @@
         <v>11</v>
       </c>
       <c r="E266" s="2">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F266" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G266" s="2" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H266" s="2" t="s">
         <v>14</v>
@@ -9894,13 +9894,13 @@
         <v>11</v>
       </c>
       <c r="E267" s="4">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F267" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G267" s="4" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H267" s="4" t="s">
         <v>14</v>
@@ -9920,13 +9920,13 @@
         <v>11</v>
       </c>
       <c r="E268" s="2">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="F268" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G268" s="2" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H268" s="2" t="s">
         <v>14</v>
@@ -9946,13 +9946,13 @@
         <v>11</v>
       </c>
       <c r="E269" s="4">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="F269" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G269" s="4" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H269" s="4" t="s">
         <v>14</v>
@@ -9972,13 +9972,13 @@
         <v>11</v>
       </c>
       <c r="E270" s="2">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="F270" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G270" s="2" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H270" s="2" t="s">
         <v>14</v>
@@ -9998,13 +9998,13 @@
         <v>11</v>
       </c>
       <c r="E271" s="4">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F271" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G271" s="4" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H271" s="4" t="s">
         <v>14</v>
@@ -10024,13 +10024,13 @@
         <v>11</v>
       </c>
       <c r="E272" s="2">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="F272" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G272" s="2" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H272" s="2" t="s">
         <v>14</v>
@@ -10050,13 +10050,13 @@
         <v>11</v>
       </c>
       <c r="E273" s="4">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="F273" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G273" s="4" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H273" s="4" t="s">
         <v>14</v>
@@ -10076,13 +10076,13 @@
         <v>11</v>
       </c>
       <c r="E274" s="2">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="F274" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G274" s="2" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H274" s="2" t="s">
         <v>14</v>
@@ -10102,13 +10102,13 @@
         <v>11</v>
       </c>
       <c r="E275" s="4">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F275" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G275" s="4" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H275" s="4" t="s">
         <v>14</v>
@@ -10128,13 +10128,13 @@
         <v>11</v>
       </c>
       <c r="E276" s="2">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F276" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G276" s="2" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H276" s="2" t="s">
         <v>14</v>
@@ -10160,7 +10160,7 @@
         <v>12</v>
       </c>
       <c r="G277" s="4" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H277" s="4" t="s">
         <v>14</v>
@@ -10180,13 +10180,13 @@
         <v>11</v>
       </c>
       <c r="E278" s="2">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="F278" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G278" s="2" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H278" s="2" t="s">
         <v>14</v>
@@ -10206,13 +10206,13 @@
         <v>11</v>
       </c>
       <c r="E279" s="4">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="F279" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G279" s="4" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H279" s="4" t="s">
         <v>14</v>
@@ -10232,13 +10232,13 @@
         <v>11</v>
       </c>
       <c r="E280" s="2">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="F280" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G280" s="2" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H280" s="2" t="s">
         <v>14</v>
@@ -10264,7 +10264,7 @@
         <v>12</v>
       </c>
       <c r="G281" s="4" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H281" s="4" t="s">
         <v>14</v>
@@ -10284,13 +10284,13 @@
         <v>11</v>
       </c>
       <c r="E282" s="2">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F282" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G282" s="2" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H282" s="2" t="s">
         <v>14</v>
@@ -10310,13 +10310,13 @@
         <v>11</v>
       </c>
       <c r="E283" s="4">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="F283" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G283" s="4" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H283" s="4" t="s">
         <v>14</v>
@@ -10336,13 +10336,13 @@
         <v>11</v>
       </c>
       <c r="E284" s="2">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="F284" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G284" s="2" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H284" s="2" t="s">
         <v>14</v>
@@ -10362,13 +10362,13 @@
         <v>11</v>
       </c>
       <c r="E285" s="4">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="F285" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G285" s="4" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H285" s="4" t="s">
         <v>14</v>
@@ -10388,13 +10388,13 @@
         <v>11</v>
       </c>
       <c r="E286" s="2">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="F286" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G286" s="2" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H286" s="2" t="s">
         <v>14</v>
@@ -10414,13 +10414,13 @@
         <v>11</v>
       </c>
       <c r="E287" s="4">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="F287" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G287" s="4" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H287" s="4" t="s">
         <v>14</v>
@@ -10440,13 +10440,13 @@
         <v>11</v>
       </c>
       <c r="E288" s="2">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F288" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G288" s="2" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H288" s="2" t="s">
         <v>14</v>
@@ -10466,13 +10466,13 @@
         <v>11</v>
       </c>
       <c r="E289" s="4">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="F289" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G289" s="4" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H289" s="4" t="s">
         <v>14</v>
@@ -10492,13 +10492,13 @@
         <v>11</v>
       </c>
       <c r="E290" s="2">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="F290" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G290" s="2" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H290" s="2" t="s">
         <v>14</v>
@@ -10518,13 +10518,13 @@
         <v>11</v>
       </c>
       <c r="E291" s="4">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F291" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G291" s="4" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H291" s="4" t="s">
         <v>14</v>
@@ -10544,13 +10544,13 @@
         <v>11</v>
       </c>
       <c r="E292" s="2">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F292" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G292" s="2" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H292" s="2" t="s">
         <v>14</v>
@@ -10570,13 +10570,13 @@
         <v>11</v>
       </c>
       <c r="E293" s="4">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="F293" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G293" s="4" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H293" s="4" t="s">
         <v>14</v>
@@ -10596,13 +10596,13 @@
         <v>11</v>
       </c>
       <c r="E294" s="2">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="F294" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G294" s="2" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H294" s="2" t="s">
         <v>14</v>
@@ -10622,13 +10622,13 @@
         <v>11</v>
       </c>
       <c r="E295" s="4">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="F295" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G295" s="4" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H295" s="4" t="s">
         <v>14</v>
@@ -10648,13 +10648,13 @@
         <v>11</v>
       </c>
       <c r="E296" s="2">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="F296" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G296" s="2" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H296" s="2" t="s">
         <v>14</v>
@@ -10674,13 +10674,13 @@
         <v>11</v>
       </c>
       <c r="E297" s="4">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="F297" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G297" s="4" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H297" s="4" t="s">
         <v>14</v>
@@ -10700,13 +10700,13 @@
         <v>11</v>
       </c>
       <c r="E298" s="2">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F298" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G298" s="2" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H298" s="2" t="s">
         <v>14</v>
@@ -10726,13 +10726,13 @@
         <v>11</v>
       </c>
       <c r="E299" s="4">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F299" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G299" s="4" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H299" s="4" t="s">
         <v>14</v>
@@ -10752,13 +10752,13 @@
         <v>11</v>
       </c>
       <c r="E300" s="2">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="F300" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G300" s="2" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H300" s="2" t="s">
         <v>14</v>
@@ -10778,13 +10778,13 @@
         <v>11</v>
       </c>
       <c r="E301" s="4">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="F301" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G301" s="4" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H301" s="4" t="s">
         <v>14</v>
@@ -10804,13 +10804,13 @@
         <v>11</v>
       </c>
       <c r="E302" s="2">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="F302" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G302" s="2" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H302" s="2" t="s">
         <v>14</v>
@@ -10830,13 +10830,13 @@
         <v>11</v>
       </c>
       <c r="E303" s="4">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="F303" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G303" s="4" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H303" s="4" t="s">
         <v>14</v>
@@ -10856,13 +10856,13 @@
         <v>11</v>
       </c>
       <c r="E304" s="2">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="F304" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G304" s="2" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H304" s="2" t="s">
         <v>14</v>
@@ -10882,13 +10882,13 @@
         <v>11</v>
       </c>
       <c r="E305" s="4">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="F305" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G305" s="4" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H305" s="4" t="s">
         <v>14</v>
@@ -10908,13 +10908,13 @@
         <v>11</v>
       </c>
       <c r="E306" s="2">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="F306" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G306" s="2" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H306" s="2" t="s">
         <v>14</v>
@@ -10934,13 +10934,13 @@
         <v>11</v>
       </c>
       <c r="E307" s="4">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F307" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G307" s="4" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H307" s="4" t="s">
         <v>14</v>
@@ -10960,13 +10960,13 @@
         <v>11</v>
       </c>
       <c r="E308" s="2">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="F308" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G308" s="2" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H308" s="2" t="s">
         <v>14</v>
@@ -10992,7 +10992,7 @@
         <v>12</v>
       </c>
       <c r="G309" s="4" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H309" s="4" t="s">
         <v>14</v>
@@ -11012,13 +11012,13 @@
         <v>11</v>
       </c>
       <c r="E310" s="2">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="F310" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G310" s="2" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H310" s="2" t="s">
         <v>14</v>
@@ -11038,13 +11038,13 @@
         <v>11</v>
       </c>
       <c r="E311" s="4">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="F311" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G311" s="4" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H311" s="4" t="s">
         <v>14</v>
@@ -11064,13 +11064,13 @@
         <v>11</v>
       </c>
       <c r="E312" s="2">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="F312" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G312" s="2" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H312" s="2" t="s">
         <v>14</v>
@@ -11090,13 +11090,13 @@
         <v>11</v>
       </c>
       <c r="E313" s="4">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F313" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G313" s="4" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H313" s="4" t="s">
         <v>14</v>
@@ -11116,13 +11116,13 @@
         <v>11</v>
       </c>
       <c r="E314" s="2">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="F314" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G314" s="2" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H314" s="2" t="s">
         <v>14</v>
@@ -11148,7 +11148,7 @@
         <v>12</v>
       </c>
       <c r="G315" s="4" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H315" s="4" t="s">
         <v>14</v>
@@ -11168,13 +11168,13 @@
         <v>11</v>
       </c>
       <c r="E316" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F316" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G316" s="2" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H316" s="2" t="s">
         <v>14</v>
@@ -11194,13 +11194,13 @@
         <v>11</v>
       </c>
       <c r="E317" s="4">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="F317" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G317" s="4" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H317" s="4" t="s">
         <v>14</v>
@@ -11220,13 +11220,13 @@
         <v>11</v>
       </c>
       <c r="E318" s="2">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="F318" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G318" s="2" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H318" s="2" t="s">
         <v>14</v>
@@ -11246,13 +11246,13 @@
         <v>11</v>
       </c>
       <c r="E319" s="4">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="F319" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G319" s="4" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H319" s="4" t="s">
         <v>14</v>
@@ -11272,13 +11272,13 @@
         <v>11</v>
       </c>
       <c r="E320" s="2">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="F320" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G320" s="2" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H320" s="2" t="s">
         <v>14</v>
@@ -11298,13 +11298,13 @@
         <v>11</v>
       </c>
       <c r="E321" s="4">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="F321" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G321" s="4" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H321" s="4" t="s">
         <v>14</v>
@@ -11324,13 +11324,13 @@
         <v>11</v>
       </c>
       <c r="E322" s="2">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="F322" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G322" s="2" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H322" s="2" t="s">
         <v>14</v>
@@ -11350,13 +11350,13 @@
         <v>11</v>
       </c>
       <c r="E323" s="4">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="F323" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G323" s="4" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H323" s="4" t="s">
         <v>14</v>
@@ -11376,13 +11376,13 @@
         <v>11</v>
       </c>
       <c r="E324" s="2">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F324" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G324" s="2" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H324" s="2" t="s">
         <v>14</v>
@@ -11402,13 +11402,13 @@
         <v>11</v>
       </c>
       <c r="E325" s="4">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="F325" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G325" s="4" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H325" s="4" t="s">
         <v>14</v>
@@ -11428,13 +11428,13 @@
         <v>11</v>
       </c>
       <c r="E326" s="2">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="F326" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G326" s="2" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H326" s="2" t="s">
         <v>14</v>
@@ -11454,13 +11454,13 @@
         <v>11</v>
       </c>
       <c r="E327" s="4">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F327" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G327" s="4" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H327" s="4" t="s">
         <v>14</v>
@@ -11480,13 +11480,13 @@
         <v>11</v>
       </c>
       <c r="E328" s="2">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="F328" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G328" s="2" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H328" s="2" t="s">
         <v>14</v>
@@ -11506,13 +11506,13 @@
         <v>11</v>
       </c>
       <c r="E329" s="4">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="F329" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G329" s="4" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H329" s="4" t="s">
         <v>14</v>
@@ -11532,13 +11532,13 @@
         <v>11</v>
       </c>
       <c r="E330" s="2">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="F330" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G330" s="2" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H330" s="2" t="s">
         <v>14</v>
@@ -11558,13 +11558,13 @@
         <v>11</v>
       </c>
       <c r="E331" s="4">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="F331" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G331" s="4" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H331" s="4" t="s">
         <v>14</v>
@@ -11584,13 +11584,13 @@
         <v>11</v>
       </c>
       <c r="E332" s="2">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F332" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G332" s="2" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H332" s="2" t="s">
         <v>14</v>
@@ -11610,13 +11610,13 @@
         <v>11</v>
       </c>
       <c r="E333" s="4">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="F333" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G333" s="4" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H333" s="4" t="s">
         <v>14</v>
@@ -11636,13 +11636,13 @@
         <v>11</v>
       </c>
       <c r="E334" s="2">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="F334" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G334" s="2" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H334" s="2" t="s">
         <v>14</v>
@@ -11662,13 +11662,13 @@
         <v>11</v>
       </c>
       <c r="E335" s="4">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="F335" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G335" s="4" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H335" s="4" t="s">
         <v>14</v>
@@ -11688,13 +11688,13 @@
         <v>11</v>
       </c>
       <c r="E336" s="2">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F336" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G336" s="2" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H336" s="2" t="s">
         <v>14</v>
@@ -11714,13 +11714,13 @@
         <v>11</v>
       </c>
       <c r="E337" s="4">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="F337" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G337" s="4" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H337" s="4" t="s">
         <v>14</v>
@@ -11740,13 +11740,13 @@
         <v>11</v>
       </c>
       <c r="E338" s="2">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="F338" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G338" s="2" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H338" s="2" t="s">
         <v>14</v>
@@ -11766,13 +11766,13 @@
         <v>11</v>
       </c>
       <c r="E339" s="4">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="F339" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G339" s="4" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H339" s="4" t="s">
         <v>14</v>
@@ -11792,13 +11792,13 @@
         <v>11</v>
       </c>
       <c r="E340" s="2">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="F340" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G340" s="2" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H340" s="2" t="s">
         <v>14</v>
@@ -11818,13 +11818,13 @@
         <v>11</v>
       </c>
       <c r="E341" s="4">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="F341" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G341" s="4" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H341" s="4" t="s">
         <v>14</v>
@@ -11844,13 +11844,13 @@
         <v>11</v>
       </c>
       <c r="E342" s="2">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="F342" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G342" s="2" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H342" s="2" t="s">
         <v>14</v>
@@ -11870,13 +11870,13 @@
         <v>11</v>
       </c>
       <c r="E343" s="4">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="F343" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G343" s="4" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H343" s="4" t="s">
         <v>14</v>
@@ -11896,13 +11896,13 @@
         <v>11</v>
       </c>
       <c r="E344" s="2">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="F344" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G344" s="2" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H344" s="2" t="s">
         <v>14</v>
@@ -11922,13 +11922,13 @@
         <v>11</v>
       </c>
       <c r="E345" s="4">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="F345" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G345" s="4" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H345" s="4" t="s">
         <v>14</v>
@@ -11948,13 +11948,13 @@
         <v>11</v>
       </c>
       <c r="E346" s="2">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="F346" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G346" s="2" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H346" s="2" t="s">
         <v>14</v>
@@ -11974,13 +11974,13 @@
         <v>11</v>
       </c>
       <c r="E347" s="4">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="F347" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G347" s="4" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H347" s="4" t="s">
         <v>14</v>
@@ -12000,13 +12000,13 @@
         <v>11</v>
       </c>
       <c r="E348" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F348" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G348" s="2" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H348" s="2" t="s">
         <v>14</v>
@@ -12026,13 +12026,13 @@
         <v>11</v>
       </c>
       <c r="E349" s="4">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="F349" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G349" s="4" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H349" s="4" t="s">
         <v>14</v>
@@ -12052,13 +12052,13 @@
         <v>11</v>
       </c>
       <c r="E350" s="2">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="F350" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G350" s="2" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H350" s="2" t="s">
         <v>14</v>
@@ -12078,13 +12078,13 @@
         <v>11</v>
       </c>
       <c r="E351" s="4">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="F351" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G351" s="4" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H351" s="4" t="s">
         <v>14</v>
@@ -12104,13 +12104,13 @@
         <v>11</v>
       </c>
       <c r="E352" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F352" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G352" s="2" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H352" s="2" t="s">
         <v>14</v>
@@ -12130,13 +12130,13 @@
         <v>11</v>
       </c>
       <c r="E353" s="4">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F353" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G353" s="4" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H353" s="4" t="s">
         <v>14</v>
@@ -12156,13 +12156,13 @@
         <v>11</v>
       </c>
       <c r="E354" s="2">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F354" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G354" s="2" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H354" s="2" t="s">
         <v>14</v>
@@ -12182,13 +12182,13 @@
         <v>11</v>
       </c>
       <c r="E355" s="4">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F355" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G355" s="4" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H355" s="4" t="s">
         <v>14</v>
@@ -12208,13 +12208,13 @@
         <v>11</v>
       </c>
       <c r="E356" s="2">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="F356" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G356" s="2" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H356" s="2" t="s">
         <v>14</v>
@@ -12234,13 +12234,13 @@
         <v>11</v>
       </c>
       <c r="E357" s="4">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F357" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G357" s="4" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H357" s="4" t="s">
         <v>14</v>
@@ -12260,13 +12260,13 @@
         <v>11</v>
       </c>
       <c r="E358" s="2">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F358" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G358" s="2" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H358" s="2" t="s">
         <v>14</v>
@@ -12286,13 +12286,13 @@
         <v>11</v>
       </c>
       <c r="E359" s="4">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F359" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G359" s="4" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H359" s="4" t="s">
         <v>14</v>
@@ -12312,13 +12312,13 @@
         <v>11</v>
       </c>
       <c r="E360" s="2">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="F360" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G360" s="2" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H360" s="2" t="s">
         <v>14</v>
@@ -12338,13 +12338,13 @@
         <v>11</v>
       </c>
       <c r="E361" s="4">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="F361" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G361" s="4" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H361" s="4" t="s">
         <v>14</v>
@@ -12364,13 +12364,13 @@
         <v>11</v>
       </c>
       <c r="E362" s="2">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F362" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G362" s="2" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H362" s="2" t="s">
         <v>14</v>
@@ -12390,13 +12390,13 @@
         <v>11</v>
       </c>
       <c r="E363" s="4">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="F363" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G363" s="4" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H363" s="4" t="s">
         <v>14</v>
@@ -12416,13 +12416,13 @@
         <v>11</v>
       </c>
       <c r="E364" s="2">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="F364" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G364" s="2" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H364" s="2" t="s">
         <v>14</v>
@@ -12442,13 +12442,13 @@
         <v>11</v>
       </c>
       <c r="E365" s="4">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="F365" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G365" s="4" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H365" s="4" t="s">
         <v>14</v>
@@ -12468,13 +12468,13 @@
         <v>11</v>
       </c>
       <c r="E366" s="2">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="F366" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G366" s="2" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H366" s="2" t="s">
         <v>14</v>
@@ -12494,13 +12494,13 @@
         <v>11</v>
       </c>
       <c r="E367" s="4">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="F367" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G367" s="4" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H367" s="4" t="s">
         <v>14</v>
@@ -12520,13 +12520,13 @@
         <v>11</v>
       </c>
       <c r="E368" s="2">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="F368" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G368" s="2" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H368" s="2" t="s">
         <v>14</v>
@@ -12546,13 +12546,13 @@
         <v>11</v>
       </c>
       <c r="E369" s="4">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F369" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G369" s="4" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H369" s="4" t="s">
         <v>14</v>
@@ -12572,13 +12572,13 @@
         <v>11</v>
       </c>
       <c r="E370" s="2">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="F370" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G370" s="2" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H370" s="2" t="s">
         <v>14</v>
@@ -12598,13 +12598,13 @@
         <v>11</v>
       </c>
       <c r="E371" s="4">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F371" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G371" s="4" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H371" s="4" t="s">
         <v>14</v>
@@ -12624,13 +12624,13 @@
         <v>11</v>
       </c>
       <c r="E372" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F372" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G372" s="2" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H372" s="2" t="s">
         <v>14</v>
@@ -12650,13 +12650,13 @@
         <v>11</v>
       </c>
       <c r="E373" s="4">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="F373" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G373" s="4" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H373" s="4" t="s">
         <v>14</v>
@@ -12676,13 +12676,13 @@
         <v>11</v>
       </c>
       <c r="E374" s="2">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F374" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G374" s="2" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H374" s="2" t="s">
         <v>14</v>
@@ -12702,13 +12702,13 @@
         <v>11</v>
       </c>
       <c r="E375" s="4">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F375" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G375" s="4" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H375" s="4" t="s">
         <v>14</v>
@@ -12728,13 +12728,13 @@
         <v>11</v>
       </c>
       <c r="E376" s="2">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F376" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G376" s="2" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H376" s="2" t="s">
         <v>14</v>
@@ -12754,13 +12754,13 @@
         <v>11</v>
       </c>
       <c r="E377" s="4">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="F377" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G377" s="4" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H377" s="4" t="s">
         <v>14</v>
@@ -12786,7 +12786,7 @@
         <v>12</v>
       </c>
       <c r="G378" s="2" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H378" s="2" t="s">
         <v>14</v>
@@ -12806,13 +12806,13 @@
         <v>11</v>
       </c>
       <c r="E379" s="4">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F379" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G379" s="4" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H379" s="4" t="s">
         <v>14</v>
@@ -12832,13 +12832,13 @@
         <v>11</v>
       </c>
       <c r="E380" s="2">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="F380" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G380" s="2" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H380" s="2" t="s">
         <v>14</v>
@@ -12858,13 +12858,13 @@
         <v>11</v>
       </c>
       <c r="E381" s="4">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F381" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G381" s="4" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H381" s="4" t="s">
         <v>14</v>
@@ -12884,13 +12884,13 @@
         <v>11</v>
       </c>
       <c r="E382" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F382" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G382" s="2" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H382" s="2" t="s">
         <v>14</v>
@@ -12910,13 +12910,13 @@
         <v>11</v>
       </c>
       <c r="E383" s="4">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="F383" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G383" s="4" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H383" s="4" t="s">
         <v>14</v>
@@ -12936,13 +12936,13 @@
         <v>11</v>
       </c>
       <c r="E384" s="2">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="F384" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G384" s="2" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H384" s="2" t="s">
         <v>14</v>
@@ -12962,13 +12962,13 @@
         <v>11</v>
       </c>
       <c r="E385" s="4">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="F385" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G385" s="4" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H385" s="4" t="s">
         <v>14</v>
@@ -12988,13 +12988,13 @@
         <v>11</v>
       </c>
       <c r="E386" s="2">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F386" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G386" s="2" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H386" s="2" t="s">
         <v>14</v>
@@ -13014,13 +13014,13 @@
         <v>11</v>
       </c>
       <c r="E387" s="4">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F387" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G387" s="4" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H387" s="4" t="s">
         <v>14</v>
@@ -13040,13 +13040,13 @@
         <v>11</v>
       </c>
       <c r="E388" s="2">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="F388" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G388" s="2" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H388" s="2" t="s">
         <v>14</v>
@@ -13066,13 +13066,13 @@
         <v>11</v>
       </c>
       <c r="E389" s="4">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="F389" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G389" s="4" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H389" s="4" t="s">
         <v>14</v>
@@ -13092,13 +13092,13 @@
         <v>11</v>
       </c>
       <c r="E390" s="2">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="F390" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G390" s="2" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H390" s="2" t="s">
         <v>14</v>
@@ -13118,13 +13118,13 @@
         <v>11</v>
       </c>
       <c r="E391" s="4">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="F391" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G391" s="4" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H391" s="4" t="s">
         <v>14</v>
@@ -13144,13 +13144,13 @@
         <v>11</v>
       </c>
       <c r="E392" s="2">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="F392" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G392" s="2" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H392" s="2" t="s">
         <v>14</v>
@@ -13170,13 +13170,13 @@
         <v>11</v>
       </c>
       <c r="E393" s="4">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="F393" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G393" s="4" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H393" s="4" t="s">
         <v>14</v>
@@ -13196,13 +13196,13 @@
         <v>11</v>
       </c>
       <c r="E394" s="2">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="F394" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G394" s="2" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H394" s="2" t="s">
         <v>14</v>
@@ -13222,13 +13222,13 @@
         <v>11</v>
       </c>
       <c r="E395" s="4">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F395" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G395" s="4" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H395" s="4" t="s">
         <v>14</v>
@@ -13248,13 +13248,13 @@
         <v>11</v>
       </c>
       <c r="E396" s="2">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="F396" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G396" s="2" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H396" s="2" t="s">
         <v>14</v>
@@ -13274,13 +13274,13 @@
         <v>11</v>
       </c>
       <c r="E397" s="4">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F397" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G397" s="4" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H397" s="4" t="s">
         <v>14</v>
@@ -13300,13 +13300,13 @@
         <v>11</v>
       </c>
       <c r="E398" s="2">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="F398" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G398" s="2" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H398" s="2" t="s">
         <v>14</v>
@@ -13326,13 +13326,13 @@
         <v>11</v>
       </c>
       <c r="E399" s="4">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="F399" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G399" s="4" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H399" s="4" t="s">
         <v>14</v>
@@ -13352,13 +13352,13 @@
         <v>11</v>
       </c>
       <c r="E400" s="2">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="F400" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G400" s="2" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H400" s="2" t="s">
         <v>14</v>
@@ -13378,13 +13378,13 @@
         <v>11</v>
       </c>
       <c r="E401" s="4">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="F401" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G401" s="4" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H401" s="4" t="s">
         <v>14</v>

--- a/reports/Mobile_Appium_E2E_Test_Report_400.xlsx
+++ b/reports/Mobile_Appium_E2E_Test_Report_400.xlsx
@@ -52,7 +52,7 @@
     <t>PASSED</t>
   </si>
   <si>
-    <t>2026-08-07T04:03:04.297Z</t>
+    <t>2026-08-07T14:58:56.839Z</t>
   </si>
   <si>
     <t>Verified Android Activity lifecycle and Capacitor native plugin interface</t>
@@ -64,6 +64,9 @@
     <t>Native Authentication Flow - Mobile Assertion #2: Verify native shell component interaction</t>
   </si>
   <si>
+    <t>2026-08-07T14:58:56.840Z</t>
+  </si>
+  <si>
     <t>MOB-TC-0003</t>
   </si>
   <si>
@@ -425,9 +428,6 @@
   </si>
   <si>
     <t>Screen Orientation Swap - Mobile Assertion #1: Verify native shell component interaction</t>
-  </si>
-  <si>
-    <t>2026-08-07T04:03:04.298Z</t>
   </si>
   <si>
     <t>MOB-TC-0062</t>
@@ -3004,7 +3004,7 @@
         <v>11</v>
       </c>
       <c r="E2" s="2">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>12</v>
@@ -3030,13 +3030,13 @@
         <v>11</v>
       </c>
       <c r="E3" s="4">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="H3" s="4" t="s">
         <v>14</v>
@@ -3044,25 +3044,25 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E4" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F4" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>14</v>
@@ -3070,25 +3070,25 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B5" s="4" t="s">
         <v>9</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D5" s="4" t="s">
         <v>11</v>
       </c>
       <c r="E5" s="4">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="F5" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="H5" s="4" t="s">
         <v>14</v>
@@ -3096,13 +3096,13 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>11</v>
@@ -3114,7 +3114,7 @@
         <v>12</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>14</v>
@@ -3122,25 +3122,25 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B7" s="4" t="s">
         <v>9</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>11</v>
       </c>
       <c r="E7" s="4">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F7" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="H7" s="4" t="s">
         <v>14</v>
@@ -3148,25 +3148,25 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E8" s="2">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F8" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>14</v>
@@ -3174,25 +3174,25 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B9" s="4" t="s">
         <v>9</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D9" s="4" t="s">
         <v>11</v>
       </c>
       <c r="E9" s="4">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F9" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="H9" s="4" t="s">
         <v>14</v>
@@ -3200,25 +3200,25 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C10" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E10" s="2">
         <v>30</v>
       </c>
-      <c r="D10" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E10" s="2">
-        <v>20</v>
-      </c>
       <c r="F10" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>14</v>
@@ -3226,25 +3226,25 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B11" s="4" t="s">
         <v>9</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D11" s="4" t="s">
         <v>11</v>
       </c>
       <c r="E11" s="4">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="F11" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="H11" s="4" t="s">
         <v>14</v>
@@ -3252,25 +3252,25 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E12" s="2">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="F12" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>14</v>
@@ -3278,25 +3278,25 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B13" s="4" t="s">
         <v>9</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D13" s="4" t="s">
         <v>11</v>
       </c>
       <c r="E13" s="4">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="F13" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="H13" s="4" t="s">
         <v>14</v>
@@ -3304,25 +3304,25 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E14" s="2">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="H14" s="2" t="s">
         <v>14</v>
@@ -3330,25 +3330,25 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B15" s="4" t="s">
         <v>9</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D15" s="4" t="s">
         <v>11</v>
       </c>
       <c r="E15" s="4">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="F15" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="H15" s="4" t="s">
         <v>14</v>
@@ -3356,25 +3356,25 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E16" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F16" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="H16" s="2" t="s">
         <v>14</v>
@@ -3382,25 +3382,25 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B17" s="4" t="s">
         <v>9</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D17" s="4" t="s">
         <v>11</v>
       </c>
       <c r="E17" s="4">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F17" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="H17" s="4" t="s">
         <v>14</v>
@@ -3408,25 +3408,25 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E18" s="2">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="F18" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="H18" s="2" t="s">
         <v>14</v>
@@ -3434,25 +3434,25 @@
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B19" s="4" t="s">
         <v>9</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D19" s="4" t="s">
         <v>11</v>
       </c>
       <c r="E19" s="4">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="F19" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="H19" s="4" t="s">
         <v>14</v>
@@ -3460,25 +3460,25 @@
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E20" s="2">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="F20" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="H20" s="2" t="s">
         <v>14</v>
@@ -3486,25 +3486,25 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B21" s="4" t="s">
         <v>9</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D21" s="4" t="s">
         <v>11</v>
       </c>
       <c r="E21" s="4">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F21" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="H21" s="4" t="s">
         <v>14</v>
@@ -3512,25 +3512,25 @@
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E22" s="2">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F22" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="H22" s="2" t="s">
         <v>14</v>
@@ -3538,25 +3538,25 @@
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D23" s="4" t="s">
         <v>11</v>
       </c>
       <c r="E23" s="4">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="F23" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G23" s="4" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="H23" s="4" t="s">
         <v>14</v>
@@ -3564,25 +3564,25 @@
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E24" s="2">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="F24" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="H24" s="2" t="s">
         <v>14</v>
@@ -3590,25 +3590,25 @@
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D25" s="4" t="s">
         <v>11</v>
       </c>
       <c r="E25" s="4">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="F25" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G25" s="4" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="H25" s="4" t="s">
         <v>14</v>
@@ -3616,25 +3616,25 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E26" s="2">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F26" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="H26" s="2" t="s">
         <v>14</v>
@@ -3642,25 +3642,25 @@
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D27" s="4" t="s">
         <v>11</v>
       </c>
       <c r="E27" s="4">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F27" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G27" s="4" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="H27" s="4" t="s">
         <v>14</v>
@@ -3668,25 +3668,25 @@
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E28" s="2">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="F28" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="H28" s="2" t="s">
         <v>14</v>
@@ -3694,25 +3694,25 @@
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D29" s="4" t="s">
         <v>11</v>
       </c>
       <c r="E29" s="4">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F29" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G29" s="4" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="H29" s="4" t="s">
         <v>14</v>
@@ -3720,25 +3720,25 @@
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E30" s="2">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="F30" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="H30" s="2" t="s">
         <v>14</v>
@@ -3746,25 +3746,25 @@
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D31" s="4" t="s">
         <v>11</v>
       </c>
       <c r="E31" s="4">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="F31" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G31" s="4" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="H31" s="4" t="s">
         <v>14</v>
@@ -3772,25 +3772,25 @@
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E32" s="2">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="F32" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="H32" s="2" t="s">
         <v>14</v>
@@ -3798,25 +3798,25 @@
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D33" s="4" t="s">
         <v>11</v>
       </c>
       <c r="E33" s="4">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F33" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G33" s="4" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="H33" s="4" t="s">
         <v>14</v>
@@ -3824,25 +3824,25 @@
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E34" s="2">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="F34" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="H34" s="2" t="s">
         <v>14</v>
@@ -3850,25 +3850,25 @@
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D35" s="4" t="s">
         <v>11</v>
       </c>
       <c r="E35" s="4">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F35" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G35" s="4" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="H35" s="4" t="s">
         <v>14</v>
@@ -3876,25 +3876,25 @@
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E36" s="2">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="F36" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="H36" s="2" t="s">
         <v>14</v>
@@ -3902,25 +3902,25 @@
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D37" s="4" t="s">
         <v>11</v>
       </c>
       <c r="E37" s="4">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="F37" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G37" s="4" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="H37" s="4" t="s">
         <v>14</v>
@@ -3928,25 +3928,25 @@
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E38" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F38" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="H38" s="2" t="s">
         <v>14</v>
@@ -3954,25 +3954,25 @@
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D39" s="4" t="s">
         <v>11</v>
       </c>
       <c r="E39" s="4">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="F39" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G39" s="4" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="H39" s="4" t="s">
         <v>14</v>
@@ -3980,25 +3980,25 @@
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E40" s="2">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="F40" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="H40" s="2" t="s">
         <v>14</v>
@@ -4006,25 +4006,25 @@
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" s="4" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D41" s="4" t="s">
         <v>11</v>
       </c>
       <c r="E41" s="4">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="F41" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G41" s="4" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="H41" s="4" t="s">
         <v>14</v>
@@ -4032,25 +4032,25 @@
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E42" s="2">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="F42" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="H42" s="2" t="s">
         <v>14</v>
@@ -4058,13 +4058,13 @@
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D43" s="4" t="s">
         <v>11</v>
@@ -4076,7 +4076,7 @@
         <v>12</v>
       </c>
       <c r="G43" s="4" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="H43" s="4" t="s">
         <v>14</v>
@@ -4084,25 +4084,25 @@
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E44" s="2">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="F44" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="H44" s="2" t="s">
         <v>14</v>
@@ -4110,25 +4110,25 @@
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" s="4" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D45" s="4" t="s">
         <v>11</v>
       </c>
       <c r="E45" s="4">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="F45" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G45" s="4" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="H45" s="4" t="s">
         <v>14</v>
@@ -4136,25 +4136,25 @@
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D46" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E46" s="2">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="F46" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="H46" s="2" t="s">
         <v>14</v>
@@ -4162,25 +4162,25 @@
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" s="4" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D47" s="4" t="s">
         <v>11</v>
       </c>
       <c r="E47" s="4">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="F47" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G47" s="4" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="H47" s="4" t="s">
         <v>14</v>
@@ -4188,25 +4188,25 @@
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D48" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E48" s="2">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="F48" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="H48" s="2" t="s">
         <v>14</v>
@@ -4214,25 +4214,25 @@
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" s="4" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D49" s="4" t="s">
         <v>11</v>
       </c>
       <c r="E49" s="4">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="F49" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G49" s="4" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="H49" s="4" t="s">
         <v>14</v>
@@ -4240,25 +4240,25 @@
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D50" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E50" s="2">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="F50" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="H50" s="2" t="s">
         <v>14</v>
@@ -4266,25 +4266,25 @@
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" s="4" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D51" s="4" t="s">
         <v>11</v>
       </c>
       <c r="E51" s="4">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="F51" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G51" s="4" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="H51" s="4" t="s">
         <v>14</v>
@@ -4292,25 +4292,25 @@
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D52" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E52" s="2">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F52" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="H52" s="2" t="s">
         <v>14</v>
@@ -4318,25 +4318,25 @@
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" s="4" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D53" s="4" t="s">
         <v>11</v>
       </c>
       <c r="E53" s="4">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="F53" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G53" s="4" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="H53" s="4" t="s">
         <v>14</v>
@@ -4344,25 +4344,25 @@
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D54" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E54" s="2">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F54" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="H54" s="2" t="s">
         <v>14</v>
@@ -4370,25 +4370,25 @@
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" s="4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D55" s="4" t="s">
         <v>11</v>
       </c>
       <c r="E55" s="4">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="F55" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G55" s="4" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="H55" s="4" t="s">
         <v>14</v>
@@ -4396,25 +4396,25 @@
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D56" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E56" s="2">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F56" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="H56" s="2" t="s">
         <v>14</v>
@@ -4422,25 +4422,25 @@
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" s="4" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D57" s="4" t="s">
         <v>11</v>
       </c>
       <c r="E57" s="4">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="F57" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G57" s="4" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="H57" s="4" t="s">
         <v>14</v>
@@ -4448,25 +4448,25 @@
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D58" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E58" s="2">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="F58" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="H58" s="2" t="s">
         <v>14</v>
@@ -4474,13 +4474,13 @@
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" s="4" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D59" s="4" t="s">
         <v>11</v>
@@ -4492,7 +4492,7 @@
         <v>12</v>
       </c>
       <c r="G59" s="4" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="H59" s="4" t="s">
         <v>14</v>
@@ -4500,25 +4500,25 @@
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D60" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E60" s="2">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="F60" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="H60" s="2" t="s">
         <v>14</v>
@@ -4526,25 +4526,25 @@
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" s="4" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D61" s="4" t="s">
         <v>11</v>
       </c>
       <c r="E61" s="4">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="F61" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G61" s="4" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="H61" s="4" t="s">
         <v>14</v>
@@ -4552,25 +4552,25 @@
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D62" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E62" s="2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F62" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H62" s="2" t="s">
         <v>14</v>
@@ -4581,7 +4581,7 @@
         <v>139</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C63" s="4" t="s">
         <v>140</v>
@@ -4590,13 +4590,13 @@
         <v>11</v>
       </c>
       <c r="E63" s="4">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="F63" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G63" s="4" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H63" s="4" t="s">
         <v>14</v>
@@ -4607,7 +4607,7 @@
         <v>141</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C64" s="2" t="s">
         <v>142</v>
@@ -4616,13 +4616,13 @@
         <v>11</v>
       </c>
       <c r="E64" s="2">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="F64" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H64" s="2" t="s">
         <v>14</v>
@@ -4633,7 +4633,7 @@
         <v>143</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C65" s="4" t="s">
         <v>144</v>
@@ -4642,13 +4642,13 @@
         <v>11</v>
       </c>
       <c r="E65" s="4">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F65" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G65" s="4" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H65" s="4" t="s">
         <v>14</v>
@@ -4659,7 +4659,7 @@
         <v>145</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C66" s="2" t="s">
         <v>146</v>
@@ -4668,13 +4668,13 @@
         <v>11</v>
       </c>
       <c r="E66" s="2">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F66" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H66" s="2" t="s">
         <v>14</v>
@@ -4685,7 +4685,7 @@
         <v>147</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C67" s="4" t="s">
         <v>148</v>
@@ -4694,13 +4694,13 @@
         <v>11</v>
       </c>
       <c r="E67" s="4">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="F67" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G67" s="4" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H67" s="4" t="s">
         <v>14</v>
@@ -4711,7 +4711,7 @@
         <v>149</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C68" s="2" t="s">
         <v>150</v>
@@ -4720,13 +4720,13 @@
         <v>11</v>
       </c>
       <c r="E68" s="2">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="F68" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H68" s="2" t="s">
         <v>14</v>
@@ -4737,7 +4737,7 @@
         <v>151</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C69" s="4" t="s">
         <v>152</v>
@@ -4746,13 +4746,13 @@
         <v>11</v>
       </c>
       <c r="E69" s="4">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F69" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G69" s="4" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H69" s="4" t="s">
         <v>14</v>
@@ -4763,7 +4763,7 @@
         <v>153</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C70" s="2" t="s">
         <v>154</v>
@@ -4772,13 +4772,13 @@
         <v>11</v>
       </c>
       <c r="E70" s="2">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="F70" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H70" s="2" t="s">
         <v>14</v>
@@ -4789,7 +4789,7 @@
         <v>155</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C71" s="4" t="s">
         <v>156</v>
@@ -4798,13 +4798,13 @@
         <v>11</v>
       </c>
       <c r="E71" s="4">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F71" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G71" s="4" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H71" s="4" t="s">
         <v>14</v>
@@ -4815,7 +4815,7 @@
         <v>157</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C72" s="2" t="s">
         <v>158</v>
@@ -4824,13 +4824,13 @@
         <v>11</v>
       </c>
       <c r="E72" s="2">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="F72" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H72" s="2" t="s">
         <v>14</v>
@@ -4841,7 +4841,7 @@
         <v>159</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C73" s="4" t="s">
         <v>160</v>
@@ -4850,13 +4850,13 @@
         <v>11</v>
       </c>
       <c r="E73" s="4">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F73" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G73" s="4" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H73" s="4" t="s">
         <v>14</v>
@@ -4867,7 +4867,7 @@
         <v>161</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C74" s="2" t="s">
         <v>162</v>
@@ -4876,13 +4876,13 @@
         <v>11</v>
       </c>
       <c r="E74" s="2">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="F74" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H74" s="2" t="s">
         <v>14</v>
@@ -4893,7 +4893,7 @@
         <v>163</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C75" s="4" t="s">
         <v>164</v>
@@ -4902,13 +4902,13 @@
         <v>11</v>
       </c>
       <c r="E75" s="4">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="F75" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G75" s="4" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H75" s="4" t="s">
         <v>14</v>
@@ -4919,7 +4919,7 @@
         <v>165</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C76" s="2" t="s">
         <v>166</v>
@@ -4928,13 +4928,13 @@
         <v>11</v>
       </c>
       <c r="E76" s="2">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F76" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H76" s="2" t="s">
         <v>14</v>
@@ -4945,7 +4945,7 @@
         <v>167</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C77" s="4" t="s">
         <v>168</v>
@@ -4954,13 +4954,13 @@
         <v>11</v>
       </c>
       <c r="E77" s="4">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F77" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G77" s="4" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H77" s="4" t="s">
         <v>14</v>
@@ -4971,7 +4971,7 @@
         <v>169</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C78" s="2" t="s">
         <v>170</v>
@@ -4980,13 +4980,13 @@
         <v>11</v>
       </c>
       <c r="E78" s="2">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F78" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H78" s="2" t="s">
         <v>14</v>
@@ -4997,7 +4997,7 @@
         <v>171</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C79" s="4" t="s">
         <v>172</v>
@@ -5006,13 +5006,13 @@
         <v>11</v>
       </c>
       <c r="E79" s="4">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="F79" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G79" s="4" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H79" s="4" t="s">
         <v>14</v>
@@ -5023,7 +5023,7 @@
         <v>173</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C80" s="2" t="s">
         <v>174</v>
@@ -5032,13 +5032,13 @@
         <v>11</v>
       </c>
       <c r="E80" s="2">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="F80" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H80" s="2" t="s">
         <v>14</v>
@@ -5049,7 +5049,7 @@
         <v>175</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C81" s="4" t="s">
         <v>176</v>
@@ -5058,13 +5058,13 @@
         <v>11</v>
       </c>
       <c r="E81" s="4">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="F81" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G81" s="4" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H81" s="4" t="s">
         <v>14</v>
@@ -5084,13 +5084,13 @@
         <v>11</v>
       </c>
       <c r="E82" s="2">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F82" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H82" s="2" t="s">
         <v>14</v>
@@ -5110,13 +5110,13 @@
         <v>11</v>
       </c>
       <c r="E83" s="4">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F83" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G83" s="4" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H83" s="4" t="s">
         <v>14</v>
@@ -5136,13 +5136,13 @@
         <v>11</v>
       </c>
       <c r="E84" s="2">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="F84" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G84" s="2" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H84" s="2" t="s">
         <v>14</v>
@@ -5162,13 +5162,13 @@
         <v>11</v>
       </c>
       <c r="E85" s="4">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="F85" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G85" s="4" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H85" s="4" t="s">
         <v>14</v>
@@ -5188,13 +5188,13 @@
         <v>11</v>
       </c>
       <c r="E86" s="2">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="F86" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G86" s="2" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H86" s="2" t="s">
         <v>14</v>
@@ -5214,13 +5214,13 @@
         <v>11</v>
       </c>
       <c r="E87" s="4">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="F87" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G87" s="4" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H87" s="4" t="s">
         <v>14</v>
@@ -5240,13 +5240,13 @@
         <v>11</v>
       </c>
       <c r="E88" s="2">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="F88" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G88" s="2" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H88" s="2" t="s">
         <v>14</v>
@@ -5266,13 +5266,13 @@
         <v>11</v>
       </c>
       <c r="E89" s="4">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F89" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G89" s="4" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H89" s="4" t="s">
         <v>14</v>
@@ -5298,7 +5298,7 @@
         <v>12</v>
       </c>
       <c r="G90" s="2" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H90" s="2" t="s">
         <v>14</v>
@@ -5318,13 +5318,13 @@
         <v>11</v>
       </c>
       <c r="E91" s="4">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="F91" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G91" s="4" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H91" s="4" t="s">
         <v>14</v>
@@ -5344,13 +5344,13 @@
         <v>11</v>
       </c>
       <c r="E92" s="2">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="F92" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G92" s="2" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H92" s="2" t="s">
         <v>14</v>
@@ -5370,13 +5370,13 @@
         <v>11</v>
       </c>
       <c r="E93" s="4">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="F93" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G93" s="4" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H93" s="4" t="s">
         <v>14</v>
@@ -5396,13 +5396,13 @@
         <v>11</v>
       </c>
       <c r="E94" s="2">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F94" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G94" s="2" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H94" s="2" t="s">
         <v>14</v>
@@ -5422,13 +5422,13 @@
         <v>11</v>
       </c>
       <c r="E95" s="4">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="F95" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G95" s="4" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H95" s="4" t="s">
         <v>14</v>
@@ -5448,13 +5448,13 @@
         <v>11</v>
       </c>
       <c r="E96" s="2">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="F96" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G96" s="2" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H96" s="2" t="s">
         <v>14</v>
@@ -5474,13 +5474,13 @@
         <v>11</v>
       </c>
       <c r="E97" s="4">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="F97" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G97" s="4" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H97" s="4" t="s">
         <v>14</v>
@@ -5500,13 +5500,13 @@
         <v>11</v>
       </c>
       <c r="E98" s="2">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="F98" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G98" s="2" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H98" s="2" t="s">
         <v>14</v>
@@ -5526,13 +5526,13 @@
         <v>11</v>
       </c>
       <c r="E99" s="4">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F99" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G99" s="4" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H99" s="4" t="s">
         <v>14</v>
@@ -5552,13 +5552,13 @@
         <v>11</v>
       </c>
       <c r="E100" s="2">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="F100" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G100" s="2" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H100" s="2" t="s">
         <v>14</v>
@@ -5578,13 +5578,13 @@
         <v>11</v>
       </c>
       <c r="E101" s="4">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="F101" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G101" s="4" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H101" s="4" t="s">
         <v>14</v>
@@ -5604,13 +5604,13 @@
         <v>11</v>
       </c>
       <c r="E102" s="2">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="F102" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G102" s="2" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H102" s="2" t="s">
         <v>14</v>
@@ -5630,13 +5630,13 @@
         <v>11</v>
       </c>
       <c r="E103" s="4">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F103" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G103" s="4" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H103" s="4" t="s">
         <v>14</v>
@@ -5656,13 +5656,13 @@
         <v>11</v>
       </c>
       <c r="E104" s="2">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="F104" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G104" s="2" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H104" s="2" t="s">
         <v>14</v>
@@ -5682,13 +5682,13 @@
         <v>11</v>
       </c>
       <c r="E105" s="4">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F105" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G105" s="4" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H105" s="4" t="s">
         <v>14</v>
@@ -5708,13 +5708,13 @@
         <v>11</v>
       </c>
       <c r="E106" s="2">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="F106" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G106" s="2" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H106" s="2" t="s">
         <v>14</v>
@@ -5734,13 +5734,13 @@
         <v>11</v>
       </c>
       <c r="E107" s="4">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="F107" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G107" s="4" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H107" s="4" t="s">
         <v>14</v>
@@ -5760,13 +5760,13 @@
         <v>11</v>
       </c>
       <c r="E108" s="2">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="F108" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G108" s="2" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H108" s="2" t="s">
         <v>14</v>
@@ -5786,13 +5786,13 @@
         <v>11</v>
       </c>
       <c r="E109" s="4">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="F109" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G109" s="4" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H109" s="4" t="s">
         <v>14</v>
@@ -5812,13 +5812,13 @@
         <v>11</v>
       </c>
       <c r="E110" s="2">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="F110" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G110" s="2" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H110" s="2" t="s">
         <v>14</v>
@@ -5838,13 +5838,13 @@
         <v>11</v>
       </c>
       <c r="E111" s="4">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="F111" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G111" s="4" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H111" s="4" t="s">
         <v>14</v>
@@ -5864,13 +5864,13 @@
         <v>11</v>
       </c>
       <c r="E112" s="2">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="F112" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G112" s="2" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H112" s="2" t="s">
         <v>14</v>
@@ -5890,13 +5890,13 @@
         <v>11</v>
       </c>
       <c r="E113" s="4">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="F113" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G113" s="4" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H113" s="4" t="s">
         <v>14</v>
@@ -5916,13 +5916,13 @@
         <v>11</v>
       </c>
       <c r="E114" s="2">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="F114" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G114" s="2" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H114" s="2" t="s">
         <v>14</v>
@@ -5942,13 +5942,13 @@
         <v>11</v>
       </c>
       <c r="E115" s="4">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="F115" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G115" s="4" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H115" s="4" t="s">
         <v>14</v>
@@ -5968,13 +5968,13 @@
         <v>11</v>
       </c>
       <c r="E116" s="2">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="F116" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G116" s="2" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H116" s="2" t="s">
         <v>14</v>
@@ -5994,13 +5994,13 @@
         <v>11</v>
       </c>
       <c r="E117" s="4">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="F117" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G117" s="4" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H117" s="4" t="s">
         <v>14</v>
@@ -6020,13 +6020,13 @@
         <v>11</v>
       </c>
       <c r="E118" s="2">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F118" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G118" s="2" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H118" s="2" t="s">
         <v>14</v>
@@ -6046,13 +6046,13 @@
         <v>11</v>
       </c>
       <c r="E119" s="4">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F119" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G119" s="4" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H119" s="4" t="s">
         <v>14</v>
@@ -6072,13 +6072,13 @@
         <v>11</v>
       </c>
       <c r="E120" s="2">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="F120" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G120" s="2" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H120" s="2" t="s">
         <v>14</v>
@@ -6098,13 +6098,13 @@
         <v>11</v>
       </c>
       <c r="E121" s="4">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F121" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G121" s="4" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H121" s="4" t="s">
         <v>14</v>
@@ -6124,13 +6124,13 @@
         <v>11</v>
       </c>
       <c r="E122" s="2">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="F122" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G122" s="2" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H122" s="2" t="s">
         <v>14</v>
@@ -6150,13 +6150,13 @@
         <v>11</v>
       </c>
       <c r="E123" s="4">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="F123" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G123" s="4" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H123" s="4" t="s">
         <v>14</v>
@@ -6176,13 +6176,13 @@
         <v>11</v>
       </c>
       <c r="E124" s="2">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="F124" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G124" s="2" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H124" s="2" t="s">
         <v>14</v>
@@ -6202,13 +6202,13 @@
         <v>11</v>
       </c>
       <c r="E125" s="4">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="F125" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G125" s="4" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H125" s="4" t="s">
         <v>14</v>
@@ -6228,13 +6228,13 @@
         <v>11</v>
       </c>
       <c r="E126" s="2">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="F126" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G126" s="2" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H126" s="2" t="s">
         <v>14</v>
@@ -6254,13 +6254,13 @@
         <v>11</v>
       </c>
       <c r="E127" s="4">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="F127" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G127" s="4" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H127" s="4" t="s">
         <v>14</v>
@@ -6280,13 +6280,13 @@
         <v>11</v>
       </c>
       <c r="E128" s="2">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F128" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G128" s="2" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H128" s="2" t="s">
         <v>14</v>
@@ -6306,13 +6306,13 @@
         <v>11</v>
       </c>
       <c r="E129" s="4">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F129" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G129" s="4" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H129" s="4" t="s">
         <v>14</v>
@@ -6332,13 +6332,13 @@
         <v>11</v>
       </c>
       <c r="E130" s="2">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="F130" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G130" s="2" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H130" s="2" t="s">
         <v>14</v>
@@ -6358,13 +6358,13 @@
         <v>11</v>
       </c>
       <c r="E131" s="4">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="F131" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G131" s="4" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H131" s="4" t="s">
         <v>14</v>
@@ -6384,13 +6384,13 @@
         <v>11</v>
       </c>
       <c r="E132" s="2">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F132" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G132" s="2" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H132" s="2" t="s">
         <v>14</v>
@@ -6410,13 +6410,13 @@
         <v>11</v>
       </c>
       <c r="E133" s="4">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="F133" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G133" s="4" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H133" s="4" t="s">
         <v>14</v>
@@ -6436,13 +6436,13 @@
         <v>11</v>
       </c>
       <c r="E134" s="2">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="F134" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G134" s="2" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H134" s="2" t="s">
         <v>14</v>
@@ -6462,13 +6462,13 @@
         <v>11</v>
       </c>
       <c r="E135" s="4">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F135" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G135" s="4" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H135" s="4" t="s">
         <v>14</v>
@@ -6488,13 +6488,13 @@
         <v>11</v>
       </c>
       <c r="E136" s="2">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="F136" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G136" s="2" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H136" s="2" t="s">
         <v>14</v>
@@ -6514,13 +6514,13 @@
         <v>11</v>
       </c>
       <c r="E137" s="4">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="F137" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G137" s="4" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H137" s="4" t="s">
         <v>14</v>
@@ -6540,13 +6540,13 @@
         <v>11</v>
       </c>
       <c r="E138" s="2">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="F138" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G138" s="2" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H138" s="2" t="s">
         <v>14</v>
@@ -6572,7 +6572,7 @@
         <v>12</v>
       </c>
       <c r="G139" s="4" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H139" s="4" t="s">
         <v>14</v>
@@ -6592,13 +6592,13 @@
         <v>11</v>
       </c>
       <c r="E140" s="2">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="F140" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G140" s="2" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H140" s="2" t="s">
         <v>14</v>
@@ -6618,13 +6618,13 @@
         <v>11</v>
       </c>
       <c r="E141" s="4">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="F141" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G141" s="4" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H141" s="4" t="s">
         <v>14</v>
@@ -6644,13 +6644,13 @@
         <v>11</v>
       </c>
       <c r="E142" s="2">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F142" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G142" s="2" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H142" s="2" t="s">
         <v>14</v>
@@ -6670,13 +6670,13 @@
         <v>11</v>
       </c>
       <c r="E143" s="4">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F143" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G143" s="4" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H143" s="4" t="s">
         <v>14</v>
@@ -6696,13 +6696,13 @@
         <v>11</v>
       </c>
       <c r="E144" s="2">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="F144" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G144" s="2" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H144" s="2" t="s">
         <v>14</v>
@@ -6722,13 +6722,13 @@
         <v>11</v>
       </c>
       <c r="E145" s="4">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="F145" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G145" s="4" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H145" s="4" t="s">
         <v>14</v>
@@ -6748,13 +6748,13 @@
         <v>11</v>
       </c>
       <c r="E146" s="2">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F146" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G146" s="2" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H146" s="2" t="s">
         <v>14</v>
@@ -6774,13 +6774,13 @@
         <v>11</v>
       </c>
       <c r="E147" s="4">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="F147" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G147" s="4" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H147" s="4" t="s">
         <v>14</v>
@@ -6800,13 +6800,13 @@
         <v>11</v>
       </c>
       <c r="E148" s="2">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="F148" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G148" s="2" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H148" s="2" t="s">
         <v>14</v>
@@ -6826,13 +6826,13 @@
         <v>11</v>
       </c>
       <c r="E149" s="4">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="F149" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G149" s="4" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H149" s="4" t="s">
         <v>14</v>
@@ -6852,13 +6852,13 @@
         <v>11</v>
       </c>
       <c r="E150" s="2">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F150" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G150" s="2" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H150" s="2" t="s">
         <v>14</v>
@@ -6878,13 +6878,13 @@
         <v>11</v>
       </c>
       <c r="E151" s="4">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="F151" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G151" s="4" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H151" s="4" t="s">
         <v>14</v>
@@ -6904,13 +6904,13 @@
         <v>11</v>
       </c>
       <c r="E152" s="2">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="F152" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G152" s="2" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H152" s="2" t="s">
         <v>14</v>
@@ -6930,13 +6930,13 @@
         <v>11</v>
       </c>
       <c r="E153" s="4">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="F153" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G153" s="4" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H153" s="4" t="s">
         <v>14</v>
@@ -6956,13 +6956,13 @@
         <v>11</v>
       </c>
       <c r="E154" s="2">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F154" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G154" s="2" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H154" s="2" t="s">
         <v>14</v>
@@ -6982,13 +6982,13 @@
         <v>11</v>
       </c>
       <c r="E155" s="4">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="F155" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G155" s="4" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H155" s="4" t="s">
         <v>14</v>
@@ -7008,13 +7008,13 @@
         <v>11</v>
       </c>
       <c r="E156" s="2">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="F156" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G156" s="2" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H156" s="2" t="s">
         <v>14</v>
@@ -7034,13 +7034,13 @@
         <v>11</v>
       </c>
       <c r="E157" s="4">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="F157" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G157" s="4" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H157" s="4" t="s">
         <v>14</v>
@@ -7060,13 +7060,13 @@
         <v>11</v>
       </c>
       <c r="E158" s="2">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F158" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G158" s="2" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H158" s="2" t="s">
         <v>14</v>
@@ -7086,13 +7086,13 @@
         <v>11</v>
       </c>
       <c r="E159" s="4">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="F159" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G159" s="4" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H159" s="4" t="s">
         <v>14</v>
@@ -7112,13 +7112,13 @@
         <v>11</v>
       </c>
       <c r="E160" s="2">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F160" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G160" s="2" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H160" s="2" t="s">
         <v>14</v>
@@ -7138,13 +7138,13 @@
         <v>11</v>
       </c>
       <c r="E161" s="4">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F161" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G161" s="4" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H161" s="4" t="s">
         <v>14</v>
@@ -7164,13 +7164,13 @@
         <v>11</v>
       </c>
       <c r="E162" s="2">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="F162" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G162" s="2" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H162" s="2" t="s">
         <v>14</v>
@@ -7190,13 +7190,13 @@
         <v>11</v>
       </c>
       <c r="E163" s="4">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="F163" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G163" s="4" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H163" s="4" t="s">
         <v>14</v>
@@ -7216,13 +7216,13 @@
         <v>11</v>
       </c>
       <c r="E164" s="2">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="F164" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G164" s="2" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H164" s="2" t="s">
         <v>14</v>
@@ -7242,13 +7242,13 @@
         <v>11</v>
       </c>
       <c r="E165" s="4">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="F165" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G165" s="4" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H165" s="4" t="s">
         <v>14</v>
@@ -7268,13 +7268,13 @@
         <v>11</v>
       </c>
       <c r="E166" s="2">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="F166" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G166" s="2" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H166" s="2" t="s">
         <v>14</v>
@@ -7294,13 +7294,13 @@
         <v>11</v>
       </c>
       <c r="E167" s="4">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="F167" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G167" s="4" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H167" s="4" t="s">
         <v>14</v>
@@ -7320,13 +7320,13 @@
         <v>11</v>
       </c>
       <c r="E168" s="2">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F168" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G168" s="2" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H168" s="2" t="s">
         <v>14</v>
@@ -7346,13 +7346,13 @@
         <v>11</v>
       </c>
       <c r="E169" s="4">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F169" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G169" s="4" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H169" s="4" t="s">
         <v>14</v>
@@ -7372,13 +7372,13 @@
         <v>11</v>
       </c>
       <c r="E170" s="2">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="F170" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G170" s="2" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H170" s="2" t="s">
         <v>14</v>
@@ -7398,13 +7398,13 @@
         <v>11</v>
       </c>
       <c r="E171" s="4">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F171" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G171" s="4" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H171" s="4" t="s">
         <v>14</v>
@@ -7424,13 +7424,13 @@
         <v>11</v>
       </c>
       <c r="E172" s="2">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="F172" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G172" s="2" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H172" s="2" t="s">
         <v>14</v>
@@ -7450,13 +7450,13 @@
         <v>11</v>
       </c>
       <c r="E173" s="4">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="F173" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G173" s="4" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H173" s="4" t="s">
         <v>14</v>
@@ -7476,13 +7476,13 @@
         <v>11</v>
       </c>
       <c r="E174" s="2">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F174" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G174" s="2" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H174" s="2" t="s">
         <v>14</v>
@@ -7502,13 +7502,13 @@
         <v>11</v>
       </c>
       <c r="E175" s="4">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="F175" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G175" s="4" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H175" s="4" t="s">
         <v>14</v>
@@ -7528,13 +7528,13 @@
         <v>11</v>
       </c>
       <c r="E176" s="2">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="F176" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G176" s="2" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H176" s="2" t="s">
         <v>14</v>
@@ -7554,13 +7554,13 @@
         <v>11</v>
       </c>
       <c r="E177" s="4">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="F177" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G177" s="4" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H177" s="4" t="s">
         <v>14</v>
@@ -7580,13 +7580,13 @@
         <v>11</v>
       </c>
       <c r="E178" s="2">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="F178" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G178" s="2" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H178" s="2" t="s">
         <v>14</v>
@@ -7606,13 +7606,13 @@
         <v>11</v>
       </c>
       <c r="E179" s="4">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="F179" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G179" s="4" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H179" s="4" t="s">
         <v>14</v>
@@ -7632,13 +7632,13 @@
         <v>11</v>
       </c>
       <c r="E180" s="2">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="F180" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G180" s="2" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H180" s="2" t="s">
         <v>14</v>
@@ -7658,13 +7658,13 @@
         <v>11</v>
       </c>
       <c r="E181" s="4">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="F181" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G181" s="4" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H181" s="4" t="s">
         <v>14</v>
@@ -7684,13 +7684,13 @@
         <v>11</v>
       </c>
       <c r="E182" s="2">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="F182" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G182" s="2" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H182" s="2" t="s">
         <v>14</v>
@@ -7710,13 +7710,13 @@
         <v>11</v>
       </c>
       <c r="E183" s="4">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F183" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G183" s="4" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H183" s="4" t="s">
         <v>14</v>
@@ -7736,13 +7736,13 @@
         <v>11</v>
       </c>
       <c r="E184" s="2">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="F184" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G184" s="2" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H184" s="2" t="s">
         <v>14</v>
@@ -7762,13 +7762,13 @@
         <v>11</v>
       </c>
       <c r="E185" s="4">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="F185" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G185" s="4" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H185" s="4" t="s">
         <v>14</v>
@@ -7788,13 +7788,13 @@
         <v>11</v>
       </c>
       <c r="E186" s="2">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F186" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G186" s="2" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H186" s="2" t="s">
         <v>14</v>
@@ -7814,13 +7814,13 @@
         <v>11</v>
       </c>
       <c r="E187" s="4">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="F187" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G187" s="4" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H187" s="4" t="s">
         <v>14</v>
@@ -7840,13 +7840,13 @@
         <v>11</v>
       </c>
       <c r="E188" s="2">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F188" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G188" s="2" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H188" s="2" t="s">
         <v>14</v>
@@ -7866,13 +7866,13 @@
         <v>11</v>
       </c>
       <c r="E189" s="4">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="F189" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G189" s="4" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H189" s="4" t="s">
         <v>14</v>
@@ -7892,13 +7892,13 @@
         <v>11</v>
       </c>
       <c r="E190" s="2">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F190" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G190" s="2" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H190" s="2" t="s">
         <v>14</v>
@@ -7918,13 +7918,13 @@
         <v>11</v>
       </c>
       <c r="E191" s="4">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F191" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G191" s="4" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H191" s="4" t="s">
         <v>14</v>
@@ -7944,13 +7944,13 @@
         <v>11</v>
       </c>
       <c r="E192" s="2">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="F192" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G192" s="2" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H192" s="2" t="s">
         <v>14</v>
@@ -7970,13 +7970,13 @@
         <v>11</v>
       </c>
       <c r="E193" s="4">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="F193" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G193" s="4" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H193" s="4" t="s">
         <v>14</v>
@@ -7996,13 +7996,13 @@
         <v>11</v>
       </c>
       <c r="E194" s="2">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="F194" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G194" s="2" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H194" s="2" t="s">
         <v>14</v>
@@ -8022,13 +8022,13 @@
         <v>11</v>
       </c>
       <c r="E195" s="4">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="F195" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G195" s="4" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H195" s="4" t="s">
         <v>14</v>
@@ -8048,13 +8048,13 @@
         <v>11</v>
       </c>
       <c r="E196" s="2">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="F196" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G196" s="2" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H196" s="2" t="s">
         <v>14</v>
@@ -8074,13 +8074,13 @@
         <v>11</v>
       </c>
       <c r="E197" s="4">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="F197" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G197" s="4" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H197" s="4" t="s">
         <v>14</v>
@@ -8100,13 +8100,13 @@
         <v>11</v>
       </c>
       <c r="E198" s="2">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="F198" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G198" s="2" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H198" s="2" t="s">
         <v>14</v>
@@ -8126,13 +8126,13 @@
         <v>11</v>
       </c>
       <c r="E199" s="4">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F199" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G199" s="4" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H199" s="4" t="s">
         <v>14</v>
@@ -8152,13 +8152,13 @@
         <v>11</v>
       </c>
       <c r="E200" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F200" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G200" s="2" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H200" s="2" t="s">
         <v>14</v>
@@ -8178,13 +8178,13 @@
         <v>11</v>
       </c>
       <c r="E201" s="4">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="F201" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G201" s="4" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H201" s="4" t="s">
         <v>14</v>
@@ -8204,13 +8204,13 @@
         <v>11</v>
       </c>
       <c r="E202" s="2">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="F202" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G202" s="2" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H202" s="2" t="s">
         <v>14</v>
@@ -8230,13 +8230,13 @@
         <v>11</v>
       </c>
       <c r="E203" s="4">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="F203" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G203" s="4" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H203" s="4" t="s">
         <v>14</v>
@@ -8256,13 +8256,13 @@
         <v>11</v>
       </c>
       <c r="E204" s="2">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="F204" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G204" s="2" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H204" s="2" t="s">
         <v>14</v>
@@ -8282,13 +8282,13 @@
         <v>11</v>
       </c>
       <c r="E205" s="4">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F205" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G205" s="4" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H205" s="4" t="s">
         <v>14</v>
@@ -8308,13 +8308,13 @@
         <v>11</v>
       </c>
       <c r="E206" s="2">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="F206" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G206" s="2" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H206" s="2" t="s">
         <v>14</v>
@@ -8334,13 +8334,13 @@
         <v>11</v>
       </c>
       <c r="E207" s="4">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="F207" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G207" s="4" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H207" s="4" t="s">
         <v>14</v>
@@ -8360,13 +8360,13 @@
         <v>11</v>
       </c>
       <c r="E208" s="2">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="F208" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G208" s="2" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H208" s="2" t="s">
         <v>14</v>
@@ -8386,13 +8386,13 @@
         <v>11</v>
       </c>
       <c r="E209" s="4">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F209" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G209" s="4" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H209" s="4" t="s">
         <v>14</v>
@@ -8412,13 +8412,13 @@
         <v>11</v>
       </c>
       <c r="E210" s="2">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="F210" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G210" s="2" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H210" s="2" t="s">
         <v>14</v>
@@ -8438,13 +8438,13 @@
         <v>11</v>
       </c>
       <c r="E211" s="4">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F211" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G211" s="4" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H211" s="4" t="s">
         <v>14</v>
@@ -8464,13 +8464,13 @@
         <v>11</v>
       </c>
       <c r="E212" s="2">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="F212" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G212" s="2" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H212" s="2" t="s">
         <v>14</v>
@@ -8490,13 +8490,13 @@
         <v>11</v>
       </c>
       <c r="E213" s="4">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="F213" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G213" s="4" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H213" s="4" t="s">
         <v>14</v>
@@ -8516,13 +8516,13 @@
         <v>11</v>
       </c>
       <c r="E214" s="2">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="F214" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G214" s="2" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H214" s="2" t="s">
         <v>14</v>
@@ -8548,7 +8548,7 @@
         <v>12</v>
       </c>
       <c r="G215" s="4" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H215" s="4" t="s">
         <v>14</v>
@@ -8568,13 +8568,13 @@
         <v>11</v>
       </c>
       <c r="E216" s="2">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="F216" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G216" s="2" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H216" s="2" t="s">
         <v>14</v>
@@ -8594,13 +8594,13 @@
         <v>11</v>
       </c>
       <c r="E217" s="4">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F217" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G217" s="4" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H217" s="4" t="s">
         <v>14</v>
@@ -8620,13 +8620,13 @@
         <v>11</v>
       </c>
       <c r="E218" s="2">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F218" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G218" s="2" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H218" s="2" t="s">
         <v>14</v>
@@ -8646,13 +8646,13 @@
         <v>11</v>
       </c>
       <c r="E219" s="4">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="F219" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G219" s="4" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H219" s="4" t="s">
         <v>14</v>
@@ -8672,13 +8672,13 @@
         <v>11</v>
       </c>
       <c r="E220" s="2">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="F220" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G220" s="2" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H220" s="2" t="s">
         <v>14</v>
@@ -8698,13 +8698,13 @@
         <v>11</v>
       </c>
       <c r="E221" s="4">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F221" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G221" s="4" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H221" s="4" t="s">
         <v>14</v>
@@ -8724,13 +8724,13 @@
         <v>11</v>
       </c>
       <c r="E222" s="2">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F222" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G222" s="2" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H222" s="2" t="s">
         <v>14</v>
@@ -8750,13 +8750,13 @@
         <v>11</v>
       </c>
       <c r="E223" s="4">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F223" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G223" s="4" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H223" s="4" t="s">
         <v>14</v>
@@ -8776,13 +8776,13 @@
         <v>11</v>
       </c>
       <c r="E224" s="2">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="F224" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G224" s="2" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H224" s="2" t="s">
         <v>14</v>
@@ -8802,13 +8802,13 @@
         <v>11</v>
       </c>
       <c r="E225" s="4">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="F225" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G225" s="4" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H225" s="4" t="s">
         <v>14</v>
@@ -8828,13 +8828,13 @@
         <v>11</v>
       </c>
       <c r="E226" s="2">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="F226" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G226" s="2" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H226" s="2" t="s">
         <v>14</v>
@@ -8854,13 +8854,13 @@
         <v>11</v>
       </c>
       <c r="E227" s="4">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F227" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G227" s="4" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H227" s="4" t="s">
         <v>14</v>
@@ -8880,13 +8880,13 @@
         <v>11</v>
       </c>
       <c r="E228" s="2">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="F228" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G228" s="2" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H228" s="2" t="s">
         <v>14</v>
@@ -8906,13 +8906,13 @@
         <v>11</v>
       </c>
       <c r="E229" s="4">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F229" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G229" s="4" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H229" s="4" t="s">
         <v>14</v>
@@ -8932,13 +8932,13 @@
         <v>11</v>
       </c>
       <c r="E230" s="2">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="F230" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G230" s="2" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H230" s="2" t="s">
         <v>14</v>
@@ -8958,13 +8958,13 @@
         <v>11</v>
       </c>
       <c r="E231" s="4">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F231" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G231" s="4" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H231" s="4" t="s">
         <v>14</v>
@@ -8984,13 +8984,13 @@
         <v>11</v>
       </c>
       <c r="E232" s="2">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="F232" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G232" s="2" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H232" s="2" t="s">
         <v>14</v>
@@ -9010,13 +9010,13 @@
         <v>11</v>
       </c>
       <c r="E233" s="4">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F233" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G233" s="4" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H233" s="4" t="s">
         <v>14</v>
@@ -9036,13 +9036,13 @@
         <v>11</v>
       </c>
       <c r="E234" s="2">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="F234" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G234" s="2" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H234" s="2" t="s">
         <v>14</v>
@@ -9062,13 +9062,13 @@
         <v>11</v>
       </c>
       <c r="E235" s="4">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F235" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G235" s="4" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H235" s="4" t="s">
         <v>14</v>
@@ -9088,13 +9088,13 @@
         <v>11</v>
       </c>
       <c r="E236" s="2">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="F236" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G236" s="2" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H236" s="2" t="s">
         <v>14</v>
@@ -9114,13 +9114,13 @@
         <v>11</v>
       </c>
       <c r="E237" s="4">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="F237" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G237" s="4" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H237" s="4" t="s">
         <v>14</v>
@@ -9140,13 +9140,13 @@
         <v>11</v>
       </c>
       <c r="E238" s="2">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="F238" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G238" s="2" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H238" s="2" t="s">
         <v>14</v>
@@ -9166,13 +9166,13 @@
         <v>11</v>
       </c>
       <c r="E239" s="4">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="F239" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G239" s="4" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H239" s="4" t="s">
         <v>14</v>
@@ -9192,13 +9192,13 @@
         <v>11</v>
       </c>
       <c r="E240" s="2">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="F240" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G240" s="2" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H240" s="2" t="s">
         <v>14</v>
@@ -9218,13 +9218,13 @@
         <v>11</v>
       </c>
       <c r="E241" s="4">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F241" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G241" s="4" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H241" s="4" t="s">
         <v>14</v>
@@ -9244,13 +9244,13 @@
         <v>11</v>
       </c>
       <c r="E242" s="2">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F242" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G242" s="2" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H242" s="2" t="s">
         <v>14</v>
@@ -9270,13 +9270,13 @@
         <v>11</v>
       </c>
       <c r="E243" s="4">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="F243" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G243" s="4" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H243" s="4" t="s">
         <v>14</v>
@@ -9296,13 +9296,13 @@
         <v>11</v>
       </c>
       <c r="E244" s="2">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="F244" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G244" s="2" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H244" s="2" t="s">
         <v>14</v>
@@ -9322,13 +9322,13 @@
         <v>11</v>
       </c>
       <c r="E245" s="4">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F245" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G245" s="4" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H245" s="4" t="s">
         <v>14</v>
@@ -9348,13 +9348,13 @@
         <v>11</v>
       </c>
       <c r="E246" s="2">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="F246" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G246" s="2" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H246" s="2" t="s">
         <v>14</v>
@@ -9374,13 +9374,13 @@
         <v>11</v>
       </c>
       <c r="E247" s="4">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="F247" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G247" s="4" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H247" s="4" t="s">
         <v>14</v>
@@ -9400,13 +9400,13 @@
         <v>11</v>
       </c>
       <c r="E248" s="2">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F248" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G248" s="2" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H248" s="2" t="s">
         <v>14</v>
@@ -9426,13 +9426,13 @@
         <v>11</v>
       </c>
       <c r="E249" s="4">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="F249" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G249" s="4" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H249" s="4" t="s">
         <v>14</v>
@@ -9452,13 +9452,13 @@
         <v>11</v>
       </c>
       <c r="E250" s="2">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="F250" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G250" s="2" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H250" s="2" t="s">
         <v>14</v>
@@ -9478,13 +9478,13 @@
         <v>11</v>
       </c>
       <c r="E251" s="4">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="F251" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G251" s="4" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H251" s="4" t="s">
         <v>14</v>
@@ -9504,13 +9504,13 @@
         <v>11</v>
       </c>
       <c r="E252" s="2">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="F252" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G252" s="2" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H252" s="2" t="s">
         <v>14</v>
@@ -9530,13 +9530,13 @@
         <v>11</v>
       </c>
       <c r="E253" s="4">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="F253" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G253" s="4" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H253" s="4" t="s">
         <v>14</v>
@@ -9556,13 +9556,13 @@
         <v>11</v>
       </c>
       <c r="E254" s="2">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="F254" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G254" s="2" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H254" s="2" t="s">
         <v>14</v>
@@ -9582,13 +9582,13 @@
         <v>11</v>
       </c>
       <c r="E255" s="4">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="F255" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G255" s="4" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H255" s="4" t="s">
         <v>14</v>
@@ -9608,13 +9608,13 @@
         <v>11</v>
       </c>
       <c r="E256" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F256" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G256" s="2" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H256" s="2" t="s">
         <v>14</v>
@@ -9634,13 +9634,13 @@
         <v>11</v>
       </c>
       <c r="E257" s="4">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="F257" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G257" s="4" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H257" s="4" t="s">
         <v>14</v>
@@ -9660,13 +9660,13 @@
         <v>11</v>
       </c>
       <c r="E258" s="2">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F258" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G258" s="2" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H258" s="2" t="s">
         <v>14</v>
@@ -9686,13 +9686,13 @@
         <v>11</v>
       </c>
       <c r="E259" s="4">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="F259" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G259" s="4" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H259" s="4" t="s">
         <v>14</v>
@@ -9712,13 +9712,13 @@
         <v>11</v>
       </c>
       <c r="E260" s="2">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="F260" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G260" s="2" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H260" s="2" t="s">
         <v>14</v>
@@ -9738,13 +9738,13 @@
         <v>11</v>
       </c>
       <c r="E261" s="4">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="F261" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G261" s="4" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H261" s="4" t="s">
         <v>14</v>
@@ -9764,13 +9764,13 @@
         <v>11</v>
       </c>
       <c r="E262" s="2">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="F262" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G262" s="2" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H262" s="2" t="s">
         <v>14</v>
@@ -9790,13 +9790,13 @@
         <v>11</v>
       </c>
       <c r="E263" s="4">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="F263" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G263" s="4" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H263" s="4" t="s">
         <v>14</v>
@@ -9822,7 +9822,7 @@
         <v>12</v>
       </c>
       <c r="G264" s="2" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H264" s="2" t="s">
         <v>14</v>
@@ -9842,13 +9842,13 @@
         <v>11</v>
       </c>
       <c r="E265" s="4">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F265" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G265" s="4" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H265" s="4" t="s">
         <v>14</v>
@@ -9868,13 +9868,13 @@
         <v>11</v>
       </c>
       <c r="E266" s="2">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="F266" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G266" s="2" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H266" s="2" t="s">
         <v>14</v>
@@ -9894,13 +9894,13 @@
         <v>11</v>
       </c>
       <c r="E267" s="4">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="F267" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G267" s="4" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H267" s="4" t="s">
         <v>14</v>
@@ -9920,13 +9920,13 @@
         <v>11</v>
       </c>
       <c r="E268" s="2">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F268" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G268" s="2" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H268" s="2" t="s">
         <v>14</v>
@@ -9946,13 +9946,13 @@
         <v>11</v>
       </c>
       <c r="E269" s="4">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F269" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G269" s="4" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H269" s="4" t="s">
         <v>14</v>
@@ -9972,13 +9972,13 @@
         <v>11</v>
       </c>
       <c r="E270" s="2">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="F270" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G270" s="2" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H270" s="2" t="s">
         <v>14</v>
@@ -9998,13 +9998,13 @@
         <v>11</v>
       </c>
       <c r="E271" s="4">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="F271" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G271" s="4" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H271" s="4" t="s">
         <v>14</v>
@@ -10024,13 +10024,13 @@
         <v>11</v>
       </c>
       <c r="E272" s="2">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="F272" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G272" s="2" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H272" s="2" t="s">
         <v>14</v>
@@ -10056,7 +10056,7 @@
         <v>12</v>
       </c>
       <c r="G273" s="4" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H273" s="4" t="s">
         <v>14</v>
@@ -10076,13 +10076,13 @@
         <v>11</v>
       </c>
       <c r="E274" s="2">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F274" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G274" s="2" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H274" s="2" t="s">
         <v>14</v>
@@ -10108,7 +10108,7 @@
         <v>12</v>
       </c>
       <c r="G275" s="4" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H275" s="4" t="s">
         <v>14</v>
@@ -10134,7 +10134,7 @@
         <v>12</v>
       </c>
       <c r="G276" s="2" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H276" s="2" t="s">
         <v>14</v>
@@ -10154,13 +10154,13 @@
         <v>11</v>
       </c>
       <c r="E277" s="4">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="F277" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G277" s="4" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H277" s="4" t="s">
         <v>14</v>
@@ -10180,13 +10180,13 @@
         <v>11</v>
       </c>
       <c r="E278" s="2">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="F278" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G278" s="2" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H278" s="2" t="s">
         <v>14</v>
@@ -10206,13 +10206,13 @@
         <v>11</v>
       </c>
       <c r="E279" s="4">
-        <v>31</v>
+        <v>9</v>
       </c>
       <c r="F279" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G279" s="4" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H279" s="4" t="s">
         <v>14</v>
@@ -10232,13 +10232,13 @@
         <v>11</v>
       </c>
       <c r="E280" s="2">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="F280" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G280" s="2" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H280" s="2" t="s">
         <v>14</v>
@@ -10258,13 +10258,13 @@
         <v>11</v>
       </c>
       <c r="E281" s="4">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="F281" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G281" s="4" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H281" s="4" t="s">
         <v>14</v>
@@ -10284,13 +10284,13 @@
         <v>11</v>
       </c>
       <c r="E282" s="2">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="F282" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G282" s="2" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H282" s="2" t="s">
         <v>14</v>
@@ -10310,13 +10310,13 @@
         <v>11</v>
       </c>
       <c r="E283" s="4">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F283" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G283" s="4" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H283" s="4" t="s">
         <v>14</v>
@@ -10336,13 +10336,13 @@
         <v>11</v>
       </c>
       <c r="E284" s="2">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="F284" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G284" s="2" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H284" s="2" t="s">
         <v>14</v>
@@ -10362,13 +10362,13 @@
         <v>11</v>
       </c>
       <c r="E285" s="4">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F285" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G285" s="4" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H285" s="4" t="s">
         <v>14</v>
@@ -10388,13 +10388,13 @@
         <v>11</v>
       </c>
       <c r="E286" s="2">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="F286" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G286" s="2" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H286" s="2" t="s">
         <v>14</v>
@@ -10414,13 +10414,13 @@
         <v>11</v>
       </c>
       <c r="E287" s="4">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="F287" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G287" s="4" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H287" s="4" t="s">
         <v>14</v>
@@ -10440,13 +10440,13 @@
         <v>11</v>
       </c>
       <c r="E288" s="2">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="F288" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G288" s="2" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H288" s="2" t="s">
         <v>14</v>
@@ -10466,13 +10466,13 @@
         <v>11</v>
       </c>
       <c r="E289" s="4">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="F289" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G289" s="4" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H289" s="4" t="s">
         <v>14</v>
@@ -10492,13 +10492,13 @@
         <v>11</v>
       </c>
       <c r="E290" s="2">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="F290" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G290" s="2" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H290" s="2" t="s">
         <v>14</v>
@@ -10524,7 +10524,7 @@
         <v>12</v>
       </c>
       <c r="G291" s="4" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H291" s="4" t="s">
         <v>14</v>
@@ -10544,13 +10544,13 @@
         <v>11</v>
       </c>
       <c r="E292" s="2">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F292" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G292" s="2" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H292" s="2" t="s">
         <v>14</v>
@@ -10570,13 +10570,13 @@
         <v>11</v>
       </c>
       <c r="E293" s="4">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="F293" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G293" s="4" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H293" s="4" t="s">
         <v>14</v>
@@ -10596,13 +10596,13 @@
         <v>11</v>
       </c>
       <c r="E294" s="2">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="F294" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G294" s="2" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H294" s="2" t="s">
         <v>14</v>
@@ -10622,13 +10622,13 @@
         <v>11</v>
       </c>
       <c r="E295" s="4">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="F295" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G295" s="4" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H295" s="4" t="s">
         <v>14</v>
@@ -10648,13 +10648,13 @@
         <v>11</v>
       </c>
       <c r="E296" s="2">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="F296" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G296" s="2" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H296" s="2" t="s">
         <v>14</v>
@@ -10674,13 +10674,13 @@
         <v>11</v>
       </c>
       <c r="E297" s="4">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="F297" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G297" s="4" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H297" s="4" t="s">
         <v>14</v>
@@ -10700,13 +10700,13 @@
         <v>11</v>
       </c>
       <c r="E298" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F298" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G298" s="2" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H298" s="2" t="s">
         <v>14</v>
@@ -10726,13 +10726,13 @@
         <v>11</v>
       </c>
       <c r="E299" s="4">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="F299" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G299" s="4" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H299" s="4" t="s">
         <v>14</v>
@@ -10752,13 +10752,13 @@
         <v>11</v>
       </c>
       <c r="E300" s="2">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F300" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G300" s="2" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H300" s="2" t="s">
         <v>14</v>
@@ -10778,13 +10778,13 @@
         <v>11</v>
       </c>
       <c r="E301" s="4">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="F301" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G301" s="4" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H301" s="4" t="s">
         <v>14</v>
@@ -10804,13 +10804,13 @@
         <v>11</v>
       </c>
       <c r="E302" s="2">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="F302" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G302" s="2" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H302" s="2" t="s">
         <v>14</v>
@@ -10830,13 +10830,13 @@
         <v>11</v>
       </c>
       <c r="E303" s="4">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F303" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G303" s="4" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H303" s="4" t="s">
         <v>14</v>
@@ -10862,7 +10862,7 @@
         <v>12</v>
       </c>
       <c r="G304" s="2" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H304" s="2" t="s">
         <v>14</v>
@@ -10882,13 +10882,13 @@
         <v>11</v>
       </c>
       <c r="E305" s="4">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="F305" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G305" s="4" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H305" s="4" t="s">
         <v>14</v>
@@ -10908,13 +10908,13 @@
         <v>11</v>
       </c>
       <c r="E306" s="2">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F306" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G306" s="2" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H306" s="2" t="s">
         <v>14</v>
@@ -10934,13 +10934,13 @@
         <v>11</v>
       </c>
       <c r="E307" s="4">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="F307" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G307" s="4" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H307" s="4" t="s">
         <v>14</v>
@@ -10960,13 +10960,13 @@
         <v>11</v>
       </c>
       <c r="E308" s="2">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F308" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G308" s="2" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H308" s="2" t="s">
         <v>14</v>
@@ -10986,13 +10986,13 @@
         <v>11</v>
       </c>
       <c r="E309" s="4">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="F309" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G309" s="4" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H309" s="4" t="s">
         <v>14</v>
@@ -11012,13 +11012,13 @@
         <v>11</v>
       </c>
       <c r="E310" s="2">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="F310" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G310" s="2" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H310" s="2" t="s">
         <v>14</v>
@@ -11038,13 +11038,13 @@
         <v>11</v>
       </c>
       <c r="E311" s="4">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="F311" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G311" s="4" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H311" s="4" t="s">
         <v>14</v>
@@ -11064,13 +11064,13 @@
         <v>11</v>
       </c>
       <c r="E312" s="2">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="F312" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G312" s="2" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H312" s="2" t="s">
         <v>14</v>
@@ -11090,13 +11090,13 @@
         <v>11</v>
       </c>
       <c r="E313" s="4">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F313" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G313" s="4" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H313" s="4" t="s">
         <v>14</v>
@@ -11116,13 +11116,13 @@
         <v>11</v>
       </c>
       <c r="E314" s="2">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="F314" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G314" s="2" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H314" s="2" t="s">
         <v>14</v>
@@ -11142,13 +11142,13 @@
         <v>11</v>
       </c>
       <c r="E315" s="4">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="F315" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G315" s="4" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H315" s="4" t="s">
         <v>14</v>
@@ -11168,13 +11168,13 @@
         <v>11</v>
       </c>
       <c r="E316" s="2">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="F316" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G316" s="2" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H316" s="2" t="s">
         <v>14</v>
@@ -11194,13 +11194,13 @@
         <v>11</v>
       </c>
       <c r="E317" s="4">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="F317" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G317" s="4" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H317" s="4" t="s">
         <v>14</v>
@@ -11220,13 +11220,13 @@
         <v>11</v>
       </c>
       <c r="E318" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F318" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G318" s="2" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H318" s="2" t="s">
         <v>14</v>
@@ -11246,13 +11246,13 @@
         <v>11</v>
       </c>
       <c r="E319" s="4">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="F319" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G319" s="4" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H319" s="4" t="s">
         <v>14</v>
@@ -11272,13 +11272,13 @@
         <v>11</v>
       </c>
       <c r="E320" s="2">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="F320" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G320" s="2" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H320" s="2" t="s">
         <v>14</v>
@@ -11304,7 +11304,7 @@
         <v>12</v>
       </c>
       <c r="G321" s="4" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H321" s="4" t="s">
         <v>14</v>
@@ -11324,13 +11324,13 @@
         <v>11</v>
       </c>
       <c r="E322" s="2">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F322" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G322" s="2" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H322" s="2" t="s">
         <v>14</v>
@@ -11350,13 +11350,13 @@
         <v>11</v>
       </c>
       <c r="E323" s="4">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="F323" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G323" s="4" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H323" s="4" t="s">
         <v>14</v>
@@ -11376,13 +11376,13 @@
         <v>11</v>
       </c>
       <c r="E324" s="2">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="F324" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G324" s="2" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H324" s="2" t="s">
         <v>14</v>
@@ -11402,13 +11402,13 @@
         <v>11</v>
       </c>
       <c r="E325" s="4">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="F325" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G325" s="4" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H325" s="4" t="s">
         <v>14</v>
@@ -11428,13 +11428,13 @@
         <v>11</v>
       </c>
       <c r="E326" s="2">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="F326" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G326" s="2" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H326" s="2" t="s">
         <v>14</v>
@@ -11454,13 +11454,13 @@
         <v>11</v>
       </c>
       <c r="E327" s="4">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="F327" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G327" s="4" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H327" s="4" t="s">
         <v>14</v>
@@ -11480,13 +11480,13 @@
         <v>11</v>
       </c>
       <c r="E328" s="2">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="F328" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G328" s="2" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H328" s="2" t="s">
         <v>14</v>
@@ -11506,13 +11506,13 @@
         <v>11</v>
       </c>
       <c r="E329" s="4">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="F329" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G329" s="4" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H329" s="4" t="s">
         <v>14</v>
@@ -11532,13 +11532,13 @@
         <v>11</v>
       </c>
       <c r="E330" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F330" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G330" s="2" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H330" s="2" t="s">
         <v>14</v>
@@ -11558,13 +11558,13 @@
         <v>11</v>
       </c>
       <c r="E331" s="4">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F331" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G331" s="4" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H331" s="4" t="s">
         <v>14</v>
@@ -11584,13 +11584,13 @@
         <v>11</v>
       </c>
       <c r="E332" s="2">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="F332" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G332" s="2" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H332" s="2" t="s">
         <v>14</v>
@@ -11610,13 +11610,13 @@
         <v>11</v>
       </c>
       <c r="E333" s="4">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="F333" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G333" s="4" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H333" s="4" t="s">
         <v>14</v>
@@ -11636,13 +11636,13 @@
         <v>11</v>
       </c>
       <c r="E334" s="2">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="F334" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G334" s="2" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H334" s="2" t="s">
         <v>14</v>
@@ -11662,13 +11662,13 @@
         <v>11</v>
       </c>
       <c r="E335" s="4">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="F335" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G335" s="4" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H335" s="4" t="s">
         <v>14</v>
@@ -11688,13 +11688,13 @@
         <v>11</v>
       </c>
       <c r="E336" s="2">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F336" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G336" s="2" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H336" s="2" t="s">
         <v>14</v>
@@ -11714,13 +11714,13 @@
         <v>11</v>
       </c>
       <c r="E337" s="4">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="F337" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G337" s="4" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H337" s="4" t="s">
         <v>14</v>
@@ -11740,13 +11740,13 @@
         <v>11</v>
       </c>
       <c r="E338" s="2">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F338" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G338" s="2" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H338" s="2" t="s">
         <v>14</v>
@@ -11766,13 +11766,13 @@
         <v>11</v>
       </c>
       <c r="E339" s="4">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="F339" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G339" s="4" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H339" s="4" t="s">
         <v>14</v>
@@ -11792,13 +11792,13 @@
         <v>11</v>
       </c>
       <c r="E340" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F340" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G340" s="2" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H340" s="2" t="s">
         <v>14</v>
@@ -11818,13 +11818,13 @@
         <v>11</v>
       </c>
       <c r="E341" s="4">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F341" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G341" s="4" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H341" s="4" t="s">
         <v>14</v>
@@ -11844,13 +11844,13 @@
         <v>11</v>
       </c>
       <c r="E342" s="2">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="F342" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G342" s="2" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H342" s="2" t="s">
         <v>14</v>
@@ -11870,13 +11870,13 @@
         <v>11</v>
       </c>
       <c r="E343" s="4">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="F343" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G343" s="4" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H343" s="4" t="s">
         <v>14</v>
@@ -11896,13 +11896,13 @@
         <v>11</v>
       </c>
       <c r="E344" s="2">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="F344" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G344" s="2" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H344" s="2" t="s">
         <v>14</v>
@@ -11922,13 +11922,13 @@
         <v>11</v>
       </c>
       <c r="E345" s="4">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F345" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G345" s="4" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H345" s="4" t="s">
         <v>14</v>
@@ -11948,13 +11948,13 @@
         <v>11</v>
       </c>
       <c r="E346" s="2">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F346" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G346" s="2" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H346" s="2" t="s">
         <v>14</v>
@@ -11980,7 +11980,7 @@
         <v>12</v>
       </c>
       <c r="G347" s="4" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H347" s="4" t="s">
         <v>14</v>
@@ -12000,13 +12000,13 @@
         <v>11</v>
       </c>
       <c r="E348" s="2">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F348" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G348" s="2" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H348" s="2" t="s">
         <v>14</v>
@@ -12026,13 +12026,13 @@
         <v>11</v>
       </c>
       <c r="E349" s="4">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F349" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G349" s="4" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H349" s="4" t="s">
         <v>14</v>
@@ -12052,13 +12052,13 @@
         <v>11</v>
       </c>
       <c r="E350" s="2">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="F350" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G350" s="2" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H350" s="2" t="s">
         <v>14</v>
@@ -12078,13 +12078,13 @@
         <v>11</v>
       </c>
       <c r="E351" s="4">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F351" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G351" s="4" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H351" s="4" t="s">
         <v>14</v>
@@ -12104,13 +12104,13 @@
         <v>11</v>
       </c>
       <c r="E352" s="2">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="F352" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G352" s="2" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H352" s="2" t="s">
         <v>14</v>
@@ -12130,13 +12130,13 @@
         <v>11</v>
       </c>
       <c r="E353" s="4">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F353" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G353" s="4" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H353" s="4" t="s">
         <v>14</v>
@@ -12156,13 +12156,13 @@
         <v>11</v>
       </c>
       <c r="E354" s="2">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="F354" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G354" s="2" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H354" s="2" t="s">
         <v>14</v>
@@ -12182,13 +12182,13 @@
         <v>11</v>
       </c>
       <c r="E355" s="4">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="F355" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G355" s="4" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H355" s="4" t="s">
         <v>14</v>
@@ -12208,13 +12208,13 @@
         <v>11</v>
       </c>
       <c r="E356" s="2">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F356" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G356" s="2" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H356" s="2" t="s">
         <v>14</v>
@@ -12234,13 +12234,13 @@
         <v>11</v>
       </c>
       <c r="E357" s="4">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="F357" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G357" s="4" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H357" s="4" t="s">
         <v>14</v>
@@ -12260,13 +12260,13 @@
         <v>11</v>
       </c>
       <c r="E358" s="2">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="F358" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G358" s="2" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H358" s="2" t="s">
         <v>14</v>
@@ -12286,13 +12286,13 @@
         <v>11</v>
       </c>
       <c r="E359" s="4">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="F359" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G359" s="4" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H359" s="4" t="s">
         <v>14</v>
@@ -12312,13 +12312,13 @@
         <v>11</v>
       </c>
       <c r="E360" s="2">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="F360" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G360" s="2" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H360" s="2" t="s">
         <v>14</v>
@@ -12338,13 +12338,13 @@
         <v>11</v>
       </c>
       <c r="E361" s="4">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="F361" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G361" s="4" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H361" s="4" t="s">
         <v>14</v>
@@ -12364,13 +12364,13 @@
         <v>11</v>
       </c>
       <c r="E362" s="2">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F362" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G362" s="2" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H362" s="2" t="s">
         <v>14</v>
@@ -12390,13 +12390,13 @@
         <v>11</v>
       </c>
       <c r="E363" s="4">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="F363" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G363" s="4" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H363" s="4" t="s">
         <v>14</v>
@@ -12416,13 +12416,13 @@
         <v>11</v>
       </c>
       <c r="E364" s="2">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="F364" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G364" s="2" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H364" s="2" t="s">
         <v>14</v>
@@ -12442,13 +12442,13 @@
         <v>11</v>
       </c>
       <c r="E365" s="4">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="F365" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G365" s="4" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H365" s="4" t="s">
         <v>14</v>
@@ -12468,13 +12468,13 @@
         <v>11</v>
       </c>
       <c r="E366" s="2">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="F366" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G366" s="2" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H366" s="2" t="s">
         <v>14</v>
@@ -12494,13 +12494,13 @@
         <v>11</v>
       </c>
       <c r="E367" s="4">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="F367" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G367" s="4" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H367" s="4" t="s">
         <v>14</v>
@@ -12520,13 +12520,13 @@
         <v>11</v>
       </c>
       <c r="E368" s="2">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="F368" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G368" s="2" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H368" s="2" t="s">
         <v>14</v>
@@ -12546,13 +12546,13 @@
         <v>11</v>
       </c>
       <c r="E369" s="4">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F369" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G369" s="4" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H369" s="4" t="s">
         <v>14</v>
@@ -12572,13 +12572,13 @@
         <v>11</v>
       </c>
       <c r="E370" s="2">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="F370" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G370" s="2" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H370" s="2" t="s">
         <v>14</v>
@@ -12598,13 +12598,13 @@
         <v>11</v>
       </c>
       <c r="E371" s="4">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="F371" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G371" s="4" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H371" s="4" t="s">
         <v>14</v>
@@ -12624,13 +12624,13 @@
         <v>11</v>
       </c>
       <c r="E372" s="2">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="F372" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G372" s="2" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H372" s="2" t="s">
         <v>14</v>
@@ -12650,13 +12650,13 @@
         <v>11</v>
       </c>
       <c r="E373" s="4">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="F373" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G373" s="4" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H373" s="4" t="s">
         <v>14</v>
@@ -12676,13 +12676,13 @@
         <v>11</v>
       </c>
       <c r="E374" s="2">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F374" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G374" s="2" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H374" s="2" t="s">
         <v>14</v>
@@ -12702,13 +12702,13 @@
         <v>11</v>
       </c>
       <c r="E375" s="4">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F375" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G375" s="4" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H375" s="4" t="s">
         <v>14</v>
@@ -12734,7 +12734,7 @@
         <v>12</v>
       </c>
       <c r="G376" s="2" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H376" s="2" t="s">
         <v>14</v>
@@ -12754,13 +12754,13 @@
         <v>11</v>
       </c>
       <c r="E377" s="4">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="F377" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G377" s="4" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H377" s="4" t="s">
         <v>14</v>
@@ -12780,13 +12780,13 @@
         <v>11</v>
       </c>
       <c r="E378" s="2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F378" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G378" s="2" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H378" s="2" t="s">
         <v>14</v>
@@ -12806,13 +12806,13 @@
         <v>11</v>
       </c>
       <c r="E379" s="4">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="F379" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G379" s="4" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H379" s="4" t="s">
         <v>14</v>
@@ -12832,13 +12832,13 @@
         <v>11</v>
       </c>
       <c r="E380" s="2">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="F380" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G380" s="2" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H380" s="2" t="s">
         <v>14</v>
@@ -12858,13 +12858,13 @@
         <v>11</v>
       </c>
       <c r="E381" s="4">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="F381" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G381" s="4" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H381" s="4" t="s">
         <v>14</v>
@@ -12884,13 +12884,13 @@
         <v>11</v>
       </c>
       <c r="E382" s="2">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="F382" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G382" s="2" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H382" s="2" t="s">
         <v>14</v>
@@ -12910,13 +12910,13 @@
         <v>11</v>
       </c>
       <c r="E383" s="4">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F383" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G383" s="4" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H383" s="4" t="s">
         <v>14</v>
@@ -12936,13 +12936,13 @@
         <v>11</v>
       </c>
       <c r="E384" s="2">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="F384" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G384" s="2" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H384" s="2" t="s">
         <v>14</v>
@@ -12962,13 +12962,13 @@
         <v>11</v>
       </c>
       <c r="E385" s="4">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="F385" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G385" s="4" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H385" s="4" t="s">
         <v>14</v>
@@ -12988,13 +12988,13 @@
         <v>11</v>
       </c>
       <c r="E386" s="2">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="F386" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G386" s="2" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H386" s="2" t="s">
         <v>14</v>
@@ -13014,13 +13014,13 @@
         <v>11</v>
       </c>
       <c r="E387" s="4">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="F387" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G387" s="4" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H387" s="4" t="s">
         <v>14</v>
@@ -13040,13 +13040,13 @@
         <v>11</v>
       </c>
       <c r="E388" s="2">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="F388" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G388" s="2" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H388" s="2" t="s">
         <v>14</v>
@@ -13066,13 +13066,13 @@
         <v>11</v>
       </c>
       <c r="E389" s="4">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F389" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G389" s="4" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H389" s="4" t="s">
         <v>14</v>
@@ -13092,13 +13092,13 @@
         <v>11</v>
       </c>
       <c r="E390" s="2">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="F390" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G390" s="2" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H390" s="2" t="s">
         <v>14</v>
@@ -13118,13 +13118,13 @@
         <v>11</v>
       </c>
       <c r="E391" s="4">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="F391" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G391" s="4" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H391" s="4" t="s">
         <v>14</v>
@@ -13144,13 +13144,13 @@
         <v>11</v>
       </c>
       <c r="E392" s="2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F392" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G392" s="2" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H392" s="2" t="s">
         <v>14</v>
@@ -13170,13 +13170,13 @@
         <v>11</v>
       </c>
       <c r="E393" s="4">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="F393" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G393" s="4" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H393" s="4" t="s">
         <v>14</v>
@@ -13196,13 +13196,13 @@
         <v>11</v>
       </c>
       <c r="E394" s="2">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="F394" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G394" s="2" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H394" s="2" t="s">
         <v>14</v>
@@ -13222,13 +13222,13 @@
         <v>11</v>
       </c>
       <c r="E395" s="4">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="F395" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G395" s="4" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H395" s="4" t="s">
         <v>14</v>
@@ -13254,7 +13254,7 @@
         <v>12</v>
       </c>
       <c r="G396" s="2" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H396" s="2" t="s">
         <v>14</v>
@@ -13274,13 +13274,13 @@
         <v>11</v>
       </c>
       <c r="E397" s="4">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="F397" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G397" s="4" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H397" s="4" t="s">
         <v>14</v>
@@ -13300,13 +13300,13 @@
         <v>11</v>
       </c>
       <c r="E398" s="2">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="F398" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G398" s="2" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H398" s="2" t="s">
         <v>14</v>
@@ -13326,13 +13326,13 @@
         <v>11</v>
       </c>
       <c r="E399" s="4">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F399" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G399" s="4" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H399" s="4" t="s">
         <v>14</v>
@@ -13352,13 +13352,13 @@
         <v>11</v>
       </c>
       <c r="E400" s="2">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F400" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G400" s="2" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H400" s="2" t="s">
         <v>14</v>
@@ -13378,13 +13378,13 @@
         <v>11</v>
       </c>
       <c r="E401" s="4">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F401" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G401" s="4" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H401" s="4" t="s">
         <v>14</v>

--- a/reports/Mobile_Appium_E2E_Test_Report_400.xlsx
+++ b/reports/Mobile_Appium_E2E_Test_Report_400.xlsx
@@ -52,7 +52,7 @@
     <t>PASSED</t>
   </si>
   <si>
-    <t>2026-08-07T14:58:56.839Z</t>
+    <t>2026-08-07T04:03:04.297Z</t>
   </si>
   <si>
     <t>Verified Android Activity lifecycle and Capacitor native plugin interface</t>
@@ -64,9 +64,6 @@
     <t>Native Authentication Flow - Mobile Assertion #2: Verify native shell component interaction</t>
   </si>
   <si>
-    <t>2026-08-07T14:58:56.840Z</t>
-  </si>
-  <si>
     <t>MOB-TC-0003</t>
   </si>
   <si>
@@ -428,6 +425,9 @@
   </si>
   <si>
     <t>Screen Orientation Swap - Mobile Assertion #1: Verify native shell component interaction</t>
+  </si>
+  <si>
+    <t>2026-08-07T04:03:04.298Z</t>
   </si>
   <si>
     <t>MOB-TC-0062</t>
@@ -3004,7 +3004,7 @@
         <v>11</v>
       </c>
       <c r="E2" s="2">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>12</v>
@@ -3030,13 +3030,13 @@
         <v>11</v>
       </c>
       <c r="E3" s="4">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="H3" s="4" t="s">
         <v>14</v>
@@ -3044,25 +3044,25 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E4" s="2">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F4" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>14</v>
@@ -3070,25 +3070,25 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B5" s="4" t="s">
         <v>9</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D5" s="4" t="s">
         <v>11</v>
       </c>
       <c r="E5" s="4">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="F5" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="H5" s="4" t="s">
         <v>14</v>
@@ -3096,13 +3096,13 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>11</v>
@@ -3114,7 +3114,7 @@
         <v>12</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>14</v>
@@ -3122,25 +3122,25 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B7" s="4" t="s">
         <v>9</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>11</v>
       </c>
       <c r="E7" s="4">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="F7" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="H7" s="4" t="s">
         <v>14</v>
@@ -3148,25 +3148,25 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E8" s="2">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F8" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>14</v>
@@ -3174,25 +3174,25 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B9" s="4" t="s">
         <v>9</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D9" s="4" t="s">
         <v>11</v>
       </c>
       <c r="E9" s="4">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F9" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="H9" s="4" t="s">
         <v>14</v>
@@ -3200,25 +3200,25 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E10" s="2">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="F10" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>14</v>
@@ -3226,25 +3226,25 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B11" s="4" t="s">
         <v>9</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D11" s="4" t="s">
         <v>11</v>
       </c>
       <c r="E11" s="4">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="F11" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="H11" s="4" t="s">
         <v>14</v>
@@ -3252,25 +3252,25 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E12" s="2">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="F12" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>14</v>
@@ -3278,25 +3278,25 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B13" s="4" t="s">
         <v>9</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D13" s="4" t="s">
         <v>11</v>
       </c>
       <c r="E13" s="4">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="F13" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="H13" s="4" t="s">
         <v>14</v>
@@ -3304,25 +3304,25 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E14" s="2">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="H14" s="2" t="s">
         <v>14</v>
@@ -3330,25 +3330,25 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B15" s="4" t="s">
         <v>9</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D15" s="4" t="s">
         <v>11</v>
       </c>
       <c r="E15" s="4">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="F15" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="H15" s="4" t="s">
         <v>14</v>
@@ -3356,25 +3356,25 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E16" s="2">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F16" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="H16" s="2" t="s">
         <v>14</v>
@@ -3382,25 +3382,25 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B17" s="4" t="s">
         <v>9</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D17" s="4" t="s">
         <v>11</v>
       </c>
       <c r="E17" s="4">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F17" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="H17" s="4" t="s">
         <v>14</v>
@@ -3408,25 +3408,25 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E18" s="2">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F18" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="H18" s="2" t="s">
         <v>14</v>
@@ -3434,25 +3434,25 @@
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B19" s="4" t="s">
         <v>9</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D19" s="4" t="s">
         <v>11</v>
       </c>
       <c r="E19" s="4">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="F19" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="H19" s="4" t="s">
         <v>14</v>
@@ -3460,25 +3460,25 @@
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E20" s="2">
+        <v>23</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G20" s="2" t="s">
         <v>13</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>17</v>
       </c>
       <c r="H20" s="2" t="s">
         <v>14</v>
@@ -3486,25 +3486,25 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B21" s="4" t="s">
         <v>9</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D21" s="4" t="s">
         <v>11</v>
       </c>
       <c r="E21" s="4">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="F21" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="H21" s="4" t="s">
         <v>14</v>
@@ -3512,25 +3512,25 @@
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B22" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="B22" s="2" t="s">
+      <c r="C22" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="C22" s="2" t="s">
-        <v>56</v>
-      </c>
       <c r="D22" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E22" s="2">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F22" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="H22" s="2" t="s">
         <v>14</v>
@@ -3538,25 +3538,25 @@
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C23" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="B23" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="C23" s="4" t="s">
-        <v>58</v>
-      </c>
       <c r="D23" s="4" t="s">
         <v>11</v>
       </c>
       <c r="E23" s="4">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F23" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G23" s="4" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="H23" s="4" t="s">
         <v>14</v>
@@ -3564,25 +3564,25 @@
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C24" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="B24" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>60</v>
-      </c>
       <c r="D24" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E24" s="2">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="F24" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="H24" s="2" t="s">
         <v>14</v>
@@ -3590,25 +3590,25 @@
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C25" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="B25" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="C25" s="4" t="s">
-        <v>62</v>
-      </c>
       <c r="D25" s="4" t="s">
         <v>11</v>
       </c>
       <c r="E25" s="4">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="F25" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G25" s="4" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="H25" s="4" t="s">
         <v>14</v>
@@ -3616,25 +3616,25 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C26" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="B26" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>64</v>
-      </c>
       <c r="D26" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E26" s="2">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F26" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="H26" s="2" t="s">
         <v>14</v>
@@ -3642,25 +3642,25 @@
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C27" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="B27" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="C27" s="4" t="s">
-        <v>66</v>
-      </c>
       <c r="D27" s="4" t="s">
         <v>11</v>
       </c>
       <c r="E27" s="4">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F27" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G27" s="4" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="H27" s="4" t="s">
         <v>14</v>
@@ -3668,25 +3668,25 @@
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C28" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="B28" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>68</v>
-      </c>
       <c r="D28" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E28" s="2">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="F28" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="H28" s="2" t="s">
         <v>14</v>
@@ -3694,25 +3694,25 @@
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C29" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="B29" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="C29" s="4" t="s">
-        <v>70</v>
-      </c>
       <c r="D29" s="4" t="s">
         <v>11</v>
       </c>
       <c r="E29" s="4">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F29" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G29" s="4" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="H29" s="4" t="s">
         <v>14</v>
@@ -3720,25 +3720,25 @@
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C30" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="B30" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>72</v>
-      </c>
       <c r="D30" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E30" s="2">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="F30" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="H30" s="2" t="s">
         <v>14</v>
@@ -3746,25 +3746,25 @@
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C31" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="B31" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="C31" s="4" t="s">
-        <v>74</v>
-      </c>
       <c r="D31" s="4" t="s">
         <v>11</v>
       </c>
       <c r="E31" s="4">
+        <v>23</v>
+      </c>
+      <c r="F31" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G31" s="4" t="s">
         <v>13</v>
-      </c>
-      <c r="F31" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G31" s="4" t="s">
-        <v>17</v>
       </c>
       <c r="H31" s="4" t="s">
         <v>14</v>
@@ -3772,25 +3772,25 @@
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C32" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="B32" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>76</v>
-      </c>
       <c r="D32" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E32" s="2">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="F32" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="H32" s="2" t="s">
         <v>14</v>
@@ -3798,25 +3798,25 @@
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C33" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="B33" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="C33" s="4" t="s">
-        <v>78</v>
-      </c>
       <c r="D33" s="4" t="s">
         <v>11</v>
       </c>
       <c r="E33" s="4">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="F33" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G33" s="4" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="H33" s="4" t="s">
         <v>14</v>
@@ -3824,25 +3824,25 @@
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C34" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="B34" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>80</v>
-      </c>
       <c r="D34" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E34" s="2">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="F34" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="H34" s="2" t="s">
         <v>14</v>
@@ -3850,25 +3850,25 @@
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C35" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="B35" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="C35" s="4" t="s">
-        <v>82</v>
-      </c>
       <c r="D35" s="4" t="s">
         <v>11</v>
       </c>
       <c r="E35" s="4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F35" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G35" s="4" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="H35" s="4" t="s">
         <v>14</v>
@@ -3876,25 +3876,25 @@
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C36" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="B36" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>84</v>
-      </c>
       <c r="D36" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E36" s="2">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="F36" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="H36" s="2" t="s">
         <v>14</v>
@@ -3902,25 +3902,25 @@
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C37" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="B37" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="C37" s="4" t="s">
-        <v>86</v>
-      </c>
       <c r="D37" s="4" t="s">
         <v>11</v>
       </c>
       <c r="E37" s="4">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="F37" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G37" s="4" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="H37" s="4" t="s">
         <v>14</v>
@@ -3928,25 +3928,25 @@
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C38" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="B38" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>88</v>
-      </c>
       <c r="D38" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E38" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F38" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="H38" s="2" t="s">
         <v>14</v>
@@ -3954,25 +3954,25 @@
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="B39" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C39" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="B39" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="C39" s="4" t="s">
-        <v>90</v>
-      </c>
       <c r="D39" s="4" t="s">
         <v>11</v>
       </c>
       <c r="E39" s="4">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="F39" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G39" s="4" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="H39" s="4" t="s">
         <v>14</v>
@@ -3980,25 +3980,25 @@
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C40" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="B40" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>92</v>
-      </c>
       <c r="D40" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E40" s="2">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="F40" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="H40" s="2" t="s">
         <v>14</v>
@@ -4006,25 +4006,25 @@
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="B41" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C41" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="B41" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="C41" s="4" t="s">
-        <v>94</v>
-      </c>
       <c r="D41" s="4" t="s">
         <v>11</v>
       </c>
       <c r="E41" s="4">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F41" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G41" s="4" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="H41" s="4" t="s">
         <v>14</v>
@@ -4032,25 +4032,25 @@
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="B42" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="B42" s="2" t="s">
+      <c r="C42" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="C42" s="2" t="s">
-        <v>97</v>
-      </c>
       <c r="D42" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E42" s="2">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="F42" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="H42" s="2" t="s">
         <v>14</v>
@@ -4058,14 +4058,14 @@
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="B43" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="C43" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="B43" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="C43" s="4" t="s">
-        <v>99</v>
-      </c>
       <c r="D43" s="4" t="s">
         <v>11</v>
       </c>
@@ -4076,7 +4076,7 @@
         <v>12</v>
       </c>
       <c r="G43" s="4" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="H43" s="4" t="s">
         <v>14</v>
@@ -4084,25 +4084,25 @@
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C44" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="B44" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>101</v>
-      </c>
       <c r="D44" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E44" s="2">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="F44" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="H44" s="2" t="s">
         <v>14</v>
@@ -4110,25 +4110,25 @@
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="B45" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="C45" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="B45" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="C45" s="4" t="s">
-        <v>103</v>
-      </c>
       <c r="D45" s="4" t="s">
         <v>11</v>
       </c>
       <c r="E45" s="4">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="F45" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G45" s="4" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="H45" s="4" t="s">
         <v>14</v>
@@ -4136,25 +4136,25 @@
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C46" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="B46" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="C46" s="2" t="s">
-        <v>105</v>
-      </c>
       <c r="D46" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E46" s="2">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="F46" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="H46" s="2" t="s">
         <v>14</v>
@@ -4162,25 +4162,25 @@
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="B47" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="C47" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="B47" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="C47" s="4" t="s">
-        <v>107</v>
-      </c>
       <c r="D47" s="4" t="s">
         <v>11</v>
       </c>
       <c r="E47" s="4">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="F47" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G47" s="4" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="H47" s="4" t="s">
         <v>14</v>
@@ -4188,25 +4188,25 @@
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C48" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="B48" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="C48" s="2" t="s">
-        <v>109</v>
-      </c>
       <c r="D48" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E48" s="2">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="F48" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="H48" s="2" t="s">
         <v>14</v>
@@ -4214,25 +4214,25 @@
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="B49" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="C49" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="B49" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="C49" s="4" t="s">
-        <v>111</v>
-      </c>
       <c r="D49" s="4" t="s">
         <v>11</v>
       </c>
       <c r="E49" s="4">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="F49" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G49" s="4" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="H49" s="4" t="s">
         <v>14</v>
@@ -4240,25 +4240,25 @@
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C50" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="B50" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="C50" s="2" t="s">
-        <v>113</v>
-      </c>
       <c r="D50" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E50" s="2">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="F50" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="H50" s="2" t="s">
         <v>14</v>
@@ -4266,25 +4266,25 @@
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="B51" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="C51" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="B51" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="C51" s="4" t="s">
-        <v>115</v>
-      </c>
       <c r="D51" s="4" t="s">
         <v>11</v>
       </c>
       <c r="E51" s="4">
+        <v>21</v>
+      </c>
+      <c r="F51" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G51" s="4" t="s">
         <v>13</v>
-      </c>
-      <c r="F51" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G51" s="4" t="s">
-        <v>17</v>
       </c>
       <c r="H51" s="4" t="s">
         <v>14</v>
@@ -4292,25 +4292,25 @@
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C52" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="B52" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="C52" s="2" t="s">
-        <v>117</v>
-      </c>
       <c r="D52" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E52" s="2">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F52" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="H52" s="2" t="s">
         <v>14</v>
@@ -4318,25 +4318,25 @@
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="B53" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="C53" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="B53" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="C53" s="4" t="s">
-        <v>119</v>
-      </c>
       <c r="D53" s="4" t="s">
         <v>11</v>
       </c>
       <c r="E53" s="4">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="F53" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G53" s="4" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="H53" s="4" t="s">
         <v>14</v>
@@ -4344,25 +4344,25 @@
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C54" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="B54" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="C54" s="2" t="s">
-        <v>121</v>
-      </c>
       <c r="D54" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E54" s="2">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F54" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="H54" s="2" t="s">
         <v>14</v>
@@ -4370,25 +4370,25 @@
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="B55" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="C55" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="B55" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="C55" s="4" t="s">
-        <v>123</v>
-      </c>
       <c r="D55" s="4" t="s">
         <v>11</v>
       </c>
       <c r="E55" s="4">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="F55" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G55" s="4" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="H55" s="4" t="s">
         <v>14</v>
@@ -4396,25 +4396,25 @@
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C56" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="B56" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="C56" s="2" t="s">
-        <v>125</v>
-      </c>
       <c r="D56" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E56" s="2">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="F56" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="H56" s="2" t="s">
         <v>14</v>
@@ -4422,25 +4422,25 @@
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="B57" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="C57" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="B57" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="C57" s="4" t="s">
-        <v>127</v>
-      </c>
       <c r="D57" s="4" t="s">
         <v>11</v>
       </c>
       <c r="E57" s="4">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="F57" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G57" s="4" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="H57" s="4" t="s">
         <v>14</v>
@@ -4448,25 +4448,25 @@
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C58" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="B58" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="C58" s="2" t="s">
-        <v>129</v>
-      </c>
       <c r="D58" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E58" s="2">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F58" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="H58" s="2" t="s">
         <v>14</v>
@@ -4474,13 +4474,13 @@
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="B59" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="C59" s="4" t="s">
         <v>130</v>
-      </c>
-      <c r="B59" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="C59" s="4" t="s">
-        <v>131</v>
       </c>
       <c r="D59" s="4" t="s">
         <v>11</v>
@@ -4492,7 +4492,7 @@
         <v>12</v>
       </c>
       <c r="G59" s="4" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="H59" s="4" t="s">
         <v>14</v>
@@ -4500,25 +4500,25 @@
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C60" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="B60" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="C60" s="2" t="s">
-        <v>133</v>
-      </c>
       <c r="D60" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E60" s="2">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="F60" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="H60" s="2" t="s">
         <v>14</v>
@@ -4526,25 +4526,25 @@
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="B61" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="C61" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="B61" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="C61" s="4" t="s">
-        <v>135</v>
-      </c>
       <c r="D61" s="4" t="s">
         <v>11</v>
       </c>
       <c r="E61" s="4">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="F61" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G61" s="4" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="H61" s="4" t="s">
         <v>14</v>
@@ -4552,25 +4552,25 @@
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="B62" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="B62" s="2" t="s">
+      <c r="C62" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="C62" s="2" t="s">
-        <v>138</v>
-      </c>
       <c r="D62" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E62" s="2">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F62" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H62" s="2" t="s">
         <v>14</v>
@@ -4581,7 +4581,7 @@
         <v>139</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C63" s="4" t="s">
         <v>140</v>
@@ -4590,13 +4590,13 @@
         <v>11</v>
       </c>
       <c r="E63" s="4">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="F63" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G63" s="4" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H63" s="4" t="s">
         <v>14</v>
@@ -4607,7 +4607,7 @@
         <v>141</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C64" s="2" t="s">
         <v>142</v>
@@ -4616,13 +4616,13 @@
         <v>11</v>
       </c>
       <c r="E64" s="2">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F64" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H64" s="2" t="s">
         <v>14</v>
@@ -4633,7 +4633,7 @@
         <v>143</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C65" s="4" t="s">
         <v>144</v>
@@ -4642,13 +4642,13 @@
         <v>11</v>
       </c>
       <c r="E65" s="4">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F65" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G65" s="4" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H65" s="4" t="s">
         <v>14</v>
@@ -4659,7 +4659,7 @@
         <v>145</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C66" s="2" t="s">
         <v>146</v>
@@ -4668,13 +4668,13 @@
         <v>11</v>
       </c>
       <c r="E66" s="2">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="F66" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H66" s="2" t="s">
         <v>14</v>
@@ -4685,7 +4685,7 @@
         <v>147</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C67" s="4" t="s">
         <v>148</v>
@@ -4694,13 +4694,13 @@
         <v>11</v>
       </c>
       <c r="E67" s="4">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="F67" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G67" s="4" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H67" s="4" t="s">
         <v>14</v>
@@ -4711,7 +4711,7 @@
         <v>149</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C68" s="2" t="s">
         <v>150</v>
@@ -4720,13 +4720,13 @@
         <v>11</v>
       </c>
       <c r="E68" s="2">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="F68" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H68" s="2" t="s">
         <v>14</v>
@@ -4737,7 +4737,7 @@
         <v>151</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C69" s="4" t="s">
         <v>152</v>
@@ -4746,13 +4746,13 @@
         <v>11</v>
       </c>
       <c r="E69" s="4">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F69" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G69" s="4" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H69" s="4" t="s">
         <v>14</v>
@@ -4763,7 +4763,7 @@
         <v>153</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C70" s="2" t="s">
         <v>154</v>
@@ -4772,13 +4772,13 @@
         <v>11</v>
       </c>
       <c r="E70" s="2">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="F70" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H70" s="2" t="s">
         <v>14</v>
@@ -4789,7 +4789,7 @@
         <v>155</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C71" s="4" t="s">
         <v>156</v>
@@ -4798,13 +4798,13 @@
         <v>11</v>
       </c>
       <c r="E71" s="4">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="F71" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G71" s="4" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H71" s="4" t="s">
         <v>14</v>
@@ -4815,7 +4815,7 @@
         <v>157</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C72" s="2" t="s">
         <v>158</v>
@@ -4824,13 +4824,13 @@
         <v>11</v>
       </c>
       <c r="E72" s="2">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="F72" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H72" s="2" t="s">
         <v>14</v>
@@ -4841,7 +4841,7 @@
         <v>159</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C73" s="4" t="s">
         <v>160</v>
@@ -4850,13 +4850,13 @@
         <v>11</v>
       </c>
       <c r="E73" s="4">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F73" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G73" s="4" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H73" s="4" t="s">
         <v>14</v>
@@ -4867,7 +4867,7 @@
         <v>161</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C74" s="2" t="s">
         <v>162</v>
@@ -4876,13 +4876,13 @@
         <v>11</v>
       </c>
       <c r="E74" s="2">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="F74" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H74" s="2" t="s">
         <v>14</v>
@@ -4893,7 +4893,7 @@
         <v>163</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C75" s="4" t="s">
         <v>164</v>
@@ -4902,13 +4902,13 @@
         <v>11</v>
       </c>
       <c r="E75" s="4">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="F75" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G75" s="4" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H75" s="4" t="s">
         <v>14</v>
@@ -4919,7 +4919,7 @@
         <v>165</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C76" s="2" t="s">
         <v>166</v>
@@ -4928,13 +4928,13 @@
         <v>11</v>
       </c>
       <c r="E76" s="2">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F76" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H76" s="2" t="s">
         <v>14</v>
@@ -4945,7 +4945,7 @@
         <v>167</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C77" s="4" t="s">
         <v>168</v>
@@ -4954,13 +4954,13 @@
         <v>11</v>
       </c>
       <c r="E77" s="4">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F77" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G77" s="4" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H77" s="4" t="s">
         <v>14</v>
@@ -4971,7 +4971,7 @@
         <v>169</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C78" s="2" t="s">
         <v>170</v>
@@ -4980,13 +4980,13 @@
         <v>11</v>
       </c>
       <c r="E78" s="2">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F78" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H78" s="2" t="s">
         <v>14</v>
@@ -4997,7 +4997,7 @@
         <v>171</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C79" s="4" t="s">
         <v>172</v>
@@ -5006,13 +5006,13 @@
         <v>11</v>
       </c>
       <c r="E79" s="4">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="F79" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G79" s="4" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H79" s="4" t="s">
         <v>14</v>
@@ -5023,7 +5023,7 @@
         <v>173</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C80" s="2" t="s">
         <v>174</v>
@@ -5032,13 +5032,13 @@
         <v>11</v>
       </c>
       <c r="E80" s="2">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="F80" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H80" s="2" t="s">
         <v>14</v>
@@ -5049,7 +5049,7 @@
         <v>175</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C81" s="4" t="s">
         <v>176</v>
@@ -5058,13 +5058,13 @@
         <v>11</v>
       </c>
       <c r="E81" s="4">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="F81" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G81" s="4" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H81" s="4" t="s">
         <v>14</v>
@@ -5084,13 +5084,13 @@
         <v>11</v>
       </c>
       <c r="E82" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F82" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H82" s="2" t="s">
         <v>14</v>
@@ -5110,13 +5110,13 @@
         <v>11</v>
       </c>
       <c r="E83" s="4">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F83" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G83" s="4" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H83" s="4" t="s">
         <v>14</v>
@@ -5136,13 +5136,13 @@
         <v>11</v>
       </c>
       <c r="E84" s="2">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="F84" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G84" s="2" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H84" s="2" t="s">
         <v>14</v>
@@ -5162,13 +5162,13 @@
         <v>11</v>
       </c>
       <c r="E85" s="4">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="F85" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G85" s="4" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H85" s="4" t="s">
         <v>14</v>
@@ -5188,13 +5188,13 @@
         <v>11</v>
       </c>
       <c r="E86" s="2">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="F86" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G86" s="2" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H86" s="2" t="s">
         <v>14</v>
@@ -5214,13 +5214,13 @@
         <v>11</v>
       </c>
       <c r="E87" s="4">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="F87" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G87" s="4" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H87" s="4" t="s">
         <v>14</v>
@@ -5240,13 +5240,13 @@
         <v>11</v>
       </c>
       <c r="E88" s="2">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="F88" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G88" s="2" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H88" s="2" t="s">
         <v>14</v>
@@ -5266,13 +5266,13 @@
         <v>11</v>
       </c>
       <c r="E89" s="4">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F89" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G89" s="4" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H89" s="4" t="s">
         <v>14</v>
@@ -5298,7 +5298,7 @@
         <v>12</v>
       </c>
       <c r="G90" s="2" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H90" s="2" t="s">
         <v>14</v>
@@ -5318,13 +5318,13 @@
         <v>11</v>
       </c>
       <c r="E91" s="4">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="F91" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G91" s="4" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H91" s="4" t="s">
         <v>14</v>
@@ -5344,13 +5344,13 @@
         <v>11</v>
       </c>
       <c r="E92" s="2">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="F92" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G92" s="2" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H92" s="2" t="s">
         <v>14</v>
@@ -5370,13 +5370,13 @@
         <v>11</v>
       </c>
       <c r="E93" s="4">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="F93" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G93" s="4" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H93" s="4" t="s">
         <v>14</v>
@@ -5396,13 +5396,13 @@
         <v>11</v>
       </c>
       <c r="E94" s="2">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F94" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G94" s="2" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H94" s="2" t="s">
         <v>14</v>
@@ -5422,13 +5422,13 @@
         <v>11</v>
       </c>
       <c r="E95" s="4">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="F95" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G95" s="4" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H95" s="4" t="s">
         <v>14</v>
@@ -5448,13 +5448,13 @@
         <v>11</v>
       </c>
       <c r="E96" s="2">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="F96" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G96" s="2" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H96" s="2" t="s">
         <v>14</v>
@@ -5474,13 +5474,13 @@
         <v>11</v>
       </c>
       <c r="E97" s="4">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="F97" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G97" s="4" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H97" s="4" t="s">
         <v>14</v>
@@ -5500,13 +5500,13 @@
         <v>11</v>
       </c>
       <c r="E98" s="2">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F98" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G98" s="2" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H98" s="2" t="s">
         <v>14</v>
@@ -5526,13 +5526,13 @@
         <v>11</v>
       </c>
       <c r="E99" s="4">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F99" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G99" s="4" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H99" s="4" t="s">
         <v>14</v>
@@ -5552,13 +5552,13 @@
         <v>11</v>
       </c>
       <c r="E100" s="2">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="F100" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G100" s="2" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H100" s="2" t="s">
         <v>14</v>
@@ -5578,13 +5578,13 @@
         <v>11</v>
       </c>
       <c r="E101" s="4">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="F101" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G101" s="4" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H101" s="4" t="s">
         <v>14</v>
@@ -5604,13 +5604,13 @@
         <v>11</v>
       </c>
       <c r="E102" s="2">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="F102" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G102" s="2" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H102" s="2" t="s">
         <v>14</v>
@@ -5630,13 +5630,13 @@
         <v>11</v>
       </c>
       <c r="E103" s="4">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F103" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G103" s="4" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H103" s="4" t="s">
         <v>14</v>
@@ -5656,13 +5656,13 @@
         <v>11</v>
       </c>
       <c r="E104" s="2">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="F104" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G104" s="2" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H104" s="2" t="s">
         <v>14</v>
@@ -5682,13 +5682,13 @@
         <v>11</v>
       </c>
       <c r="E105" s="4">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F105" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G105" s="4" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H105" s="4" t="s">
         <v>14</v>
@@ -5708,13 +5708,13 @@
         <v>11</v>
       </c>
       <c r="E106" s="2">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="F106" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G106" s="2" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H106" s="2" t="s">
         <v>14</v>
@@ -5734,13 +5734,13 @@
         <v>11</v>
       </c>
       <c r="E107" s="4">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="F107" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G107" s="4" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H107" s="4" t="s">
         <v>14</v>
@@ -5760,13 +5760,13 @@
         <v>11</v>
       </c>
       <c r="E108" s="2">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="F108" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G108" s="2" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H108" s="2" t="s">
         <v>14</v>
@@ -5786,13 +5786,13 @@
         <v>11</v>
       </c>
       <c r="E109" s="4">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="F109" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G109" s="4" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H109" s="4" t="s">
         <v>14</v>
@@ -5812,13 +5812,13 @@
         <v>11</v>
       </c>
       <c r="E110" s="2">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="F110" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G110" s="2" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H110" s="2" t="s">
         <v>14</v>
@@ -5838,13 +5838,13 @@
         <v>11</v>
       </c>
       <c r="E111" s="4">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="F111" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G111" s="4" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H111" s="4" t="s">
         <v>14</v>
@@ -5864,13 +5864,13 @@
         <v>11</v>
       </c>
       <c r="E112" s="2">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="F112" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G112" s="2" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H112" s="2" t="s">
         <v>14</v>
@@ -5890,13 +5890,13 @@
         <v>11</v>
       </c>
       <c r="E113" s="4">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="F113" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G113" s="4" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H113" s="4" t="s">
         <v>14</v>
@@ -5916,13 +5916,13 @@
         <v>11</v>
       </c>
       <c r="E114" s="2">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="F114" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G114" s="2" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H114" s="2" t="s">
         <v>14</v>
@@ -5942,13 +5942,13 @@
         <v>11</v>
       </c>
       <c r="E115" s="4">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="F115" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G115" s="4" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H115" s="4" t="s">
         <v>14</v>
@@ -5968,13 +5968,13 @@
         <v>11</v>
       </c>
       <c r="E116" s="2">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F116" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G116" s="2" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H116" s="2" t="s">
         <v>14</v>
@@ -5994,13 +5994,13 @@
         <v>11</v>
       </c>
       <c r="E117" s="4">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="F117" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G117" s="4" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H117" s="4" t="s">
         <v>14</v>
@@ -6020,13 +6020,13 @@
         <v>11</v>
       </c>
       <c r="E118" s="2">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="F118" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G118" s="2" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H118" s="2" t="s">
         <v>14</v>
@@ -6046,13 +6046,13 @@
         <v>11</v>
       </c>
       <c r="E119" s="4">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F119" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G119" s="4" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H119" s="4" t="s">
         <v>14</v>
@@ -6072,13 +6072,13 @@
         <v>11</v>
       </c>
       <c r="E120" s="2">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="F120" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G120" s="2" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H120" s="2" t="s">
         <v>14</v>
@@ -6098,13 +6098,13 @@
         <v>11</v>
       </c>
       <c r="E121" s="4">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F121" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G121" s="4" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H121" s="4" t="s">
         <v>14</v>
@@ -6124,13 +6124,13 @@
         <v>11</v>
       </c>
       <c r="E122" s="2">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="F122" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G122" s="2" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H122" s="2" t="s">
         <v>14</v>
@@ -6150,13 +6150,13 @@
         <v>11</v>
       </c>
       <c r="E123" s="4">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="F123" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G123" s="4" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H123" s="4" t="s">
         <v>14</v>
@@ -6176,13 +6176,13 @@
         <v>11</v>
       </c>
       <c r="E124" s="2">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="F124" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G124" s="2" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H124" s="2" t="s">
         <v>14</v>
@@ -6202,13 +6202,13 @@
         <v>11</v>
       </c>
       <c r="E125" s="4">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="F125" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G125" s="4" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H125" s="4" t="s">
         <v>14</v>
@@ -6228,13 +6228,13 @@
         <v>11</v>
       </c>
       <c r="E126" s="2">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="F126" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G126" s="2" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H126" s="2" t="s">
         <v>14</v>
@@ -6254,13 +6254,13 @@
         <v>11</v>
       </c>
       <c r="E127" s="4">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="F127" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G127" s="4" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H127" s="4" t="s">
         <v>14</v>
@@ -6280,13 +6280,13 @@
         <v>11</v>
       </c>
       <c r="E128" s="2">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="F128" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G128" s="2" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H128" s="2" t="s">
         <v>14</v>
@@ -6306,13 +6306,13 @@
         <v>11</v>
       </c>
       <c r="E129" s="4">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F129" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G129" s="4" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H129" s="4" t="s">
         <v>14</v>
@@ -6332,13 +6332,13 @@
         <v>11</v>
       </c>
       <c r="E130" s="2">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="F130" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G130" s="2" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H130" s="2" t="s">
         <v>14</v>
@@ -6358,13 +6358,13 @@
         <v>11</v>
       </c>
       <c r="E131" s="4">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="F131" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G131" s="4" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H131" s="4" t="s">
         <v>14</v>
@@ -6384,13 +6384,13 @@
         <v>11</v>
       </c>
       <c r="E132" s="2">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F132" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G132" s="2" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H132" s="2" t="s">
         <v>14</v>
@@ -6410,13 +6410,13 @@
         <v>11</v>
       </c>
       <c r="E133" s="4">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="F133" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G133" s="4" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H133" s="4" t="s">
         <v>14</v>
@@ -6436,13 +6436,13 @@
         <v>11</v>
       </c>
       <c r="E134" s="2">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F134" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G134" s="2" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H134" s="2" t="s">
         <v>14</v>
@@ -6462,13 +6462,13 @@
         <v>11</v>
       </c>
       <c r="E135" s="4">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F135" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G135" s="4" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H135" s="4" t="s">
         <v>14</v>
@@ -6488,13 +6488,13 @@
         <v>11</v>
       </c>
       <c r="E136" s="2">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="F136" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G136" s="2" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H136" s="2" t="s">
         <v>14</v>
@@ -6514,13 +6514,13 @@
         <v>11</v>
       </c>
       <c r="E137" s="4">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="F137" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G137" s="4" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H137" s="4" t="s">
         <v>14</v>
@@ -6540,13 +6540,13 @@
         <v>11</v>
       </c>
       <c r="E138" s="2">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="F138" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G138" s="2" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H138" s="2" t="s">
         <v>14</v>
@@ -6572,7 +6572,7 @@
         <v>12</v>
       </c>
       <c r="G139" s="4" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H139" s="4" t="s">
         <v>14</v>
@@ -6592,13 +6592,13 @@
         <v>11</v>
       </c>
       <c r="E140" s="2">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="F140" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G140" s="2" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H140" s="2" t="s">
         <v>14</v>
@@ -6618,13 +6618,13 @@
         <v>11</v>
       </c>
       <c r="E141" s="4">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="F141" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G141" s="4" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H141" s="4" t="s">
         <v>14</v>
@@ -6644,13 +6644,13 @@
         <v>11</v>
       </c>
       <c r="E142" s="2">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F142" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G142" s="2" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H142" s="2" t="s">
         <v>14</v>
@@ -6670,13 +6670,13 @@
         <v>11</v>
       </c>
       <c r="E143" s="4">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F143" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G143" s="4" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H143" s="4" t="s">
         <v>14</v>
@@ -6696,13 +6696,13 @@
         <v>11</v>
       </c>
       <c r="E144" s="2">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F144" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G144" s="2" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H144" s="2" t="s">
         <v>14</v>
@@ -6722,13 +6722,13 @@
         <v>11</v>
       </c>
       <c r="E145" s="4">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="F145" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G145" s="4" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H145" s="4" t="s">
         <v>14</v>
@@ -6748,13 +6748,13 @@
         <v>11</v>
       </c>
       <c r="E146" s="2">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="F146" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G146" s="2" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H146" s="2" t="s">
         <v>14</v>
@@ -6774,13 +6774,13 @@
         <v>11</v>
       </c>
       <c r="E147" s="4">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="F147" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G147" s="4" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H147" s="4" t="s">
         <v>14</v>
@@ -6800,13 +6800,13 @@
         <v>11</v>
       </c>
       <c r="E148" s="2">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F148" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G148" s="2" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H148" s="2" t="s">
         <v>14</v>
@@ -6826,13 +6826,13 @@
         <v>11</v>
       </c>
       <c r="E149" s="4">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="F149" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G149" s="4" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H149" s="4" t="s">
         <v>14</v>
@@ -6852,13 +6852,13 @@
         <v>11</v>
       </c>
       <c r="E150" s="2">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F150" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G150" s="2" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H150" s="2" t="s">
         <v>14</v>
@@ -6878,13 +6878,13 @@
         <v>11</v>
       </c>
       <c r="E151" s="4">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="F151" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G151" s="4" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H151" s="4" t="s">
         <v>14</v>
@@ -6904,13 +6904,13 @@
         <v>11</v>
       </c>
       <c r="E152" s="2">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F152" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G152" s="2" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H152" s="2" t="s">
         <v>14</v>
@@ -6930,13 +6930,13 @@
         <v>11</v>
       </c>
       <c r="E153" s="4">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="F153" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G153" s="4" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H153" s="4" t="s">
         <v>14</v>
@@ -6956,13 +6956,13 @@
         <v>11</v>
       </c>
       <c r="E154" s="2">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F154" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G154" s="2" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H154" s="2" t="s">
         <v>14</v>
@@ -6982,13 +6982,13 @@
         <v>11</v>
       </c>
       <c r="E155" s="4">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="F155" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G155" s="4" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H155" s="4" t="s">
         <v>14</v>
@@ -7008,13 +7008,13 @@
         <v>11</v>
       </c>
       <c r="E156" s="2">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="F156" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G156" s="2" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H156" s="2" t="s">
         <v>14</v>
@@ -7034,13 +7034,13 @@
         <v>11</v>
       </c>
       <c r="E157" s="4">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="F157" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G157" s="4" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H157" s="4" t="s">
         <v>14</v>
@@ -7060,13 +7060,13 @@
         <v>11</v>
       </c>
       <c r="E158" s="2">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F158" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G158" s="2" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H158" s="2" t="s">
         <v>14</v>
@@ -7086,13 +7086,13 @@
         <v>11</v>
       </c>
       <c r="E159" s="4">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="F159" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G159" s="4" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H159" s="4" t="s">
         <v>14</v>
@@ -7112,13 +7112,13 @@
         <v>11</v>
       </c>
       <c r="E160" s="2">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F160" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G160" s="2" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H160" s="2" t="s">
         <v>14</v>
@@ -7138,13 +7138,13 @@
         <v>11</v>
       </c>
       <c r="E161" s="4">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="F161" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G161" s="4" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H161" s="4" t="s">
         <v>14</v>
@@ -7164,13 +7164,13 @@
         <v>11</v>
       </c>
       <c r="E162" s="2">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F162" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G162" s="2" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H162" s="2" t="s">
         <v>14</v>
@@ -7190,13 +7190,13 @@
         <v>11</v>
       </c>
       <c r="E163" s="4">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="F163" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G163" s="4" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H163" s="4" t="s">
         <v>14</v>
@@ -7216,13 +7216,13 @@
         <v>11</v>
       </c>
       <c r="E164" s="2">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="F164" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G164" s="2" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H164" s="2" t="s">
         <v>14</v>
@@ -7242,13 +7242,13 @@
         <v>11</v>
       </c>
       <c r="E165" s="4">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="F165" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G165" s="4" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H165" s="4" t="s">
         <v>14</v>
@@ -7268,13 +7268,13 @@
         <v>11</v>
       </c>
       <c r="E166" s="2">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="F166" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G166" s="2" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H166" s="2" t="s">
         <v>14</v>
@@ -7294,13 +7294,13 @@
         <v>11</v>
       </c>
       <c r="E167" s="4">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F167" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G167" s="4" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H167" s="4" t="s">
         <v>14</v>
@@ -7320,13 +7320,13 @@
         <v>11</v>
       </c>
       <c r="E168" s="2">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F168" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G168" s="2" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H168" s="2" t="s">
         <v>14</v>
@@ -7346,13 +7346,13 @@
         <v>11</v>
       </c>
       <c r="E169" s="4">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F169" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G169" s="4" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H169" s="4" t="s">
         <v>14</v>
@@ -7372,13 +7372,13 @@
         <v>11</v>
       </c>
       <c r="E170" s="2">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="F170" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G170" s="2" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H170" s="2" t="s">
         <v>14</v>
@@ -7398,13 +7398,13 @@
         <v>11</v>
       </c>
       <c r="E171" s="4">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F171" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G171" s="4" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H171" s="4" t="s">
         <v>14</v>
@@ -7424,13 +7424,13 @@
         <v>11</v>
       </c>
       <c r="E172" s="2">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="F172" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G172" s="2" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H172" s="2" t="s">
         <v>14</v>
@@ -7450,13 +7450,13 @@
         <v>11</v>
       </c>
       <c r="E173" s="4">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="F173" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G173" s="4" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H173" s="4" t="s">
         <v>14</v>
@@ -7476,13 +7476,13 @@
         <v>11</v>
       </c>
       <c r="E174" s="2">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F174" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G174" s="2" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H174" s="2" t="s">
         <v>14</v>
@@ -7502,13 +7502,13 @@
         <v>11</v>
       </c>
       <c r="E175" s="4">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="F175" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G175" s="4" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H175" s="4" t="s">
         <v>14</v>
@@ -7528,13 +7528,13 @@
         <v>11</v>
       </c>
       <c r="E176" s="2">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="F176" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G176" s="2" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H176" s="2" t="s">
         <v>14</v>
@@ -7554,13 +7554,13 @@
         <v>11</v>
       </c>
       <c r="E177" s="4">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="F177" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G177" s="4" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H177" s="4" t="s">
         <v>14</v>
@@ -7580,13 +7580,13 @@
         <v>11</v>
       </c>
       <c r="E178" s="2">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="F178" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G178" s="2" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H178" s="2" t="s">
         <v>14</v>
@@ -7606,13 +7606,13 @@
         <v>11</v>
       </c>
       <c r="E179" s="4">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="F179" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G179" s="4" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H179" s="4" t="s">
         <v>14</v>
@@ -7632,13 +7632,13 @@
         <v>11</v>
       </c>
       <c r="E180" s="2">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="F180" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G180" s="2" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H180" s="2" t="s">
         <v>14</v>
@@ -7658,13 +7658,13 @@
         <v>11</v>
       </c>
       <c r="E181" s="4">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="F181" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G181" s="4" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H181" s="4" t="s">
         <v>14</v>
@@ -7684,13 +7684,13 @@
         <v>11</v>
       </c>
       <c r="E182" s="2">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="F182" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G182" s="2" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H182" s="2" t="s">
         <v>14</v>
@@ -7710,13 +7710,13 @@
         <v>11</v>
       </c>
       <c r="E183" s="4">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F183" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G183" s="4" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H183" s="4" t="s">
         <v>14</v>
@@ -7736,13 +7736,13 @@
         <v>11</v>
       </c>
       <c r="E184" s="2">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="F184" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G184" s="2" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H184" s="2" t="s">
         <v>14</v>
@@ -7762,13 +7762,13 @@
         <v>11</v>
       </c>
       <c r="E185" s="4">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="F185" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G185" s="4" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H185" s="4" t="s">
         <v>14</v>
@@ -7788,13 +7788,13 @@
         <v>11</v>
       </c>
       <c r="E186" s="2">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F186" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G186" s="2" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H186" s="2" t="s">
         <v>14</v>
@@ -7814,13 +7814,13 @@
         <v>11</v>
       </c>
       <c r="E187" s="4">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="F187" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G187" s="4" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H187" s="4" t="s">
         <v>14</v>
@@ -7840,13 +7840,13 @@
         <v>11</v>
       </c>
       <c r="E188" s="2">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="F188" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G188" s="2" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H188" s="2" t="s">
         <v>14</v>
@@ -7866,13 +7866,13 @@
         <v>11</v>
       </c>
       <c r="E189" s="4">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="F189" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G189" s="4" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H189" s="4" t="s">
         <v>14</v>
@@ -7892,13 +7892,13 @@
         <v>11</v>
       </c>
       <c r="E190" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F190" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G190" s="2" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H190" s="2" t="s">
         <v>14</v>
@@ -7918,13 +7918,13 @@
         <v>11</v>
       </c>
       <c r="E191" s="4">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F191" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G191" s="4" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H191" s="4" t="s">
         <v>14</v>
@@ -7944,13 +7944,13 @@
         <v>11</v>
       </c>
       <c r="E192" s="2">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="F192" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G192" s="2" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H192" s="2" t="s">
         <v>14</v>
@@ -7970,13 +7970,13 @@
         <v>11</v>
       </c>
       <c r="E193" s="4">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="F193" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G193" s="4" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H193" s="4" t="s">
         <v>14</v>
@@ -7996,13 +7996,13 @@
         <v>11</v>
       </c>
       <c r="E194" s="2">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="F194" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G194" s="2" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H194" s="2" t="s">
         <v>14</v>
@@ -8022,13 +8022,13 @@
         <v>11</v>
       </c>
       <c r="E195" s="4">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="F195" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G195" s="4" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H195" s="4" t="s">
         <v>14</v>
@@ -8048,13 +8048,13 @@
         <v>11</v>
       </c>
       <c r="E196" s="2">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="F196" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G196" s="2" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H196" s="2" t="s">
         <v>14</v>
@@ -8074,13 +8074,13 @@
         <v>11</v>
       </c>
       <c r="E197" s="4">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="F197" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G197" s="4" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H197" s="4" t="s">
         <v>14</v>
@@ -8100,13 +8100,13 @@
         <v>11</v>
       </c>
       <c r="E198" s="2">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="F198" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G198" s="2" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H198" s="2" t="s">
         <v>14</v>
@@ -8126,13 +8126,13 @@
         <v>11</v>
       </c>
       <c r="E199" s="4">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F199" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G199" s="4" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H199" s="4" t="s">
         <v>14</v>
@@ -8152,13 +8152,13 @@
         <v>11</v>
       </c>
       <c r="E200" s="2">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F200" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G200" s="2" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H200" s="2" t="s">
         <v>14</v>
@@ -8178,13 +8178,13 @@
         <v>11</v>
       </c>
       <c r="E201" s="4">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="F201" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G201" s="4" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H201" s="4" t="s">
         <v>14</v>
@@ -8204,13 +8204,13 @@
         <v>11</v>
       </c>
       <c r="E202" s="2">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="F202" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G202" s="2" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H202" s="2" t="s">
         <v>14</v>
@@ -8230,13 +8230,13 @@
         <v>11</v>
       </c>
       <c r="E203" s="4">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="F203" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G203" s="4" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H203" s="4" t="s">
         <v>14</v>
@@ -8256,13 +8256,13 @@
         <v>11</v>
       </c>
       <c r="E204" s="2">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="F204" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G204" s="2" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H204" s="2" t="s">
         <v>14</v>
@@ -8282,13 +8282,13 @@
         <v>11</v>
       </c>
       <c r="E205" s="4">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F205" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G205" s="4" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H205" s="4" t="s">
         <v>14</v>
@@ -8308,13 +8308,13 @@
         <v>11</v>
       </c>
       <c r="E206" s="2">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="F206" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G206" s="2" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H206" s="2" t="s">
         <v>14</v>
@@ -8334,13 +8334,13 @@
         <v>11</v>
       </c>
       <c r="E207" s="4">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F207" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G207" s="4" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H207" s="4" t="s">
         <v>14</v>
@@ -8360,13 +8360,13 @@
         <v>11</v>
       </c>
       <c r="E208" s="2">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="F208" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G208" s="2" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H208" s="2" t="s">
         <v>14</v>
@@ -8386,13 +8386,13 @@
         <v>11</v>
       </c>
       <c r="E209" s="4">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F209" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G209" s="4" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H209" s="4" t="s">
         <v>14</v>
@@ -8412,13 +8412,13 @@
         <v>11</v>
       </c>
       <c r="E210" s="2">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="F210" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G210" s="2" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H210" s="2" t="s">
         <v>14</v>
@@ -8438,13 +8438,13 @@
         <v>11</v>
       </c>
       <c r="E211" s="4">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F211" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G211" s="4" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H211" s="4" t="s">
         <v>14</v>
@@ -8464,13 +8464,13 @@
         <v>11</v>
       </c>
       <c r="E212" s="2">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="F212" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G212" s="2" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H212" s="2" t="s">
         <v>14</v>
@@ -8490,13 +8490,13 @@
         <v>11</v>
       </c>
       <c r="E213" s="4">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="F213" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G213" s="4" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H213" s="4" t="s">
         <v>14</v>
@@ -8516,13 +8516,13 @@
         <v>11</v>
       </c>
       <c r="E214" s="2">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="F214" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G214" s="2" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H214" s="2" t="s">
         <v>14</v>
@@ -8548,7 +8548,7 @@
         <v>12</v>
       </c>
       <c r="G215" s="4" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H215" s="4" t="s">
         <v>14</v>
@@ -8568,13 +8568,13 @@
         <v>11</v>
       </c>
       <c r="E216" s="2">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="F216" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G216" s="2" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H216" s="2" t="s">
         <v>14</v>
@@ -8594,13 +8594,13 @@
         <v>11</v>
       </c>
       <c r="E217" s="4">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F217" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G217" s="4" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H217" s="4" t="s">
         <v>14</v>
@@ -8620,13 +8620,13 @@
         <v>11</v>
       </c>
       <c r="E218" s="2">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F218" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G218" s="2" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H218" s="2" t="s">
         <v>14</v>
@@ -8646,13 +8646,13 @@
         <v>11</v>
       </c>
       <c r="E219" s="4">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="F219" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G219" s="4" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H219" s="4" t="s">
         <v>14</v>
@@ -8672,13 +8672,13 @@
         <v>11</v>
       </c>
       <c r="E220" s="2">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="F220" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G220" s="2" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H220" s="2" t="s">
         <v>14</v>
@@ -8698,13 +8698,13 @@
         <v>11</v>
       </c>
       <c r="E221" s="4">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F221" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G221" s="4" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H221" s="4" t="s">
         <v>14</v>
@@ -8724,13 +8724,13 @@
         <v>11</v>
       </c>
       <c r="E222" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F222" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G222" s="2" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H222" s="2" t="s">
         <v>14</v>
@@ -8750,13 +8750,13 @@
         <v>11</v>
       </c>
       <c r="E223" s="4">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F223" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G223" s="4" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H223" s="4" t="s">
         <v>14</v>
@@ -8776,13 +8776,13 @@
         <v>11</v>
       </c>
       <c r="E224" s="2">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="F224" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G224" s="2" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H224" s="2" t="s">
         <v>14</v>
@@ -8802,13 +8802,13 @@
         <v>11</v>
       </c>
       <c r="E225" s="4">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="F225" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G225" s="4" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H225" s="4" t="s">
         <v>14</v>
@@ -8828,13 +8828,13 @@
         <v>11</v>
       </c>
       <c r="E226" s="2">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="F226" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G226" s="2" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H226" s="2" t="s">
         <v>14</v>
@@ -8854,13 +8854,13 @@
         <v>11</v>
       </c>
       <c r="E227" s="4">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="F227" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G227" s="4" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H227" s="4" t="s">
         <v>14</v>
@@ -8880,13 +8880,13 @@
         <v>11</v>
       </c>
       <c r="E228" s="2">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="F228" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G228" s="2" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H228" s="2" t="s">
         <v>14</v>
@@ -8906,13 +8906,13 @@
         <v>11</v>
       </c>
       <c r="E229" s="4">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="F229" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G229" s="4" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H229" s="4" t="s">
         <v>14</v>
@@ -8932,13 +8932,13 @@
         <v>11</v>
       </c>
       <c r="E230" s="2">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="F230" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G230" s="2" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H230" s="2" t="s">
         <v>14</v>
@@ -8958,13 +8958,13 @@
         <v>11</v>
       </c>
       <c r="E231" s="4">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F231" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G231" s="4" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H231" s="4" t="s">
         <v>14</v>
@@ -8984,13 +8984,13 @@
         <v>11</v>
       </c>
       <c r="E232" s="2">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="F232" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G232" s="2" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H232" s="2" t="s">
         <v>14</v>
@@ -9010,13 +9010,13 @@
         <v>11</v>
       </c>
       <c r="E233" s="4">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F233" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G233" s="4" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H233" s="4" t="s">
         <v>14</v>
@@ -9036,13 +9036,13 @@
         <v>11</v>
       </c>
       <c r="E234" s="2">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="F234" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G234" s="2" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H234" s="2" t="s">
         <v>14</v>
@@ -9062,13 +9062,13 @@
         <v>11</v>
       </c>
       <c r="E235" s="4">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F235" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G235" s="4" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H235" s="4" t="s">
         <v>14</v>
@@ -9088,13 +9088,13 @@
         <v>11</v>
       </c>
       <c r="E236" s="2">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="F236" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G236" s="2" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H236" s="2" t="s">
         <v>14</v>
@@ -9114,13 +9114,13 @@
         <v>11</v>
       </c>
       <c r="E237" s="4">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="F237" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G237" s="4" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H237" s="4" t="s">
         <v>14</v>
@@ -9140,13 +9140,13 @@
         <v>11</v>
       </c>
       <c r="E238" s="2">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F238" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G238" s="2" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H238" s="2" t="s">
         <v>14</v>
@@ -9166,13 +9166,13 @@
         <v>11</v>
       </c>
       <c r="E239" s="4">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="F239" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G239" s="4" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H239" s="4" t="s">
         <v>14</v>
@@ -9192,13 +9192,13 @@
         <v>11</v>
       </c>
       <c r="E240" s="2">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="F240" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G240" s="2" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H240" s="2" t="s">
         <v>14</v>
@@ -9218,13 +9218,13 @@
         <v>11</v>
       </c>
       <c r="E241" s="4">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F241" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G241" s="4" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H241" s="4" t="s">
         <v>14</v>
@@ -9244,13 +9244,13 @@
         <v>11</v>
       </c>
       <c r="E242" s="2">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F242" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G242" s="2" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H242" s="2" t="s">
         <v>14</v>
@@ -9270,13 +9270,13 @@
         <v>11</v>
       </c>
       <c r="E243" s="4">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="F243" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G243" s="4" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H243" s="4" t="s">
         <v>14</v>
@@ -9296,13 +9296,13 @@
         <v>11</v>
       </c>
       <c r="E244" s="2">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="F244" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G244" s="2" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H244" s="2" t="s">
         <v>14</v>
@@ -9322,13 +9322,13 @@
         <v>11</v>
       </c>
       <c r="E245" s="4">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="F245" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G245" s="4" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H245" s="4" t="s">
         <v>14</v>
@@ -9348,13 +9348,13 @@
         <v>11</v>
       </c>
       <c r="E246" s="2">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="F246" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G246" s="2" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H246" s="2" t="s">
         <v>14</v>
@@ -9374,13 +9374,13 @@
         <v>11</v>
       </c>
       <c r="E247" s="4">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="F247" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G247" s="4" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H247" s="4" t="s">
         <v>14</v>
@@ -9400,13 +9400,13 @@
         <v>11</v>
       </c>
       <c r="E248" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F248" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G248" s="2" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H248" s="2" t="s">
         <v>14</v>
@@ -9426,13 +9426,13 @@
         <v>11</v>
       </c>
       <c r="E249" s="4">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="F249" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G249" s="4" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H249" s="4" t="s">
         <v>14</v>
@@ -9452,13 +9452,13 @@
         <v>11</v>
       </c>
       <c r="E250" s="2">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="F250" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G250" s="2" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H250" s="2" t="s">
         <v>14</v>
@@ -9478,13 +9478,13 @@
         <v>11</v>
       </c>
       <c r="E251" s="4">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="F251" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G251" s="4" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H251" s="4" t="s">
         <v>14</v>
@@ -9504,13 +9504,13 @@
         <v>11</v>
       </c>
       <c r="E252" s="2">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="F252" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G252" s="2" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H252" s="2" t="s">
         <v>14</v>
@@ -9530,13 +9530,13 @@
         <v>11</v>
       </c>
       <c r="E253" s="4">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F253" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G253" s="4" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H253" s="4" t="s">
         <v>14</v>
@@ -9556,13 +9556,13 @@
         <v>11</v>
       </c>
       <c r="E254" s="2">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="F254" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G254" s="2" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H254" s="2" t="s">
         <v>14</v>
@@ -9582,13 +9582,13 @@
         <v>11</v>
       </c>
       <c r="E255" s="4">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="F255" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G255" s="4" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H255" s="4" t="s">
         <v>14</v>
@@ -9608,13 +9608,13 @@
         <v>11</v>
       </c>
       <c r="E256" s="2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F256" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G256" s="2" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H256" s="2" t="s">
         <v>14</v>
@@ -9634,13 +9634,13 @@
         <v>11</v>
       </c>
       <c r="E257" s="4">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="F257" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G257" s="4" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H257" s="4" t="s">
         <v>14</v>
@@ -9660,13 +9660,13 @@
         <v>11</v>
       </c>
       <c r="E258" s="2">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F258" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G258" s="2" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H258" s="2" t="s">
         <v>14</v>
@@ -9686,13 +9686,13 @@
         <v>11</v>
       </c>
       <c r="E259" s="4">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="F259" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G259" s="4" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H259" s="4" t="s">
         <v>14</v>
@@ -9712,13 +9712,13 @@
         <v>11</v>
       </c>
       <c r="E260" s="2">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="F260" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G260" s="2" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H260" s="2" t="s">
         <v>14</v>
@@ -9738,13 +9738,13 @@
         <v>11</v>
       </c>
       <c r="E261" s="4">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="F261" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G261" s="4" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H261" s="4" t="s">
         <v>14</v>
@@ -9764,13 +9764,13 @@
         <v>11</v>
       </c>
       <c r="E262" s="2">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="F262" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G262" s="2" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H262" s="2" t="s">
         <v>14</v>
@@ -9790,13 +9790,13 @@
         <v>11</v>
       </c>
       <c r="E263" s="4">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="F263" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G263" s="4" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H263" s="4" t="s">
         <v>14</v>
@@ -9822,7 +9822,7 @@
         <v>12</v>
       </c>
       <c r="G264" s="2" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H264" s="2" t="s">
         <v>14</v>
@@ -9842,13 +9842,13 @@
         <v>11</v>
       </c>
       <c r="E265" s="4">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F265" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G265" s="4" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H265" s="4" t="s">
         <v>14</v>
@@ -9868,13 +9868,13 @@
         <v>11</v>
       </c>
       <c r="E266" s="2">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F266" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G266" s="2" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H266" s="2" t="s">
         <v>14</v>
@@ -9894,13 +9894,13 @@
         <v>11</v>
       </c>
       <c r="E267" s="4">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="F267" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G267" s="4" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H267" s="4" t="s">
         <v>14</v>
@@ -9920,13 +9920,13 @@
         <v>11</v>
       </c>
       <c r="E268" s="2">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F268" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G268" s="2" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H268" s="2" t="s">
         <v>14</v>
@@ -9946,13 +9946,13 @@
         <v>11</v>
       </c>
       <c r="E269" s="4">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F269" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G269" s="4" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H269" s="4" t="s">
         <v>14</v>
@@ -9972,13 +9972,13 @@
         <v>11</v>
       </c>
       <c r="E270" s="2">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="F270" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G270" s="2" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H270" s="2" t="s">
         <v>14</v>
@@ -9998,13 +9998,13 @@
         <v>11</v>
       </c>
       <c r="E271" s="4">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="F271" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G271" s="4" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H271" s="4" t="s">
         <v>14</v>
@@ -10024,13 +10024,13 @@
         <v>11</v>
       </c>
       <c r="E272" s="2">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="F272" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G272" s="2" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H272" s="2" t="s">
         <v>14</v>
@@ -10056,7 +10056,7 @@
         <v>12</v>
       </c>
       <c r="G273" s="4" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H273" s="4" t="s">
         <v>14</v>
@@ -10076,13 +10076,13 @@
         <v>11</v>
       </c>
       <c r="E274" s="2">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F274" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G274" s="2" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H274" s="2" t="s">
         <v>14</v>
@@ -10108,7 +10108,7 @@
         <v>12</v>
       </c>
       <c r="G275" s="4" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H275" s="4" t="s">
         <v>14</v>
@@ -10134,7 +10134,7 @@
         <v>12</v>
       </c>
       <c r="G276" s="2" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H276" s="2" t="s">
         <v>14</v>
@@ -10154,13 +10154,13 @@
         <v>11</v>
       </c>
       <c r="E277" s="4">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="F277" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G277" s="4" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H277" s="4" t="s">
         <v>14</v>
@@ -10180,13 +10180,13 @@
         <v>11</v>
       </c>
       <c r="E278" s="2">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="F278" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G278" s="2" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H278" s="2" t="s">
         <v>14</v>
@@ -10206,13 +10206,13 @@
         <v>11</v>
       </c>
       <c r="E279" s="4">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="F279" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G279" s="4" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H279" s="4" t="s">
         <v>14</v>
@@ -10232,13 +10232,13 @@
         <v>11</v>
       </c>
       <c r="E280" s="2">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="F280" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G280" s="2" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H280" s="2" t="s">
         <v>14</v>
@@ -10258,13 +10258,13 @@
         <v>11</v>
       </c>
       <c r="E281" s="4">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="F281" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G281" s="4" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H281" s="4" t="s">
         <v>14</v>
@@ -10284,13 +10284,13 @@
         <v>11</v>
       </c>
       <c r="E282" s="2">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="F282" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G282" s="2" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H282" s="2" t="s">
         <v>14</v>
@@ -10310,13 +10310,13 @@
         <v>11</v>
       </c>
       <c r="E283" s="4">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F283" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G283" s="4" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H283" s="4" t="s">
         <v>14</v>
@@ -10336,13 +10336,13 @@
         <v>11</v>
       </c>
       <c r="E284" s="2">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="F284" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G284" s="2" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H284" s="2" t="s">
         <v>14</v>
@@ -10362,13 +10362,13 @@
         <v>11</v>
       </c>
       <c r="E285" s="4">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F285" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G285" s="4" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H285" s="4" t="s">
         <v>14</v>
@@ -10388,13 +10388,13 @@
         <v>11</v>
       </c>
       <c r="E286" s="2">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="F286" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G286" s="2" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H286" s="2" t="s">
         <v>14</v>
@@ -10414,13 +10414,13 @@
         <v>11</v>
       </c>
       <c r="E287" s="4">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="F287" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G287" s="4" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H287" s="4" t="s">
         <v>14</v>
@@ -10440,13 +10440,13 @@
         <v>11</v>
       </c>
       <c r="E288" s="2">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="F288" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G288" s="2" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H288" s="2" t="s">
         <v>14</v>
@@ -10466,13 +10466,13 @@
         <v>11</v>
       </c>
       <c r="E289" s="4">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="F289" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G289" s="4" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H289" s="4" t="s">
         <v>14</v>
@@ -10492,13 +10492,13 @@
         <v>11</v>
       </c>
       <c r="E290" s="2">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="F290" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G290" s="2" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H290" s="2" t="s">
         <v>14</v>
@@ -10524,7 +10524,7 @@
         <v>12</v>
       </c>
       <c r="G291" s="4" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H291" s="4" t="s">
         <v>14</v>
@@ -10544,13 +10544,13 @@
         <v>11</v>
       </c>
       <c r="E292" s="2">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F292" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G292" s="2" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H292" s="2" t="s">
         <v>14</v>
@@ -10570,13 +10570,13 @@
         <v>11</v>
       </c>
       <c r="E293" s="4">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="F293" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G293" s="4" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H293" s="4" t="s">
         <v>14</v>
@@ -10596,13 +10596,13 @@
         <v>11</v>
       </c>
       <c r="E294" s="2">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="F294" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G294" s="2" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H294" s="2" t="s">
         <v>14</v>
@@ -10622,13 +10622,13 @@
         <v>11</v>
       </c>
       <c r="E295" s="4">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="F295" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G295" s="4" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H295" s="4" t="s">
         <v>14</v>
@@ -10648,13 +10648,13 @@
         <v>11</v>
       </c>
       <c r="E296" s="2">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="F296" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G296" s="2" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H296" s="2" t="s">
         <v>14</v>
@@ -10674,13 +10674,13 @@
         <v>11</v>
       </c>
       <c r="E297" s="4">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="F297" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G297" s="4" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H297" s="4" t="s">
         <v>14</v>
@@ -10700,13 +10700,13 @@
         <v>11</v>
       </c>
       <c r="E298" s="2">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F298" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G298" s="2" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H298" s="2" t="s">
         <v>14</v>
@@ -10726,13 +10726,13 @@
         <v>11</v>
       </c>
       <c r="E299" s="4">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F299" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G299" s="4" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H299" s="4" t="s">
         <v>14</v>
@@ -10752,13 +10752,13 @@
         <v>11</v>
       </c>
       <c r="E300" s="2">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F300" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G300" s="2" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H300" s="2" t="s">
         <v>14</v>
@@ -10778,13 +10778,13 @@
         <v>11</v>
       </c>
       <c r="E301" s="4">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="F301" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G301" s="4" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H301" s="4" t="s">
         <v>14</v>
@@ -10804,13 +10804,13 @@
         <v>11</v>
       </c>
       <c r="E302" s="2">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="F302" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G302" s="2" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H302" s="2" t="s">
         <v>14</v>
@@ -10830,13 +10830,13 @@
         <v>11</v>
       </c>
       <c r="E303" s="4">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F303" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G303" s="4" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H303" s="4" t="s">
         <v>14</v>
@@ -10862,7 +10862,7 @@
         <v>12</v>
       </c>
       <c r="G304" s="2" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H304" s="2" t="s">
         <v>14</v>
@@ -10882,13 +10882,13 @@
         <v>11</v>
       </c>
       <c r="E305" s="4">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="F305" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G305" s="4" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H305" s="4" t="s">
         <v>14</v>
@@ -10908,13 +10908,13 @@
         <v>11</v>
       </c>
       <c r="E306" s="2">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F306" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G306" s="2" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H306" s="2" t="s">
         <v>14</v>
@@ -10934,13 +10934,13 @@
         <v>11</v>
       </c>
       <c r="E307" s="4">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F307" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G307" s="4" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H307" s="4" t="s">
         <v>14</v>
@@ -10960,13 +10960,13 @@
         <v>11</v>
       </c>
       <c r="E308" s="2">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F308" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G308" s="2" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H308" s="2" t="s">
         <v>14</v>
@@ -10986,13 +10986,13 @@
         <v>11</v>
       </c>
       <c r="E309" s="4">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="F309" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G309" s="4" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H309" s="4" t="s">
         <v>14</v>
@@ -11012,13 +11012,13 @@
         <v>11</v>
       </c>
       <c r="E310" s="2">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="F310" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G310" s="2" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H310" s="2" t="s">
         <v>14</v>
@@ -11038,13 +11038,13 @@
         <v>11</v>
       </c>
       <c r="E311" s="4">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="F311" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G311" s="4" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H311" s="4" t="s">
         <v>14</v>
@@ -11064,13 +11064,13 @@
         <v>11</v>
       </c>
       <c r="E312" s="2">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="F312" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G312" s="2" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H312" s="2" t="s">
         <v>14</v>
@@ -11090,13 +11090,13 @@
         <v>11</v>
       </c>
       <c r="E313" s="4">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F313" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G313" s="4" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H313" s="4" t="s">
         <v>14</v>
@@ -11116,13 +11116,13 @@
         <v>11</v>
       </c>
       <c r="E314" s="2">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F314" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G314" s="2" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H314" s="2" t="s">
         <v>14</v>
@@ -11142,13 +11142,13 @@
         <v>11</v>
       </c>
       <c r="E315" s="4">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="F315" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G315" s="4" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H315" s="4" t="s">
         <v>14</v>
@@ -11168,13 +11168,13 @@
         <v>11</v>
       </c>
       <c r="E316" s="2">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="F316" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G316" s="2" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H316" s="2" t="s">
         <v>14</v>
@@ -11194,13 +11194,13 @@
         <v>11</v>
       </c>
       <c r="E317" s="4">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="F317" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G317" s="4" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H317" s="4" t="s">
         <v>14</v>
@@ -11220,13 +11220,13 @@
         <v>11</v>
       </c>
       <c r="E318" s="2">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F318" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G318" s="2" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H318" s="2" t="s">
         <v>14</v>
@@ -11246,13 +11246,13 @@
         <v>11</v>
       </c>
       <c r="E319" s="4">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="F319" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G319" s="4" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H319" s="4" t="s">
         <v>14</v>
@@ -11272,13 +11272,13 @@
         <v>11</v>
       </c>
       <c r="E320" s="2">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="F320" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G320" s="2" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H320" s="2" t="s">
         <v>14</v>
@@ -11304,7 +11304,7 @@
         <v>12</v>
       </c>
       <c r="G321" s="4" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H321" s="4" t="s">
         <v>14</v>
@@ -11324,13 +11324,13 @@
         <v>11</v>
       </c>
       <c r="E322" s="2">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F322" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G322" s="2" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H322" s="2" t="s">
         <v>14</v>
@@ -11350,13 +11350,13 @@
         <v>11</v>
       </c>
       <c r="E323" s="4">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="F323" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G323" s="4" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H323" s="4" t="s">
         <v>14</v>
@@ -11376,13 +11376,13 @@
         <v>11</v>
       </c>
       <c r="E324" s="2">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="F324" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G324" s="2" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H324" s="2" t="s">
         <v>14</v>
@@ -11402,13 +11402,13 @@
         <v>11</v>
       </c>
       <c r="E325" s="4">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="F325" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G325" s="4" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H325" s="4" t="s">
         <v>14</v>
@@ -11428,13 +11428,13 @@
         <v>11</v>
       </c>
       <c r="E326" s="2">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="F326" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G326" s="2" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H326" s="2" t="s">
         <v>14</v>
@@ -11454,13 +11454,13 @@
         <v>11</v>
       </c>
       <c r="E327" s="4">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="F327" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G327" s="4" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H327" s="4" t="s">
         <v>14</v>
@@ -11480,13 +11480,13 @@
         <v>11</v>
       </c>
       <c r="E328" s="2">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="F328" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G328" s="2" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H328" s="2" t="s">
         <v>14</v>
@@ -11506,13 +11506,13 @@
         <v>11</v>
       </c>
       <c r="E329" s="4">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="F329" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G329" s="4" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H329" s="4" t="s">
         <v>14</v>
@@ -11532,13 +11532,13 @@
         <v>11</v>
       </c>
       <c r="E330" s="2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F330" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G330" s="2" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H330" s="2" t="s">
         <v>14</v>
@@ -11558,13 +11558,13 @@
         <v>11</v>
       </c>
       <c r="E331" s="4">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F331" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G331" s="4" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H331" s="4" t="s">
         <v>14</v>
@@ -11584,13 +11584,13 @@
         <v>11</v>
       </c>
       <c r="E332" s="2">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="F332" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G332" s="2" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H332" s="2" t="s">
         <v>14</v>
@@ -11610,13 +11610,13 @@
         <v>11</v>
       </c>
       <c r="E333" s="4">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="F333" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G333" s="4" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H333" s="4" t="s">
         <v>14</v>
@@ -11636,13 +11636,13 @@
         <v>11</v>
       </c>
       <c r="E334" s="2">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="F334" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G334" s="2" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H334" s="2" t="s">
         <v>14</v>
@@ -11662,13 +11662,13 @@
         <v>11</v>
       </c>
       <c r="E335" s="4">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="F335" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G335" s="4" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H335" s="4" t="s">
         <v>14</v>
@@ -11688,13 +11688,13 @@
         <v>11</v>
       </c>
       <c r="E336" s="2">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F336" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G336" s="2" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H336" s="2" t="s">
         <v>14</v>
@@ -11714,13 +11714,13 @@
         <v>11</v>
       </c>
       <c r="E337" s="4">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="F337" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G337" s="4" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H337" s="4" t="s">
         <v>14</v>
@@ -11740,13 +11740,13 @@
         <v>11</v>
       </c>
       <c r="E338" s="2">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="F338" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G338" s="2" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H338" s="2" t="s">
         <v>14</v>
@@ -11766,13 +11766,13 @@
         <v>11</v>
       </c>
       <c r="E339" s="4">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="F339" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G339" s="4" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H339" s="4" t="s">
         <v>14</v>
@@ -11792,13 +11792,13 @@
         <v>11</v>
       </c>
       <c r="E340" s="2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F340" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G340" s="2" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H340" s="2" t="s">
         <v>14</v>
@@ -11818,13 +11818,13 @@
         <v>11</v>
       </c>
       <c r="E341" s="4">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F341" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G341" s="4" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H341" s="4" t="s">
         <v>14</v>
@@ -11844,13 +11844,13 @@
         <v>11</v>
       </c>
       <c r="E342" s="2">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="F342" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G342" s="2" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H342" s="2" t="s">
         <v>14</v>
@@ -11870,13 +11870,13 @@
         <v>11</v>
       </c>
       <c r="E343" s="4">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="F343" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G343" s="4" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H343" s="4" t="s">
         <v>14</v>
@@ -11896,13 +11896,13 @@
         <v>11</v>
       </c>
       <c r="E344" s="2">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="F344" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G344" s="2" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H344" s="2" t="s">
         <v>14</v>
@@ -11922,13 +11922,13 @@
         <v>11</v>
       </c>
       <c r="E345" s="4">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F345" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G345" s="4" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H345" s="4" t="s">
         <v>14</v>
@@ -11948,13 +11948,13 @@
         <v>11</v>
       </c>
       <c r="E346" s="2">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F346" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G346" s="2" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H346" s="2" t="s">
         <v>14</v>
@@ -11980,7 +11980,7 @@
         <v>12</v>
       </c>
       <c r="G347" s="4" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H347" s="4" t="s">
         <v>14</v>
@@ -12000,13 +12000,13 @@
         <v>11</v>
       </c>
       <c r="E348" s="2">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F348" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G348" s="2" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H348" s="2" t="s">
         <v>14</v>
@@ -12026,13 +12026,13 @@
         <v>11</v>
       </c>
       <c r="E349" s="4">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F349" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G349" s="4" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H349" s="4" t="s">
         <v>14</v>
@@ -12052,13 +12052,13 @@
         <v>11</v>
       </c>
       <c r="E350" s="2">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="F350" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G350" s="2" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H350" s="2" t="s">
         <v>14</v>
@@ -12078,13 +12078,13 @@
         <v>11</v>
       </c>
       <c r="E351" s="4">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F351" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G351" s="4" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H351" s="4" t="s">
         <v>14</v>
@@ -12104,13 +12104,13 @@
         <v>11</v>
       </c>
       <c r="E352" s="2">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="F352" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G352" s="2" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H352" s="2" t="s">
         <v>14</v>
@@ -12130,13 +12130,13 @@
         <v>11</v>
       </c>
       <c r="E353" s="4">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F353" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G353" s="4" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H353" s="4" t="s">
         <v>14</v>
@@ -12156,13 +12156,13 @@
         <v>11</v>
       </c>
       <c r="E354" s="2">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="F354" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G354" s="2" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H354" s="2" t="s">
         <v>14</v>
@@ -12182,13 +12182,13 @@
         <v>11</v>
       </c>
       <c r="E355" s="4">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="F355" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G355" s="4" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H355" s="4" t="s">
         <v>14</v>
@@ -12208,13 +12208,13 @@
         <v>11</v>
       </c>
       <c r="E356" s="2">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F356" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G356" s="2" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H356" s="2" t="s">
         <v>14</v>
@@ -12234,13 +12234,13 @@
         <v>11</v>
       </c>
       <c r="E357" s="4">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F357" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G357" s="4" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H357" s="4" t="s">
         <v>14</v>
@@ -12260,13 +12260,13 @@
         <v>11</v>
       </c>
       <c r="E358" s="2">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="F358" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G358" s="2" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H358" s="2" t="s">
         <v>14</v>
@@ -12286,13 +12286,13 @@
         <v>11</v>
       </c>
       <c r="E359" s="4">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="F359" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G359" s="4" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H359" s="4" t="s">
         <v>14</v>
@@ -12312,13 +12312,13 @@
         <v>11</v>
       </c>
       <c r="E360" s="2">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="F360" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G360" s="2" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H360" s="2" t="s">
         <v>14</v>
@@ -12338,13 +12338,13 @@
         <v>11</v>
       </c>
       <c r="E361" s="4">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="F361" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G361" s="4" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H361" s="4" t="s">
         <v>14</v>
@@ -12364,13 +12364,13 @@
         <v>11</v>
       </c>
       <c r="E362" s="2">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F362" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G362" s="2" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H362" s="2" t="s">
         <v>14</v>
@@ -12390,13 +12390,13 @@
         <v>11</v>
       </c>
       <c r="E363" s="4">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F363" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G363" s="4" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H363" s="4" t="s">
         <v>14</v>
@@ -12416,13 +12416,13 @@
         <v>11</v>
       </c>
       <c r="E364" s="2">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="F364" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G364" s="2" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H364" s="2" t="s">
         <v>14</v>
@@ -12442,13 +12442,13 @@
         <v>11</v>
       </c>
       <c r="E365" s="4">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="F365" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G365" s="4" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H365" s="4" t="s">
         <v>14</v>
@@ -12468,13 +12468,13 @@
         <v>11</v>
       </c>
       <c r="E366" s="2">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="F366" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G366" s="2" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H366" s="2" t="s">
         <v>14</v>
@@ -12494,13 +12494,13 @@
         <v>11</v>
       </c>
       <c r="E367" s="4">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="F367" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G367" s="4" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H367" s="4" t="s">
         <v>14</v>
@@ -12520,13 +12520,13 @@
         <v>11</v>
       </c>
       <c r="E368" s="2">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="F368" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G368" s="2" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H368" s="2" t="s">
         <v>14</v>
@@ -12546,13 +12546,13 @@
         <v>11</v>
       </c>
       <c r="E369" s="4">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F369" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G369" s="4" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H369" s="4" t="s">
         <v>14</v>
@@ -12572,13 +12572,13 @@
         <v>11</v>
       </c>
       <c r="E370" s="2">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="F370" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G370" s="2" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H370" s="2" t="s">
         <v>14</v>
@@ -12598,13 +12598,13 @@
         <v>11</v>
       </c>
       <c r="E371" s="4">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="F371" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G371" s="4" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H371" s="4" t="s">
         <v>14</v>
@@ -12624,13 +12624,13 @@
         <v>11</v>
       </c>
       <c r="E372" s="2">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="F372" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G372" s="2" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H372" s="2" t="s">
         <v>14</v>
@@ -12650,13 +12650,13 @@
         <v>11</v>
       </c>
       <c r="E373" s="4">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F373" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G373" s="4" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H373" s="4" t="s">
         <v>14</v>
@@ -12676,13 +12676,13 @@
         <v>11</v>
       </c>
       <c r="E374" s="2">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F374" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G374" s="2" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H374" s="2" t="s">
         <v>14</v>
@@ -12702,13 +12702,13 @@
         <v>11</v>
       </c>
       <c r="E375" s="4">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F375" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G375" s="4" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H375" s="4" t="s">
         <v>14</v>
@@ -12734,7 +12734,7 @@
         <v>12</v>
       </c>
       <c r="G376" s="2" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H376" s="2" t="s">
         <v>14</v>
@@ -12754,13 +12754,13 @@
         <v>11</v>
       </c>
       <c r="E377" s="4">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F377" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G377" s="4" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H377" s="4" t="s">
         <v>14</v>
@@ -12780,13 +12780,13 @@
         <v>11</v>
       </c>
       <c r="E378" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F378" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G378" s="2" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H378" s="2" t="s">
         <v>14</v>
@@ -12806,13 +12806,13 @@
         <v>11</v>
       </c>
       <c r="E379" s="4">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F379" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G379" s="4" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H379" s="4" t="s">
         <v>14</v>
@@ -12832,13 +12832,13 @@
         <v>11</v>
       </c>
       <c r="E380" s="2">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="F380" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G380" s="2" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H380" s="2" t="s">
         <v>14</v>
@@ -12858,13 +12858,13 @@
         <v>11</v>
       </c>
       <c r="E381" s="4">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="F381" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G381" s="4" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H381" s="4" t="s">
         <v>14</v>
@@ -12884,13 +12884,13 @@
         <v>11</v>
       </c>
       <c r="E382" s="2">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="F382" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G382" s="2" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H382" s="2" t="s">
         <v>14</v>
@@ -12910,13 +12910,13 @@
         <v>11</v>
       </c>
       <c r="E383" s="4">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F383" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G383" s="4" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H383" s="4" t="s">
         <v>14</v>
@@ -12936,13 +12936,13 @@
         <v>11</v>
       </c>
       <c r="E384" s="2">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="F384" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G384" s="2" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H384" s="2" t="s">
         <v>14</v>
@@ -12962,13 +12962,13 @@
         <v>11</v>
       </c>
       <c r="E385" s="4">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="F385" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G385" s="4" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H385" s="4" t="s">
         <v>14</v>
@@ -12988,13 +12988,13 @@
         <v>11</v>
       </c>
       <c r="E386" s="2">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="F386" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G386" s="2" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H386" s="2" t="s">
         <v>14</v>
@@ -13014,13 +13014,13 @@
         <v>11</v>
       </c>
       <c r="E387" s="4">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="F387" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G387" s="4" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H387" s="4" t="s">
         <v>14</v>
@@ -13040,13 +13040,13 @@
         <v>11</v>
       </c>
       <c r="E388" s="2">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="F388" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G388" s="2" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H388" s="2" t="s">
         <v>14</v>
@@ -13066,13 +13066,13 @@
         <v>11</v>
       </c>
       <c r="E389" s="4">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="F389" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G389" s="4" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H389" s="4" t="s">
         <v>14</v>
@@ -13092,13 +13092,13 @@
         <v>11</v>
       </c>
       <c r="E390" s="2">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F390" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G390" s="2" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H390" s="2" t="s">
         <v>14</v>
@@ -13118,13 +13118,13 @@
         <v>11</v>
       </c>
       <c r="E391" s="4">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="F391" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G391" s="4" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H391" s="4" t="s">
         <v>14</v>
@@ -13144,13 +13144,13 @@
         <v>11</v>
       </c>
       <c r="E392" s="2">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F392" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G392" s="2" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H392" s="2" t="s">
         <v>14</v>
@@ -13170,13 +13170,13 @@
         <v>11</v>
       </c>
       <c r="E393" s="4">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="F393" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G393" s="4" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H393" s="4" t="s">
         <v>14</v>
@@ -13196,13 +13196,13 @@
         <v>11</v>
       </c>
       <c r="E394" s="2">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="F394" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G394" s="2" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H394" s="2" t="s">
         <v>14</v>
@@ -13222,13 +13222,13 @@
         <v>11</v>
       </c>
       <c r="E395" s="4">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F395" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G395" s="4" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H395" s="4" t="s">
         <v>14</v>
@@ -13254,7 +13254,7 @@
         <v>12</v>
       </c>
       <c r="G396" s="2" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H396" s="2" t="s">
         <v>14</v>
@@ -13274,13 +13274,13 @@
         <v>11</v>
       </c>
       <c r="E397" s="4">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="F397" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G397" s="4" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H397" s="4" t="s">
         <v>14</v>
@@ -13300,13 +13300,13 @@
         <v>11</v>
       </c>
       <c r="E398" s="2">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="F398" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G398" s="2" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H398" s="2" t="s">
         <v>14</v>
@@ -13326,13 +13326,13 @@
         <v>11</v>
       </c>
       <c r="E399" s="4">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F399" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G399" s="4" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H399" s="4" t="s">
         <v>14</v>
@@ -13352,13 +13352,13 @@
         <v>11</v>
       </c>
       <c r="E400" s="2">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F400" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G400" s="2" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H400" s="2" t="s">
         <v>14</v>
@@ -13378,13 +13378,13 @@
         <v>11</v>
       </c>
       <c r="E401" s="4">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F401" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G401" s="4" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H401" s="4" t="s">
         <v>14</v>

--- a/reports/Mobile_Appium_E2E_Test_Report_400.xlsx
+++ b/reports/Mobile_Appium_E2E_Test_Report_400.xlsx
@@ -52,7 +52,7 @@
     <t>PASSED</t>
   </si>
   <si>
-    <t>2026-08-07T15:03:11.343Z</t>
+    <t>2026-08-07T15:22:43.166Z</t>
   </si>
   <si>
     <t>Verified Android Activity lifecycle and Capacitor native plugin interface</t>
@@ -3001,7 +3001,7 @@
         <v>11</v>
       </c>
       <c r="E2" s="2">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>12</v>
@@ -3027,7 +3027,7 @@
         <v>11</v>
       </c>
       <c r="E3" s="4">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>12</v>
@@ -3053,7 +3053,7 @@
         <v>11</v>
       </c>
       <c r="E4" s="2">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="F4" s="3" t="s">
         <v>12</v>
@@ -3079,7 +3079,7 @@
         <v>11</v>
       </c>
       <c r="E5" s="4">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F5" s="3" t="s">
         <v>12</v>
@@ -3105,7 +3105,7 @@
         <v>11</v>
       </c>
       <c r="E6" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F6" s="3" t="s">
         <v>12</v>
@@ -3131,7 +3131,7 @@
         <v>11</v>
       </c>
       <c r="E7" s="4">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="F7" s="3" t="s">
         <v>12</v>
@@ -3157,7 +3157,7 @@
         <v>11</v>
       </c>
       <c r="E8" s="2">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F8" s="3" t="s">
         <v>12</v>
@@ -3183,7 +3183,7 @@
         <v>11</v>
       </c>
       <c r="E9" s="4">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="F9" s="3" t="s">
         <v>12</v>
@@ -3209,7 +3209,7 @@
         <v>11</v>
       </c>
       <c r="E10" s="2">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="F10" s="3" t="s">
         <v>12</v>
@@ -3235,7 +3235,7 @@
         <v>11</v>
       </c>
       <c r="E11" s="4">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F11" s="3" t="s">
         <v>12</v>
@@ -3261,7 +3261,7 @@
         <v>11</v>
       </c>
       <c r="E12" s="2">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="F12" s="3" t="s">
         <v>12</v>
@@ -3287,7 +3287,7 @@
         <v>11</v>
       </c>
       <c r="E13" s="4">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="F13" s="3" t="s">
         <v>12</v>
@@ -3313,7 +3313,7 @@
         <v>11</v>
       </c>
       <c r="E14" s="2">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>12</v>
@@ -3339,7 +3339,7 @@
         <v>11</v>
       </c>
       <c r="E15" s="4">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="F15" s="3" t="s">
         <v>12</v>
@@ -3365,7 +3365,7 @@
         <v>11</v>
       </c>
       <c r="E16" s="2">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F16" s="3" t="s">
         <v>12</v>
@@ -3391,7 +3391,7 @@
         <v>11</v>
       </c>
       <c r="E17" s="4">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="F17" s="3" t="s">
         <v>12</v>
@@ -3417,7 +3417,7 @@
         <v>11</v>
       </c>
       <c r="E18" s="2">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="F18" s="3" t="s">
         <v>12</v>
@@ -3443,7 +3443,7 @@
         <v>11</v>
       </c>
       <c r="E19" s="4">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="F19" s="3" t="s">
         <v>12</v>
@@ -3469,7 +3469,7 @@
         <v>11</v>
       </c>
       <c r="E20" s="2">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="F20" s="3" t="s">
         <v>12</v>
@@ -3495,7 +3495,7 @@
         <v>11</v>
       </c>
       <c r="E21" s="4">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="F21" s="3" t="s">
         <v>12</v>
@@ -3521,7 +3521,7 @@
         <v>11</v>
       </c>
       <c r="E22" s="2">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F22" s="3" t="s">
         <v>12</v>
@@ -3547,7 +3547,7 @@
         <v>11</v>
       </c>
       <c r="E23" s="4">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="F23" s="3" t="s">
         <v>12</v>
@@ -3573,7 +3573,7 @@
         <v>11</v>
       </c>
       <c r="E24" s="2">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="F24" s="3" t="s">
         <v>12</v>
@@ -3599,7 +3599,7 @@
         <v>11</v>
       </c>
       <c r="E25" s="4">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="F25" s="3" t="s">
         <v>12</v>
@@ -3625,7 +3625,7 @@
         <v>11</v>
       </c>
       <c r="E26" s="2">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="F26" s="3" t="s">
         <v>12</v>
@@ -3651,7 +3651,7 @@
         <v>11</v>
       </c>
       <c r="E27" s="4">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="F27" s="3" t="s">
         <v>12</v>
@@ -3677,7 +3677,7 @@
         <v>11</v>
       </c>
       <c r="E28" s="2">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="F28" s="3" t="s">
         <v>12</v>
@@ -3703,7 +3703,7 @@
         <v>11</v>
       </c>
       <c r="E29" s="4">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="F29" s="3" t="s">
         <v>12</v>
@@ -3729,7 +3729,7 @@
         <v>11</v>
       </c>
       <c r="E30" s="2">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="F30" s="3" t="s">
         <v>12</v>
@@ -3755,7 +3755,7 @@
         <v>11</v>
       </c>
       <c r="E31" s="4">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F31" s="3" t="s">
         <v>12</v>
@@ -3781,7 +3781,7 @@
         <v>11</v>
       </c>
       <c r="E32" s="2">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="F32" s="3" t="s">
         <v>12</v>
@@ -3807,7 +3807,7 @@
         <v>11</v>
       </c>
       <c r="E33" s="4">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="F33" s="3" t="s">
         <v>12</v>
@@ -3833,7 +3833,7 @@
         <v>11</v>
       </c>
       <c r="E34" s="2">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="F34" s="3" t="s">
         <v>12</v>
@@ -3859,7 +3859,7 @@
         <v>11</v>
       </c>
       <c r="E35" s="4">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="F35" s="3" t="s">
         <v>12</v>
@@ -3885,7 +3885,7 @@
         <v>11</v>
       </c>
       <c r="E36" s="2">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="F36" s="3" t="s">
         <v>12</v>
@@ -3911,7 +3911,7 @@
         <v>11</v>
       </c>
       <c r="E37" s="4">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="F37" s="3" t="s">
         <v>12</v>
@@ -3937,7 +3937,7 @@
         <v>11</v>
       </c>
       <c r="E38" s="2">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="F38" s="3" t="s">
         <v>12</v>
@@ -3963,7 +3963,7 @@
         <v>11</v>
       </c>
       <c r="E39" s="4">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F39" s="3" t="s">
         <v>12</v>
@@ -3989,7 +3989,7 @@
         <v>11</v>
       </c>
       <c r="E40" s="2">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="F40" s="3" t="s">
         <v>12</v>
@@ -4015,7 +4015,7 @@
         <v>11</v>
       </c>
       <c r="E41" s="4">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="F41" s="3" t="s">
         <v>12</v>
@@ -4041,7 +4041,7 @@
         <v>11</v>
       </c>
       <c r="E42" s="2">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="F42" s="3" t="s">
         <v>12</v>
@@ -4067,7 +4067,7 @@
         <v>11</v>
       </c>
       <c r="E43" s="4">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="F43" s="3" t="s">
         <v>12</v>
@@ -4093,7 +4093,7 @@
         <v>11</v>
       </c>
       <c r="E44" s="2">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="F44" s="3" t="s">
         <v>12</v>
@@ -4119,7 +4119,7 @@
         <v>11</v>
       </c>
       <c r="E45" s="4">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="F45" s="3" t="s">
         <v>12</v>
@@ -4145,7 +4145,7 @@
         <v>11</v>
       </c>
       <c r="E46" s="2">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="F46" s="3" t="s">
         <v>12</v>
@@ -4171,7 +4171,7 @@
         <v>11</v>
       </c>
       <c r="E47" s="4">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="F47" s="3" t="s">
         <v>12</v>
@@ -4197,7 +4197,7 @@
         <v>11</v>
       </c>
       <c r="E48" s="2">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="F48" s="3" t="s">
         <v>12</v>
@@ -4223,7 +4223,7 @@
         <v>11</v>
       </c>
       <c r="E49" s="4">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="F49" s="3" t="s">
         <v>12</v>
@@ -4249,7 +4249,7 @@
         <v>11</v>
       </c>
       <c r="E50" s="2">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="F50" s="3" t="s">
         <v>12</v>
@@ -4275,7 +4275,7 @@
         <v>11</v>
       </c>
       <c r="E51" s="4">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="F51" s="3" t="s">
         <v>12</v>
@@ -4301,7 +4301,7 @@
         <v>11</v>
       </c>
       <c r="E52" s="2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F52" s="3" t="s">
         <v>12</v>
@@ -4327,7 +4327,7 @@
         <v>11</v>
       </c>
       <c r="E53" s="4">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="F53" s="3" t="s">
         <v>12</v>
@@ -4353,7 +4353,7 @@
         <v>11</v>
       </c>
       <c r="E54" s="2">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="F54" s="3" t="s">
         <v>12</v>
@@ -4379,7 +4379,7 @@
         <v>11</v>
       </c>
       <c r="E55" s="4">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="F55" s="3" t="s">
         <v>12</v>
@@ -4405,7 +4405,7 @@
         <v>11</v>
       </c>
       <c r="E56" s="2">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F56" s="3" t="s">
         <v>12</v>
@@ -4431,7 +4431,7 @@
         <v>11</v>
       </c>
       <c r="E57" s="4">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="F57" s="3" t="s">
         <v>12</v>
@@ -4457,7 +4457,7 @@
         <v>11</v>
       </c>
       <c r="E58" s="2">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="F58" s="3" t="s">
         <v>12</v>
@@ -4483,7 +4483,7 @@
         <v>11</v>
       </c>
       <c r="E59" s="4">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="F59" s="3" t="s">
         <v>12</v>
@@ -4509,7 +4509,7 @@
         <v>11</v>
       </c>
       <c r="E60" s="2">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="F60" s="3" t="s">
         <v>12</v>
@@ -4535,7 +4535,7 @@
         <v>11</v>
       </c>
       <c r="E61" s="4">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="F61" s="3" t="s">
         <v>12</v>
@@ -4561,7 +4561,7 @@
         <v>11</v>
       </c>
       <c r="E62" s="2">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F62" s="3" t="s">
         <v>12</v>
@@ -4587,7 +4587,7 @@
         <v>11</v>
       </c>
       <c r="E63" s="4">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="F63" s="3" t="s">
         <v>12</v>
@@ -4613,7 +4613,7 @@
         <v>11</v>
       </c>
       <c r="E64" s="2">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="F64" s="3" t="s">
         <v>12</v>
@@ -4639,7 +4639,7 @@
         <v>11</v>
       </c>
       <c r="E65" s="4">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="F65" s="3" t="s">
         <v>12</v>
@@ -4665,7 +4665,7 @@
         <v>11</v>
       </c>
       <c r="E66" s="2">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="F66" s="3" t="s">
         <v>12</v>
@@ -4717,7 +4717,7 @@
         <v>11</v>
       </c>
       <c r="E68" s="2">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="F68" s="3" t="s">
         <v>12</v>
@@ -4743,7 +4743,7 @@
         <v>11</v>
       </c>
       <c r="E69" s="4">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F69" s="3" t="s">
         <v>12</v>
@@ -4769,7 +4769,7 @@
         <v>11</v>
       </c>
       <c r="E70" s="2">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F70" s="3" t="s">
         <v>12</v>
@@ -4795,7 +4795,7 @@
         <v>11</v>
       </c>
       <c r="E71" s="4">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="F71" s="3" t="s">
         <v>12</v>
@@ -4847,7 +4847,7 @@
         <v>11</v>
       </c>
       <c r="E73" s="4">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F73" s="3" t="s">
         <v>12</v>
@@ -4873,7 +4873,7 @@
         <v>11</v>
       </c>
       <c r="E74" s="2">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="F74" s="3" t="s">
         <v>12</v>
@@ -4899,7 +4899,7 @@
         <v>11</v>
       </c>
       <c r="E75" s="4">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="F75" s="3" t="s">
         <v>12</v>
@@ -4925,7 +4925,7 @@
         <v>11</v>
       </c>
       <c r="E76" s="2">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="F76" s="3" t="s">
         <v>12</v>
@@ -4951,7 +4951,7 @@
         <v>11</v>
       </c>
       <c r="E77" s="4">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="F77" s="3" t="s">
         <v>12</v>
@@ -4977,7 +4977,7 @@
         <v>11</v>
       </c>
       <c r="E78" s="2">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="F78" s="3" t="s">
         <v>12</v>
@@ -5003,7 +5003,7 @@
         <v>11</v>
       </c>
       <c r="E79" s="4">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="F79" s="3" t="s">
         <v>12</v>
@@ -5029,7 +5029,7 @@
         <v>11</v>
       </c>
       <c r="E80" s="2">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="F80" s="3" t="s">
         <v>12</v>
@@ -5055,7 +5055,7 @@
         <v>11</v>
       </c>
       <c r="E81" s="4">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="F81" s="3" t="s">
         <v>12</v>
@@ -5081,7 +5081,7 @@
         <v>11</v>
       </c>
       <c r="E82" s="2">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="F82" s="3" t="s">
         <v>12</v>
@@ -5107,7 +5107,7 @@
         <v>11</v>
       </c>
       <c r="E83" s="4">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F83" s="3" t="s">
         <v>12</v>
@@ -5133,7 +5133,7 @@
         <v>11</v>
       </c>
       <c r="E84" s="2">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F84" s="3" t="s">
         <v>12</v>
@@ -5159,7 +5159,7 @@
         <v>11</v>
       </c>
       <c r="E85" s="4">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="F85" s="3" t="s">
         <v>12</v>
@@ -5185,7 +5185,7 @@
         <v>11</v>
       </c>
       <c r="E86" s="2">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="F86" s="3" t="s">
         <v>12</v>
@@ -5211,7 +5211,7 @@
         <v>11</v>
       </c>
       <c r="E87" s="4">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="F87" s="3" t="s">
         <v>12</v>
@@ -5263,7 +5263,7 @@
         <v>11</v>
       </c>
       <c r="E89" s="4">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F89" s="3" t="s">
         <v>12</v>
@@ -5289,7 +5289,7 @@
         <v>11</v>
       </c>
       <c r="E90" s="2">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="F90" s="3" t="s">
         <v>12</v>
@@ -5315,7 +5315,7 @@
         <v>11</v>
       </c>
       <c r="E91" s="4">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F91" s="3" t="s">
         <v>12</v>
@@ -5341,7 +5341,7 @@
         <v>11</v>
       </c>
       <c r="E92" s="2">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="F92" s="3" t="s">
         <v>12</v>
@@ -5367,7 +5367,7 @@
         <v>11</v>
       </c>
       <c r="E93" s="4">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="F93" s="3" t="s">
         <v>12</v>
@@ -5393,7 +5393,7 @@
         <v>11</v>
       </c>
       <c r="E94" s="2">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F94" s="3" t="s">
         <v>12</v>
@@ -5419,7 +5419,7 @@
         <v>11</v>
       </c>
       <c r="E95" s="4">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="F95" s="3" t="s">
         <v>12</v>
@@ -5445,7 +5445,7 @@
         <v>11</v>
       </c>
       <c r="E96" s="2">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="F96" s="3" t="s">
         <v>12</v>
@@ -5497,7 +5497,7 @@
         <v>11</v>
       </c>
       <c r="E98" s="2">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="F98" s="3" t="s">
         <v>12</v>
@@ -5523,7 +5523,7 @@
         <v>11</v>
       </c>
       <c r="E99" s="4">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="F99" s="3" t="s">
         <v>12</v>
@@ -5549,7 +5549,7 @@
         <v>11</v>
       </c>
       <c r="E100" s="2">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="F100" s="3" t="s">
         <v>12</v>
@@ -5575,7 +5575,7 @@
         <v>11</v>
       </c>
       <c r="E101" s="4">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F101" s="3" t="s">
         <v>12</v>
@@ -5601,7 +5601,7 @@
         <v>11</v>
       </c>
       <c r="E102" s="2">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="F102" s="3" t="s">
         <v>12</v>
@@ -5627,7 +5627,7 @@
         <v>11</v>
       </c>
       <c r="E103" s="4">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="F103" s="3" t="s">
         <v>12</v>
@@ -5653,7 +5653,7 @@
         <v>11</v>
       </c>
       <c r="E104" s="2">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="F104" s="3" t="s">
         <v>12</v>
@@ -5679,7 +5679,7 @@
         <v>11</v>
       </c>
       <c r="E105" s="4">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F105" s="3" t="s">
         <v>12</v>
@@ -5705,7 +5705,7 @@
         <v>11</v>
       </c>
       <c r="E106" s="2">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="F106" s="3" t="s">
         <v>12</v>
@@ -5731,7 +5731,7 @@
         <v>11</v>
       </c>
       <c r="E107" s="4">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="F107" s="3" t="s">
         <v>12</v>
@@ -5757,7 +5757,7 @@
         <v>11</v>
       </c>
       <c r="E108" s="2">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="F108" s="3" t="s">
         <v>12</v>
@@ -5783,7 +5783,7 @@
         <v>11</v>
       </c>
       <c r="E109" s="4">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="F109" s="3" t="s">
         <v>12</v>
@@ -5809,7 +5809,7 @@
         <v>11</v>
       </c>
       <c r="E110" s="2">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="F110" s="3" t="s">
         <v>12</v>
@@ -5835,7 +5835,7 @@
         <v>11</v>
       </c>
       <c r="E111" s="4">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F111" s="3" t="s">
         <v>12</v>
@@ -5861,7 +5861,7 @@
         <v>11</v>
       </c>
       <c r="E112" s="2">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="F112" s="3" t="s">
         <v>12</v>
@@ -5887,7 +5887,7 @@
         <v>11</v>
       </c>
       <c r="E113" s="4">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F113" s="3" t="s">
         <v>12</v>
@@ -5913,7 +5913,7 @@
         <v>11</v>
       </c>
       <c r="E114" s="2">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="F114" s="3" t="s">
         <v>12</v>
@@ -5939,7 +5939,7 @@
         <v>11</v>
       </c>
       <c r="E115" s="4">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="F115" s="3" t="s">
         <v>12</v>
@@ -5965,7 +5965,7 @@
         <v>11</v>
       </c>
       <c r="E116" s="2">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="F116" s="3" t="s">
         <v>12</v>
@@ -5991,7 +5991,7 @@
         <v>11</v>
       </c>
       <c r="E117" s="4">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="F117" s="3" t="s">
         <v>12</v>
@@ -6017,7 +6017,7 @@
         <v>11</v>
       </c>
       <c r="E118" s="2">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="F118" s="3" t="s">
         <v>12</v>
@@ -6043,7 +6043,7 @@
         <v>11</v>
       </c>
       <c r="E119" s="4">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="F119" s="3" t="s">
         <v>12</v>
@@ -6069,7 +6069,7 @@
         <v>11</v>
       </c>
       <c r="E120" s="2">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F120" s="3" t="s">
         <v>12</v>
@@ -6095,7 +6095,7 @@
         <v>11</v>
       </c>
       <c r="E121" s="4">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F121" s="3" t="s">
         <v>12</v>
@@ -6121,7 +6121,7 @@
         <v>11</v>
       </c>
       <c r="E122" s="2">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="F122" s="3" t="s">
         <v>12</v>
@@ -6147,7 +6147,7 @@
         <v>11</v>
       </c>
       <c r="E123" s="4">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F123" s="3" t="s">
         <v>12</v>
@@ -6173,7 +6173,7 @@
         <v>11</v>
       </c>
       <c r="E124" s="2">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="F124" s="3" t="s">
         <v>12</v>
@@ -6199,7 +6199,7 @@
         <v>11</v>
       </c>
       <c r="E125" s="4">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="F125" s="3" t="s">
         <v>12</v>
@@ -6225,7 +6225,7 @@
         <v>11</v>
       </c>
       <c r="E126" s="2">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="F126" s="3" t="s">
         <v>12</v>
@@ -6251,7 +6251,7 @@
         <v>11</v>
       </c>
       <c r="E127" s="4">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="F127" s="3" t="s">
         <v>12</v>
@@ -6277,7 +6277,7 @@
         <v>11</v>
       </c>
       <c r="E128" s="2">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="F128" s="3" t="s">
         <v>12</v>
@@ -6303,7 +6303,7 @@
         <v>11</v>
       </c>
       <c r="E129" s="4">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F129" s="3" t="s">
         <v>12</v>
@@ -6329,7 +6329,7 @@
         <v>11</v>
       </c>
       <c r="E130" s="2">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F130" s="3" t="s">
         <v>12</v>
@@ -6355,7 +6355,7 @@
         <v>11</v>
       </c>
       <c r="E131" s="4">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="F131" s="3" t="s">
         <v>12</v>
@@ -6381,7 +6381,7 @@
         <v>11</v>
       </c>
       <c r="E132" s="2">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="F132" s="3" t="s">
         <v>12</v>
@@ -6407,7 +6407,7 @@
         <v>11</v>
       </c>
       <c r="E133" s="4">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="F133" s="3" t="s">
         <v>12</v>
@@ -6433,7 +6433,7 @@
         <v>11</v>
       </c>
       <c r="E134" s="2">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F134" s="3" t="s">
         <v>12</v>
@@ -6459,7 +6459,7 @@
         <v>11</v>
       </c>
       <c r="E135" s="4">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="F135" s="3" t="s">
         <v>12</v>
@@ -6485,7 +6485,7 @@
         <v>11</v>
       </c>
       <c r="E136" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F136" s="3" t="s">
         <v>12</v>
@@ -6511,7 +6511,7 @@
         <v>11</v>
       </c>
       <c r="E137" s="4">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="F137" s="3" t="s">
         <v>12</v>
@@ -6537,7 +6537,7 @@
         <v>11</v>
       </c>
       <c r="E138" s="2">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="F138" s="3" t="s">
         <v>12</v>
@@ -6563,7 +6563,7 @@
         <v>11</v>
       </c>
       <c r="E139" s="4">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="F139" s="3" t="s">
         <v>12</v>
@@ -6589,7 +6589,7 @@
         <v>11</v>
       </c>
       <c r="E140" s="2">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="F140" s="3" t="s">
         <v>12</v>
@@ -6615,7 +6615,7 @@
         <v>11</v>
       </c>
       <c r="E141" s="4">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="F141" s="3" t="s">
         <v>12</v>
@@ -6641,7 +6641,7 @@
         <v>11</v>
       </c>
       <c r="E142" s="2">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="F142" s="3" t="s">
         <v>12</v>
@@ -6667,7 +6667,7 @@
         <v>11</v>
       </c>
       <c r="E143" s="4">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="F143" s="3" t="s">
         <v>12</v>
@@ -6693,7 +6693,7 @@
         <v>11</v>
       </c>
       <c r="E144" s="2">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="F144" s="3" t="s">
         <v>12</v>
@@ -6719,7 +6719,7 @@
         <v>11</v>
       </c>
       <c r="E145" s="4">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="F145" s="3" t="s">
         <v>12</v>
@@ -6745,7 +6745,7 @@
         <v>11</v>
       </c>
       <c r="E146" s="2">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="F146" s="3" t="s">
         <v>12</v>
@@ -6771,7 +6771,7 @@
         <v>11</v>
       </c>
       <c r="E147" s="4">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="F147" s="3" t="s">
         <v>12</v>
@@ -6797,7 +6797,7 @@
         <v>11</v>
       </c>
       <c r="E148" s="2">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="F148" s="3" t="s">
         <v>12</v>
@@ -6823,7 +6823,7 @@
         <v>11</v>
       </c>
       <c r="E149" s="4">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F149" s="3" t="s">
         <v>12</v>
@@ -6849,7 +6849,7 @@
         <v>11</v>
       </c>
       <c r="E150" s="2">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="F150" s="3" t="s">
         <v>12</v>
@@ -6875,7 +6875,7 @@
         <v>11</v>
       </c>
       <c r="E151" s="4">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="F151" s="3" t="s">
         <v>12</v>
@@ -6901,7 +6901,7 @@
         <v>11</v>
       </c>
       <c r="E152" s="2">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="F152" s="3" t="s">
         <v>12</v>
@@ -6953,7 +6953,7 @@
         <v>11</v>
       </c>
       <c r="E154" s="2">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="F154" s="3" t="s">
         <v>12</v>
@@ -6979,7 +6979,7 @@
         <v>11</v>
       </c>
       <c r="E155" s="4">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="F155" s="3" t="s">
         <v>12</v>
@@ -7031,7 +7031,7 @@
         <v>11</v>
       </c>
       <c r="E157" s="4">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="F157" s="3" t="s">
         <v>12</v>
@@ -7057,7 +7057,7 @@
         <v>11</v>
       </c>
       <c r="E158" s="2">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="F158" s="3" t="s">
         <v>12</v>
@@ -7083,7 +7083,7 @@
         <v>11</v>
       </c>
       <c r="E159" s="4">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="F159" s="3" t="s">
         <v>12</v>
@@ -7109,7 +7109,7 @@
         <v>11</v>
       </c>
       <c r="E160" s="2">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F160" s="3" t="s">
         <v>12</v>
@@ -7135,7 +7135,7 @@
         <v>11</v>
       </c>
       <c r="E161" s="4">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="F161" s="3" t="s">
         <v>12</v>
@@ -7161,7 +7161,7 @@
         <v>11</v>
       </c>
       <c r="E162" s="2">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="F162" s="3" t="s">
         <v>12</v>
@@ -7187,7 +7187,7 @@
         <v>11</v>
       </c>
       <c r="E163" s="4">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F163" s="3" t="s">
         <v>12</v>
@@ -7213,7 +7213,7 @@
         <v>11</v>
       </c>
       <c r="E164" s="2">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="F164" s="3" t="s">
         <v>12</v>
@@ -7239,7 +7239,7 @@
         <v>11</v>
       </c>
       <c r="E165" s="4">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="F165" s="3" t="s">
         <v>12</v>
@@ -7265,7 +7265,7 @@
         <v>11</v>
       </c>
       <c r="E166" s="2">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="F166" s="3" t="s">
         <v>12</v>
@@ -7291,7 +7291,7 @@
         <v>11</v>
       </c>
       <c r="E167" s="4">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F167" s="3" t="s">
         <v>12</v>
@@ -7317,7 +7317,7 @@
         <v>11</v>
       </c>
       <c r="E168" s="2">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F168" s="3" t="s">
         <v>12</v>
@@ -7343,7 +7343,7 @@
         <v>11</v>
       </c>
       <c r="E169" s="4">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="F169" s="3" t="s">
         <v>12</v>
@@ -7369,7 +7369,7 @@
         <v>11</v>
       </c>
       <c r="E170" s="2">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="F170" s="3" t="s">
         <v>12</v>
@@ -7395,7 +7395,7 @@
         <v>11</v>
       </c>
       <c r="E171" s="4">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="F171" s="3" t="s">
         <v>12</v>
@@ -7447,7 +7447,7 @@
         <v>11</v>
       </c>
       <c r="E173" s="4">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="F173" s="3" t="s">
         <v>12</v>
@@ -7473,7 +7473,7 @@
         <v>11</v>
       </c>
       <c r="E174" s="2">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="F174" s="3" t="s">
         <v>12</v>
@@ -7525,7 +7525,7 @@
         <v>11</v>
       </c>
       <c r="E176" s="2">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="F176" s="3" t="s">
         <v>12</v>
@@ -7551,7 +7551,7 @@
         <v>11</v>
       </c>
       <c r="E177" s="4">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="F177" s="3" t="s">
         <v>12</v>
@@ -7577,7 +7577,7 @@
         <v>11</v>
       </c>
       <c r="E178" s="2">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="F178" s="3" t="s">
         <v>12</v>
@@ -7629,7 +7629,7 @@
         <v>11</v>
       </c>
       <c r="E180" s="2">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="F180" s="3" t="s">
         <v>12</v>
@@ -7655,7 +7655,7 @@
         <v>11</v>
       </c>
       <c r="E181" s="4">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="F181" s="3" t="s">
         <v>12</v>
@@ -7681,7 +7681,7 @@
         <v>11</v>
       </c>
       <c r="E182" s="2">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="F182" s="3" t="s">
         <v>12</v>
@@ -7707,7 +7707,7 @@
         <v>11</v>
       </c>
       <c r="E183" s="4">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="F183" s="3" t="s">
         <v>12</v>
@@ -7733,7 +7733,7 @@
         <v>11</v>
       </c>
       <c r="E184" s="2">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="F184" s="3" t="s">
         <v>12</v>
@@ -7785,7 +7785,7 @@
         <v>11</v>
       </c>
       <c r="E186" s="2">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="F186" s="3" t="s">
         <v>12</v>
@@ -7811,7 +7811,7 @@
         <v>11</v>
       </c>
       <c r="E187" s="4">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="F187" s="3" t="s">
         <v>12</v>
@@ -7837,7 +7837,7 @@
         <v>11</v>
       </c>
       <c r="E188" s="2">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="F188" s="3" t="s">
         <v>12</v>
@@ -7863,7 +7863,7 @@
         <v>11</v>
       </c>
       <c r="E189" s="4">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="F189" s="3" t="s">
         <v>12</v>
@@ -7889,7 +7889,7 @@
         <v>11</v>
       </c>
       <c r="E190" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F190" s="3" t="s">
         <v>12</v>
@@ -7915,7 +7915,7 @@
         <v>11</v>
       </c>
       <c r="E191" s="4">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F191" s="3" t="s">
         <v>12</v>
@@ -7941,7 +7941,7 @@
         <v>11</v>
       </c>
       <c r="E192" s="2">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="F192" s="3" t="s">
         <v>12</v>
@@ -7967,7 +7967,7 @@
         <v>11</v>
       </c>
       <c r="E193" s="4">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F193" s="3" t="s">
         <v>12</v>
@@ -7993,7 +7993,7 @@
         <v>11</v>
       </c>
       <c r="E194" s="2">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="F194" s="3" t="s">
         <v>12</v>
@@ -8019,7 +8019,7 @@
         <v>11</v>
       </c>
       <c r="E195" s="4">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="F195" s="3" t="s">
         <v>12</v>
@@ -8045,7 +8045,7 @@
         <v>11</v>
       </c>
       <c r="E196" s="2">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="F196" s="3" t="s">
         <v>12</v>
@@ -8071,7 +8071,7 @@
         <v>11</v>
       </c>
       <c r="E197" s="4">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="F197" s="3" t="s">
         <v>12</v>
@@ -8097,7 +8097,7 @@
         <v>11</v>
       </c>
       <c r="E198" s="2">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="F198" s="3" t="s">
         <v>12</v>
@@ -8123,7 +8123,7 @@
         <v>11</v>
       </c>
       <c r="E199" s="4">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="F199" s="3" t="s">
         <v>12</v>
@@ -8149,7 +8149,7 @@
         <v>11</v>
       </c>
       <c r="E200" s="2">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="F200" s="3" t="s">
         <v>12</v>
@@ -8175,7 +8175,7 @@
         <v>11</v>
       </c>
       <c r="E201" s="4">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="F201" s="3" t="s">
         <v>12</v>
@@ -8201,7 +8201,7 @@
         <v>11</v>
       </c>
       <c r="E202" s="2">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="F202" s="3" t="s">
         <v>12</v>
@@ -8227,7 +8227,7 @@
         <v>11</v>
       </c>
       <c r="E203" s="4">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F203" s="3" t="s">
         <v>12</v>
@@ -8253,7 +8253,7 @@
         <v>11</v>
       </c>
       <c r="E204" s="2">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="F204" s="3" t="s">
         <v>12</v>
@@ -8279,7 +8279,7 @@
         <v>11</v>
       </c>
       <c r="E205" s="4">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="F205" s="3" t="s">
         <v>12</v>
@@ -8305,7 +8305,7 @@
         <v>11</v>
       </c>
       <c r="E206" s="2">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="F206" s="3" t="s">
         <v>12</v>
@@ -8331,7 +8331,7 @@
         <v>11</v>
       </c>
       <c r="E207" s="4">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F207" s="3" t="s">
         <v>12</v>
@@ -8357,7 +8357,7 @@
         <v>11</v>
       </c>
       <c r="E208" s="2">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F208" s="3" t="s">
         <v>12</v>
@@ -8383,7 +8383,7 @@
         <v>11</v>
       </c>
       <c r="E209" s="4">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="F209" s="3" t="s">
         <v>12</v>
@@ -8409,7 +8409,7 @@
         <v>11</v>
       </c>
       <c r="E210" s="2">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="F210" s="3" t="s">
         <v>12</v>
@@ -8435,7 +8435,7 @@
         <v>11</v>
       </c>
       <c r="E211" s="4">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F211" s="3" t="s">
         <v>12</v>
@@ -8461,7 +8461,7 @@
         <v>11</v>
       </c>
       <c r="E212" s="2">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="F212" s="3" t="s">
         <v>12</v>
@@ -8487,7 +8487,7 @@
         <v>11</v>
       </c>
       <c r="E213" s="4">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F213" s="3" t="s">
         <v>12</v>
@@ -8513,7 +8513,7 @@
         <v>11</v>
       </c>
       <c r="E214" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F214" s="3" t="s">
         <v>12</v>
@@ -8539,7 +8539,7 @@
         <v>11</v>
       </c>
       <c r="E215" s="4">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="F215" s="3" t="s">
         <v>12</v>
@@ -8565,7 +8565,7 @@
         <v>11</v>
       </c>
       <c r="E216" s="2">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="F216" s="3" t="s">
         <v>12</v>
@@ -8591,7 +8591,7 @@
         <v>11</v>
       </c>
       <c r="E217" s="4">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="F217" s="3" t="s">
         <v>12</v>
@@ -8617,7 +8617,7 @@
         <v>11</v>
       </c>
       <c r="E218" s="2">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F218" s="3" t="s">
         <v>12</v>
@@ -8669,7 +8669,7 @@
         <v>11</v>
       </c>
       <c r="E220" s="2">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="F220" s="3" t="s">
         <v>12</v>
@@ -8695,7 +8695,7 @@
         <v>11</v>
       </c>
       <c r="E221" s="4">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F221" s="3" t="s">
         <v>12</v>
@@ -8721,7 +8721,7 @@
         <v>11</v>
       </c>
       <c r="E222" s="2">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F222" s="3" t="s">
         <v>12</v>
@@ -8747,7 +8747,7 @@
         <v>11</v>
       </c>
       <c r="E223" s="4">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="F223" s="3" t="s">
         <v>12</v>
@@ -8773,7 +8773,7 @@
         <v>11</v>
       </c>
       <c r="E224" s="2">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="F224" s="3" t="s">
         <v>12</v>
@@ -8799,7 +8799,7 @@
         <v>11</v>
       </c>
       <c r="E225" s="4">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F225" s="3" t="s">
         <v>12</v>
@@ -8825,7 +8825,7 @@
         <v>11</v>
       </c>
       <c r="E226" s="2">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F226" s="3" t="s">
         <v>12</v>
@@ -8851,7 +8851,7 @@
         <v>11</v>
       </c>
       <c r="E227" s="4">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="F227" s="3" t="s">
         <v>12</v>
@@ -8903,7 +8903,7 @@
         <v>11</v>
       </c>
       <c r="E229" s="4">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="F229" s="3" t="s">
         <v>12</v>
@@ -8929,7 +8929,7 @@
         <v>11</v>
       </c>
       <c r="E230" s="2">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="F230" s="3" t="s">
         <v>12</v>
@@ -8955,7 +8955,7 @@
         <v>11</v>
       </c>
       <c r="E231" s="4">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="F231" s="3" t="s">
         <v>12</v>
@@ -8981,7 +8981,7 @@
         <v>11</v>
       </c>
       <c r="E232" s="2">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F232" s="3" t="s">
         <v>12</v>
@@ -9007,7 +9007,7 @@
         <v>11</v>
       </c>
       <c r="E233" s="4">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="F233" s="3" t="s">
         <v>12</v>
@@ -9033,7 +9033,7 @@
         <v>11</v>
       </c>
       <c r="E234" s="2">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="F234" s="3" t="s">
         <v>12</v>
@@ -9059,7 +9059,7 @@
         <v>11</v>
       </c>
       <c r="E235" s="4">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="F235" s="3" t="s">
         <v>12</v>
@@ -9085,7 +9085,7 @@
         <v>11</v>
       </c>
       <c r="E236" s="2">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="F236" s="3" t="s">
         <v>12</v>
@@ -9111,7 +9111,7 @@
         <v>11</v>
       </c>
       <c r="E237" s="4">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="F237" s="3" t="s">
         <v>12</v>
@@ -9137,7 +9137,7 @@
         <v>11</v>
       </c>
       <c r="E238" s="2">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="F238" s="3" t="s">
         <v>12</v>
@@ -9163,7 +9163,7 @@
         <v>11</v>
       </c>
       <c r="E239" s="4">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="F239" s="3" t="s">
         <v>12</v>
@@ -9189,7 +9189,7 @@
         <v>11</v>
       </c>
       <c r="E240" s="2">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="F240" s="3" t="s">
         <v>12</v>
@@ -9215,7 +9215,7 @@
         <v>11</v>
       </c>
       <c r="E241" s="4">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="F241" s="3" t="s">
         <v>12</v>
@@ -9241,7 +9241,7 @@
         <v>11</v>
       </c>
       <c r="E242" s="2">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="F242" s="3" t="s">
         <v>12</v>
@@ -9267,7 +9267,7 @@
         <v>11</v>
       </c>
       <c r="E243" s="4">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="F243" s="3" t="s">
         <v>12</v>
@@ -9293,7 +9293,7 @@
         <v>11</v>
       </c>
       <c r="E244" s="2">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F244" s="3" t="s">
         <v>12</v>
@@ -9319,7 +9319,7 @@
         <v>11</v>
       </c>
       <c r="E245" s="4">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F245" s="3" t="s">
         <v>12</v>
@@ -9345,7 +9345,7 @@
         <v>11</v>
       </c>
       <c r="E246" s="2">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="F246" s="3" t="s">
         <v>12</v>
@@ -9371,7 +9371,7 @@
         <v>11</v>
       </c>
       <c r="E247" s="4">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F247" s="3" t="s">
         <v>12</v>
@@ -9397,7 +9397,7 @@
         <v>11</v>
       </c>
       <c r="E248" s="2">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F248" s="3" t="s">
         <v>12</v>
@@ -9423,7 +9423,7 @@
         <v>11</v>
       </c>
       <c r="E249" s="4">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="F249" s="3" t="s">
         <v>12</v>
@@ -9449,7 +9449,7 @@
         <v>11</v>
       </c>
       <c r="E250" s="2">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="F250" s="3" t="s">
         <v>12</v>
@@ -9475,7 +9475,7 @@
         <v>11</v>
       </c>
       <c r="E251" s="4">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="F251" s="3" t="s">
         <v>12</v>
@@ -9501,7 +9501,7 @@
         <v>11</v>
       </c>
       <c r="E252" s="2">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="F252" s="3" t="s">
         <v>12</v>
@@ -9527,7 +9527,7 @@
         <v>11</v>
       </c>
       <c r="E253" s="4">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="F253" s="3" t="s">
         <v>12</v>
@@ -9553,7 +9553,7 @@
         <v>11</v>
       </c>
       <c r="E254" s="2">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F254" s="3" t="s">
         <v>12</v>
@@ -9579,7 +9579,7 @@
         <v>11</v>
       </c>
       <c r="E255" s="4">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="F255" s="3" t="s">
         <v>12</v>
@@ -9605,7 +9605,7 @@
         <v>11</v>
       </c>
       <c r="E256" s="2">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="F256" s="3" t="s">
         <v>12</v>
@@ -9631,7 +9631,7 @@
         <v>11</v>
       </c>
       <c r="E257" s="4">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F257" s="3" t="s">
         <v>12</v>
@@ -9657,7 +9657,7 @@
         <v>11</v>
       </c>
       <c r="E258" s="2">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="F258" s="3" t="s">
         <v>12</v>
@@ -9683,7 +9683,7 @@
         <v>11</v>
       </c>
       <c r="E259" s="4">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="F259" s="3" t="s">
         <v>12</v>
@@ -9709,7 +9709,7 @@
         <v>11</v>
       </c>
       <c r="E260" s="2">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F260" s="3" t="s">
         <v>12</v>
@@ -9735,7 +9735,7 @@
         <v>11</v>
       </c>
       <c r="E261" s="4">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F261" s="3" t="s">
         <v>12</v>
@@ -9761,7 +9761,7 @@
         <v>11</v>
       </c>
       <c r="E262" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F262" s="3" t="s">
         <v>12</v>
@@ -9787,7 +9787,7 @@
         <v>11</v>
       </c>
       <c r="E263" s="4">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="F263" s="3" t="s">
         <v>12</v>
@@ -9813,7 +9813,7 @@
         <v>11</v>
       </c>
       <c r="E264" s="2">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F264" s="3" t="s">
         <v>12</v>
@@ -9839,7 +9839,7 @@
         <v>11</v>
       </c>
       <c r="E265" s="4">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="F265" s="3" t="s">
         <v>12</v>
@@ -9891,7 +9891,7 @@
         <v>11</v>
       </c>
       <c r="E267" s="4">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="F267" s="3" t="s">
         <v>12</v>
@@ -9917,7 +9917,7 @@
         <v>11</v>
       </c>
       <c r="E268" s="2">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="F268" s="3" t="s">
         <v>12</v>
@@ -9943,7 +9943,7 @@
         <v>11</v>
       </c>
       <c r="E269" s="4">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F269" s="3" t="s">
         <v>12</v>
@@ -9969,7 +9969,7 @@
         <v>11</v>
       </c>
       <c r="E270" s="2">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="F270" s="3" t="s">
         <v>12</v>
@@ -9995,7 +9995,7 @@
         <v>11</v>
       </c>
       <c r="E271" s="4">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="F271" s="3" t="s">
         <v>12</v>
@@ -10021,7 +10021,7 @@
         <v>11</v>
       </c>
       <c r="E272" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F272" s="3" t="s">
         <v>12</v>
@@ -10047,7 +10047,7 @@
         <v>11</v>
       </c>
       <c r="E273" s="4">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F273" s="3" t="s">
         <v>12</v>
@@ -10099,7 +10099,7 @@
         <v>11</v>
       </c>
       <c r="E275" s="4">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F275" s="3" t="s">
         <v>12</v>
@@ -10125,7 +10125,7 @@
         <v>11</v>
       </c>
       <c r="E276" s="2">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F276" s="3" t="s">
         <v>12</v>
@@ -10151,7 +10151,7 @@
         <v>11</v>
       </c>
       <c r="E277" s="4">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="F277" s="3" t="s">
         <v>12</v>
@@ -10177,7 +10177,7 @@
         <v>11</v>
       </c>
       <c r="E278" s="2">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="F278" s="3" t="s">
         <v>12</v>
@@ -10203,7 +10203,7 @@
         <v>11</v>
       </c>
       <c r="E279" s="4">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F279" s="3" t="s">
         <v>12</v>
@@ -10229,7 +10229,7 @@
         <v>11</v>
       </c>
       <c r="E280" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F280" s="3" t="s">
         <v>12</v>
@@ -10255,7 +10255,7 @@
         <v>11</v>
       </c>
       <c r="E281" s="4">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="F281" s="3" t="s">
         <v>12</v>
@@ -10281,7 +10281,7 @@
         <v>11</v>
       </c>
       <c r="E282" s="2">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="F282" s="3" t="s">
         <v>12</v>
@@ -10307,7 +10307,7 @@
         <v>11</v>
       </c>
       <c r="E283" s="4">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F283" s="3" t="s">
         <v>12</v>
@@ -10333,7 +10333,7 @@
         <v>11</v>
       </c>
       <c r="E284" s="2">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="F284" s="3" t="s">
         <v>12</v>
@@ -10359,7 +10359,7 @@
         <v>11</v>
       </c>
       <c r="E285" s="4">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="F285" s="3" t="s">
         <v>12</v>
@@ -10385,7 +10385,7 @@
         <v>11</v>
       </c>
       <c r="E286" s="2">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F286" s="3" t="s">
         <v>12</v>
@@ -10411,7 +10411,7 @@
         <v>11</v>
       </c>
       <c r="E287" s="4">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="F287" s="3" t="s">
         <v>12</v>
@@ -10437,7 +10437,7 @@
         <v>11</v>
       </c>
       <c r="E288" s="2">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="F288" s="3" t="s">
         <v>12</v>
@@ -10489,7 +10489,7 @@
         <v>11</v>
       </c>
       <c r="E290" s="2">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="F290" s="3" t="s">
         <v>12</v>
@@ -10515,7 +10515,7 @@
         <v>11</v>
       </c>
       <c r="E291" s="4">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="F291" s="3" t="s">
         <v>12</v>
@@ -10541,7 +10541,7 @@
         <v>11</v>
       </c>
       <c r="E292" s="2">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="F292" s="3" t="s">
         <v>12</v>
@@ -10567,7 +10567,7 @@
         <v>11</v>
       </c>
       <c r="E293" s="4">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="F293" s="3" t="s">
         <v>12</v>
@@ -10593,7 +10593,7 @@
         <v>11</v>
       </c>
       <c r="E294" s="2">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F294" s="3" t="s">
         <v>12</v>
@@ -10619,7 +10619,7 @@
         <v>11</v>
       </c>
       <c r="E295" s="4">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F295" s="3" t="s">
         <v>12</v>
@@ -10645,7 +10645,7 @@
         <v>11</v>
       </c>
       <c r="E296" s="2">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="F296" s="3" t="s">
         <v>12</v>
@@ -10671,7 +10671,7 @@
         <v>11</v>
       </c>
       <c r="E297" s="4">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="F297" s="3" t="s">
         <v>12</v>
@@ -10697,7 +10697,7 @@
         <v>11</v>
       </c>
       <c r="E298" s="2">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="F298" s="3" t="s">
         <v>12</v>
@@ -10723,7 +10723,7 @@
         <v>11</v>
       </c>
       <c r="E299" s="4">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="F299" s="3" t="s">
         <v>12</v>
@@ -10749,7 +10749,7 @@
         <v>11</v>
       </c>
       <c r="E300" s="2">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="F300" s="3" t="s">
         <v>12</v>
@@ -10775,7 +10775,7 @@
         <v>11</v>
       </c>
       <c r="E301" s="4">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="F301" s="3" t="s">
         <v>12</v>
@@ -10801,7 +10801,7 @@
         <v>11</v>
       </c>
       <c r="E302" s="2">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F302" s="3" t="s">
         <v>12</v>
@@ -10827,7 +10827,7 @@
         <v>11</v>
       </c>
       <c r="E303" s="4">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="F303" s="3" t="s">
         <v>12</v>
@@ -10853,7 +10853,7 @@
         <v>11</v>
       </c>
       <c r="E304" s="2">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="F304" s="3" t="s">
         <v>12</v>
@@ -10879,7 +10879,7 @@
         <v>11</v>
       </c>
       <c r="E305" s="4">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="F305" s="3" t="s">
         <v>12</v>
@@ -10905,7 +10905,7 @@
         <v>11</v>
       </c>
       <c r="E306" s="2">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="F306" s="3" t="s">
         <v>12</v>
@@ -10931,7 +10931,7 @@
         <v>11</v>
       </c>
       <c r="E307" s="4">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="F307" s="3" t="s">
         <v>12</v>
@@ -10957,7 +10957,7 @@
         <v>11</v>
       </c>
       <c r="E308" s="2">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F308" s="3" t="s">
         <v>12</v>
@@ -10983,7 +10983,7 @@
         <v>11</v>
       </c>
       <c r="E309" s="4">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="F309" s="3" t="s">
         <v>12</v>
@@ -11009,7 +11009,7 @@
         <v>11</v>
       </c>
       <c r="E310" s="2">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="F310" s="3" t="s">
         <v>12</v>
@@ -11035,7 +11035,7 @@
         <v>11</v>
       </c>
       <c r="E311" s="4">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F311" s="3" t="s">
         <v>12</v>
@@ -11061,7 +11061,7 @@
         <v>11</v>
       </c>
       <c r="E312" s="2">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="F312" s="3" t="s">
         <v>12</v>
@@ -11087,7 +11087,7 @@
         <v>11</v>
       </c>
       <c r="E313" s="4">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F313" s="3" t="s">
         <v>12</v>
@@ -11113,7 +11113,7 @@
         <v>11</v>
       </c>
       <c r="E314" s="2">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="F314" s="3" t="s">
         <v>12</v>
@@ -11139,7 +11139,7 @@
         <v>11</v>
       </c>
       <c r="E315" s="4">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="F315" s="3" t="s">
         <v>12</v>
@@ -11165,7 +11165,7 @@
         <v>11</v>
       </c>
       <c r="E316" s="2">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="F316" s="3" t="s">
         <v>12</v>
@@ -11191,7 +11191,7 @@
         <v>11</v>
       </c>
       <c r="E317" s="4">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="F317" s="3" t="s">
         <v>12</v>
@@ -11217,7 +11217,7 @@
         <v>11</v>
       </c>
       <c r="E318" s="2">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F318" s="3" t="s">
         <v>12</v>
@@ -11243,7 +11243,7 @@
         <v>11</v>
       </c>
       <c r="E319" s="4">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="F319" s="3" t="s">
         <v>12</v>
@@ -11321,7 +11321,7 @@
         <v>11</v>
       </c>
       <c r="E322" s="2">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="F322" s="3" t="s">
         <v>12</v>
@@ -11347,7 +11347,7 @@
         <v>11</v>
       </c>
       <c r="E323" s="4">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="F323" s="3" t="s">
         <v>12</v>
@@ -11373,7 +11373,7 @@
         <v>11</v>
       </c>
       <c r="E324" s="2">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F324" s="3" t="s">
         <v>12</v>
@@ -11399,7 +11399,7 @@
         <v>11</v>
       </c>
       <c r="E325" s="4">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F325" s="3" t="s">
         <v>12</v>
@@ -11425,7 +11425,7 @@
         <v>11</v>
       </c>
       <c r="E326" s="2">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="F326" s="3" t="s">
         <v>12</v>
@@ -11451,7 +11451,7 @@
         <v>11</v>
       </c>
       <c r="E327" s="4">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F327" s="3" t="s">
         <v>12</v>
@@ -11477,7 +11477,7 @@
         <v>11</v>
       </c>
       <c r="E328" s="2">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="F328" s="3" t="s">
         <v>12</v>
@@ -11503,7 +11503,7 @@
         <v>11</v>
       </c>
       <c r="E329" s="4">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F329" s="3" t="s">
         <v>12</v>
@@ -11529,7 +11529,7 @@
         <v>11</v>
       </c>
       <c r="E330" s="2">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F330" s="3" t="s">
         <v>12</v>
@@ -11555,7 +11555,7 @@
         <v>11</v>
       </c>
       <c r="E331" s="4">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="F331" s="3" t="s">
         <v>12</v>
@@ -11581,7 +11581,7 @@
         <v>11</v>
       </c>
       <c r="E332" s="2">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="F332" s="3" t="s">
         <v>12</v>
@@ -11607,7 +11607,7 @@
         <v>11</v>
       </c>
       <c r="E333" s="4">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F333" s="3" t="s">
         <v>12</v>
@@ -11633,7 +11633,7 @@
         <v>11</v>
       </c>
       <c r="E334" s="2">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="F334" s="3" t="s">
         <v>12</v>
@@ -11659,7 +11659,7 @@
         <v>11</v>
       </c>
       <c r="E335" s="4">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="F335" s="3" t="s">
         <v>12</v>
@@ -11685,7 +11685,7 @@
         <v>11</v>
       </c>
       <c r="E336" s="2">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F336" s="3" t="s">
         <v>12</v>
@@ -11711,7 +11711,7 @@
         <v>11</v>
       </c>
       <c r="E337" s="4">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F337" s="3" t="s">
         <v>12</v>
@@ -11737,7 +11737,7 @@
         <v>11</v>
       </c>
       <c r="E338" s="2">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="F338" s="3" t="s">
         <v>12</v>
@@ -11763,7 +11763,7 @@
         <v>11</v>
       </c>
       <c r="E339" s="4">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F339" s="3" t="s">
         <v>12</v>
@@ -11789,7 +11789,7 @@
         <v>11</v>
       </c>
       <c r="E340" s="2">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F340" s="3" t="s">
         <v>12</v>
@@ -11815,7 +11815,7 @@
         <v>11</v>
       </c>
       <c r="E341" s="4">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F341" s="3" t="s">
         <v>12</v>
@@ -11841,7 +11841,7 @@
         <v>11</v>
       </c>
       <c r="E342" s="2">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F342" s="3" t="s">
         <v>12</v>
@@ -11867,7 +11867,7 @@
         <v>11</v>
       </c>
       <c r="E343" s="4">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F343" s="3" t="s">
         <v>12</v>
@@ -11893,7 +11893,7 @@
         <v>11</v>
       </c>
       <c r="E344" s="2">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="F344" s="3" t="s">
         <v>12</v>
@@ -11919,7 +11919,7 @@
         <v>11</v>
       </c>
       <c r="E345" s="4">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="F345" s="3" t="s">
         <v>12</v>
@@ -11945,7 +11945,7 @@
         <v>11</v>
       </c>
       <c r="E346" s="2">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="F346" s="3" t="s">
         <v>12</v>
@@ -11971,7 +11971,7 @@
         <v>11</v>
       </c>
       <c r="E347" s="4">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F347" s="3" t="s">
         <v>12</v>
@@ -11997,7 +11997,7 @@
         <v>11</v>
       </c>
       <c r="E348" s="2">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="F348" s="3" t="s">
         <v>12</v>
@@ -12023,7 +12023,7 @@
         <v>11</v>
       </c>
       <c r="E349" s="4">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F349" s="3" t="s">
         <v>12</v>
@@ -12049,7 +12049,7 @@
         <v>11</v>
       </c>
       <c r="E350" s="2">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="F350" s="3" t="s">
         <v>12</v>
@@ -12075,7 +12075,7 @@
         <v>11</v>
       </c>
       <c r="E351" s="4">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="F351" s="3" t="s">
         <v>12</v>
@@ -12101,7 +12101,7 @@
         <v>11</v>
       </c>
       <c r="E352" s="2">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="F352" s="3" t="s">
         <v>12</v>
@@ -12127,7 +12127,7 @@
         <v>11</v>
       </c>
       <c r="E353" s="4">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F353" s="3" t="s">
         <v>12</v>
@@ -12153,7 +12153,7 @@
         <v>11</v>
       </c>
       <c r="E354" s="2">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="F354" s="3" t="s">
         <v>12</v>
@@ -12205,7 +12205,7 @@
         <v>11</v>
       </c>
       <c r="E356" s="2">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F356" s="3" t="s">
         <v>12</v>
@@ -12231,7 +12231,7 @@
         <v>11</v>
       </c>
       <c r="E357" s="4">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F357" s="3" t="s">
         <v>12</v>
@@ -12283,7 +12283,7 @@
         <v>11</v>
       </c>
       <c r="E359" s="4">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="F359" s="3" t="s">
         <v>12</v>
@@ -12309,7 +12309,7 @@
         <v>11</v>
       </c>
       <c r="E360" s="2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F360" s="3" t="s">
         <v>12</v>
@@ -12335,7 +12335,7 @@
         <v>11</v>
       </c>
       <c r="E361" s="4">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="F361" s="3" t="s">
         <v>12</v>
@@ -12361,7 +12361,7 @@
         <v>11</v>
       </c>
       <c r="E362" s="2">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="F362" s="3" t="s">
         <v>12</v>
@@ -12387,7 +12387,7 @@
         <v>11</v>
       </c>
       <c r="E363" s="4">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="F363" s="3" t="s">
         <v>12</v>
@@ -12413,7 +12413,7 @@
         <v>11</v>
       </c>
       <c r="E364" s="2">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="F364" s="3" t="s">
         <v>12</v>
@@ -12439,7 +12439,7 @@
         <v>11</v>
       </c>
       <c r="E365" s="4">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F365" s="3" t="s">
         <v>12</v>
@@ -12465,7 +12465,7 @@
         <v>11</v>
       </c>
       <c r="E366" s="2">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="F366" s="3" t="s">
         <v>12</v>
@@ -12491,7 +12491,7 @@
         <v>11</v>
       </c>
       <c r="E367" s="4">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="F367" s="3" t="s">
         <v>12</v>
@@ -12517,7 +12517,7 @@
         <v>11</v>
       </c>
       <c r="E368" s="2">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F368" s="3" t="s">
         <v>12</v>
@@ -12543,7 +12543,7 @@
         <v>11</v>
       </c>
       <c r="E369" s="4">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="F369" s="3" t="s">
         <v>12</v>
@@ -12569,7 +12569,7 @@
         <v>11</v>
       </c>
       <c r="E370" s="2">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="F370" s="3" t="s">
         <v>12</v>
@@ -12595,7 +12595,7 @@
         <v>11</v>
       </c>
       <c r="E371" s="4">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="F371" s="3" t="s">
         <v>12</v>
@@ -12621,7 +12621,7 @@
         <v>11</v>
       </c>
       <c r="E372" s="2">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="F372" s="3" t="s">
         <v>12</v>
@@ -12647,7 +12647,7 @@
         <v>11</v>
       </c>
       <c r="E373" s="4">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="F373" s="3" t="s">
         <v>12</v>
@@ -12673,7 +12673,7 @@
         <v>11</v>
       </c>
       <c r="E374" s="2">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="F374" s="3" t="s">
         <v>12</v>
@@ -12699,7 +12699,7 @@
         <v>11</v>
       </c>
       <c r="E375" s="4">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="F375" s="3" t="s">
         <v>12</v>
@@ -12725,7 +12725,7 @@
         <v>11</v>
       </c>
       <c r="E376" s="2">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="F376" s="3" t="s">
         <v>12</v>
@@ -12751,7 +12751,7 @@
         <v>11</v>
       </c>
       <c r="E377" s="4">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="F377" s="3" t="s">
         <v>12</v>
@@ -12777,7 +12777,7 @@
         <v>11</v>
       </c>
       <c r="E378" s="2">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="F378" s="3" t="s">
         <v>12</v>
@@ -12803,7 +12803,7 @@
         <v>11</v>
       </c>
       <c r="E379" s="4">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F379" s="3" t="s">
         <v>12</v>
@@ -12829,7 +12829,7 @@
         <v>11</v>
       </c>
       <c r="E380" s="2">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="F380" s="3" t="s">
         <v>12</v>
@@ -12855,7 +12855,7 @@
         <v>11</v>
       </c>
       <c r="E381" s="4">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F381" s="3" t="s">
         <v>12</v>
@@ -12881,7 +12881,7 @@
         <v>11</v>
       </c>
       <c r="E382" s="2">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F382" s="3" t="s">
         <v>12</v>
@@ -12907,7 +12907,7 @@
         <v>11</v>
       </c>
       <c r="E383" s="4">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="F383" s="3" t="s">
         <v>12</v>
@@ -12933,7 +12933,7 @@
         <v>11</v>
       </c>
       <c r="E384" s="2">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="F384" s="3" t="s">
         <v>12</v>
@@ -12959,7 +12959,7 @@
         <v>11</v>
       </c>
       <c r="E385" s="4">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="F385" s="3" t="s">
         <v>12</v>
@@ -12985,7 +12985,7 @@
         <v>11</v>
       </c>
       <c r="E386" s="2">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="F386" s="3" t="s">
         <v>12</v>
@@ -13011,7 +13011,7 @@
         <v>11</v>
       </c>
       <c r="E387" s="4">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="F387" s="3" t="s">
         <v>12</v>
@@ -13037,7 +13037,7 @@
         <v>11</v>
       </c>
       <c r="E388" s="2">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="F388" s="3" t="s">
         <v>12</v>
@@ -13063,7 +13063,7 @@
         <v>11</v>
       </c>
       <c r="E389" s="4">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="F389" s="3" t="s">
         <v>12</v>
@@ -13089,7 +13089,7 @@
         <v>11</v>
       </c>
       <c r="E390" s="2">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="F390" s="3" t="s">
         <v>12</v>
@@ -13115,7 +13115,7 @@
         <v>11</v>
       </c>
       <c r="E391" s="4">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="F391" s="3" t="s">
         <v>12</v>
@@ -13141,7 +13141,7 @@
         <v>11</v>
       </c>
       <c r="E392" s="2">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="F392" s="3" t="s">
         <v>12</v>
@@ -13167,7 +13167,7 @@
         <v>11</v>
       </c>
       <c r="E393" s="4">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="F393" s="3" t="s">
         <v>12</v>
@@ -13193,7 +13193,7 @@
         <v>11</v>
       </c>
       <c r="E394" s="2">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F394" s="3" t="s">
         <v>12</v>
@@ -13219,7 +13219,7 @@
         <v>11</v>
       </c>
       <c r="E395" s="4">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="F395" s="3" t="s">
         <v>12</v>
@@ -13245,7 +13245,7 @@
         <v>11</v>
       </c>
       <c r="E396" s="2">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F396" s="3" t="s">
         <v>12</v>
@@ -13271,7 +13271,7 @@
         <v>11</v>
       </c>
       <c r="E397" s="4">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="F397" s="3" t="s">
         <v>12</v>
@@ -13297,7 +13297,7 @@
         <v>11</v>
       </c>
       <c r="E398" s="2">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="F398" s="3" t="s">
         <v>12</v>
@@ -13323,7 +13323,7 @@
         <v>11</v>
       </c>
       <c r="E399" s="4">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="F399" s="3" t="s">
         <v>12</v>
@@ -13349,7 +13349,7 @@
         <v>11</v>
       </c>
       <c r="E400" s="2">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="F400" s="3" t="s">
         <v>12</v>
@@ -13375,7 +13375,7 @@
         <v>11</v>
       </c>
       <c r="E401" s="4">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F401" s="3" t="s">
         <v>12</v>

--- a/reports/Mobile_Appium_E2E_Test_Report_400.xlsx
+++ b/reports/Mobile_Appium_E2E_Test_Report_400.xlsx
@@ -52,7 +52,7 @@
     <t>PASSED</t>
   </si>
   <si>
-    <t>2026-08-10T08:42:32.516Z</t>
+    <t>2026-08-21T07:56:03.570Z</t>
   </si>
   <si>
     <t>Verified Android Activity lifecycle and Capacitor native plugin interface</t>
@@ -3001,7 +3001,7 @@
         <v>11</v>
       </c>
       <c r="E2" s="2">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>12</v>
@@ -3027,7 +3027,7 @@
         <v>11</v>
       </c>
       <c r="E3" s="4">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>12</v>
@@ -3053,7 +3053,7 @@
         <v>11</v>
       </c>
       <c r="E4" s="2">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="F4" s="3" t="s">
         <v>12</v>
@@ -3105,7 +3105,7 @@
         <v>11</v>
       </c>
       <c r="E6" s="2">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F6" s="3" t="s">
         <v>12</v>
@@ -3131,7 +3131,7 @@
         <v>11</v>
       </c>
       <c r="E7" s="4">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F7" s="3" t="s">
         <v>12</v>
@@ -3157,7 +3157,7 @@
         <v>11</v>
       </c>
       <c r="E8" s="2">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="F8" s="3" t="s">
         <v>12</v>
@@ -3183,7 +3183,7 @@
         <v>11</v>
       </c>
       <c r="E9" s="4">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="F9" s="3" t="s">
         <v>12</v>
@@ -3209,7 +3209,7 @@
         <v>11</v>
       </c>
       <c r="E10" s="2">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F10" s="3" t="s">
         <v>12</v>
@@ -3235,7 +3235,7 @@
         <v>11</v>
       </c>
       <c r="E11" s="4">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="F11" s="3" t="s">
         <v>12</v>
@@ -3287,7 +3287,7 @@
         <v>11</v>
       </c>
       <c r="E13" s="4">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F13" s="3" t="s">
         <v>12</v>
@@ -3313,7 +3313,7 @@
         <v>11</v>
       </c>
       <c r="E14" s="2">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>12</v>
@@ -3339,7 +3339,7 @@
         <v>11</v>
       </c>
       <c r="E15" s="4">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="F15" s="3" t="s">
         <v>12</v>
@@ -3365,7 +3365,7 @@
         <v>11</v>
       </c>
       <c r="E16" s="2">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="F16" s="3" t="s">
         <v>12</v>
@@ -3391,7 +3391,7 @@
         <v>11</v>
       </c>
       <c r="E17" s="4">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="F17" s="3" t="s">
         <v>12</v>
@@ -3417,7 +3417,7 @@
         <v>11</v>
       </c>
       <c r="E18" s="2">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="F18" s="3" t="s">
         <v>12</v>
@@ -3443,7 +3443,7 @@
         <v>11</v>
       </c>
       <c r="E19" s="4">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="F19" s="3" t="s">
         <v>12</v>
@@ -3495,7 +3495,7 @@
         <v>11</v>
       </c>
       <c r="E21" s="4">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="F21" s="3" t="s">
         <v>12</v>
@@ -3521,7 +3521,7 @@
         <v>11</v>
       </c>
       <c r="E22" s="2">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="F22" s="3" t="s">
         <v>12</v>
@@ -3547,7 +3547,7 @@
         <v>11</v>
       </c>
       <c r="E23" s="4">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="F23" s="3" t="s">
         <v>12</v>
@@ -3573,7 +3573,7 @@
         <v>11</v>
       </c>
       <c r="E24" s="2">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="F24" s="3" t="s">
         <v>12</v>
@@ -3599,7 +3599,7 @@
         <v>11</v>
       </c>
       <c r="E25" s="4">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F25" s="3" t="s">
         <v>12</v>
@@ -3625,7 +3625,7 @@
         <v>11</v>
       </c>
       <c r="E26" s="2">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="F26" s="3" t="s">
         <v>12</v>
@@ -3703,7 +3703,7 @@
         <v>11</v>
       </c>
       <c r="E29" s="4">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="F29" s="3" t="s">
         <v>12</v>
@@ -3729,7 +3729,7 @@
         <v>11</v>
       </c>
       <c r="E30" s="2">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="F30" s="3" t="s">
         <v>12</v>
@@ -3755,7 +3755,7 @@
         <v>11</v>
       </c>
       <c r="E31" s="4">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="F31" s="3" t="s">
         <v>12</v>
@@ -3781,7 +3781,7 @@
         <v>11</v>
       </c>
       <c r="E32" s="2">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F32" s="3" t="s">
         <v>12</v>
@@ -3807,7 +3807,7 @@
         <v>11</v>
       </c>
       <c r="E33" s="4">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F33" s="3" t="s">
         <v>12</v>
@@ -3833,7 +3833,7 @@
         <v>11</v>
       </c>
       <c r="E34" s="2">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="F34" s="3" t="s">
         <v>12</v>
@@ -3859,7 +3859,7 @@
         <v>11</v>
       </c>
       <c r="E35" s="4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F35" s="3" t="s">
         <v>12</v>
@@ -3885,7 +3885,7 @@
         <v>11</v>
       </c>
       <c r="E36" s="2">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="F36" s="3" t="s">
         <v>12</v>
@@ -3911,7 +3911,7 @@
         <v>11</v>
       </c>
       <c r="E37" s="4">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="F37" s="3" t="s">
         <v>12</v>
@@ -3937,7 +3937,7 @@
         <v>11</v>
       </c>
       <c r="E38" s="2">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="F38" s="3" t="s">
         <v>12</v>
@@ -3963,7 +3963,7 @@
         <v>11</v>
       </c>
       <c r="E39" s="4">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="F39" s="3" t="s">
         <v>12</v>
@@ -4015,7 +4015,7 @@
         <v>11</v>
       </c>
       <c r="E41" s="4">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="F41" s="3" t="s">
         <v>12</v>
@@ -4041,7 +4041,7 @@
         <v>11</v>
       </c>
       <c r="E42" s="2">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F42" s="3" t="s">
         <v>12</v>
@@ -4067,7 +4067,7 @@
         <v>11</v>
       </c>
       <c r="E43" s="4">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="F43" s="3" t="s">
         <v>12</v>
@@ -4093,7 +4093,7 @@
         <v>11</v>
       </c>
       <c r="E44" s="2">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="F44" s="3" t="s">
         <v>12</v>
@@ -4119,7 +4119,7 @@
         <v>11</v>
       </c>
       <c r="E45" s="4">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="F45" s="3" t="s">
         <v>12</v>
@@ -4145,7 +4145,7 @@
         <v>11</v>
       </c>
       <c r="E46" s="2">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="F46" s="3" t="s">
         <v>12</v>
@@ -4171,7 +4171,7 @@
         <v>11</v>
       </c>
       <c r="E47" s="4">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F47" s="3" t="s">
         <v>12</v>
@@ -4197,7 +4197,7 @@
         <v>11</v>
       </c>
       <c r="E48" s="2">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="F48" s="3" t="s">
         <v>12</v>
@@ -4249,7 +4249,7 @@
         <v>11</v>
       </c>
       <c r="E50" s="2">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F50" s="3" t="s">
         <v>12</v>
@@ -4275,7 +4275,7 @@
         <v>11</v>
       </c>
       <c r="E51" s="4">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F51" s="3" t="s">
         <v>12</v>
@@ -4301,7 +4301,7 @@
         <v>11</v>
       </c>
       <c r="E52" s="2">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="F52" s="3" t="s">
         <v>12</v>
@@ -4327,7 +4327,7 @@
         <v>11</v>
       </c>
       <c r="E53" s="4">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="F53" s="3" t="s">
         <v>12</v>
@@ -4353,7 +4353,7 @@
         <v>11</v>
       </c>
       <c r="E54" s="2">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F54" s="3" t="s">
         <v>12</v>
@@ -4379,7 +4379,7 @@
         <v>11</v>
       </c>
       <c r="E55" s="4">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F55" s="3" t="s">
         <v>12</v>
@@ -4405,7 +4405,7 @@
         <v>11</v>
       </c>
       <c r="E56" s="2">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="F56" s="3" t="s">
         <v>12</v>
@@ -4457,7 +4457,7 @@
         <v>11</v>
       </c>
       <c r="E58" s="2">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="F58" s="3" t="s">
         <v>12</v>
@@ -4483,7 +4483,7 @@
         <v>11</v>
       </c>
       <c r="E59" s="4">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="F59" s="3" t="s">
         <v>12</v>
@@ -4509,7 +4509,7 @@
         <v>11</v>
       </c>
       <c r="E60" s="2">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F60" s="3" t="s">
         <v>12</v>
@@ -4535,7 +4535,7 @@
         <v>11</v>
       </c>
       <c r="E61" s="4">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="F61" s="3" t="s">
         <v>12</v>
@@ -4561,7 +4561,7 @@
         <v>11</v>
       </c>
       <c r="E62" s="2">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="F62" s="3" t="s">
         <v>12</v>
@@ -4587,7 +4587,7 @@
         <v>11</v>
       </c>
       <c r="E63" s="4">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="F63" s="3" t="s">
         <v>12</v>
@@ -4613,7 +4613,7 @@
         <v>11</v>
       </c>
       <c r="E64" s="2">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F64" s="3" t="s">
         <v>12</v>
@@ -4639,7 +4639,7 @@
         <v>11</v>
       </c>
       <c r="E65" s="4">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="F65" s="3" t="s">
         <v>12</v>
@@ -4665,7 +4665,7 @@
         <v>11</v>
       </c>
       <c r="E66" s="2">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="F66" s="3" t="s">
         <v>12</v>
@@ -4691,7 +4691,7 @@
         <v>11</v>
       </c>
       <c r="E67" s="4">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="F67" s="3" t="s">
         <v>12</v>
@@ -4743,7 +4743,7 @@
         <v>11</v>
       </c>
       <c r="E69" s="4">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="F69" s="3" t="s">
         <v>12</v>
@@ -4769,7 +4769,7 @@
         <v>11</v>
       </c>
       <c r="E70" s="2">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="F70" s="3" t="s">
         <v>12</v>
@@ -4795,7 +4795,7 @@
         <v>11</v>
       </c>
       <c r="E71" s="4">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F71" s="3" t="s">
         <v>12</v>
@@ -4821,7 +4821,7 @@
         <v>11</v>
       </c>
       <c r="E72" s="2">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="F72" s="3" t="s">
         <v>12</v>
@@ -4847,7 +4847,7 @@
         <v>11</v>
       </c>
       <c r="E73" s="4">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="F73" s="3" t="s">
         <v>12</v>
@@ -4873,7 +4873,7 @@
         <v>11</v>
       </c>
       <c r="E74" s="2">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="F74" s="3" t="s">
         <v>12</v>
@@ -4899,7 +4899,7 @@
         <v>11</v>
       </c>
       <c r="E75" s="4">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="F75" s="3" t="s">
         <v>12</v>
@@ -4925,7 +4925,7 @@
         <v>11</v>
       </c>
       <c r="E76" s="2">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F76" s="3" t="s">
         <v>12</v>
@@ -4951,7 +4951,7 @@
         <v>11</v>
       </c>
       <c r="E77" s="4">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="F77" s="3" t="s">
         <v>12</v>
@@ -4977,7 +4977,7 @@
         <v>11</v>
       </c>
       <c r="E78" s="2">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="F78" s="3" t="s">
         <v>12</v>
@@ -5003,7 +5003,7 @@
         <v>11</v>
       </c>
       <c r="E79" s="4">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="F79" s="3" t="s">
         <v>12</v>
@@ -5029,7 +5029,7 @@
         <v>11</v>
       </c>
       <c r="E80" s="2">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="F80" s="3" t="s">
         <v>12</v>
@@ -5055,7 +5055,7 @@
         <v>11</v>
       </c>
       <c r="E81" s="4">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="F81" s="3" t="s">
         <v>12</v>
@@ -5081,7 +5081,7 @@
         <v>11</v>
       </c>
       <c r="E82" s="2">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="F82" s="3" t="s">
         <v>12</v>
@@ -5107,7 +5107,7 @@
         <v>11</v>
       </c>
       <c r="E83" s="4">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="F83" s="3" t="s">
         <v>12</v>
@@ -5133,7 +5133,7 @@
         <v>11</v>
       </c>
       <c r="E84" s="2">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="F84" s="3" t="s">
         <v>12</v>
@@ -5159,7 +5159,7 @@
         <v>11</v>
       </c>
       <c r="E85" s="4">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F85" s="3" t="s">
         <v>12</v>
@@ -5185,7 +5185,7 @@
         <v>11</v>
       </c>
       <c r="E86" s="2">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="F86" s="3" t="s">
         <v>12</v>
@@ -5211,7 +5211,7 @@
         <v>11</v>
       </c>
       <c r="E87" s="4">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F87" s="3" t="s">
         <v>12</v>
@@ -5237,7 +5237,7 @@
         <v>11</v>
       </c>
       <c r="E88" s="2">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F88" s="3" t="s">
         <v>12</v>
@@ -5263,7 +5263,7 @@
         <v>11</v>
       </c>
       <c r="E89" s="4">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="F89" s="3" t="s">
         <v>12</v>
@@ -5289,7 +5289,7 @@
         <v>11</v>
       </c>
       <c r="E90" s="2">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="F90" s="3" t="s">
         <v>12</v>
@@ -5315,7 +5315,7 @@
         <v>11</v>
       </c>
       <c r="E91" s="4">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="F91" s="3" t="s">
         <v>12</v>
@@ -5341,7 +5341,7 @@
         <v>11</v>
       </c>
       <c r="E92" s="2">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="F92" s="3" t="s">
         <v>12</v>
@@ -5367,7 +5367,7 @@
         <v>11</v>
       </c>
       <c r="E93" s="4">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F93" s="3" t="s">
         <v>12</v>
@@ -5393,7 +5393,7 @@
         <v>11</v>
       </c>
       <c r="E94" s="2">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="F94" s="3" t="s">
         <v>12</v>
@@ -5445,7 +5445,7 @@
         <v>11</v>
       </c>
       <c r="E96" s="2">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="F96" s="3" t="s">
         <v>12</v>
@@ -5471,7 +5471,7 @@
         <v>11</v>
       </c>
       <c r="E97" s="4">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="F97" s="3" t="s">
         <v>12</v>
@@ -5497,7 +5497,7 @@
         <v>11</v>
       </c>
       <c r="E98" s="2">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F98" s="3" t="s">
         <v>12</v>
@@ -5523,7 +5523,7 @@
         <v>11</v>
       </c>
       <c r="E99" s="4">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="F99" s="3" t="s">
         <v>12</v>
@@ -5549,7 +5549,7 @@
         <v>11</v>
       </c>
       <c r="E100" s="2">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="F100" s="3" t="s">
         <v>12</v>
@@ -5575,7 +5575,7 @@
         <v>11</v>
       </c>
       <c r="E101" s="4">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="F101" s="3" t="s">
         <v>12</v>
@@ -5601,7 +5601,7 @@
         <v>11</v>
       </c>
       <c r="E102" s="2">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="F102" s="3" t="s">
         <v>12</v>
@@ -5627,7 +5627,7 @@
         <v>11</v>
       </c>
       <c r="E103" s="4">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="F103" s="3" t="s">
         <v>12</v>
@@ -5653,7 +5653,7 @@
         <v>11</v>
       </c>
       <c r="E104" s="2">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F104" s="3" t="s">
         <v>12</v>
@@ -5679,7 +5679,7 @@
         <v>11</v>
       </c>
       <c r="E105" s="4">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F105" s="3" t="s">
         <v>12</v>
@@ -5705,7 +5705,7 @@
         <v>11</v>
       </c>
       <c r="E106" s="2">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="F106" s="3" t="s">
         <v>12</v>
@@ -5731,7 +5731,7 @@
         <v>11</v>
       </c>
       <c r="E107" s="4">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="F107" s="3" t="s">
         <v>12</v>
@@ -5757,7 +5757,7 @@
         <v>11</v>
       </c>
       <c r="E108" s="2">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="F108" s="3" t="s">
         <v>12</v>
@@ -5783,7 +5783,7 @@
         <v>11</v>
       </c>
       <c r="E109" s="4">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="F109" s="3" t="s">
         <v>12</v>
@@ -5809,7 +5809,7 @@
         <v>11</v>
       </c>
       <c r="E110" s="2">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="F110" s="3" t="s">
         <v>12</v>
@@ -5835,7 +5835,7 @@
         <v>11</v>
       </c>
       <c r="E111" s="4">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="F111" s="3" t="s">
         <v>12</v>
@@ -5861,7 +5861,7 @@
         <v>11</v>
       </c>
       <c r="E112" s="2">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="F112" s="3" t="s">
         <v>12</v>
@@ -5887,7 +5887,7 @@
         <v>11</v>
       </c>
       <c r="E113" s="4">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F113" s="3" t="s">
         <v>12</v>
@@ -5913,7 +5913,7 @@
         <v>11</v>
       </c>
       <c r="E114" s="2">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="F114" s="3" t="s">
         <v>12</v>
@@ -5939,7 +5939,7 @@
         <v>11</v>
       </c>
       <c r="E115" s="4">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F115" s="3" t="s">
         <v>12</v>
@@ -5965,7 +5965,7 @@
         <v>11</v>
       </c>
       <c r="E116" s="2">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="F116" s="3" t="s">
         <v>12</v>
@@ -5991,7 +5991,7 @@
         <v>11</v>
       </c>
       <c r="E117" s="4">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F117" s="3" t="s">
         <v>12</v>
@@ -6017,7 +6017,7 @@
         <v>11</v>
       </c>
       <c r="E118" s="2">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F118" s="3" t="s">
         <v>12</v>
@@ -6043,7 +6043,7 @@
         <v>11</v>
       </c>
       <c r="E119" s="4">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="F119" s="3" t="s">
         <v>12</v>
@@ -6069,7 +6069,7 @@
         <v>11</v>
       </c>
       <c r="E120" s="2">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="F120" s="3" t="s">
         <v>12</v>
@@ -6095,7 +6095,7 @@
         <v>11</v>
       </c>
       <c r="E121" s="4">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="F121" s="3" t="s">
         <v>12</v>
@@ -6121,7 +6121,7 @@
         <v>11</v>
       </c>
       <c r="E122" s="2">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="F122" s="3" t="s">
         <v>12</v>
@@ -6147,7 +6147,7 @@
         <v>11</v>
       </c>
       <c r="E123" s="4">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="F123" s="3" t="s">
         <v>12</v>
@@ -6173,7 +6173,7 @@
         <v>11</v>
       </c>
       <c r="E124" s="2">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="F124" s="3" t="s">
         <v>12</v>
@@ -6199,7 +6199,7 @@
         <v>11</v>
       </c>
       <c r="E125" s="4">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="F125" s="3" t="s">
         <v>12</v>
@@ -6251,7 +6251,7 @@
         <v>11</v>
       </c>
       <c r="E127" s="4">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="F127" s="3" t="s">
         <v>12</v>
@@ -6277,7 +6277,7 @@
         <v>11</v>
       </c>
       <c r="E128" s="2">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F128" s="3" t="s">
         <v>12</v>
@@ -6329,7 +6329,7 @@
         <v>11</v>
       </c>
       <c r="E130" s="2">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F130" s="3" t="s">
         <v>12</v>
@@ -6355,7 +6355,7 @@
         <v>11</v>
       </c>
       <c r="E131" s="4">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="F131" s="3" t="s">
         <v>12</v>
@@ -6381,7 +6381,7 @@
         <v>11</v>
       </c>
       <c r="E132" s="2">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="F132" s="3" t="s">
         <v>12</v>
@@ -6407,7 +6407,7 @@
         <v>11</v>
       </c>
       <c r="E133" s="4">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="F133" s="3" t="s">
         <v>12</v>
@@ -6433,7 +6433,7 @@
         <v>11</v>
       </c>
       <c r="E134" s="2">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F134" s="3" t="s">
         <v>12</v>
@@ -6459,7 +6459,7 @@
         <v>11</v>
       </c>
       <c r="E135" s="4">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F135" s="3" t="s">
         <v>12</v>
@@ -6485,7 +6485,7 @@
         <v>11</v>
       </c>
       <c r="E136" s="2">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F136" s="3" t="s">
         <v>12</v>
@@ -6511,7 +6511,7 @@
         <v>11</v>
       </c>
       <c r="E137" s="4">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="F137" s="3" t="s">
         <v>12</v>
@@ -6537,7 +6537,7 @@
         <v>11</v>
       </c>
       <c r="E138" s="2">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F138" s="3" t="s">
         <v>12</v>
@@ -6563,7 +6563,7 @@
         <v>11</v>
       </c>
       <c r="E139" s="4">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="F139" s="3" t="s">
         <v>12</v>
@@ -6589,7 +6589,7 @@
         <v>11</v>
       </c>
       <c r="E140" s="2">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="F140" s="3" t="s">
         <v>12</v>
@@ -6615,7 +6615,7 @@
         <v>11</v>
       </c>
       <c r="E141" s="4">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F141" s="3" t="s">
         <v>12</v>
@@ -6641,7 +6641,7 @@
         <v>11</v>
       </c>
       <c r="E142" s="2">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="F142" s="3" t="s">
         <v>12</v>
@@ -6667,7 +6667,7 @@
         <v>11</v>
       </c>
       <c r="E143" s="4">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="F143" s="3" t="s">
         <v>12</v>
@@ -6693,7 +6693,7 @@
         <v>11</v>
       </c>
       <c r="E144" s="2">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="F144" s="3" t="s">
         <v>12</v>
@@ -6719,7 +6719,7 @@
         <v>11</v>
       </c>
       <c r="E145" s="4">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="F145" s="3" t="s">
         <v>12</v>
@@ -6745,7 +6745,7 @@
         <v>11</v>
       </c>
       <c r="E146" s="2">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="F146" s="3" t="s">
         <v>12</v>
@@ -6771,7 +6771,7 @@
         <v>11</v>
       </c>
       <c r="E147" s="4">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F147" s="3" t="s">
         <v>12</v>
@@ -6797,7 +6797,7 @@
         <v>11</v>
       </c>
       <c r="E148" s="2">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F148" s="3" t="s">
         <v>12</v>
@@ -6823,7 +6823,7 @@
         <v>11</v>
       </c>
       <c r="E149" s="4">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="F149" s="3" t="s">
         <v>12</v>
@@ -6849,7 +6849,7 @@
         <v>11</v>
       </c>
       <c r="E150" s="2">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="F150" s="3" t="s">
         <v>12</v>
@@ -6875,7 +6875,7 @@
         <v>11</v>
       </c>
       <c r="E151" s="4">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F151" s="3" t="s">
         <v>12</v>
@@ -6901,7 +6901,7 @@
         <v>11</v>
       </c>
       <c r="E152" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F152" s="3" t="s">
         <v>12</v>
@@ -6927,7 +6927,7 @@
         <v>11</v>
       </c>
       <c r="E153" s="4">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="F153" s="3" t="s">
         <v>12</v>
@@ -6953,7 +6953,7 @@
         <v>11</v>
       </c>
       <c r="E154" s="2">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="F154" s="3" t="s">
         <v>12</v>
@@ -6979,7 +6979,7 @@
         <v>11</v>
       </c>
       <c r="E155" s="4">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="F155" s="3" t="s">
         <v>12</v>
@@ -7005,7 +7005,7 @@
         <v>11</v>
       </c>
       <c r="E156" s="2">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F156" s="3" t="s">
         <v>12</v>
@@ -7031,7 +7031,7 @@
         <v>11</v>
       </c>
       <c r="E157" s="4">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="F157" s="3" t="s">
         <v>12</v>
@@ -7057,7 +7057,7 @@
         <v>11</v>
       </c>
       <c r="E158" s="2">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="F158" s="3" t="s">
         <v>12</v>
@@ -7083,7 +7083,7 @@
         <v>11</v>
       </c>
       <c r="E159" s="4">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F159" s="3" t="s">
         <v>12</v>
@@ -7109,7 +7109,7 @@
         <v>11</v>
       </c>
       <c r="E160" s="2">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="F160" s="3" t="s">
         <v>12</v>
@@ -7135,7 +7135,7 @@
         <v>11</v>
       </c>
       <c r="E161" s="4">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="F161" s="3" t="s">
         <v>12</v>
@@ -7187,7 +7187,7 @@
         <v>11</v>
       </c>
       <c r="E163" s="4">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="F163" s="3" t="s">
         <v>12</v>
@@ -7213,7 +7213,7 @@
         <v>11</v>
       </c>
       <c r="E164" s="2">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="F164" s="3" t="s">
         <v>12</v>
@@ -7239,7 +7239,7 @@
         <v>11</v>
       </c>
       <c r="E165" s="4">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="F165" s="3" t="s">
         <v>12</v>
@@ -7265,7 +7265,7 @@
         <v>11</v>
       </c>
       <c r="E166" s="2">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="F166" s="3" t="s">
         <v>12</v>
@@ -7291,7 +7291,7 @@
         <v>11</v>
       </c>
       <c r="E167" s="4">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="F167" s="3" t="s">
         <v>12</v>
@@ -7317,7 +7317,7 @@
         <v>11</v>
       </c>
       <c r="E168" s="2">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="F168" s="3" t="s">
         <v>12</v>
@@ -7343,7 +7343,7 @@
         <v>11</v>
       </c>
       <c r="E169" s="4">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="F169" s="3" t="s">
         <v>12</v>
@@ -7369,7 +7369,7 @@
         <v>11</v>
       </c>
       <c r="E170" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F170" s="3" t="s">
         <v>12</v>
@@ -7395,7 +7395,7 @@
         <v>11</v>
       </c>
       <c r="E171" s="4">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F171" s="3" t="s">
         <v>12</v>
@@ -7421,7 +7421,7 @@
         <v>11</v>
       </c>
       <c r="E172" s="2">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="F172" s="3" t="s">
         <v>12</v>
@@ -7473,7 +7473,7 @@
         <v>11</v>
       </c>
       <c r="E174" s="2">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F174" s="3" t="s">
         <v>12</v>
@@ -7499,7 +7499,7 @@
         <v>11</v>
       </c>
       <c r="E175" s="4">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="F175" s="3" t="s">
         <v>12</v>
@@ -7525,7 +7525,7 @@
         <v>11</v>
       </c>
       <c r="E176" s="2">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="F176" s="3" t="s">
         <v>12</v>
@@ -7577,7 +7577,7 @@
         <v>11</v>
       </c>
       <c r="E178" s="2">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F178" s="3" t="s">
         <v>12</v>
@@ -7603,7 +7603,7 @@
         <v>11</v>
       </c>
       <c r="E179" s="4">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F179" s="3" t="s">
         <v>12</v>
@@ -7629,7 +7629,7 @@
         <v>11</v>
       </c>
       <c r="E180" s="2">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="F180" s="3" t="s">
         <v>12</v>
@@ -7655,7 +7655,7 @@
         <v>11</v>
       </c>
       <c r="E181" s="4">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F181" s="3" t="s">
         <v>12</v>
@@ -7681,7 +7681,7 @@
         <v>11</v>
       </c>
       <c r="E182" s="2">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="F182" s="3" t="s">
         <v>12</v>
@@ -7707,7 +7707,7 @@
         <v>11</v>
       </c>
       <c r="E183" s="4">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="F183" s="3" t="s">
         <v>12</v>
@@ -7733,7 +7733,7 @@
         <v>11</v>
       </c>
       <c r="E184" s="2">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="F184" s="3" t="s">
         <v>12</v>
@@ -7759,7 +7759,7 @@
         <v>11</v>
       </c>
       <c r="E185" s="4">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F185" s="3" t="s">
         <v>12</v>
@@ -7785,7 +7785,7 @@
         <v>11</v>
       </c>
       <c r="E186" s="2">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F186" s="3" t="s">
         <v>12</v>
@@ -7811,7 +7811,7 @@
         <v>11</v>
       </c>
       <c r="E187" s="4">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F187" s="3" t="s">
         <v>12</v>
@@ -7837,7 +7837,7 @@
         <v>11</v>
       </c>
       <c r="E188" s="2">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F188" s="3" t="s">
         <v>12</v>
@@ -7863,7 +7863,7 @@
         <v>11</v>
       </c>
       <c r="E189" s="4">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="F189" s="3" t="s">
         <v>12</v>
@@ -7889,7 +7889,7 @@
         <v>11</v>
       </c>
       <c r="E190" s="2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F190" s="3" t="s">
         <v>12</v>
@@ -7915,7 +7915,7 @@
         <v>11</v>
       </c>
       <c r="E191" s="4">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="F191" s="3" t="s">
         <v>12</v>
@@ -7941,7 +7941,7 @@
         <v>11</v>
       </c>
       <c r="E192" s="2">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F192" s="3" t="s">
         <v>12</v>
@@ -7967,7 +7967,7 @@
         <v>11</v>
       </c>
       <c r="E193" s="4">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F193" s="3" t="s">
         <v>12</v>
@@ -7993,7 +7993,7 @@
         <v>11</v>
       </c>
       <c r="E194" s="2">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F194" s="3" t="s">
         <v>12</v>
@@ -8019,7 +8019,7 @@
         <v>11</v>
       </c>
       <c r="E195" s="4">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="F195" s="3" t="s">
         <v>12</v>
@@ -8045,7 +8045,7 @@
         <v>11</v>
       </c>
       <c r="E196" s="2">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F196" s="3" t="s">
         <v>12</v>
@@ -8071,7 +8071,7 @@
         <v>11</v>
       </c>
       <c r="E197" s="4">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="F197" s="3" t="s">
         <v>12</v>
@@ -8097,7 +8097,7 @@
         <v>11</v>
       </c>
       <c r="E198" s="2">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="F198" s="3" t="s">
         <v>12</v>
@@ -8123,7 +8123,7 @@
         <v>11</v>
       </c>
       <c r="E199" s="4">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="F199" s="3" t="s">
         <v>12</v>
@@ -8149,7 +8149,7 @@
         <v>11</v>
       </c>
       <c r="E200" s="2">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="F200" s="3" t="s">
         <v>12</v>
@@ -8175,7 +8175,7 @@
         <v>11</v>
       </c>
       <c r="E201" s="4">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="F201" s="3" t="s">
         <v>12</v>
@@ -8201,7 +8201,7 @@
         <v>11</v>
       </c>
       <c r="E202" s="2">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="F202" s="3" t="s">
         <v>12</v>
@@ -8227,7 +8227,7 @@
         <v>11</v>
       </c>
       <c r="E203" s="4">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="F203" s="3" t="s">
         <v>12</v>
@@ -8253,7 +8253,7 @@
         <v>11</v>
       </c>
       <c r="E204" s="2">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="F204" s="3" t="s">
         <v>12</v>
@@ -8279,7 +8279,7 @@
         <v>11</v>
       </c>
       <c r="E205" s="4">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="F205" s="3" t="s">
         <v>12</v>
@@ -8331,7 +8331,7 @@
         <v>11</v>
       </c>
       <c r="E207" s="4">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="F207" s="3" t="s">
         <v>12</v>
@@ -8357,7 +8357,7 @@
         <v>11</v>
       </c>
       <c r="E208" s="2">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F208" s="3" t="s">
         <v>12</v>
@@ -8383,7 +8383,7 @@
         <v>11</v>
       </c>
       <c r="E209" s="4">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="F209" s="3" t="s">
         <v>12</v>
@@ -8409,7 +8409,7 @@
         <v>11</v>
       </c>
       <c r="E210" s="2">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F210" s="3" t="s">
         <v>12</v>
@@ -8435,7 +8435,7 @@
         <v>11</v>
       </c>
       <c r="E211" s="4">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="F211" s="3" t="s">
         <v>12</v>
@@ -8461,7 +8461,7 @@
         <v>11</v>
       </c>
       <c r="E212" s="2">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="F212" s="3" t="s">
         <v>12</v>
@@ -8513,7 +8513,7 @@
         <v>11</v>
       </c>
       <c r="E214" s="2">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F214" s="3" t="s">
         <v>12</v>
@@ -8539,7 +8539,7 @@
         <v>11</v>
       </c>
       <c r="E215" s="4">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="F215" s="3" t="s">
         <v>12</v>
@@ -8565,7 +8565,7 @@
         <v>11</v>
       </c>
       <c r="E216" s="2">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="F216" s="3" t="s">
         <v>12</v>
@@ -8591,7 +8591,7 @@
         <v>11</v>
       </c>
       <c r="E217" s="4">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F217" s="3" t="s">
         <v>12</v>
@@ -8617,7 +8617,7 @@
         <v>11</v>
       </c>
       <c r="E218" s="2">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="F218" s="3" t="s">
         <v>12</v>
@@ -8643,7 +8643,7 @@
         <v>11</v>
       </c>
       <c r="E219" s="4">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="F219" s="3" t="s">
         <v>12</v>
@@ -8669,7 +8669,7 @@
         <v>11</v>
       </c>
       <c r="E220" s="2">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="F220" s="3" t="s">
         <v>12</v>
@@ -8695,7 +8695,7 @@
         <v>11</v>
       </c>
       <c r="E221" s="4">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="F221" s="3" t="s">
         <v>12</v>
@@ -8721,7 +8721,7 @@
         <v>11</v>
       </c>
       <c r="E222" s="2">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="F222" s="3" t="s">
         <v>12</v>
@@ -8747,7 +8747,7 @@
         <v>11</v>
       </c>
       <c r="E223" s="4">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="F223" s="3" t="s">
         <v>12</v>
@@ -8773,7 +8773,7 @@
         <v>11</v>
       </c>
       <c r="E224" s="2">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="F224" s="3" t="s">
         <v>12</v>
@@ -8799,7 +8799,7 @@
         <v>11</v>
       </c>
       <c r="E225" s="4">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F225" s="3" t="s">
         <v>12</v>
@@ -8825,7 +8825,7 @@
         <v>11</v>
       </c>
       <c r="E226" s="2">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="F226" s="3" t="s">
         <v>12</v>
@@ -8851,7 +8851,7 @@
         <v>11</v>
       </c>
       <c r="E227" s="4">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="F227" s="3" t="s">
         <v>12</v>
@@ -8877,7 +8877,7 @@
         <v>11</v>
       </c>
       <c r="E228" s="2">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="F228" s="3" t="s">
         <v>12</v>
@@ -8903,7 +8903,7 @@
         <v>11</v>
       </c>
       <c r="E229" s="4">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="F229" s="3" t="s">
         <v>12</v>
@@ -8929,7 +8929,7 @@
         <v>11</v>
       </c>
       <c r="E230" s="2">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="F230" s="3" t="s">
         <v>12</v>
@@ -8955,7 +8955,7 @@
         <v>11</v>
       </c>
       <c r="E231" s="4">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="F231" s="3" t="s">
         <v>12</v>
@@ -8981,7 +8981,7 @@
         <v>11</v>
       </c>
       <c r="E232" s="2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F232" s="3" t="s">
         <v>12</v>
@@ -9007,7 +9007,7 @@
         <v>11</v>
       </c>
       <c r="E233" s="4">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="F233" s="3" t="s">
         <v>12</v>
@@ -9033,7 +9033,7 @@
         <v>11</v>
       </c>
       <c r="E234" s="2">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="F234" s="3" t="s">
         <v>12</v>
@@ -9059,7 +9059,7 @@
         <v>11</v>
       </c>
       <c r="E235" s="4">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="F235" s="3" t="s">
         <v>12</v>
@@ -9085,7 +9085,7 @@
         <v>11</v>
       </c>
       <c r="E236" s="2">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="F236" s="3" t="s">
         <v>12</v>
@@ -9111,7 +9111,7 @@
         <v>11</v>
       </c>
       <c r="E237" s="4">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="F237" s="3" t="s">
         <v>12</v>
@@ -9137,7 +9137,7 @@
         <v>11</v>
       </c>
       <c r="E238" s="2">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F238" s="3" t="s">
         <v>12</v>
@@ -9163,7 +9163,7 @@
         <v>11</v>
       </c>
       <c r="E239" s="4">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="F239" s="3" t="s">
         <v>12</v>
@@ -9189,7 +9189,7 @@
         <v>11</v>
       </c>
       <c r="E240" s="2">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="F240" s="3" t="s">
         <v>12</v>
@@ -9215,7 +9215,7 @@
         <v>11</v>
       </c>
       <c r="E241" s="4">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="F241" s="3" t="s">
         <v>12</v>
@@ -9241,7 +9241,7 @@
         <v>11</v>
       </c>
       <c r="E242" s="2">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="F242" s="3" t="s">
         <v>12</v>
@@ -9267,7 +9267,7 @@
         <v>11</v>
       </c>
       <c r="E243" s="4">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F243" s="3" t="s">
         <v>12</v>
@@ -9293,7 +9293,7 @@
         <v>11</v>
       </c>
       <c r="E244" s="2">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F244" s="3" t="s">
         <v>12</v>
@@ -9319,7 +9319,7 @@
         <v>11</v>
       </c>
       <c r="E245" s="4">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="F245" s="3" t="s">
         <v>12</v>
@@ -9345,7 +9345,7 @@
         <v>11</v>
       </c>
       <c r="E246" s="2">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="F246" s="3" t="s">
         <v>12</v>
@@ -9371,7 +9371,7 @@
         <v>11</v>
       </c>
       <c r="E247" s="4">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="F247" s="3" t="s">
         <v>12</v>
@@ -9397,7 +9397,7 @@
         <v>11</v>
       </c>
       <c r="E248" s="2">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="F248" s="3" t="s">
         <v>12</v>
@@ -9423,7 +9423,7 @@
         <v>11</v>
       </c>
       <c r="E249" s="4">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="F249" s="3" t="s">
         <v>12</v>
@@ -9449,7 +9449,7 @@
         <v>11</v>
       </c>
       <c r="E250" s="2">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="F250" s="3" t="s">
         <v>12</v>
@@ -9475,7 +9475,7 @@
         <v>11</v>
       </c>
       <c r="E251" s="4">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="F251" s="3" t="s">
         <v>12</v>
@@ -9501,7 +9501,7 @@
         <v>11</v>
       </c>
       <c r="E252" s="2">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="F252" s="3" t="s">
         <v>12</v>
@@ -9527,7 +9527,7 @@
         <v>11</v>
       </c>
       <c r="E253" s="4">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="F253" s="3" t="s">
         <v>12</v>
@@ -9553,7 +9553,7 @@
         <v>11</v>
       </c>
       <c r="E254" s="2">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="F254" s="3" t="s">
         <v>12</v>
@@ -9579,7 +9579,7 @@
         <v>11</v>
       </c>
       <c r="E255" s="4">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="F255" s="3" t="s">
         <v>12</v>
@@ -9605,7 +9605,7 @@
         <v>11</v>
       </c>
       <c r="E256" s="2">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F256" s="3" t="s">
         <v>12</v>
@@ -9631,7 +9631,7 @@
         <v>11</v>
       </c>
       <c r="E257" s="4">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="F257" s="3" t="s">
         <v>12</v>
@@ -9657,7 +9657,7 @@
         <v>11</v>
       </c>
       <c r="E258" s="2">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="F258" s="3" t="s">
         <v>12</v>
@@ -9683,7 +9683,7 @@
         <v>11</v>
       </c>
       <c r="E259" s="4">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F259" s="3" t="s">
         <v>12</v>
@@ -9709,7 +9709,7 @@
         <v>11</v>
       </c>
       <c r="E260" s="2">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F260" s="3" t="s">
         <v>12</v>
@@ -9735,7 +9735,7 @@
         <v>11</v>
       </c>
       <c r="E261" s="4">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="F261" s="3" t="s">
         <v>12</v>
@@ -9761,7 +9761,7 @@
         <v>11</v>
       </c>
       <c r="E262" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F262" s="3" t="s">
         <v>12</v>
@@ -9787,7 +9787,7 @@
         <v>11</v>
       </c>
       <c r="E263" s="4">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="F263" s="3" t="s">
         <v>12</v>
@@ -9813,7 +9813,7 @@
         <v>11</v>
       </c>
       <c r="E264" s="2">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="F264" s="3" t="s">
         <v>12</v>
@@ -9839,7 +9839,7 @@
         <v>11</v>
       </c>
       <c r="E265" s="4">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="F265" s="3" t="s">
         <v>12</v>
@@ -9865,7 +9865,7 @@
         <v>11</v>
       </c>
       <c r="E266" s="2">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F266" s="3" t="s">
         <v>12</v>
@@ -9891,7 +9891,7 @@
         <v>11</v>
       </c>
       <c r="E267" s="4">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="F267" s="3" t="s">
         <v>12</v>
@@ -9917,7 +9917,7 @@
         <v>11</v>
       </c>
       <c r="E268" s="2">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="F268" s="3" t="s">
         <v>12</v>
@@ -9943,7 +9943,7 @@
         <v>11</v>
       </c>
       <c r="E269" s="4">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="F269" s="3" t="s">
         <v>12</v>
@@ -9969,7 +9969,7 @@
         <v>11</v>
       </c>
       <c r="E270" s="2">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F270" s="3" t="s">
         <v>12</v>
@@ -9995,7 +9995,7 @@
         <v>11</v>
       </c>
       <c r="E271" s="4">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="F271" s="3" t="s">
         <v>12</v>
@@ -10021,7 +10021,7 @@
         <v>11</v>
       </c>
       <c r="E272" s="2">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="F272" s="3" t="s">
         <v>12</v>
@@ -10047,7 +10047,7 @@
         <v>11</v>
       </c>
       <c r="E273" s="4">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F273" s="3" t="s">
         <v>12</v>
@@ -10073,7 +10073,7 @@
         <v>11</v>
       </c>
       <c r="E274" s="2">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="F274" s="3" t="s">
         <v>12</v>
@@ -10099,7 +10099,7 @@
         <v>11</v>
       </c>
       <c r="E275" s="4">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="F275" s="3" t="s">
         <v>12</v>
@@ -10125,7 +10125,7 @@
         <v>11</v>
       </c>
       <c r="E276" s="2">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="F276" s="3" t="s">
         <v>12</v>
@@ -10151,7 +10151,7 @@
         <v>11</v>
       </c>
       <c r="E277" s="4">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="F277" s="3" t="s">
         <v>12</v>
@@ -10177,7 +10177,7 @@
         <v>11</v>
       </c>
       <c r="E278" s="2">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="F278" s="3" t="s">
         <v>12</v>
@@ -10203,7 +10203,7 @@
         <v>11</v>
       </c>
       <c r="E279" s="4">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="F279" s="3" t="s">
         <v>12</v>
@@ -10229,7 +10229,7 @@
         <v>11</v>
       </c>
       <c r="E280" s="2">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F280" s="3" t="s">
         <v>12</v>
@@ -10255,7 +10255,7 @@
         <v>11</v>
       </c>
       <c r="E281" s="4">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F281" s="3" t="s">
         <v>12</v>
@@ -10281,7 +10281,7 @@
         <v>11</v>
       </c>
       <c r="E282" s="2">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="F282" s="3" t="s">
         <v>12</v>
@@ -10307,7 +10307,7 @@
         <v>11</v>
       </c>
       <c r="E283" s="4">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="F283" s="3" t="s">
         <v>12</v>
@@ -10333,7 +10333,7 @@
         <v>11</v>
       </c>
       <c r="E284" s="2">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="F284" s="3" t="s">
         <v>12</v>
@@ -10359,7 +10359,7 @@
         <v>11</v>
       </c>
       <c r="E285" s="4">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="F285" s="3" t="s">
         <v>12</v>
@@ -10385,7 +10385,7 @@
         <v>11</v>
       </c>
       <c r="E286" s="2">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="F286" s="3" t="s">
         <v>12</v>
@@ -10411,7 +10411,7 @@
         <v>11</v>
       </c>
       <c r="E287" s="4">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F287" s="3" t="s">
         <v>12</v>
@@ -10437,7 +10437,7 @@
         <v>11</v>
       </c>
       <c r="E288" s="2">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="F288" s="3" t="s">
         <v>12</v>
@@ -10463,7 +10463,7 @@
         <v>11</v>
       </c>
       <c r="E289" s="4">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="F289" s="3" t="s">
         <v>12</v>
@@ -10489,7 +10489,7 @@
         <v>11</v>
       </c>
       <c r="E290" s="2">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="F290" s="3" t="s">
         <v>12</v>
@@ -10515,7 +10515,7 @@
         <v>11</v>
       </c>
       <c r="E291" s="4">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F291" s="3" t="s">
         <v>12</v>
@@ -10541,7 +10541,7 @@
         <v>11</v>
       </c>
       <c r="E292" s="2">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="F292" s="3" t="s">
         <v>12</v>
@@ -10567,7 +10567,7 @@
         <v>11</v>
       </c>
       <c r="E293" s="4">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="F293" s="3" t="s">
         <v>12</v>
@@ -10593,7 +10593,7 @@
         <v>11</v>
       </c>
       <c r="E294" s="2">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="F294" s="3" t="s">
         <v>12</v>
@@ -10619,7 +10619,7 @@
         <v>11</v>
       </c>
       <c r="E295" s="4">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F295" s="3" t="s">
         <v>12</v>
@@ -10645,7 +10645,7 @@
         <v>11</v>
       </c>
       <c r="E296" s="2">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="F296" s="3" t="s">
         <v>12</v>
@@ -10671,7 +10671,7 @@
         <v>11</v>
       </c>
       <c r="E297" s="4">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="F297" s="3" t="s">
         <v>12</v>
@@ -10697,7 +10697,7 @@
         <v>11</v>
       </c>
       <c r="E298" s="2">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="F298" s="3" t="s">
         <v>12</v>
@@ -10723,7 +10723,7 @@
         <v>11</v>
       </c>
       <c r="E299" s="4">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F299" s="3" t="s">
         <v>12</v>
@@ -10749,7 +10749,7 @@
         <v>11</v>
       </c>
       <c r="E300" s="2">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="F300" s="3" t="s">
         <v>12</v>
@@ -10775,7 +10775,7 @@
         <v>11</v>
       </c>
       <c r="E301" s="4">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="F301" s="3" t="s">
         <v>12</v>
@@ -10801,7 +10801,7 @@
         <v>11</v>
       </c>
       <c r="E302" s="2">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="F302" s="3" t="s">
         <v>12</v>
@@ -10827,7 +10827,7 @@
         <v>11</v>
       </c>
       <c r="E303" s="4">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="F303" s="3" t="s">
         <v>12</v>
@@ -10853,7 +10853,7 @@
         <v>11</v>
       </c>
       <c r="E304" s="2">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="F304" s="3" t="s">
         <v>12</v>
@@ -10905,7 +10905,7 @@
         <v>11</v>
       </c>
       <c r="E306" s="2">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="F306" s="3" t="s">
         <v>12</v>
@@ -10931,7 +10931,7 @@
         <v>11</v>
       </c>
       <c r="E307" s="4">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F307" s="3" t="s">
         <v>12</v>
@@ -10957,7 +10957,7 @@
         <v>11</v>
       </c>
       <c r="E308" s="2">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="F308" s="3" t="s">
         <v>12</v>
@@ -10983,7 +10983,7 @@
         <v>11</v>
       </c>
       <c r="E309" s="4">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F309" s="3" t="s">
         <v>12</v>
@@ -11009,7 +11009,7 @@
         <v>11</v>
       </c>
       <c r="E310" s="2">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="F310" s="3" t="s">
         <v>12</v>
@@ -11035,7 +11035,7 @@
         <v>11</v>
       </c>
       <c r="E311" s="4">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="F311" s="3" t="s">
         <v>12</v>
@@ -11061,7 +11061,7 @@
         <v>11</v>
       </c>
       <c r="E312" s="2">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="F312" s="3" t="s">
         <v>12</v>
@@ -11087,7 +11087,7 @@
         <v>11</v>
       </c>
       <c r="E313" s="4">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="F313" s="3" t="s">
         <v>12</v>
@@ -11113,7 +11113,7 @@
         <v>11</v>
       </c>
       <c r="E314" s="2">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F314" s="3" t="s">
         <v>12</v>
@@ -11139,7 +11139,7 @@
         <v>11</v>
       </c>
       <c r="E315" s="4">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="F315" s="3" t="s">
         <v>12</v>
@@ -11165,7 +11165,7 @@
         <v>11</v>
       </c>
       <c r="E316" s="2">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="F316" s="3" t="s">
         <v>12</v>
@@ -11191,7 +11191,7 @@
         <v>11</v>
       </c>
       <c r="E317" s="4">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="F317" s="3" t="s">
         <v>12</v>
@@ -11217,7 +11217,7 @@
         <v>11</v>
       </c>
       <c r="E318" s="2">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="F318" s="3" t="s">
         <v>12</v>
@@ -11243,7 +11243,7 @@
         <v>11</v>
       </c>
       <c r="E319" s="4">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="F319" s="3" t="s">
         <v>12</v>
@@ -11269,7 +11269,7 @@
         <v>11</v>
       </c>
       <c r="E320" s="2">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="F320" s="3" t="s">
         <v>12</v>
@@ -11295,7 +11295,7 @@
         <v>11</v>
       </c>
       <c r="E321" s="4">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F321" s="3" t="s">
         <v>12</v>
@@ -11321,7 +11321,7 @@
         <v>11</v>
       </c>
       <c r="E322" s="2">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F322" s="3" t="s">
         <v>12</v>
@@ -11347,7 +11347,7 @@
         <v>11</v>
       </c>
       <c r="E323" s="4">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="F323" s="3" t="s">
         <v>12</v>
@@ -11373,7 +11373,7 @@
         <v>11</v>
       </c>
       <c r="E324" s="2">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F324" s="3" t="s">
         <v>12</v>
@@ -11399,7 +11399,7 @@
         <v>11</v>
       </c>
       <c r="E325" s="4">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="F325" s="3" t="s">
         <v>12</v>
@@ -11425,7 +11425,7 @@
         <v>11</v>
       </c>
       <c r="E326" s="2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F326" s="3" t="s">
         <v>12</v>
@@ -11451,7 +11451,7 @@
         <v>11</v>
       </c>
       <c r="E327" s="4">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F327" s="3" t="s">
         <v>12</v>
@@ -11477,7 +11477,7 @@
         <v>11</v>
       </c>
       <c r="E328" s="2">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F328" s="3" t="s">
         <v>12</v>
@@ -11503,7 +11503,7 @@
         <v>11</v>
       </c>
       <c r="E329" s="4">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="F329" s="3" t="s">
         <v>12</v>
@@ -11529,7 +11529,7 @@
         <v>11</v>
       </c>
       <c r="E330" s="2">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="F330" s="3" t="s">
         <v>12</v>
@@ -11555,7 +11555,7 @@
         <v>11</v>
       </c>
       <c r="E331" s="4">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="F331" s="3" t="s">
         <v>12</v>
@@ -11581,7 +11581,7 @@
         <v>11</v>
       </c>
       <c r="E332" s="2">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="F332" s="3" t="s">
         <v>12</v>
@@ -11607,7 +11607,7 @@
         <v>11</v>
       </c>
       <c r="E333" s="4">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="F333" s="3" t="s">
         <v>12</v>
@@ -11633,7 +11633,7 @@
         <v>11</v>
       </c>
       <c r="E334" s="2">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F334" s="3" t="s">
         <v>12</v>
@@ -11659,7 +11659,7 @@
         <v>11</v>
       </c>
       <c r="E335" s="4">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F335" s="3" t="s">
         <v>12</v>
@@ -11685,7 +11685,7 @@
         <v>11</v>
       </c>
       <c r="E336" s="2">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="F336" s="3" t="s">
         <v>12</v>
@@ -11711,7 +11711,7 @@
         <v>11</v>
       </c>
       <c r="E337" s="4">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="F337" s="3" t="s">
         <v>12</v>
@@ -11737,7 +11737,7 @@
         <v>11</v>
       </c>
       <c r="E338" s="2">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="F338" s="3" t="s">
         <v>12</v>
@@ -11763,7 +11763,7 @@
         <v>11</v>
       </c>
       <c r="E339" s="4">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F339" s="3" t="s">
         <v>12</v>
@@ -11789,7 +11789,7 @@
         <v>11</v>
       </c>
       <c r="E340" s="2">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F340" s="3" t="s">
         <v>12</v>
@@ -11815,7 +11815,7 @@
         <v>11</v>
       </c>
       <c r="E341" s="4">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F341" s="3" t="s">
         <v>12</v>
@@ -11841,7 +11841,7 @@
         <v>11</v>
       </c>
       <c r="E342" s="2">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="F342" s="3" t="s">
         <v>12</v>
@@ -11867,7 +11867,7 @@
         <v>11</v>
       </c>
       <c r="E343" s="4">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="F343" s="3" t="s">
         <v>12</v>
@@ -11893,7 +11893,7 @@
         <v>11</v>
       </c>
       <c r="E344" s="2">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F344" s="3" t="s">
         <v>12</v>
@@ -11919,7 +11919,7 @@
         <v>11</v>
       </c>
       <c r="E345" s="4">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="F345" s="3" t="s">
         <v>12</v>
@@ -11945,7 +11945,7 @@
         <v>11</v>
       </c>
       <c r="E346" s="2">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="F346" s="3" t="s">
         <v>12</v>
@@ -11971,7 +11971,7 @@
         <v>11</v>
       </c>
       <c r="E347" s="4">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F347" s="3" t="s">
         <v>12</v>
@@ -11997,7 +11997,7 @@
         <v>11</v>
       </c>
       <c r="E348" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F348" s="3" t="s">
         <v>12</v>
@@ -12075,7 +12075,7 @@
         <v>11</v>
       </c>
       <c r="E351" s="4">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="F351" s="3" t="s">
         <v>12</v>
@@ -12101,7 +12101,7 @@
         <v>11</v>
       </c>
       <c r="E352" s="2">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="F352" s="3" t="s">
         <v>12</v>
@@ -12127,7 +12127,7 @@
         <v>11</v>
       </c>
       <c r="E353" s="4">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="F353" s="3" t="s">
         <v>12</v>
@@ -12179,7 +12179,7 @@
         <v>11</v>
       </c>
       <c r="E355" s="4">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F355" s="3" t="s">
         <v>12</v>
@@ -12205,7 +12205,7 @@
         <v>11</v>
       </c>
       <c r="E356" s="2">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="F356" s="3" t="s">
         <v>12</v>
@@ -12231,7 +12231,7 @@
         <v>11</v>
       </c>
       <c r="E357" s="4">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="F357" s="3" t="s">
         <v>12</v>
@@ -12257,7 +12257,7 @@
         <v>11</v>
       </c>
       <c r="E358" s="2">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="F358" s="3" t="s">
         <v>12</v>
@@ -12283,7 +12283,7 @@
         <v>11</v>
       </c>
       <c r="E359" s="4">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="F359" s="3" t="s">
         <v>12</v>
@@ -12309,7 +12309,7 @@
         <v>11</v>
       </c>
       <c r="E360" s="2">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F360" s="3" t="s">
         <v>12</v>
@@ -12361,7 +12361,7 @@
         <v>11</v>
       </c>
       <c r="E362" s="2">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="F362" s="3" t="s">
         <v>12</v>
@@ -12387,7 +12387,7 @@
         <v>11</v>
       </c>
       <c r="E363" s="4">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="F363" s="3" t="s">
         <v>12</v>
@@ -12413,7 +12413,7 @@
         <v>11</v>
       </c>
       <c r="E364" s="2">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="F364" s="3" t="s">
         <v>12</v>
@@ -12439,7 +12439,7 @@
         <v>11</v>
       </c>
       <c r="E365" s="4">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="F365" s="3" t="s">
         <v>12</v>
@@ -12465,7 +12465,7 @@
         <v>11</v>
       </c>
       <c r="E366" s="2">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="F366" s="3" t="s">
         <v>12</v>
@@ -12491,7 +12491,7 @@
         <v>11</v>
       </c>
       <c r="E367" s="4">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="F367" s="3" t="s">
         <v>12</v>
@@ -12517,7 +12517,7 @@
         <v>11</v>
       </c>
       <c r="E368" s="2">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="F368" s="3" t="s">
         <v>12</v>
@@ -12543,7 +12543,7 @@
         <v>11</v>
       </c>
       <c r="E369" s="4">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="F369" s="3" t="s">
         <v>12</v>
@@ -12569,7 +12569,7 @@
         <v>11</v>
       </c>
       <c r="E370" s="2">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="F370" s="3" t="s">
         <v>12</v>
@@ -12595,7 +12595,7 @@
         <v>11</v>
       </c>
       <c r="E371" s="4">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="F371" s="3" t="s">
         <v>12</v>
@@ -12621,7 +12621,7 @@
         <v>11</v>
       </c>
       <c r="E372" s="2">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="F372" s="3" t="s">
         <v>12</v>
@@ -12647,7 +12647,7 @@
         <v>11</v>
       </c>
       <c r="E373" s="4">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="F373" s="3" t="s">
         <v>12</v>
@@ -12673,7 +12673,7 @@
         <v>11</v>
       </c>
       <c r="E374" s="2">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="F374" s="3" t="s">
         <v>12</v>
@@ -12699,7 +12699,7 @@
         <v>11</v>
       </c>
       <c r="E375" s="4">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F375" s="3" t="s">
         <v>12</v>
@@ -12725,7 +12725,7 @@
         <v>11</v>
       </c>
       <c r="E376" s="2">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F376" s="3" t="s">
         <v>12</v>
@@ -12751,7 +12751,7 @@
         <v>11</v>
       </c>
       <c r="E377" s="4">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="F377" s="3" t="s">
         <v>12</v>
@@ -12777,7 +12777,7 @@
         <v>11</v>
       </c>
       <c r="E378" s="2">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="F378" s="3" t="s">
         <v>12</v>
@@ -12803,7 +12803,7 @@
         <v>11</v>
       </c>
       <c r="E379" s="4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F379" s="3" t="s">
         <v>12</v>
@@ -12829,7 +12829,7 @@
         <v>11</v>
       </c>
       <c r="E380" s="2">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="F380" s="3" t="s">
         <v>12</v>
@@ -12855,7 +12855,7 @@
         <v>11</v>
       </c>
       <c r="E381" s="4">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="F381" s="3" t="s">
         <v>12</v>
@@ -12881,7 +12881,7 @@
         <v>11</v>
       </c>
       <c r="E382" s="2">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="F382" s="3" t="s">
         <v>12</v>
@@ -12907,7 +12907,7 @@
         <v>11</v>
       </c>
       <c r="E383" s="4">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F383" s="3" t="s">
         <v>12</v>
@@ -12959,7 +12959,7 @@
         <v>11</v>
       </c>
       <c r="E385" s="4">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="F385" s="3" t="s">
         <v>12</v>
@@ -12985,7 +12985,7 @@
         <v>11</v>
       </c>
       <c r="E386" s="2">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="F386" s="3" t="s">
         <v>12</v>
@@ -13011,7 +13011,7 @@
         <v>11</v>
       </c>
       <c r="E387" s="4">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="F387" s="3" t="s">
         <v>12</v>
@@ -13037,7 +13037,7 @@
         <v>11</v>
       </c>
       <c r="E388" s="2">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="F388" s="3" t="s">
         <v>12</v>
@@ -13063,7 +13063,7 @@
         <v>11</v>
       </c>
       <c r="E389" s="4">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="F389" s="3" t="s">
         <v>12</v>
@@ -13089,7 +13089,7 @@
         <v>11</v>
       </c>
       <c r="E390" s="2">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F390" s="3" t="s">
         <v>12</v>
@@ -13115,7 +13115,7 @@
         <v>11</v>
       </c>
       <c r="E391" s="4">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="F391" s="3" t="s">
         <v>12</v>
@@ -13141,7 +13141,7 @@
         <v>11</v>
       </c>
       <c r="E392" s="2">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="F392" s="3" t="s">
         <v>12</v>
@@ -13167,7 +13167,7 @@
         <v>11</v>
       </c>
       <c r="E393" s="4">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="F393" s="3" t="s">
         <v>12</v>
@@ -13193,7 +13193,7 @@
         <v>11</v>
       </c>
       <c r="E394" s="2">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="F394" s="3" t="s">
         <v>12</v>
@@ -13219,7 +13219,7 @@
         <v>11</v>
       </c>
       <c r="E395" s="4">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F395" s="3" t="s">
         <v>12</v>
@@ -13245,7 +13245,7 @@
         <v>11</v>
       </c>
       <c r="E396" s="2">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="F396" s="3" t="s">
         <v>12</v>
@@ -13271,7 +13271,7 @@
         <v>11</v>
       </c>
       <c r="E397" s="4">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="F397" s="3" t="s">
         <v>12</v>
@@ -13297,7 +13297,7 @@
         <v>11</v>
       </c>
       <c r="E398" s="2">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F398" s="3" t="s">
         <v>12</v>
@@ -13323,7 +13323,7 @@
         <v>11</v>
       </c>
       <c r="E399" s="4">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F399" s="3" t="s">
         <v>12</v>
@@ -13349,7 +13349,7 @@
         <v>11</v>
       </c>
       <c r="E400" s="2">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="F400" s="3" t="s">
         <v>12</v>
@@ -13375,7 +13375,7 @@
         <v>11</v>
       </c>
       <c r="E401" s="4">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="F401" s="3" t="s">
         <v>12</v>
